--- a/content/jahrgaenge/Jg6.xlsx
+++ b/content/jahrgaenge/Jg6.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="219">
   <si>
     <t>Hinweise zu Jg6.xlsx</t>
   </si>
@@ -497,14 +497,195 @@
   </si>
   <si>
     <t>Bausteinzeitraum 31.08. bis 02.10.2026</t>
+  </si>
+  <si>
+    <t>klar</t>
+  </si>
+  <si>
+    <t>Besinn-Dich-Tage</t>
+  </si>
+  <si>
+    <t>besinntage</t>
+  </si>
+  <si>
+    <t>letzte Schulwoche</t>
+  </si>
+  <si>
+    <t>letzte-woche</t>
+  </si>
+  <si>
+    <t>jg6-de-1</t>
+  </si>
+  <si>
+    <t>jg6-ma-1</t>
+  </si>
+  <si>
+    <t>ma</t>
+  </si>
+  <si>
+    <t>jg6-bio-1</t>
+  </si>
+  <si>
+    <t>jg6-en-1</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>jg6-geo-1</t>
+  </si>
+  <si>
+    <t>geo</t>
+  </si>
+  <si>
+    <t>jg6-ma-2</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>jg6-de-2</t>
+  </si>
+  <si>
+    <t>jg6-bio-2</t>
+  </si>
+  <si>
+    <t>jg6-en-2</t>
+  </si>
+  <si>
+    <t>jg6-geo-2</t>
+  </si>
+  <si>
+    <t>jg6-bio-3</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>jg6-ma-3</t>
+  </si>
+  <si>
+    <t>jg6-de-3</t>
+  </si>
+  <si>
+    <t>wahl</t>
+  </si>
+  <si>
+    <t>jg6-en-3</t>
+  </si>
+  <si>
+    <t>jg6-geo-3</t>
+  </si>
+  <si>
+    <t>jg6-en-4</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>jg6-ma-4</t>
+  </si>
+  <si>
+    <t>jg6-bio-4</t>
+  </si>
+  <si>
+    <t>jg6-de-4</t>
+  </si>
+  <si>
+    <t>jg6-geo-4</t>
+  </si>
+  <si>
+    <t>jg6-de-5</t>
+  </si>
+  <si>
+    <t>jg6-ma-5</t>
+  </si>
+  <si>
+    <t>jg6-bio-5</t>
+  </si>
+  <si>
+    <t>jg6-en-5</t>
+  </si>
+  <si>
+    <t>jg6-geo-5</t>
+  </si>
+  <si>
+    <t>Satzglieder</t>
+  </si>
+  <si>
+    <t>Zuordnungen</t>
+  </si>
+  <si>
+    <t>Wirbellose Tiere in ihren Lebensräumen</t>
+  </si>
+  <si>
+    <t>The Secret of Maple Hill</t>
+  </si>
+  <si>
+    <t>Europa</t>
+  </si>
+  <si>
+    <t>Konstruieren von Dreiecken</t>
+  </si>
+  <si>
+    <t>Fabeln</t>
+  </si>
+  <si>
+    <t>Unter der Lupe</t>
+  </si>
+  <si>
+    <t>Christmas</t>
+  </si>
+  <si>
+    <t>Klima in Europa</t>
+  </si>
+  <si>
+    <t>Der Wald als Lebensgemeinschaft</t>
+  </si>
+  <si>
+    <t>weitere Dreieckseigenschaften und Vierecksberechnung</t>
+  </si>
+  <si>
+    <t>Ocean City ODER Herr der Diebe</t>
+  </si>
+  <si>
+    <t>Peacemakers</t>
+  </si>
+  <si>
+    <t>Nordeuropa</t>
+  </si>
+  <si>
+    <t>Pip and the Umbrella Room</t>
+  </si>
+  <si>
+    <t>Eigenschaften und Darstellen von Prismen</t>
+  </si>
+  <si>
+    <t>Samenpflanzen</t>
+  </si>
+  <si>
+    <t>Beschreiben und Berichten</t>
+  </si>
+  <si>
+    <t>Südeuropa</t>
+  </si>
+  <si>
+    <t>Redewendungen und Sprichwörter</t>
+  </si>
+  <si>
+    <t>Volumen von Prismen</t>
+  </si>
+  <si>
+    <t>Exkursionen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd.mm.yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -542,7 +723,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -557,6 +738,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1925,7 +2107,7 @@
     <mergeCell ref="B72:D72"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1956,7 +2138,7 @@
   </sheetData>
   <autoFilter ref="A1:D1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -1992,6 +2174,9 @@
       <c r="A2">
         <v>6</v>
       </c>
+      <c r="B2" t="s">
+        <v>159</v>
+      </c>
       <c r="C2" t="s">
         <v>17</v>
       </c>
@@ -2000,19 +2185,22 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B500">
+      <formula1>"verspielt,klar,sachlich"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B2:B500">
       <formula1>"verspielt,klar,sachlich"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="13" style="5" customWidth="1"/>
@@ -2034,21 +2222,66 @@
         <v>34</v>
       </c>
     </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B2" s="8">
+        <v>46283</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="8">
+        <v>46468</v>
+      </c>
+      <c r="B3" s="8">
+        <v>46472</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="8">
+        <v>46573</v>
+      </c>
+      <c r="B4" s="8">
+        <v>46577</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D4" t="s">
+        <v>163</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" sqref="D10:D500">
+      <formula1>"themenwoche,soul-basics,puffer,kennenlernen,einfuehrung,besinntage,fvu,letzte-woche,sonstiges"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D2:D500">
       <formula1>"themenwoche,soul-basics,puffer,kennenlernen,einfuehrung,besinntage,fvu,letzte-woche,sonstiges"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2099,24 +2332,980 @@
         <v>21</v>
       </c>
     </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>16</v>
+      </c>
+      <c r="G2" s="8">
+        <v>46251</v>
+      </c>
+      <c r="H2" s="8">
+        <v>46325</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" t="s">
+        <v>164</v>
+      </c>
+      <c r="K2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>16</v>
+      </c>
+      <c r="G3" s="8">
+        <v>46251</v>
+      </c>
+      <c r="H3" s="8">
+        <v>46276</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>165</v>
+      </c>
+      <c r="K3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4">
+        <v>16</v>
+      </c>
+      <c r="G4" s="8">
+        <v>46251</v>
+      </c>
+      <c r="H4" s="8">
+        <v>46276</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" t="s">
+        <v>167</v>
+      </c>
+      <c r="K4" t="s">
+        <v>65</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>16</v>
+      </c>
+      <c r="G5" s="8">
+        <v>46286</v>
+      </c>
+      <c r="H5" s="8">
+        <v>46325</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" t="s">
+        <v>168</v>
+      </c>
+      <c r="K5" t="s">
+        <v>65</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6">
+        <v>16</v>
+      </c>
+      <c r="G6" s="8">
+        <v>46286</v>
+      </c>
+      <c r="H6" s="8">
+        <v>46325</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6" t="s">
+        <v>170</v>
+      </c>
+      <c r="K6" t="s">
+        <v>65</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7">
+        <v>16</v>
+      </c>
+      <c r="G7" s="8">
+        <v>46328</v>
+      </c>
+      <c r="H7" s="8">
+        <v>46395</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" t="s">
+        <v>172</v>
+      </c>
+      <c r="K7" t="s">
+        <v>65</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8">
+        <v>16</v>
+      </c>
+      <c r="G8" s="8">
+        <v>46328</v>
+      </c>
+      <c r="H8" s="8">
+        <v>46353</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" t="s">
+        <v>174</v>
+      </c>
+      <c r="K8" t="s">
+        <v>65</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" t="s">
+        <v>173</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9">
+        <v>16</v>
+      </c>
+      <c r="G9" s="8">
+        <v>46328</v>
+      </c>
+      <c r="H9" s="8">
+        <v>46353</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" t="s">
+        <v>175</v>
+      </c>
+      <c r="K9" t="s">
+        <v>65</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" t="s">
+        <v>173</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10">
+        <v>16</v>
+      </c>
+      <c r="G10" s="8">
+        <v>46356</v>
+      </c>
+      <c r="H10" s="8">
+        <v>46395</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" t="s">
+        <v>176</v>
+      </c>
+      <c r="K10" t="s">
+        <v>65</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B11" t="s">
+        <v>171</v>
+      </c>
+      <c r="C11" t="s">
+        <v>173</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11">
+        <v>16</v>
+      </c>
+      <c r="G11" s="8">
+        <v>46356</v>
+      </c>
+      <c r="H11" s="8">
+        <v>46395</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" t="s">
+        <v>177</v>
+      </c>
+      <c r="K11" t="s">
+        <v>65</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" t="s">
+        <v>179</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12">
+        <v>16</v>
+      </c>
+      <c r="G12" s="8">
+        <v>46398</v>
+      </c>
+      <c r="H12" s="8">
+        <v>46465</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" t="s">
+        <v>178</v>
+      </c>
+      <c r="K12" t="s">
+        <v>65</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B13" t="s">
+        <v>166</v>
+      </c>
+      <c r="C13" t="s">
+        <v>179</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13">
+        <v>16</v>
+      </c>
+      <c r="G13" s="8">
+        <v>46398</v>
+      </c>
+      <c r="H13" s="8">
+        <v>46423</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" t="s">
+        <v>180</v>
+      </c>
+      <c r="K13" t="s">
+        <v>65</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" t="s">
+        <v>179</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14">
+        <v>16</v>
+      </c>
+      <c r="G14" s="8">
+        <v>46398</v>
+      </c>
+      <c r="H14" s="8">
+        <v>46423</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" t="s">
+        <v>181</v>
+      </c>
+      <c r="K14" t="s">
+        <v>182</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>183</v>
+      </c>
+      <c r="B15" t="s">
+        <v>169</v>
+      </c>
+      <c r="C15" t="s">
+        <v>179</v>
+      </c>
+      <c r="D15">
+        <v>2</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15">
+        <v>16</v>
+      </c>
+      <c r="G15" s="8">
+        <v>46440</v>
+      </c>
+      <c r="H15" s="8">
+        <v>46465</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" t="s">
+        <v>183</v>
+      </c>
+      <c r="K15" t="s">
+        <v>65</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>184</v>
+      </c>
+      <c r="B16" t="s">
+        <v>171</v>
+      </c>
+      <c r="C16" t="s">
+        <v>179</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16">
+        <v>16</v>
+      </c>
+      <c r="G16" s="8">
+        <v>46440</v>
+      </c>
+      <c r="H16" s="8">
+        <v>46465</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" t="s">
+        <v>184</v>
+      </c>
+      <c r="K16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>185</v>
+      </c>
+      <c r="B17" t="s">
+        <v>169</v>
+      </c>
+      <c r="C17" t="s">
+        <v>186</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17">
+        <v>16</v>
+      </c>
+      <c r="G17" s="8">
+        <v>46482</v>
+      </c>
+      <c r="H17" s="8">
+        <v>46542</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" t="s">
+        <v>185</v>
+      </c>
+      <c r="K17" t="s">
+        <v>65</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>187</v>
+      </c>
+      <c r="B18" t="s">
+        <v>166</v>
+      </c>
+      <c r="C18" t="s">
+        <v>186</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18">
+        <v>16</v>
+      </c>
+      <c r="G18" s="8">
+        <v>46482</v>
+      </c>
+      <c r="H18" s="8">
+        <v>46507</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" t="s">
+        <v>187</v>
+      </c>
+      <c r="K18" t="s">
+        <v>65</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>188</v>
+      </c>
+      <c r="B19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" t="s">
+        <v>186</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19">
+        <v>16</v>
+      </c>
+      <c r="G19" s="8">
+        <v>46482</v>
+      </c>
+      <c r="H19" s="8">
+        <v>46507</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" t="s">
+        <v>188</v>
+      </c>
+      <c r="K19" t="s">
+        <v>65</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>189</v>
+      </c>
+      <c r="B20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" t="s">
+        <v>186</v>
+      </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20">
+        <v>16</v>
+      </c>
+      <c r="G20" s="8">
+        <v>46510</v>
+      </c>
+      <c r="H20" s="8">
+        <v>46542</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" t="s">
+        <v>189</v>
+      </c>
+      <c r="K20" t="s">
+        <v>65</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B21" t="s">
+        <v>171</v>
+      </c>
+      <c r="C21" t="s">
+        <v>186</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21">
+        <v>16</v>
+      </c>
+      <c r="G21" s="8">
+        <v>46510</v>
+      </c>
+      <c r="H21" s="8">
+        <v>46542</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" t="s">
+        <v>190</v>
+      </c>
+      <c r="K21" t="s">
+        <v>65</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>191</v>
+      </c>
+      <c r="B22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22">
+        <v>8</v>
+      </c>
+      <c r="G22" s="8">
+        <v>46545</v>
+      </c>
+      <c r="H22" s="8">
+        <v>46570</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" t="s">
+        <v>191</v>
+      </c>
+      <c r="K22" t="s">
+        <v>65</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>192</v>
+      </c>
+      <c r="B23" t="s">
+        <v>166</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23">
+        <v>8</v>
+      </c>
+      <c r="G23" s="8">
+        <v>46545</v>
+      </c>
+      <c r="H23" s="8">
+        <v>46556</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" t="s">
+        <v>192</v>
+      </c>
+      <c r="K23" t="s">
+        <v>65</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>193</v>
+      </c>
+      <c r="B24" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24">
+        <v>3</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24">
+        <v>8</v>
+      </c>
+      <c r="G24" s="8">
+        <v>46545</v>
+      </c>
+      <c r="H24" s="8">
+        <v>46556</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" t="s">
+        <v>193</v>
+      </c>
+      <c r="K24" t="s">
+        <v>65</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>194</v>
+      </c>
+      <c r="B25" t="s">
+        <v>169</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25">
+        <v>8</v>
+      </c>
+      <c r="G25" s="8">
+        <v>46559</v>
+      </c>
+      <c r="H25" s="8">
+        <v>46570</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J25" t="s">
+        <v>194</v>
+      </c>
+      <c r="K25" t="s">
+        <v>65</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>195</v>
+      </c>
+      <c r="B26" t="s">
+        <v>171</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26">
+        <v>8</v>
+      </c>
+      <c r="G26" s="8">
+        <v>46559</v>
+      </c>
+      <c r="H26" s="8">
+        <v>46570</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" t="s">
+        <v>195</v>
+      </c>
+      <c r="K26" t="s">
+        <v>65</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1"/>
-  <dataValidations count="2">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B500">
+      <formula1>"de,ma,en,bio,geo,fvu,offen"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B2:B500">
       <formula1>"de,ma,en,bio,geo,fvu,offen"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="K10:K500">
+      <formula1>"fest,wahl,vorlaeufig,offen"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="K2:K500">
       <formula1>"fest,wahl,vorlaeufig,offen"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2155,15 +3344,668 @@
         <v>85</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B11" t="s">
+        <v>171</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>178</v>
+      </c>
+      <c r="B12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B13" t="s">
+        <v>166</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>183</v>
+      </c>
+      <c r="B15" t="s">
+        <v>169</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>184</v>
+      </c>
+      <c r="B16" t="s">
+        <v>171</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>185</v>
+      </c>
+      <c r="B17" t="s">
+        <v>169</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>187</v>
+      </c>
+      <c r="B18" t="s">
+        <v>166</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>188</v>
+      </c>
+      <c r="B19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>189</v>
+      </c>
+      <c r="B20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B21" t="s">
+        <v>171</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>191</v>
+      </c>
+      <c r="B22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>192</v>
+      </c>
+      <c r="B23" t="s">
+        <v>166</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>193</v>
+      </c>
+      <c r="B24" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>194</v>
+      </c>
+      <c r="B25" t="s">
+        <v>169</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>8</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>195</v>
+      </c>
+      <c r="B26" t="s">
+        <v>171</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B500">
+      <formula1>"de,ma,en,bio,geo,fvu,offen"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B2:B500">
       <formula1>"de,ma,en,bio,geo,fvu,offen"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2208,13 +4050,16 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
-  <dataValidations count="1">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" sqref="D10:D500">
+      <formula1>"pflicht,wahl"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D2:D500">
       <formula1>"pflicht,wahl"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2255,19 +4100,28 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
-  <dataValidations count="3">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B500">
+      <formula1>"de,ma,en,bio,geo,fvu,offen"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B2:B500">
       <formula1>"de,ma,en,bio,geo,fvu,offen"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C10:C500">
+      <formula1>"fach,methode,baustein"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C2:C500">
       <formula1>"fach,methode,baustein"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F10:F500">
+      <formula1>"ja,nein"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="F2:F500">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2300,16 +4154,22 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
-  <dataValidations count="2">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" sqref="A10:A500">
+      <formula1>"Mo,Di,Mi,Do,Fr"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="A2:A500">
       <formula1>"Mo,Di,Mi,Do,Fr"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E10:E500">
+      <formula1>"A,B,C"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="E2:E500">
       <formula1>"A,B,C"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -2361,21 +4221,33 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J1"/>
-  <dataValidations count="4">
+  <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B500">
+      <formula1>"input,coaching,sonstiges,entfall"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B2:B500">
       <formula1>"input,coaching,sonstiges,entfall"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C10:C500">
+      <formula1>"de,ma,en,bio,geo,fvu,offen"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="C2:C500">
       <formula1>"de,ma,en,bio,geo,fvu,offen"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E10:E500">
+      <formula1>"A,B,C"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="E2:E500">
       <formula1>"A,B,C"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="I10:I500">
+      <formula1>"ja,nein"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="I2:I500">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/content/jahrgaenge/Jg6.xlsx
+++ b/content/jahrgaenge/Jg6.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="298">
   <si>
     <t>Hinweise zu Jg6.xlsx</t>
   </si>
@@ -613,6 +613,9 @@
     <t>Satzglieder</t>
   </si>
   <si>
+    <t>Lernübersicht zur Grammatik</t>
+  </si>
+  <si>
     <t>Zuordnungen</t>
   </si>
   <si>
@@ -622,9 +625,15 @@
     <t>The Secret of Maple Hill</t>
   </si>
   <si>
+    <t>report on the events of the story – graded task</t>
+  </si>
+  <si>
     <t>Europa</t>
   </si>
   <si>
+    <t>Klimadiagramm zeichnen</t>
+  </si>
+  <si>
     <t>Konstruieren von Dreiecken</t>
   </si>
   <si>
@@ -677,6 +686,234 @@
   </si>
   <si>
     <t>Exkursionen</t>
+  </si>
+  <si>
+    <t>Sätze würfeln</t>
+  </si>
+  <si>
+    <t>M1, Satzgliedwürfel</t>
+  </si>
+  <si>
+    <t>Wiederholung aller Satzglieder</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>Der Hauptsatz</t>
+  </si>
+  <si>
+    <t>A1, Laptop</t>
+  </si>
+  <si>
+    <t>Der Nebensatz</t>
+  </si>
+  <si>
+    <t>A2, M2, Laptop</t>
+  </si>
+  <si>
+    <t>Einfache Satzreihen und Satzgefüge</t>
+  </si>
+  <si>
+    <t>A3, Laptop</t>
+  </si>
+  <si>
+    <t>Mehrgliedrige Satzgefüge</t>
+  </si>
+  <si>
+    <t>A4, Laptop</t>
+  </si>
+  <si>
+    <t>Satzbilder zeichnen</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>Zeichensetzung bei wörtlicher Rede</t>
+  </si>
+  <si>
+    <t>M3, Laptop</t>
+  </si>
+  <si>
+    <t>Begleitsätze bei wörtlicher Rede</t>
+  </si>
+  <si>
+    <t>A6, A7</t>
+  </si>
+  <si>
+    <t>Anwendung grammatischer Verfahren</t>
+  </si>
+  <si>
+    <t>A8, Laptop</t>
+  </si>
+  <si>
+    <t>Das kann ich jetzt!</t>
+  </si>
+  <si>
+    <t>M4, Material zur Gestaltung</t>
+  </si>
+  <si>
+    <t>Weiterführende Übungen</t>
+  </si>
+  <si>
+    <t>Welcome to Maple Hill</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>Falling Leaves &amp; First Feelings</t>
+  </si>
+  <si>
+    <t>M2, white paper</t>
+  </si>
+  <si>
+    <t>The Strange Note</t>
+  </si>
+  <si>
+    <t>A1, A2, or A3</t>
+  </si>
+  <si>
+    <t>The Poem in the Attic</t>
+  </si>
+  <si>
+    <t>A4, M2, white paper</t>
+  </si>
+  <si>
+    <t>What's Inside?</t>
+  </si>
+  <si>
+    <t>sensory boxes</t>
+  </si>
+  <si>
+    <t>The Mysterious Message</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>A Quiet Day</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>Whispers in the Wind</t>
+  </si>
+  <si>
+    <t>laptop, headphones</t>
+  </si>
+  <si>
+    <t>Maple Hill Side-Quests</t>
+  </si>
+  <si>
+    <t>A5, A6, A7, A8</t>
+  </si>
+  <si>
+    <t>Through the Trees</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>The Hidden Door</t>
+  </si>
+  <si>
+    <t>Escape the Forest</t>
+  </si>
+  <si>
+    <t>Between Truth and Silence</t>
+  </si>
+  <si>
+    <t>A9</t>
+  </si>
+  <si>
+    <t>Corinne's Choice – Your Task</t>
+  </si>
+  <si>
+    <t>M5, M6, or M7</t>
+  </si>
+  <si>
+    <t>A Quiet Voice Speaks</t>
+  </si>
+  <si>
+    <t>The Book with Her Name</t>
+  </si>
+  <si>
+    <t>Warm Up</t>
+  </si>
+  <si>
+    <t>A1, Hefter, Stift</t>
+  </si>
+  <si>
+    <t>Länder Europas</t>
+  </si>
+  <si>
+    <t>Atlas, A2, Lehrbuch, Hefter, Stift, Lineal</t>
+  </si>
+  <si>
+    <t>Inseln, Halbinseln, Flüsse, Gebirge Europas</t>
+  </si>
+  <si>
+    <t>A3, A4, Lehrbuch, Atlas, Heft</t>
+  </si>
+  <si>
+    <t>Europa – unser Heimatkontinent</t>
+  </si>
+  <si>
+    <t>Lehrbuch, M1, A5, Heft, Schere, Kleber</t>
+  </si>
+  <si>
+    <t>Großlandschaften Europas</t>
+  </si>
+  <si>
+    <t>Lehrbuch, Heft, A6, M2, Transparentpapier</t>
+  </si>
+  <si>
+    <t>Die Europäische Union</t>
+  </si>
+  <si>
+    <t>Lehrbuch, M3, Heft, Münzen</t>
+  </si>
+  <si>
+    <t>Ländersteckbrief</t>
+  </si>
+  <si>
+    <t>Lehrbuch, A7</t>
+  </si>
+  <si>
+    <t>Wetter und Klima / Klimadiagramm</t>
+  </si>
+  <si>
+    <t>M4, Lehrbuch, A8</t>
+  </si>
+  <si>
+    <t>Klimadiagramm auswerten</t>
+  </si>
+  <si>
+    <t>A9, A10, M4</t>
+  </si>
+  <si>
+    <t>Lehrbuch, kariertes Papier, Millimeterpapier</t>
+  </si>
+  <si>
+    <t>Gelingensnachweis</t>
+  </si>
+  <si>
+    <t>A11, Lehrbuch, Millimeterpapier</t>
+  </si>
+  <si>
+    <t>Universelles Klimadiagramm</t>
+  </si>
+  <si>
+    <t>Pappe, Stecknadeln</t>
+  </si>
+  <si>
+    <t>Vertiefung Topografie</t>
+  </si>
+  <si>
+    <t>A2, A3, A4, Atlas, Wandkarte</t>
   </si>
 </sst>
 </file>
@@ -3358,7 +3595,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>8</v>
+        <v>197</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -3378,7 +3615,7 @@
         <v>166</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
@@ -3404,7 +3641,7 @@
         <v>72</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
@@ -3430,16 +3667,16 @@
         <v>169</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>8</v>
+        <v>201</v>
+      </c>
+      <c r="F5">
+        <v>15</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>8</v>
@@ -3456,16 +3693,16 @@
         <v>171</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>8</v>
+        <v>203</v>
+      </c>
+      <c r="F6">
+        <v>11</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>8</v>
@@ -3482,7 +3719,7 @@
         <v>166</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
@@ -3508,7 +3745,7 @@
         <v>44</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>8</v>
@@ -3534,7 +3771,7 @@
         <v>72</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>8</v>
@@ -3560,7 +3797,7 @@
         <v>169</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>8</v>
@@ -3586,7 +3823,7 @@
         <v>171</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>8</v>
@@ -3612,7 +3849,7 @@
         <v>72</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>8</v>
@@ -3638,7 +3875,7 @@
         <v>166</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>8</v>
@@ -3664,10 +3901,10 @@
         <v>44</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>8</v>
@@ -3690,7 +3927,7 @@
         <v>169</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>8</v>
@@ -3716,7 +3953,7 @@
         <v>171</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>8</v>
@@ -3742,7 +3979,7 @@
         <v>169</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>8</v>
@@ -3768,7 +4005,7 @@
         <v>166</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>8</v>
@@ -3794,7 +4031,7 @@
         <v>72</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>8</v>
@@ -3820,7 +4057,7 @@
         <v>44</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>8</v>
@@ -3846,7 +4083,7 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>8</v>
@@ -3872,7 +4109,7 @@
         <v>44</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>8</v>
@@ -3898,7 +4135,7 @@
         <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>8</v>
@@ -3924,7 +4161,7 @@
         <v>72</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>8</v>
@@ -4011,7 +4248,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4046,6 +4283,1098 @@
       </c>
       <c r="H1" s="7" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="D2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2">
+        <v>45</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E3">
+        <v>45</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4">
+        <v>45</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>164</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5">
+        <v>60</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6">
+        <v>45</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D7" t="s">
+        <v>182</v>
+      </c>
+      <c r="E7">
+        <v>45</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8">
+        <v>30</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D9" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9">
+        <v>30</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>164</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10">
+        <v>60</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>164</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11">
+        <v>45</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>164</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12">
+        <v>80</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>164</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E13">
+        <v>60</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>168</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D14" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14">
+        <v>60</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>168</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15">
+        <v>60</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>168</v>
+      </c>
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D16" t="s">
+        <v>93</v>
+      </c>
+      <c r="E16">
+        <v>30</v>
+      </c>
+      <c r="F16">
+        <v>2</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>168</v>
+      </c>
+      <c r="B17">
+        <v>4</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D17" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17">
+        <v>60</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>168</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D18" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18">
+        <v>30</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>168</v>
+      </c>
+      <c r="B19">
+        <v>6</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D19" t="s">
+        <v>93</v>
+      </c>
+      <c r="E19">
+        <v>35</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>168</v>
+      </c>
+      <c r="B20">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="D20" t="s">
+        <v>182</v>
+      </c>
+      <c r="E20">
+        <v>60</v>
+      </c>
+      <c r="F20">
+        <v>2</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>168</v>
+      </c>
+      <c r="B21">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21">
+        <v>45</v>
+      </c>
+      <c r="F21">
+        <v>2</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>168</v>
+      </c>
+      <c r="B22">
+        <v>9</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22">
+        <v>80</v>
+      </c>
+      <c r="F22">
+        <v>3</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>168</v>
+      </c>
+      <c r="B23">
+        <v>10</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D23" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23">
+        <v>35</v>
+      </c>
+      <c r="F23">
+        <v>2</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>168</v>
+      </c>
+      <c r="B24">
+        <v>11</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D24" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24">
+        <v>60</v>
+      </c>
+      <c r="F24">
+        <v>3</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>168</v>
+      </c>
+      <c r="B25">
+        <v>12</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D25" t="s">
+        <v>93</v>
+      </c>
+      <c r="E25">
+        <v>60</v>
+      </c>
+      <c r="F25">
+        <v>3</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>168</v>
+      </c>
+      <c r="B26">
+        <v>13</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D26" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26">
+        <v>20</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>168</v>
+      </c>
+      <c r="B27">
+        <v>14</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D27" t="s">
+        <v>93</v>
+      </c>
+      <c r="E27">
+        <v>40</v>
+      </c>
+      <c r="F27">
+        <v>3</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>168</v>
+      </c>
+      <c r="B28">
+        <v>15</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D28" t="s">
+        <v>93</v>
+      </c>
+      <c r="E28">
+        <v>100</v>
+      </c>
+      <c r="F28">
+        <v>3</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>168</v>
+      </c>
+      <c r="B29">
+        <v>16</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D29" t="s">
+        <v>182</v>
+      </c>
+      <c r="E29">
+        <v>25</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>168</v>
+      </c>
+      <c r="B30">
+        <v>17</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D30" t="s">
+        <v>182</v>
+      </c>
+      <c r="E30">
+        <v>25</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>170</v>
+      </c>
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D31" t="s">
+        <v>93</v>
+      </c>
+      <c r="E31">
+        <v>20</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32">
+        <v>2</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D32" t="s">
+        <v>93</v>
+      </c>
+      <c r="E32">
+        <v>80</v>
+      </c>
+      <c r="F32">
+        <v>2</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>170</v>
+      </c>
+      <c r="B33">
+        <v>3</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D33" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33">
+        <v>90</v>
+      </c>
+      <c r="F33">
+        <v>2</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>170</v>
+      </c>
+      <c r="B34">
+        <v>4</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D34" t="s">
+        <v>93</v>
+      </c>
+      <c r="E34">
+        <v>45</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>170</v>
+      </c>
+      <c r="B35">
+        <v>5</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D35" t="s">
+        <v>93</v>
+      </c>
+      <c r="E35">
+        <v>45</v>
+      </c>
+      <c r="F35">
+        <v>2</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>170</v>
+      </c>
+      <c r="B36">
+        <v>6</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D36" t="s">
+        <v>182</v>
+      </c>
+      <c r="E36">
+        <v>45</v>
+      </c>
+      <c r="F36">
+        <v>2</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>170</v>
+      </c>
+      <c r="B37">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D37" t="s">
+        <v>93</v>
+      </c>
+      <c r="E37">
+        <v>60</v>
+      </c>
+      <c r="F37">
+        <v>2</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>170</v>
+      </c>
+      <c r="B38">
+        <v>8</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="D38" t="s">
+        <v>93</v>
+      </c>
+      <c r="E38">
+        <v>60</v>
+      </c>
+      <c r="F38">
+        <v>2</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>170</v>
+      </c>
+      <c r="B39">
+        <v>9</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D39" t="s">
+        <v>93</v>
+      </c>
+      <c r="E39">
+        <v>80</v>
+      </c>
+      <c r="F39">
+        <v>3</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>170</v>
+      </c>
+      <c r="B40">
+        <v>10</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D40" t="s">
+        <v>93</v>
+      </c>
+      <c r="E40">
+        <v>80</v>
+      </c>
+      <c r="F40">
+        <v>3</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>170</v>
+      </c>
+      <c r="B41">
+        <v>11</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D41" t="s">
+        <v>93</v>
+      </c>
+      <c r="E41">
+        <v>40</v>
+      </c>
+      <c r="F41">
+        <v>3</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B42">
+        <v>12</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D42" t="s">
+        <v>182</v>
+      </c>
+      <c r="E42">
+        <v>30</v>
+      </c>
+      <c r="F42">
+        <v>2</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>170</v>
+      </c>
+      <c r="B43">
+        <v>13</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D43" t="s">
+        <v>93</v>
+      </c>
+      <c r="E43">
+        <v>45</v>
+      </c>
+      <c r="F43">
+        <v>2</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/content/jahrgaenge/Jg6.xlsx
+++ b/content/jahrgaenge/Jg6.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="328">
   <si>
     <t>Hinweise zu Jg6.xlsx</t>
   </si>
@@ -914,6 +914,96 @@
   </si>
   <si>
     <t>A2, A3, A4, Atlas, Wandkarte</t>
+  </si>
+  <si>
+    <t>2026-09-23</t>
+  </si>
+  <si>
+    <t>coaching</t>
+  </si>
+  <si>
+    <t>ADM</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>HCO</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>Klimadiagramme auswerten</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>DUB</t>
+  </si>
+  <si>
+    <t>Wiederholung Satzglieder erkennen</t>
+  </si>
+  <si>
+    <t>EPP</t>
+  </si>
+  <si>
+    <t>2026-09-30</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>writing workshop</t>
+  </si>
+  <si>
+    <t>2026-10-05</t>
+  </si>
+  <si>
+    <t>2026-10-06</t>
+  </si>
+  <si>
+    <t>HS-NS erkennen, Satzbilder (Station 5 und 7)</t>
+  </si>
+  <si>
+    <t>2026-10-07</t>
+  </si>
+  <si>
+    <t>2026-10-08</t>
+  </si>
+  <si>
+    <t>Klimadiagramme zeichnen</t>
+  </si>
+  <si>
+    <t>2026-10-09</t>
+  </si>
+  <si>
+    <t>sonstiges</t>
+  </si>
+  <si>
+    <t>Pädagogischer Tag – Heimarbeit</t>
+  </si>
+  <si>
+    <t>2026-10-27</t>
+  </si>
+  <si>
+    <t>wörtliche Rede</t>
+  </si>
+  <si>
+    <t>2026-10-28</t>
+  </si>
+  <si>
+    <t>2026-10-29</t>
+  </si>
+  <si>
+    <t>Topografie – wie arbeite ich mit Wandkarten</t>
+  </si>
+  <si>
+    <t>2026-10-30</t>
+  </si>
+  <si>
+    <t>GEN – how to… (Station 13 und 14)</t>
   </si>
 </sst>
 </file>
@@ -5504,7 +5594,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="13" style="5" customWidth="1"/>
@@ -5546,6 +5636,582 @@
       </c>
       <c r="J1" s="3" t="s">
         <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="B2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="B3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D4" t="s">
+        <v>300</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="H4">
+        <v>9</v>
+      </c>
+      <c r="I4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B6" t="s">
+        <v>299</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" t="s">
+        <v>308</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B7" t="s">
+        <v>299</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" t="s">
+        <v>300</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="B8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D8" t="s">
+        <v>308</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>302</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="B10" t="s">
+        <v>299</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" t="s">
+        <v>300</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="B11" t="s">
+        <v>138</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" t="s">
+        <v>306</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="H11" t="s">
+        <v>8</v>
+      </c>
+      <c r="I11" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="B12" t="s">
+        <v>299</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s">
+        <v>308</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B13" t="s">
+        <v>138</v>
+      </c>
+      <c r="C13" t="s">
+        <v>171</v>
+      </c>
+      <c r="D13" t="s">
+        <v>300</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H13">
+        <v>10</v>
+      </c>
+      <c r="I13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B14" t="s">
+        <v>299</v>
+      </c>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" t="s">
+        <v>302</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s">
+        <v>319</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="H15" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="B16" t="s">
+        <v>138</v>
+      </c>
+      <c r="C16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" t="s">
+        <v>306</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="H16">
+        <v>9</v>
+      </c>
+      <c r="I16" t="s">
+        <v>8</v>
+      </c>
+      <c r="J16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="B17" t="s">
+        <v>299</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" t="s">
+        <v>308</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="B18" t="s">
+        <v>138</v>
+      </c>
+      <c r="C18" t="s">
+        <v>171</v>
+      </c>
+      <c r="D18" t="s">
+        <v>300</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="H18" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="B19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C19" t="s">
+        <v>169</v>
+      </c>
+      <c r="D19" t="s">
+        <v>308</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="H19" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/content/jahrgaenge/Jg6.xlsx
+++ b/content/jahrgaenge/Jg6.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2107" uniqueCount="473">
   <si>
     <t>Hinweise zu Jg6.xlsx</t>
   </si>
@@ -916,7 +916,7 @@
     <t>A2, A3, A4, Atlas, Wandkarte</t>
   </si>
   <si>
-    <t>2026-09-23</t>
+    <t>2026-08-24</t>
   </si>
   <si>
     <t>coaching</t>
@@ -925,6 +925,84 @@
     <t>ADM</t>
   </si>
   <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
+    <t>STE</t>
+  </si>
+  <si>
+    <t>Darstellung von Zuordnungen</t>
+  </si>
+  <si>
+    <t>EPP</t>
+  </si>
+  <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
+    <t>BRU</t>
+  </si>
+  <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
+    <t>DUB</t>
+  </si>
+  <si>
+    <t>Subjekt und Prädikat</t>
+  </si>
+  <si>
+    <t>BUZ</t>
+  </si>
+  <si>
+    <t>2026-08-28</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>Unterscheidung von Zuordnungen</t>
+  </si>
+  <si>
+    <t>2026-09-02</t>
+  </si>
+  <si>
+    <t>Untersuchen eines Regenwurms</t>
+  </si>
+  <si>
+    <t>2026-09-03</t>
+  </si>
+  <si>
+    <t>HS, NS, Satzreihen, Satzgefüge</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Grafische Darstellungen</t>
+  </si>
+  <si>
+    <t>2026-09-09</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>Wörtliche Rede</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>2026-09-24</t>
+  </si>
+  <si>
     <t>2026-09-25</t>
   </si>
   <si>
@@ -940,18 +1018,9 @@
     <t>2026-09-29</t>
   </si>
   <si>
-    <t>DUB</t>
-  </si>
-  <si>
     <t>Wiederholung Satzglieder erkennen</t>
   </si>
   <si>
-    <t>EPP</t>
-  </si>
-  <si>
-    <t>2026-09-30</t>
-  </si>
-  <si>
     <t>2026-10-01</t>
   </si>
   <si>
@@ -961,19 +1030,19 @@
     <t>2026-10-05</t>
   </si>
   <si>
+    <t>Klimadiagramme zeichnen</t>
+  </si>
+  <si>
     <t>2026-10-06</t>
   </si>
   <si>
     <t>HS-NS erkennen, Satzbilder (Station 5 und 7)</t>
   </si>
   <si>
-    <t>2026-10-07</t>
-  </si>
-  <si>
     <t>2026-10-08</t>
   </si>
   <si>
-    <t>Klimadiagramme zeichnen</t>
+    <t>Topografie – wie arbeite ich mit Wandkarten</t>
   </si>
   <si>
     <t>2026-10-09</t>
@@ -991,19 +1060,385 @@
     <t>wörtliche Rede</t>
   </si>
   <si>
-    <t>2026-10-28</t>
-  </si>
-  <si>
     <t>2026-10-29</t>
   </si>
   <si>
-    <t>Topografie – wie arbeite ich mit Wandkarten</t>
-  </si>
-  <si>
-    <t>2026-10-30</t>
-  </si>
-  <si>
     <t>GEN – how to… (Station 13 und 14)</t>
+  </si>
+  <si>
+    <t>2026-11-03</t>
+  </si>
+  <si>
+    <t>2026-11-04</t>
+  </si>
+  <si>
+    <t>Grundlegende Dreieckseigenschaften (Station 1-6)</t>
+  </si>
+  <si>
+    <t>2026-11-09</t>
+  </si>
+  <si>
+    <t>2026-11-10</t>
+  </si>
+  <si>
+    <t>HEC</t>
+  </si>
+  <si>
+    <t>Merkmale Fabeln und Fabeltiere (Station 3 und 4)</t>
+  </si>
+  <si>
+    <t>2026-11-11</t>
+  </si>
+  <si>
+    <t>Konstruktion nach dem Kongruenzsatz SsW</t>
+  </si>
+  <si>
+    <t>2026-11-12</t>
+  </si>
+  <si>
+    <t>OHR</t>
+  </si>
+  <si>
+    <t>2026-11-13</t>
+  </si>
+  <si>
+    <t>2026-11-16</t>
+  </si>
+  <si>
+    <t>2026-11-17</t>
+  </si>
+  <si>
+    <t>Der Aufbau einer Fabel</t>
+  </si>
+  <si>
+    <t>2026-11-19</t>
+  </si>
+  <si>
+    <t>2026-11-20</t>
+  </si>
+  <si>
+    <t>2026-11-23</t>
+  </si>
+  <si>
+    <t>2026-11-24</t>
+  </si>
+  <si>
+    <t>Eine Fabel untersuchen und Lehren einer Fabel (Station 8 und 9)</t>
+  </si>
+  <si>
+    <t>2026-11-25</t>
+  </si>
+  <si>
+    <t>Kommt mit euren Fragen!</t>
+  </si>
+  <si>
+    <t>2026-11-26</t>
+  </si>
+  <si>
+    <t>2026-11-27</t>
+  </si>
+  <si>
+    <t>2026-11-30</t>
+  </si>
+  <si>
+    <t>2026-12-01</t>
+  </si>
+  <si>
+    <t>2026-12-07</t>
+  </si>
+  <si>
+    <t>Wind und Relief</t>
+  </si>
+  <si>
+    <t>2026-12-09</t>
+  </si>
+  <si>
+    <t>2026-12-10</t>
+  </si>
+  <si>
+    <t>Working with a dictionary</t>
+  </si>
+  <si>
+    <t>2026-12-14</t>
+  </si>
+  <si>
+    <t>Golfstrom</t>
+  </si>
+  <si>
+    <t>2026-12-16</t>
+  </si>
+  <si>
+    <t>2026-12-17</t>
+  </si>
+  <si>
+    <t>Viewing and listening skills</t>
+  </si>
+  <si>
+    <t>2027-01-04</t>
+  </si>
+  <si>
+    <t>LK</t>
+  </si>
+  <si>
+    <t>2027-01-06</t>
+  </si>
+  <si>
+    <t>2027-01-07</t>
+  </si>
+  <si>
+    <t>Mediation from English to German</t>
+  </si>
+  <si>
+    <t>2027-01-18</t>
+  </si>
+  <si>
+    <t>RIK</t>
+  </si>
+  <si>
+    <t>Ocean City – Umgang mit dem Flipbook</t>
+  </si>
+  <si>
+    <t>2027-01-19</t>
+  </si>
+  <si>
+    <t>Umkreis von Dreiecken</t>
+  </si>
+  <si>
+    <t>2027-01-20</t>
+  </si>
+  <si>
+    <t>HEI</t>
+  </si>
+  <si>
+    <t>Herr der Diebe: Wie schreibe ich eine Textstelle um?</t>
+  </si>
+  <si>
+    <t>2027-01-21</t>
+  </si>
+  <si>
+    <t>Moose und Farne</t>
+  </si>
+  <si>
+    <t>2027-01-25</t>
+  </si>
+  <si>
+    <t>Ocean City – Figurenkonstellation erstellen (Station 6 und 15)</t>
+  </si>
+  <si>
+    <t>2027-01-26</t>
+  </si>
+  <si>
+    <t>Inkreis von Dreiecken</t>
+  </si>
+  <si>
+    <t>2027-01-27</t>
+  </si>
+  <si>
+    <t>2027-01-28</t>
+  </si>
+  <si>
+    <t>2027-01-29</t>
+  </si>
+  <si>
+    <t>2027-02-01</t>
+  </si>
+  <si>
+    <t>Ocean City – Rezensionen schreiben</t>
+  </si>
+  <si>
+    <t>2027-02-02</t>
+  </si>
+  <si>
+    <t>Flächeninhalt von Dreiecken</t>
+  </si>
+  <si>
+    <t>2027-02-03</t>
+  </si>
+  <si>
+    <t>2027-02-04</t>
+  </si>
+  <si>
+    <t>2027-03-01</t>
+  </si>
+  <si>
+    <t>Glaziale Serie</t>
+  </si>
+  <si>
+    <t>2027-03-02</t>
+  </si>
+  <si>
+    <t>Describing people and character / working with adjectives</t>
+  </si>
+  <si>
+    <t>2027-03-03</t>
+  </si>
+  <si>
+    <t>Pilze</t>
+  </si>
+  <si>
+    <t>2027-03-08</t>
+  </si>
+  <si>
+    <t>Vorbereitung auf den Gelingensnachweis</t>
+  </si>
+  <si>
+    <t>2027-03-09</t>
+  </si>
+  <si>
+    <t>Working with (informational) texts</t>
+  </si>
+  <si>
+    <t>2027-03-10</t>
+  </si>
+  <si>
+    <t>Nahrungsketten und -netze (Station 8, 10 und 11)</t>
+  </si>
+  <si>
+    <t>2027-03-15</t>
+  </si>
+  <si>
+    <t>Ein Landschaftsprofil auswerten</t>
+  </si>
+  <si>
+    <t>2027-03-16</t>
+  </si>
+  <si>
+    <t>2027-03-17</t>
+  </si>
+  <si>
+    <t>2027-04-13</t>
+  </si>
+  <si>
+    <t>Körpernetze</t>
+  </si>
+  <si>
+    <t>2027-04-14</t>
+  </si>
+  <si>
+    <t>2027-04-15</t>
+  </si>
+  <si>
+    <t>How to work with a team reader / Introduction to Pip and the umbrella room</t>
+  </si>
+  <si>
+    <t>2027-04-16</t>
+  </si>
+  <si>
+    <t>Das Laubblatt (Fotosynthese und Blattformen) (Station 4 und 5)</t>
+  </si>
+  <si>
+    <t>2027-04-20</t>
+  </si>
+  <si>
+    <t>Schrägbild</t>
+  </si>
+  <si>
+    <t>2027-04-21</t>
+  </si>
+  <si>
+    <t>Methode Legebild und Blütendiagramm</t>
+  </si>
+  <si>
+    <t>2027-04-22</t>
+  </si>
+  <si>
+    <t>Reading strategies</t>
+  </si>
+  <si>
+    <t>2027-04-23</t>
+  </si>
+  <si>
+    <t>Teamfahrt</t>
+  </si>
+  <si>
+    <t>2027-04-27</t>
+  </si>
+  <si>
+    <t>Oberflächeninhalt</t>
+  </si>
+  <si>
+    <t>2027-04-28</t>
+  </si>
+  <si>
+    <t>Von der Blüte zur Frucht</t>
+  </si>
+  <si>
+    <t>2027-04-29</t>
+  </si>
+  <si>
+    <t>Reading Journal Help</t>
+  </si>
+  <si>
+    <t>2027-05-04</t>
+  </si>
+  <si>
+    <t>2027-05-10</t>
+  </si>
+  <si>
+    <t>Fragen zum Gelingensnachweis</t>
+  </si>
+  <si>
+    <t>2027-05-11</t>
+  </si>
+  <si>
+    <t>TUC</t>
+  </si>
+  <si>
+    <t>Die Sprache der Profis</t>
+  </si>
+  <si>
+    <t>2027-05-12</t>
+  </si>
+  <si>
+    <t>Aktiv und Passiv</t>
+  </si>
+  <si>
+    <t>2027-05-13</t>
+  </si>
+  <si>
+    <t>Übung Topografie</t>
+  </si>
+  <si>
+    <t>2027-05-20</t>
+  </si>
+  <si>
+    <t>2027-05-24</t>
+  </si>
+  <si>
+    <t>2027-05-25</t>
+  </si>
+  <si>
+    <t>Der Unfallbericht (Station 12 und 13)</t>
+  </si>
+  <si>
+    <t>2027-05-27</t>
+  </si>
+  <si>
+    <t>2027-06-15</t>
+  </si>
+  <si>
+    <t>2027-06-16</t>
+  </si>
+  <si>
+    <t>2027-06-17</t>
+  </si>
+  <si>
+    <t>Wortbildung</t>
+  </si>
+  <si>
+    <t>2027-06-22</t>
+  </si>
+  <si>
+    <t>Erb-, Lehn- und Fremdwörter</t>
+  </si>
+  <si>
+    <t>2027-06-24</t>
+  </si>
+  <si>
+    <t>Einführung: Was ist Digital Sparks?</t>
+  </si>
+  <si>
+    <t>2027-06-29</t>
   </si>
 </sst>
 </file>
@@ -5594,7 +6029,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J121"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="13" style="5" customWidth="1"/>
@@ -5675,10 +6110,10 @@
         <v>301</v>
       </c>
       <c r="B3" t="s">
-        <v>299</v>
+        <v>138</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>166</v>
       </c>
       <c r="D3" t="s">
         <v>302</v>
@@ -5690,10 +6125,10 @@
         <v>8</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>8</v>
+        <v>303</v>
+      </c>
+      <c r="H3">
+        <v>3</v>
       </c>
       <c r="I3" t="s">
         <v>8</v>
@@ -5704,16 +6139,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B4" t="s">
-        <v>138</v>
+        <v>299</v>
       </c>
       <c r="C4" t="s">
-        <v>171</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -5722,10 +6157,10 @@
         <v>8</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="H4">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
       </c>
       <c r="I4" t="s">
         <v>8</v>
@@ -5739,10 +6174,10 @@
         <v>305</v>
       </c>
       <c r="B5" t="s">
-        <v>138</v>
+        <v>299</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
         <v>306</v>
@@ -5754,10 +6189,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="H5">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="H5" t="s">
+        <v>8</v>
       </c>
       <c r="I5" t="s">
         <v>8</v>
@@ -5768,13 +6203,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B6" t="s">
-        <v>299</v>
+        <v>138</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
         <v>308</v>
@@ -5786,10 +6221,10 @@
         <v>8</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" t="s">
-        <v>8</v>
+        <v>309</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
       </c>
       <c r="I6" t="s">
         <v>8</v>
@@ -5800,7 +6235,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B7" t="s">
         <v>299</v>
@@ -5809,7 +6244,7 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -5832,16 +6267,16 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B8" t="s">
-        <v>138</v>
+        <v>299</v>
       </c>
       <c r="C8" t="s">
-        <v>169</v>
+        <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -5850,10 +6285,10 @@
         <v>8</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="H8">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="H8" t="s">
+        <v>8</v>
       </c>
       <c r="I8" t="s">
         <v>8</v>
@@ -5864,7 +6299,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B9" t="s">
         <v>299</v>
@@ -5873,7 +6308,7 @@
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -5899,13 +6334,13 @@
         <v>312</v>
       </c>
       <c r="B10" t="s">
-        <v>299</v>
+        <v>138</v>
       </c>
       <c r="C10" t="s">
-        <v>8</v>
+        <v>166</v>
       </c>
       <c r="D10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -5914,10 +6349,10 @@
         <v>8</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H10" t="s">
-        <v>8</v>
+        <v>313</v>
+      </c>
+      <c r="H10">
+        <v>6</v>
       </c>
       <c r="I10" t="s">
         <v>8</v>
@@ -5928,16 +6363,16 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B11" t="s">
-        <v>138</v>
+        <v>299</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -5946,7 +6381,7 @@
         <v>8</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>314</v>
+        <v>8</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -5960,31 +6395,31 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="B12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" t="s">
+        <v>306</v>
+      </c>
+      <c r="E12" t="s">
+        <v>141</v>
+      </c>
+      <c r="F12" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="B12" t="s">
-        <v>299</v>
-      </c>
-      <c r="C12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" t="s">
-        <v>308</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" t="s">
-        <v>8</v>
+      <c r="H12">
+        <v>3</v>
       </c>
       <c r="I12" t="s">
-        <v>8</v>
+        <v>114</v>
       </c>
       <c r="J12" t="s">
         <v>8</v>
@@ -5998,10 +6433,10 @@
         <v>138</v>
       </c>
       <c r="C13" t="s">
-        <v>171</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -6013,7 +6448,7 @@
         <v>317</v>
       </c>
       <c r="H13">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I13" t="s">
         <v>8</v>
@@ -6024,7 +6459,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B14" t="s">
         <v>299</v>
@@ -6033,7 +6468,7 @@
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -6056,31 +6491,31 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>20</v>
+        <v>318</v>
       </c>
       <c r="B15" t="s">
+        <v>138</v>
+      </c>
+      <c r="C15" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" t="s">
+        <v>306</v>
+      </c>
+      <c r="E15" t="s">
         <v>319</v>
       </c>
-      <c r="C15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
       <c r="F15" t="s">
         <v>8</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="H15" t="s">
-        <v>8</v>
+        <v>315</v>
+      </c>
+      <c r="H15">
+        <v>3</v>
       </c>
       <c r="I15" t="s">
-        <v>8</v>
+        <v>114</v>
       </c>
       <c r="J15" t="s">
         <v>8</v>
@@ -6088,16 +6523,16 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>321</v>
+        <v>127</v>
       </c>
       <c r="B16" t="s">
-        <v>138</v>
+        <v>299</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -6106,10 +6541,10 @@
         <v>8</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="H16">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="H16" t="s">
+        <v>8</v>
       </c>
       <c r="I16" t="s">
         <v>8</v>
@@ -6120,16 +6555,16 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>323</v>
+        <v>136</v>
       </c>
       <c r="B17" t="s">
-        <v>299</v>
+        <v>138</v>
       </c>
       <c r="C17" t="s">
-        <v>8</v>
+        <v>166</v>
       </c>
       <c r="D17" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -6138,10 +6573,10 @@
         <v>8</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H17" t="s">
-        <v>8</v>
+        <v>320</v>
+      </c>
+      <c r="H17">
+        <v>11</v>
       </c>
       <c r="I17" t="s">
         <v>8</v>
@@ -6152,16 +6587,16 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>324</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s">
-        <v>138</v>
+        <v>299</v>
       </c>
       <c r="C18" t="s">
-        <v>171</v>
+        <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -6170,7 +6605,7 @@
         <v>8</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>325</v>
+        <v>8</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -6184,33 +6619,3297 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B19" t="s">
         <v>138</v>
       </c>
       <c r="C19" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" t="s">
+        <v>306</v>
+      </c>
+      <c r="E19" t="s">
+        <v>322</v>
+      </c>
+      <c r="F19" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H19">
+        <v>3</v>
+      </c>
+      <c r="I19" t="s">
+        <v>114</v>
+      </c>
+      <c r="J19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="B20" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" t="s">
+        <v>308</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="H20">
+        <v>9</v>
+      </c>
+      <c r="I20" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="B21" t="s">
+        <v>299</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" t="s">
+        <v>310</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="B22" t="s">
+        <v>299</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" t="s">
+        <v>306</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="B23" t="s">
+        <v>299</v>
+      </c>
+      <c r="C23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" t="s">
+        <v>300</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="B24" t="s">
+        <v>299</v>
+      </c>
+      <c r="C24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" t="s">
+        <v>328</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="B25" t="s">
+        <v>138</v>
+      </c>
+      <c r="C25" t="s">
+        <v>171</v>
+      </c>
+      <c r="D25" t="s">
+        <v>300</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>8</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="H25">
+        <v>9</v>
+      </c>
+      <c r="I25" t="s">
+        <v>8</v>
+      </c>
+      <c r="J25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="B26" t="s">
+        <v>138</v>
+      </c>
+      <c r="C26" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" t="s">
+        <v>308</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="H26">
+        <v>2</v>
+      </c>
+      <c r="I26" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="B27" t="s">
+        <v>299</v>
+      </c>
+      <c r="C27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" t="s">
+        <v>304</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="B28" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" t="s">
         <v>169</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D28" t="s">
+        <v>304</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>8</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="H28">
+        <v>2</v>
+      </c>
+      <c r="I28" t="s">
+        <v>8</v>
+      </c>
+      <c r="J28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="B29" t="s">
+        <v>299</v>
+      </c>
+      <c r="C29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" t="s">
+        <v>300</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" t="s">
+        <v>299</v>
+      </c>
+      <c r="C30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" t="s">
+        <v>328</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>8</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H30" t="s">
+        <v>8</v>
+      </c>
+      <c r="I30" t="s">
+        <v>8</v>
+      </c>
+      <c r="J30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B31" t="s">
+        <v>138</v>
+      </c>
+      <c r="C31" t="s">
+        <v>171</v>
+      </c>
+      <c r="D31" t="s">
+        <v>300</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>8</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="H31">
+        <v>10</v>
+      </c>
+      <c r="I31" t="s">
+        <v>8</v>
+      </c>
+      <c r="J31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="B32" t="s">
+        <v>138</v>
+      </c>
+      <c r="C32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" t="s">
         <v>308</v>
       </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>8</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="H19" t="s">
-        <v>8</v>
-      </c>
-      <c r="I19" t="s">
-        <v>8</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="H32" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="B33" t="s">
+        <v>299</v>
+      </c>
+      <c r="C33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" t="s">
+        <v>304</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="B34" t="s">
+        <v>138</v>
+      </c>
+      <c r="C34" t="s">
+        <v>171</v>
+      </c>
+      <c r="D34" t="s">
+        <v>300</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" t="s">
+        <v>8</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="H34" t="s">
+        <v>8</v>
+      </c>
+      <c r="I34" t="s">
+        <v>8</v>
+      </c>
+      <c r="J34" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="B35" t="s">
+        <v>299</v>
+      </c>
+      <c r="C35" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" t="s">
+        <v>328</v>
+      </c>
+      <c r="E35" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" t="s">
+        <v>342</v>
+      </c>
+      <c r="C36" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" t="s">
+        <v>8</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="H36" t="s">
+        <v>8</v>
+      </c>
+      <c r="I36" t="s">
+        <v>8</v>
+      </c>
+      <c r="J36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B37" t="s">
+        <v>138</v>
+      </c>
+      <c r="C37" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" t="s">
+        <v>308</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" t="s">
+        <v>8</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H37">
+        <v>9</v>
+      </c>
+      <c r="I37" t="s">
+        <v>8</v>
+      </c>
+      <c r="J37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B38" t="s">
+        <v>299</v>
+      </c>
+      <c r="C38" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" t="s">
+        <v>304</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" t="s">
+        <v>8</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H38" t="s">
+        <v>8</v>
+      </c>
+      <c r="I38" t="s">
+        <v>8</v>
+      </c>
+      <c r="J38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="B39" t="s">
+        <v>138</v>
+      </c>
+      <c r="C39" t="s">
+        <v>169</v>
+      </c>
+      <c r="D39" t="s">
+        <v>304</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" t="s">
+        <v>8</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="H39" t="s">
+        <v>8</v>
+      </c>
+      <c r="I39" t="s">
+        <v>8</v>
+      </c>
+      <c r="J39" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="B40" t="s">
+        <v>299</v>
+      </c>
+      <c r="C40" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" t="s">
+        <v>300</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" t="s">
+        <v>8</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H40" t="s">
+        <v>8</v>
+      </c>
+      <c r="I40" t="s">
+        <v>8</v>
+      </c>
+      <c r="J40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="B41" t="s">
+        <v>299</v>
+      </c>
+      <c r="C41" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" t="s">
+        <v>302</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H41" t="s">
+        <v>8</v>
+      </c>
+      <c r="I41" t="s">
+        <v>8</v>
+      </c>
+      <c r="J41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="B42" t="s">
+        <v>138</v>
+      </c>
+      <c r="C42" t="s">
+        <v>166</v>
+      </c>
+      <c r="D42" t="s">
+        <v>302</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" t="s">
+        <v>8</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="H42" t="s">
+        <v>8</v>
+      </c>
+      <c r="I42" t="s">
+        <v>8</v>
+      </c>
+      <c r="J42" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="B43" t="s">
+        <v>299</v>
+      </c>
+      <c r="C43" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" t="s">
+        <v>306</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H43" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="B44" t="s">
+        <v>138</v>
+      </c>
+      <c r="C44" t="s">
+        <v>72</v>
+      </c>
+      <c r="D44" t="s">
+        <v>140</v>
+      </c>
+      <c r="E44" t="s">
+        <v>141</v>
+      </c>
+      <c r="F44" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" t="s">
+        <v>114</v>
+      </c>
+      <c r="J44" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="B45" t="s">
+        <v>138</v>
+      </c>
+      <c r="C45" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45" t="s">
+        <v>353</v>
+      </c>
+      <c r="E45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="H45" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="B46" t="s">
+        <v>299</v>
+      </c>
+      <c r="C46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" t="s">
+        <v>302</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" t="s">
+        <v>8</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H46" t="s">
+        <v>8</v>
+      </c>
+      <c r="I46" t="s">
+        <v>8</v>
+      </c>
+      <c r="J46" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="B47" t="s">
+        <v>138</v>
+      </c>
+      <c r="C47" t="s">
+        <v>166</v>
+      </c>
+      <c r="D47" t="s">
+        <v>302</v>
+      </c>
+      <c r="E47" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="H47">
+        <v>11</v>
+      </c>
+      <c r="I47" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="B48" t="s">
+        <v>299</v>
+      </c>
+      <c r="C48" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" t="s">
+        <v>306</v>
+      </c>
+      <c r="E48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" t="s">
+        <v>8</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H48" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="B49" t="s">
+        <v>299</v>
+      </c>
+      <c r="C49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" t="s">
+        <v>358</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H49" t="s">
+        <v>8</v>
+      </c>
+      <c r="I49" t="s">
+        <v>8</v>
+      </c>
+      <c r="J49" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="B50" t="s">
+        <v>138</v>
+      </c>
+      <c r="C50" t="s">
+        <v>72</v>
+      </c>
+      <c r="D50" t="s">
+        <v>306</v>
+      </c>
+      <c r="E50" t="s">
+        <v>141</v>
+      </c>
+      <c r="F50" t="s">
+        <v>8</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H50" t="s">
+        <v>8</v>
+      </c>
+      <c r="I50" t="s">
+        <v>114</v>
+      </c>
+      <c r="J50" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="B51" t="s">
+        <v>138</v>
+      </c>
+      <c r="C51" t="s">
+        <v>72</v>
+      </c>
+      <c r="D51" t="s">
+        <v>140</v>
+      </c>
+      <c r="E51" t="s">
+        <v>319</v>
+      </c>
+      <c r="F51" t="s">
+        <v>8</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H51" t="s">
+        <v>8</v>
+      </c>
+      <c r="I51" t="s">
+        <v>114</v>
+      </c>
+      <c r="J51" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="B52" t="s">
+        <v>138</v>
+      </c>
+      <c r="C52" t="s">
+        <v>44</v>
+      </c>
+      <c r="D52" t="s">
+        <v>353</v>
+      </c>
+      <c r="E52" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="H52">
+        <v>5</v>
+      </c>
+      <c r="I52" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="B53" t="s">
+        <v>299</v>
+      </c>
+      <c r="C53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" t="s">
+        <v>302</v>
+      </c>
+      <c r="E53" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" t="s">
+        <v>8</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H53" t="s">
+        <v>8</v>
+      </c>
+      <c r="I53" t="s">
+        <v>8</v>
+      </c>
+      <c r="J53" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="B54" t="s">
+        <v>299</v>
+      </c>
+      <c r="C54" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" t="s">
+        <v>358</v>
+      </c>
+      <c r="E54" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" t="s">
+        <v>8</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H54" t="s">
+        <v>8</v>
+      </c>
+      <c r="I54" t="s">
+        <v>8</v>
+      </c>
+      <c r="J54" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="B55" t="s">
+        <v>138</v>
+      </c>
+      <c r="C55" t="s">
+        <v>72</v>
+      </c>
+      <c r="D55" t="s">
+        <v>306</v>
+      </c>
+      <c r="E55" t="s">
+        <v>319</v>
+      </c>
+      <c r="F55" t="s">
+        <v>8</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H55" t="s">
+        <v>8</v>
+      </c>
+      <c r="I55" t="s">
+        <v>114</v>
+      </c>
+      <c r="J55" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="B56" t="s">
+        <v>138</v>
+      </c>
+      <c r="C56" t="s">
+        <v>72</v>
+      </c>
+      <c r="D56" t="s">
+        <v>140</v>
+      </c>
+      <c r="E56" t="s">
+        <v>322</v>
+      </c>
+      <c r="F56" t="s">
+        <v>8</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H56" t="s">
+        <v>8</v>
+      </c>
+      <c r="I56" t="s">
+        <v>114</v>
+      </c>
+      <c r="J56" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="B57" t="s">
+        <v>138</v>
+      </c>
+      <c r="C57" t="s">
+        <v>44</v>
+      </c>
+      <c r="D57" t="s">
+        <v>353</v>
+      </c>
+      <c r="E57" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="H57" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="B58" t="s">
+        <v>138</v>
+      </c>
+      <c r="C58" t="s">
+        <v>166</v>
+      </c>
+      <c r="D58" t="s">
+        <v>302</v>
+      </c>
+      <c r="E58" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" t="s">
+        <v>8</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="H58" t="s">
+        <v>8</v>
+      </c>
+      <c r="I58" t="s">
+        <v>8</v>
+      </c>
+      <c r="J58" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="B59" t="s">
+        <v>299</v>
+      </c>
+      <c r="C59" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" t="s">
+        <v>306</v>
+      </c>
+      <c r="E59" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H59" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="B60" t="s">
+        <v>299</v>
+      </c>
+      <c r="C60" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" t="s">
+        <v>358</v>
+      </c>
+      <c r="E60" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" t="s">
+        <v>8</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H60" t="s">
+        <v>8</v>
+      </c>
+      <c r="I60" t="s">
+        <v>8</v>
+      </c>
+      <c r="J60" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="B61" t="s">
+        <v>138</v>
+      </c>
+      <c r="C61" t="s">
+        <v>72</v>
+      </c>
+      <c r="D61" t="s">
+        <v>306</v>
+      </c>
+      <c r="E61" t="s">
+        <v>322</v>
+      </c>
+      <c r="F61" t="s">
+        <v>8</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H61" t="s">
+        <v>8</v>
+      </c>
+      <c r="I61" t="s">
+        <v>114</v>
+      </c>
+      <c r="J61" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="B62" t="s">
+        <v>299</v>
+      </c>
+      <c r="C62" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" t="s">
+        <v>302</v>
+      </c>
+      <c r="E62" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="B63" t="s">
+        <v>299</v>
+      </c>
+      <c r="C63" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" t="s">
+        <v>302</v>
+      </c>
+      <c r="E63" t="s">
+        <v>8</v>
+      </c>
+      <c r="F63" t="s">
+        <v>8</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H63" t="s">
+        <v>8</v>
+      </c>
+      <c r="I63" t="s">
+        <v>8</v>
+      </c>
+      <c r="J63" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B64" t="s">
+        <v>138</v>
+      </c>
+      <c r="C64" t="s">
+        <v>171</v>
+      </c>
+      <c r="D64" t="s">
+        <v>300</v>
+      </c>
+      <c r="E64" t="s">
+        <v>8</v>
+      </c>
+      <c r="F64" t="s">
+        <v>8</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="H64">
+        <v>5</v>
+      </c>
+      <c r="I64" t="s">
+        <v>8</v>
+      </c>
+      <c r="J64" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="B65" t="s">
+        <v>138</v>
+      </c>
+      <c r="C65" t="s">
+        <v>166</v>
+      </c>
+      <c r="D65" t="s">
+        <v>302</v>
+      </c>
+      <c r="E65" t="s">
+        <v>8</v>
+      </c>
+      <c r="F65" t="s">
+        <v>8</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="H65" t="s">
+        <v>8</v>
+      </c>
+      <c r="I65" t="s">
+        <v>8</v>
+      </c>
+      <c r="J65" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="B66" t="s">
+        <v>138</v>
+      </c>
+      <c r="C66" t="s">
+        <v>169</v>
+      </c>
+      <c r="D66" t="s">
+        <v>304</v>
+      </c>
+      <c r="E66" t="s">
+        <v>8</v>
+      </c>
+      <c r="F66" t="s">
+        <v>8</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="H66">
+        <v>2</v>
+      </c>
+      <c r="I66" t="s">
+        <v>8</v>
+      </c>
+      <c r="J66" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="B67" t="s">
+        <v>138</v>
+      </c>
+      <c r="C67" t="s">
+        <v>171</v>
+      </c>
+      <c r="D67" t="s">
+        <v>300</v>
+      </c>
+      <c r="E67" t="s">
+        <v>8</v>
+      </c>
+      <c r="F67" t="s">
+        <v>8</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="H67">
+        <v>7</v>
+      </c>
+      <c r="I67" t="s">
+        <v>8</v>
+      </c>
+      <c r="J67" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="B68" t="s">
+        <v>299</v>
+      </c>
+      <c r="C68" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" t="s">
+        <v>302</v>
+      </c>
+      <c r="E68" t="s">
+        <v>8</v>
+      </c>
+      <c r="F68" t="s">
+        <v>8</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H68" t="s">
+        <v>8</v>
+      </c>
+      <c r="I68" t="s">
+        <v>8</v>
+      </c>
+      <c r="J68" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="B69" t="s">
+        <v>138</v>
+      </c>
+      <c r="C69" t="s">
+        <v>166</v>
+      </c>
+      <c r="D69" t="s">
+        <v>302</v>
+      </c>
+      <c r="E69" t="s">
+        <v>8</v>
+      </c>
+      <c r="F69" t="s">
+        <v>8</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="H69">
+        <v>11</v>
+      </c>
+      <c r="I69" t="s">
+        <v>8</v>
+      </c>
+      <c r="J69" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="B70" t="s">
+        <v>138</v>
+      </c>
+      <c r="C70" t="s">
+        <v>169</v>
+      </c>
+      <c r="D70" t="s">
+        <v>304</v>
+      </c>
+      <c r="E70" t="s">
+        <v>8</v>
+      </c>
+      <c r="F70" t="s">
+        <v>8</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="H70">
+        <v>8</v>
+      </c>
+      <c r="I70" t="s">
+        <v>8</v>
+      </c>
+      <c r="J70" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="B71" t="s">
+        <v>138</v>
+      </c>
+      <c r="C71" t="s">
+        <v>171</v>
+      </c>
+      <c r="D71" t="s">
+        <v>300</v>
+      </c>
+      <c r="E71" t="s">
+        <v>8</v>
+      </c>
+      <c r="F71" t="s">
+        <v>8</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="H71" t="s">
+        <v>8</v>
+      </c>
+      <c r="I71" t="s">
+        <v>8</v>
+      </c>
+      <c r="J71" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="B72" t="s">
+        <v>138</v>
+      </c>
+      <c r="C72" t="s">
+        <v>166</v>
+      </c>
+      <c r="D72" t="s">
+        <v>302</v>
+      </c>
+      <c r="E72" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="H72" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="B73" t="s">
+        <v>138</v>
+      </c>
+      <c r="C73" t="s">
+        <v>169</v>
+      </c>
+      <c r="D73" t="s">
+        <v>304</v>
+      </c>
+      <c r="E73" t="s">
+        <v>8</v>
+      </c>
+      <c r="F73" t="s">
+        <v>8</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="H73">
+        <v>9</v>
+      </c>
+      <c r="I73" t="s">
+        <v>8</v>
+      </c>
+      <c r="J73" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="B74" t="s">
+        <v>138</v>
+      </c>
+      <c r="C74" t="s">
+        <v>44</v>
+      </c>
+      <c r="D74" t="s">
+        <v>390</v>
+      </c>
+      <c r="E74" t="s">
+        <v>8</v>
+      </c>
+      <c r="F74" t="s">
+        <v>8</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="H74" t="s">
+        <v>8</v>
+      </c>
+      <c r="I74" t="s">
+        <v>8</v>
+      </c>
+      <c r="J74" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="B75" t="s">
+        <v>138</v>
+      </c>
+      <c r="C75" t="s">
+        <v>166</v>
+      </c>
+      <c r="D75" t="s">
+        <v>302</v>
+      </c>
+      <c r="E75" t="s">
+        <v>8</v>
+      </c>
+      <c r="F75" t="s">
+        <v>8</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="H75">
+        <v>3</v>
+      </c>
+      <c r="I75" t="s">
+        <v>8</v>
+      </c>
+      <c r="J75" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="B76" t="s">
+        <v>138</v>
+      </c>
+      <c r="C76" t="s">
+        <v>44</v>
+      </c>
+      <c r="D76" t="s">
+        <v>395</v>
+      </c>
+      <c r="E76" t="s">
+        <v>8</v>
+      </c>
+      <c r="F76" t="s">
+        <v>8</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="H76" t="s">
+        <v>8</v>
+      </c>
+      <c r="I76" t="s">
+        <v>8</v>
+      </c>
+      <c r="J76" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="B77" t="s">
+        <v>138</v>
+      </c>
+      <c r="C77" t="s">
+        <v>72</v>
+      </c>
+      <c r="D77" t="s">
+        <v>358</v>
+      </c>
+      <c r="E77" t="s">
+        <v>8</v>
+      </c>
+      <c r="F77" t="s">
+        <v>8</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="H77">
+        <v>5</v>
+      </c>
+      <c r="I77" t="s">
+        <v>8</v>
+      </c>
+      <c r="J77" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="B78" t="s">
+        <v>138</v>
+      </c>
+      <c r="C78" t="s">
+        <v>44</v>
+      </c>
+      <c r="D78" t="s">
+        <v>390</v>
+      </c>
+      <c r="E78" t="s">
+        <v>8</v>
+      </c>
+      <c r="F78" t="s">
+        <v>8</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="H78" t="s">
+        <v>8</v>
+      </c>
+      <c r="I78" t="s">
+        <v>8</v>
+      </c>
+      <c r="J78" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="B79" t="s">
+        <v>138</v>
+      </c>
+      <c r="C79" t="s">
+        <v>166</v>
+      </c>
+      <c r="D79" t="s">
+        <v>302</v>
+      </c>
+      <c r="E79" t="s">
+        <v>8</v>
+      </c>
+      <c r="F79" t="s">
+        <v>8</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="H79">
+        <v>5</v>
+      </c>
+      <c r="I79" t="s">
+        <v>8</v>
+      </c>
+      <c r="J79" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="B80" t="s">
+        <v>138</v>
+      </c>
+      <c r="C80" t="s">
+        <v>44</v>
+      </c>
+      <c r="D80" t="s">
+        <v>395</v>
+      </c>
+      <c r="E80" t="s">
+        <v>8</v>
+      </c>
+      <c r="F80" t="s">
+        <v>8</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="H80" t="s">
+        <v>8</v>
+      </c>
+      <c r="I80" t="s">
+        <v>8</v>
+      </c>
+      <c r="J80" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="B81" t="s">
+        <v>138</v>
+      </c>
+      <c r="C81" t="s">
+        <v>72</v>
+      </c>
+      <c r="D81" t="s">
+        <v>358</v>
+      </c>
+      <c r="E81" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="H81">
+        <v>5</v>
+      </c>
+      <c r="I81" t="s">
+        <v>8</v>
+      </c>
+      <c r="J81" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="B82" t="s">
+        <v>342</v>
+      </c>
+      <c r="C82" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" t="s">
+        <v>8</v>
+      </c>
+      <c r="E82" t="s">
+        <v>8</v>
+      </c>
+      <c r="F82" t="s">
+        <v>8</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="H82" t="s">
+        <v>8</v>
+      </c>
+      <c r="I82" t="s">
+        <v>8</v>
+      </c>
+      <c r="J82" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="B83" t="s">
+        <v>138</v>
+      </c>
+      <c r="C83" t="s">
+        <v>44</v>
+      </c>
+      <c r="D83" t="s">
+        <v>390</v>
+      </c>
+      <c r="E83" t="s">
+        <v>8</v>
+      </c>
+      <c r="F83" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="H83">
+        <v>18</v>
+      </c>
+      <c r="I83" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="B84" t="s">
+        <v>138</v>
+      </c>
+      <c r="C84" t="s">
+        <v>166</v>
+      </c>
+      <c r="D84" t="s">
+        <v>302</v>
+      </c>
+      <c r="E84" t="s">
+        <v>8</v>
+      </c>
+      <c r="F84" t="s">
+        <v>8</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="H84">
+        <v>8</v>
+      </c>
+      <c r="I84" t="s">
+        <v>8</v>
+      </c>
+      <c r="J84" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="B85" t="s">
+        <v>138</v>
+      </c>
+      <c r="C85" t="s">
+        <v>44</v>
+      </c>
+      <c r="D85" t="s">
+        <v>395</v>
+      </c>
+      <c r="E85" t="s">
+        <v>8</v>
+      </c>
+      <c r="F85" t="s">
+        <v>8</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="H85" t="s">
+        <v>8</v>
+      </c>
+      <c r="I85" t="s">
+        <v>8</v>
+      </c>
+      <c r="J85" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="B86" t="s">
+        <v>138</v>
+      </c>
+      <c r="C86" t="s">
+        <v>72</v>
+      </c>
+      <c r="D86" t="s">
+        <v>358</v>
+      </c>
+      <c r="E86" t="s">
+        <v>8</v>
+      </c>
+      <c r="F86" t="s">
+        <v>8</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="H86">
+        <v>5</v>
+      </c>
+      <c r="I86" t="s">
+        <v>8</v>
+      </c>
+      <c r="J86" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="B87" t="s">
+        <v>138</v>
+      </c>
+      <c r="C87" t="s">
+        <v>171</v>
+      </c>
+      <c r="D87" t="s">
+        <v>300</v>
+      </c>
+      <c r="E87" t="s">
+        <v>8</v>
+      </c>
+      <c r="F87" t="s">
+        <v>8</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="H87">
+        <v>2</v>
+      </c>
+      <c r="I87" t="s">
+        <v>8</v>
+      </c>
+      <c r="J87" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="B88" t="s">
+        <v>138</v>
+      </c>
+      <c r="C88" t="s">
+        <v>169</v>
+      </c>
+      <c r="D88" t="s">
+        <v>304</v>
+      </c>
+      <c r="E88" t="s">
+        <v>8</v>
+      </c>
+      <c r="F88" t="s">
+        <v>8</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="H88">
+        <v>2</v>
+      </c>
+      <c r="I88" t="s">
+        <v>8</v>
+      </c>
+      <c r="J88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="B89" t="s">
+        <v>138</v>
+      </c>
+      <c r="C89" t="s">
+        <v>72</v>
+      </c>
+      <c r="D89" t="s">
+        <v>306</v>
+      </c>
+      <c r="E89" t="s">
+        <v>8</v>
+      </c>
+      <c r="F89" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="H89">
+        <v>6</v>
+      </c>
+      <c r="I89" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="B90" t="s">
+        <v>138</v>
+      </c>
+      <c r="C90" t="s">
+        <v>171</v>
+      </c>
+      <c r="D90" t="s">
+        <v>300</v>
+      </c>
+      <c r="E90" t="s">
+        <v>8</v>
+      </c>
+      <c r="F90" t="s">
+        <v>8</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="H90" t="s">
+        <v>8</v>
+      </c>
+      <c r="I90" t="s">
+        <v>8</v>
+      </c>
+      <c r="J90" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="B91" t="s">
+        <v>138</v>
+      </c>
+      <c r="C91" t="s">
+        <v>169</v>
+      </c>
+      <c r="D91" t="s">
+        <v>304</v>
+      </c>
+      <c r="E91" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="H91">
+        <v>5</v>
+      </c>
+      <c r="I91" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="B92" t="s">
+        <v>138</v>
+      </c>
+      <c r="C92" t="s">
+        <v>72</v>
+      </c>
+      <c r="D92" t="s">
+        <v>306</v>
+      </c>
+      <c r="E92" t="s">
+        <v>8</v>
+      </c>
+      <c r="F92" t="s">
+        <v>8</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="H92" t="s">
+        <v>8</v>
+      </c>
+      <c r="I92" t="s">
+        <v>8</v>
+      </c>
+      <c r="J92" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="B93" t="s">
+        <v>138</v>
+      </c>
+      <c r="C93" t="s">
+        <v>171</v>
+      </c>
+      <c r="D93" t="s">
+        <v>300</v>
+      </c>
+      <c r="E93" t="s">
+        <v>8</v>
+      </c>
+      <c r="F93" t="s">
+        <v>8</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="H93">
+        <v>4</v>
+      </c>
+      <c r="I93" t="s">
+        <v>8</v>
+      </c>
+      <c r="J93" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="B94" t="s">
+        <v>138</v>
+      </c>
+      <c r="C94" t="s">
+        <v>169</v>
+      </c>
+      <c r="D94" t="s">
+        <v>304</v>
+      </c>
+      <c r="E94" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="H94">
+        <v>5</v>
+      </c>
+      <c r="I94" t="s">
+        <v>8</v>
+      </c>
+      <c r="J94" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="B95" t="s">
+        <v>138</v>
+      </c>
+      <c r="C95" t="s">
+        <v>72</v>
+      </c>
+      <c r="D95" t="s">
+        <v>306</v>
+      </c>
+      <c r="E95" t="s">
+        <v>8</v>
+      </c>
+      <c r="F95" t="s">
+        <v>8</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="H95" t="s">
+        <v>8</v>
+      </c>
+      <c r="I95" t="s">
+        <v>8</v>
+      </c>
+      <c r="J95" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="B96" t="s">
+        <v>138</v>
+      </c>
+      <c r="C96" t="s">
+        <v>166</v>
+      </c>
+      <c r="D96" t="s">
+        <v>302</v>
+      </c>
+      <c r="E96" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="H96">
+        <v>6</v>
+      </c>
+      <c r="I96" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="B97" t="s">
+        <v>342</v>
+      </c>
+      <c r="C97" t="s">
+        <v>8</v>
+      </c>
+      <c r="D97" t="s">
+        <v>8</v>
+      </c>
+      <c r="E97" t="s">
+        <v>8</v>
+      </c>
+      <c r="F97" t="s">
+        <v>8</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="H97" t="s">
+        <v>8</v>
+      </c>
+      <c r="I97" t="s">
+        <v>8</v>
+      </c>
+      <c r="J97" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="B98" t="s">
+        <v>138</v>
+      </c>
+      <c r="C98" t="s">
+        <v>169</v>
+      </c>
+      <c r="D98" t="s">
+        <v>304</v>
+      </c>
+      <c r="E98" t="s">
+        <v>8</v>
+      </c>
+      <c r="F98" t="s">
+        <v>8</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="H98">
+        <v>1</v>
+      </c>
+      <c r="I98" t="s">
+        <v>8</v>
+      </c>
+      <c r="J98" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="B99" t="s">
+        <v>138</v>
+      </c>
+      <c r="C99" t="s">
+        <v>72</v>
+      </c>
+      <c r="D99" t="s">
+        <v>306</v>
+      </c>
+      <c r="E99" t="s">
+        <v>8</v>
+      </c>
+      <c r="F99" t="s">
+        <v>8</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="H99" t="s">
+        <v>8</v>
+      </c>
+      <c r="I99" t="s">
+        <v>8</v>
+      </c>
+      <c r="J99" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="B100" t="s">
+        <v>138</v>
+      </c>
+      <c r="C100" t="s">
+        <v>166</v>
+      </c>
+      <c r="D100" t="s">
+        <v>302</v>
+      </c>
+      <c r="E100" t="s">
+        <v>8</v>
+      </c>
+      <c r="F100" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H100">
+        <v>8</v>
+      </c>
+      <c r="I100" t="s">
+        <v>8</v>
+      </c>
+      <c r="J100" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="B101" t="s">
+        <v>138</v>
+      </c>
+      <c r="C101" t="s">
+        <v>72</v>
+      </c>
+      <c r="D101" t="s">
+        <v>306</v>
+      </c>
+      <c r="E101" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="H101">
+        <v>8</v>
+      </c>
+      <c r="I101" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="B102" t="s">
+        <v>138</v>
+      </c>
+      <c r="C102" t="s">
+        <v>169</v>
+      </c>
+      <c r="D102" t="s">
+        <v>304</v>
+      </c>
+      <c r="E102" t="s">
+        <v>8</v>
+      </c>
+      <c r="F102" t="s">
+        <v>8</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="H102">
+        <v>5</v>
+      </c>
+      <c r="I102" t="s">
+        <v>8</v>
+      </c>
+      <c r="J102" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="B103" t="s">
+        <v>342</v>
+      </c>
+      <c r="C103" t="s">
+        <v>8</v>
+      </c>
+      <c r="D103" t="s">
+        <v>8</v>
+      </c>
+      <c r="E103" t="s">
+        <v>8</v>
+      </c>
+      <c r="F103" t="s">
+        <v>8</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="H103" t="s">
+        <v>8</v>
+      </c>
+      <c r="I103" t="s">
+        <v>8</v>
+      </c>
+      <c r="J103" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="B104" t="s">
+        <v>138</v>
+      </c>
+      <c r="C104" t="s">
+        <v>166</v>
+      </c>
+      <c r="D104" t="s">
+        <v>302</v>
+      </c>
+      <c r="E104" t="s">
+        <v>8</v>
+      </c>
+      <c r="F104" t="s">
+        <v>8</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="H104">
+        <v>11</v>
+      </c>
+      <c r="I104" t="s">
+        <v>8</v>
+      </c>
+      <c r="J104" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="B105" t="s">
+        <v>138</v>
+      </c>
+      <c r="C105" t="s">
+        <v>72</v>
+      </c>
+      <c r="D105" t="s">
+        <v>306</v>
+      </c>
+      <c r="E105" t="s">
+        <v>8</v>
+      </c>
+      <c r="F105" t="s">
+        <v>8</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="H105">
+        <v>10</v>
+      </c>
+      <c r="I105" t="s">
+        <v>8</v>
+      </c>
+      <c r="J105" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B106" t="s">
+        <v>138</v>
+      </c>
+      <c r="C106" t="s">
+        <v>169</v>
+      </c>
+      <c r="D106" t="s">
+        <v>304</v>
+      </c>
+      <c r="E106" t="s">
+        <v>8</v>
+      </c>
+      <c r="F106" t="s">
+        <v>8</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="H106">
+        <v>6</v>
+      </c>
+      <c r="I106" t="s">
+        <v>8</v>
+      </c>
+      <c r="J106" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="B107" t="s">
+        <v>138</v>
+      </c>
+      <c r="C107" t="s">
+        <v>169</v>
+      </c>
+      <c r="D107" t="s">
+        <v>304</v>
+      </c>
+      <c r="E107" t="s">
+        <v>8</v>
+      </c>
+      <c r="F107" t="s">
+        <v>8</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="H107">
+        <v>1</v>
+      </c>
+      <c r="I107" t="s">
+        <v>8</v>
+      </c>
+      <c r="J107" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="B108" t="s">
+        <v>138</v>
+      </c>
+      <c r="C108" t="s">
+        <v>171</v>
+      </c>
+      <c r="D108" t="s">
+        <v>300</v>
+      </c>
+      <c r="E108" t="s">
+        <v>8</v>
+      </c>
+      <c r="F108" t="s">
+        <v>8</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="H108" t="s">
+        <v>8</v>
+      </c>
+      <c r="I108" t="s">
+        <v>8</v>
+      </c>
+      <c r="J108" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="B109" t="s">
+        <v>138</v>
+      </c>
+      <c r="C109" t="s">
+        <v>44</v>
+      </c>
+      <c r="D109" t="s">
+        <v>453</v>
+      </c>
+      <c r="E109" t="s">
+        <v>8</v>
+      </c>
+      <c r="F109" t="s">
+        <v>8</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="H109">
+        <v>7</v>
+      </c>
+      <c r="I109" t="s">
+        <v>8</v>
+      </c>
+      <c r="J109" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="B110" t="s">
+        <v>138</v>
+      </c>
+      <c r="C110" t="s">
+        <v>44</v>
+      </c>
+      <c r="D110" t="s">
+        <v>395</v>
+      </c>
+      <c r="E110" t="s">
+        <v>8</v>
+      </c>
+      <c r="F110" t="s">
+        <v>8</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="H110">
+        <v>8</v>
+      </c>
+      <c r="I110" t="s">
+        <v>8</v>
+      </c>
+      <c r="J110" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="B111" t="s">
+        <v>138</v>
+      </c>
+      <c r="C111" t="s">
+        <v>171</v>
+      </c>
+      <c r="D111" t="s">
+        <v>300</v>
+      </c>
+      <c r="E111" t="s">
+        <v>8</v>
+      </c>
+      <c r="F111" t="s">
+        <v>8</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="H111" t="s">
+        <v>8</v>
+      </c>
+      <c r="I111" t="s">
+        <v>8</v>
+      </c>
+      <c r="J111" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="B112" t="s">
+        <v>138</v>
+      </c>
+      <c r="C112" t="s">
+        <v>169</v>
+      </c>
+      <c r="D112" t="s">
+        <v>304</v>
+      </c>
+      <c r="E112" t="s">
+        <v>8</v>
+      </c>
+      <c r="F112" t="s">
+        <v>8</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="H112">
+        <v>5</v>
+      </c>
+      <c r="I112" t="s">
+        <v>8</v>
+      </c>
+      <c r="J112" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A113" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="B113" t="s">
+        <v>138</v>
+      </c>
+      <c r="C113" t="s">
+        <v>171</v>
+      </c>
+      <c r="D113" t="s">
+        <v>300</v>
+      </c>
+      <c r="E113" t="s">
+        <v>8</v>
+      </c>
+      <c r="F113" t="s">
+        <v>8</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="H113" t="s">
+        <v>8</v>
+      </c>
+      <c r="I113" t="s">
+        <v>8</v>
+      </c>
+      <c r="J113" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="B114" t="s">
+        <v>138</v>
+      </c>
+      <c r="C114" t="s">
+        <v>44</v>
+      </c>
+      <c r="D114" t="s">
+        <v>453</v>
+      </c>
+      <c r="E114" t="s">
+        <v>8</v>
+      </c>
+      <c r="F114" t="s">
+        <v>8</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="H114" t="s">
+        <v>8</v>
+      </c>
+      <c r="I114" t="s">
+        <v>8</v>
+      </c>
+      <c r="J114" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A115" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="B115" t="s">
+        <v>138</v>
+      </c>
+      <c r="C115" t="s">
+        <v>169</v>
+      </c>
+      <c r="D115" t="s">
+        <v>304</v>
+      </c>
+      <c r="E115" t="s">
+        <v>8</v>
+      </c>
+      <c r="F115" t="s">
+        <v>8</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="H115">
+        <v>6</v>
+      </c>
+      <c r="I115" t="s">
+        <v>8</v>
+      </c>
+      <c r="J115" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A116" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="B116" t="s">
+        <v>138</v>
+      </c>
+      <c r="C116" t="s">
+        <v>166</v>
+      </c>
+      <c r="D116" t="s">
+        <v>302</v>
+      </c>
+      <c r="E116" t="s">
+        <v>8</v>
+      </c>
+      <c r="F116" t="s">
+        <v>8</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H116" t="s">
+        <v>8</v>
+      </c>
+      <c r="I116" t="s">
+        <v>8</v>
+      </c>
+      <c r="J116" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A117" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="B117" t="s">
+        <v>138</v>
+      </c>
+      <c r="C117" t="s">
+        <v>72</v>
+      </c>
+      <c r="D117" t="s">
+        <v>306</v>
+      </c>
+      <c r="E117" t="s">
+        <v>8</v>
+      </c>
+      <c r="F117" t="s">
+        <v>8</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H117" t="s">
+        <v>8</v>
+      </c>
+      <c r="I117" t="s">
+        <v>8</v>
+      </c>
+      <c r="J117" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A118" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="B118" t="s">
+        <v>138</v>
+      </c>
+      <c r="C118" t="s">
+        <v>44</v>
+      </c>
+      <c r="D118" t="s">
+        <v>308</v>
+      </c>
+      <c r="E118" t="s">
+        <v>8</v>
+      </c>
+      <c r="F118" t="s">
+        <v>8</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="H118" t="s">
+        <v>8</v>
+      </c>
+      <c r="I118" t="s">
+        <v>8</v>
+      </c>
+      <c r="J118" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A119" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="B119" t="s">
+        <v>138</v>
+      </c>
+      <c r="C119" t="s">
+        <v>44</v>
+      </c>
+      <c r="D119" t="s">
+        <v>308</v>
+      </c>
+      <c r="E119" t="s">
+        <v>8</v>
+      </c>
+      <c r="F119" t="s">
+        <v>8</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="H119" t="s">
+        <v>8</v>
+      </c>
+      <c r="I119" t="s">
+        <v>8</v>
+      </c>
+      <c r="J119" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A120" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="B120" t="s">
+        <v>138</v>
+      </c>
+      <c r="C120" t="s">
+        <v>171</v>
+      </c>
+      <c r="D120" t="s">
+        <v>300</v>
+      </c>
+      <c r="E120" t="s">
+        <v>8</v>
+      </c>
+      <c r="F120" t="s">
+        <v>8</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="H120" t="s">
+        <v>8</v>
+      </c>
+      <c r="I120" t="s">
+        <v>8</v>
+      </c>
+      <c r="J120" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A121" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="B121" t="s">
+        <v>138</v>
+      </c>
+      <c r="C121" t="s">
+        <v>169</v>
+      </c>
+      <c r="D121" t="s">
+        <v>304</v>
+      </c>
+      <c r="E121" t="s">
+        <v>8</v>
+      </c>
+      <c r="F121" t="s">
+        <v>8</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H121" t="s">
+        <v>8</v>
+      </c>
+      <c r="I121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J121" t="s">
         <v>8</v>
       </c>
     </row>

--- a/content/jahrgaenge/Jg6.xlsx
+++ b/content/jahrgaenge/Jg6.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2107" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="475">
   <si>
     <t>Hinweise zu Jg6.xlsx</t>
   </si>
@@ -1172,6 +1172,12 @@
   </si>
   <si>
     <t>Viewing and listening skills</t>
+  </si>
+  <si>
+    <t>2026-12-18</t>
+  </si>
+  <si>
+    <t>Weihnachtsmarkt</t>
   </si>
   <si>
     <t>2027-01-04</t>
@@ -6029,7 +6035,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J121"/>
+  <dimension ref="A1:J122"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="13" style="5" customWidth="1"/>
@@ -8286,13 +8292,13 @@
         <v>384</v>
       </c>
       <c r="B71" t="s">
-        <v>138</v>
+        <v>342</v>
       </c>
       <c r="C71" t="s">
-        <v>171</v>
+        <v>8</v>
       </c>
       <c r="D71" t="s">
-        <v>300</v>
+        <v>8</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -8321,10 +8327,10 @@
         <v>138</v>
       </c>
       <c r="C72" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D72" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -8333,7 +8339,7 @@
         <v>8</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -8347,16 +8353,16 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B73" t="s">
         <v>138</v>
       </c>
       <c r="C73" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D73" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -8365,10 +8371,10 @@
         <v>8</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="H73">
-        <v>9</v>
+        <v>369</v>
+      </c>
+      <c r="H73" t="s">
+        <v>8</v>
       </c>
       <c r="I73" t="s">
         <v>8</v>
@@ -8385,22 +8391,22 @@
         <v>138</v>
       </c>
       <c r="C74" t="s">
-        <v>44</v>
+        <v>169</v>
       </c>
       <c r="D74" t="s">
+        <v>304</v>
+      </c>
+      <c r="E74" t="s">
+        <v>8</v>
+      </c>
+      <c r="F74" t="s">
+        <v>8</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="E74" t="s">
-        <v>8</v>
-      </c>
-      <c r="F74" t="s">
-        <v>8</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="H74" t="s">
-        <v>8</v>
+      <c r="H74">
+        <v>9</v>
       </c>
       <c r="I74" t="s">
         <v>8</v>
@@ -8411,16 +8417,16 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B75" t="s">
         <v>138</v>
       </c>
       <c r="C75" t="s">
-        <v>166</v>
+        <v>44</v>
       </c>
       <c r="D75" t="s">
-        <v>302</v>
+        <v>392</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -8431,8 +8437,8 @@
       <c r="G75" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="H75">
-        <v>3</v>
+      <c r="H75" t="s">
+        <v>8</v>
       </c>
       <c r="I75" t="s">
         <v>8</v>
@@ -8449,22 +8455,22 @@
         <v>138</v>
       </c>
       <c r="C76" t="s">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="D76" t="s">
+        <v>302</v>
+      </c>
+      <c r="E76" t="s">
+        <v>8</v>
+      </c>
+      <c r="F76" t="s">
+        <v>8</v>
+      </c>
+      <c r="G76" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="E76" t="s">
-        <v>8</v>
-      </c>
-      <c r="F76" t="s">
-        <v>8</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="H76" t="s">
-        <v>8</v>
+      <c r="H76">
+        <v>3</v>
       </c>
       <c r="I76" t="s">
         <v>8</v>
@@ -8475,16 +8481,16 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B77" t="s">
         <v>138</v>
       </c>
       <c r="C77" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="D77" t="s">
-        <v>358</v>
+        <v>397</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -8495,8 +8501,8 @@
       <c r="G77" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="H77">
-        <v>5</v>
+      <c r="H77" t="s">
+        <v>8</v>
       </c>
       <c r="I77" t="s">
         <v>8</v>
@@ -8513,10 +8519,10 @@
         <v>138</v>
       </c>
       <c r="C78" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D78" t="s">
-        <v>390</v>
+        <v>358</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -8527,8 +8533,8 @@
       <c r="G78" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="H78" t="s">
-        <v>8</v>
+      <c r="H78">
+        <v>5</v>
       </c>
       <c r="I78" t="s">
         <v>8</v>
@@ -8545,10 +8551,10 @@
         <v>138</v>
       </c>
       <c r="C79" t="s">
-        <v>166</v>
+        <v>44</v>
       </c>
       <c r="D79" t="s">
-        <v>302</v>
+        <v>392</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -8559,8 +8565,8 @@
       <c r="G79" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="H79">
-        <v>5</v>
+      <c r="H79" t="s">
+        <v>8</v>
       </c>
       <c r="I79" t="s">
         <v>8</v>
@@ -8577,10 +8583,10 @@
         <v>138</v>
       </c>
       <c r="C80" t="s">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="D80" t="s">
-        <v>395</v>
+        <v>302</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -8589,10 +8595,10 @@
         <v>8</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="H80" t="s">
-        <v>8</v>
+        <v>404</v>
+      </c>
+      <c r="H80">
+        <v>5</v>
       </c>
       <c r="I80" t="s">
         <v>8</v>
@@ -8603,16 +8609,16 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B81" t="s">
         <v>138</v>
       </c>
       <c r="C81" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="D81" t="s">
-        <v>358</v>
+        <v>397</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -8623,8 +8629,8 @@
       <c r="G81" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="H81">
-        <v>5</v>
+      <c r="H81" t="s">
+        <v>8</v>
       </c>
       <c r="I81" t="s">
         <v>8</v>
@@ -8635,16 +8641,16 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B82" t="s">
-        <v>342</v>
+        <v>138</v>
       </c>
       <c r="C82" t="s">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="D82" t="s">
-        <v>8</v>
+        <v>358</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -8653,10 +8659,10 @@
         <v>8</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="H82" t="s">
-        <v>8</v>
+        <v>400</v>
+      </c>
+      <c r="H82">
+        <v>5</v>
       </c>
       <c r="I82" t="s">
         <v>8</v>
@@ -8667,16 +8673,16 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B83" t="s">
-        <v>138</v>
+        <v>342</v>
       </c>
       <c r="C83" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="D83" t="s">
-        <v>390</v>
+        <v>8</v>
       </c>
       <c r="E83" t="s">
         <v>8</v>
@@ -8685,10 +8691,10 @@
         <v>8</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="H83">
-        <v>18</v>
+        <v>343</v>
+      </c>
+      <c r="H83" t="s">
+        <v>8</v>
       </c>
       <c r="I83" t="s">
         <v>8</v>
@@ -8705,10 +8711,10 @@
         <v>138</v>
       </c>
       <c r="C84" t="s">
-        <v>166</v>
+        <v>44</v>
       </c>
       <c r="D84" t="s">
-        <v>302</v>
+        <v>392</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -8720,7 +8726,7 @@
         <v>409</v>
       </c>
       <c r="H84">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I84" t="s">
         <v>8</v>
@@ -8737,10 +8743,10 @@
         <v>138</v>
       </c>
       <c r="C85" t="s">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="D85" t="s">
-        <v>395</v>
+        <v>302</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -8749,9 +8755,9 @@
         <v>8</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="H85" t="s">
+        <v>411</v>
+      </c>
+      <c r="H85">
         <v>8</v>
       </c>
       <c r="I85" t="s">
@@ -8763,16 +8769,16 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B86" t="s">
         <v>138</v>
       </c>
       <c r="C86" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="D86" t="s">
-        <v>358</v>
+        <v>397</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -8783,8 +8789,8 @@
       <c r="G86" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="H86">
-        <v>5</v>
+      <c r="H86" t="s">
+        <v>8</v>
       </c>
       <c r="I86" t="s">
         <v>8</v>
@@ -8795,16 +8801,16 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B87" t="s">
         <v>138</v>
       </c>
       <c r="C87" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="D87" t="s">
-        <v>300</v>
+        <v>358</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -8813,10 +8819,10 @@
         <v>8</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="H87">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I87" t="s">
         <v>8</v>
@@ -8833,10 +8839,10 @@
         <v>138</v>
       </c>
       <c r="C88" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D88" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -8865,10 +8871,10 @@
         <v>138</v>
       </c>
       <c r="C89" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="D89" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -8880,7 +8886,7 @@
         <v>417</v>
       </c>
       <c r="H89">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I89" t="s">
         <v>8</v>
@@ -8897,10 +8903,10 @@
         <v>138</v>
       </c>
       <c r="C90" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="D90" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -8911,8 +8917,8 @@
       <c r="G90" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="H90" t="s">
-        <v>8</v>
+      <c r="H90">
+        <v>6</v>
       </c>
       <c r="I90" t="s">
         <v>8</v>
@@ -8929,10 +8935,10 @@
         <v>138</v>
       </c>
       <c r="C91" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D91" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -8943,8 +8949,8 @@
       <c r="G91" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="H91">
-        <v>5</v>
+      <c r="H91" t="s">
+        <v>8</v>
       </c>
       <c r="I91" t="s">
         <v>8</v>
@@ -8961,10 +8967,10 @@
         <v>138</v>
       </c>
       <c r="C92" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="D92" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -8975,8 +8981,8 @@
       <c r="G92" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="H92" t="s">
-        <v>8</v>
+      <c r="H92">
+        <v>5</v>
       </c>
       <c r="I92" t="s">
         <v>8</v>
@@ -8993,10 +8999,10 @@
         <v>138</v>
       </c>
       <c r="C93" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="D93" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -9007,8 +9013,8 @@
       <c r="G93" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="H93">
-        <v>4</v>
+      <c r="H93" t="s">
+        <v>8</v>
       </c>
       <c r="I93" t="s">
         <v>8</v>
@@ -9025,10 +9031,10 @@
         <v>138</v>
       </c>
       <c r="C94" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D94" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -9037,10 +9043,10 @@
         <v>8</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="H94">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I94" t="s">
         <v>8</v>
@@ -9051,16 +9057,16 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B95" t="s">
         <v>138</v>
       </c>
       <c r="C95" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="D95" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -9071,8 +9077,8 @@
       <c r="G95" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="H95" t="s">
-        <v>8</v>
+      <c r="H95">
+        <v>5</v>
       </c>
       <c r="I95" t="s">
         <v>8</v>
@@ -9083,16 +9089,16 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B96" t="s">
         <v>138</v>
       </c>
       <c r="C96" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
       <c r="D96" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -9101,10 +9107,10 @@
         <v>8</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="H96">
-        <v>6</v>
+        <v>425</v>
+      </c>
+      <c r="H96" t="s">
+        <v>8</v>
       </c>
       <c r="I96" t="s">
         <v>8</v>
@@ -9118,13 +9124,13 @@
         <v>430</v>
       </c>
       <c r="B97" t="s">
-        <v>342</v>
+        <v>138</v>
       </c>
       <c r="C97" t="s">
-        <v>8</v>
+        <v>166</v>
       </c>
       <c r="D97" t="s">
-        <v>8</v>
+        <v>302</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -9133,10 +9139,10 @@
         <v>8</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="H97" t="s">
-        <v>8</v>
+        <v>431</v>
+      </c>
+      <c r="H97">
+        <v>6</v>
       </c>
       <c r="I97" t="s">
         <v>8</v>
@@ -9147,16 +9153,16 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B98" t="s">
-        <v>138</v>
+        <v>342</v>
       </c>
       <c r="C98" t="s">
-        <v>169</v>
+        <v>8</v>
       </c>
       <c r="D98" t="s">
-        <v>304</v>
+        <v>8</v>
       </c>
       <c r="E98" t="s">
         <v>8</v>
@@ -9165,10 +9171,10 @@
         <v>8</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="H98">
-        <v>1</v>
+        <v>343</v>
+      </c>
+      <c r="H98" t="s">
+        <v>8</v>
       </c>
       <c r="I98" t="s">
         <v>8</v>
@@ -9185,10 +9191,10 @@
         <v>138</v>
       </c>
       <c r="C99" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="D99" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -9199,8 +9205,8 @@
       <c r="G99" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="H99" t="s">
-        <v>8</v>
+      <c r="H99">
+        <v>1</v>
       </c>
       <c r="I99" t="s">
         <v>8</v>
@@ -9217,10 +9223,10 @@
         <v>138</v>
       </c>
       <c r="C100" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
       <c r="D100" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
@@ -9231,7 +9237,7 @@
       <c r="G100" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="H100">
+      <c r="H100" t="s">
         <v>8</v>
       </c>
       <c r="I100" t="s">
@@ -9249,10 +9255,10 @@
         <v>138</v>
       </c>
       <c r="C101" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="D101" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -9281,10 +9287,10 @@
         <v>138</v>
       </c>
       <c r="C102" t="s">
-        <v>169</v>
+        <v>72</v>
       </c>
       <c r="D102" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -9296,7 +9302,7 @@
         <v>440</v>
       </c>
       <c r="H102">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I102" t="s">
         <v>8</v>
@@ -9310,13 +9316,13 @@
         <v>441</v>
       </c>
       <c r="B103" t="s">
-        <v>342</v>
+        <v>138</v>
       </c>
       <c r="C103" t="s">
-        <v>8</v>
+        <v>169</v>
       </c>
       <c r="D103" t="s">
-        <v>8</v>
+        <v>304</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -9327,8 +9333,8 @@
       <c r="G103" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="H103" t="s">
-        <v>8</v>
+      <c r="H103">
+        <v>5</v>
       </c>
       <c r="I103" t="s">
         <v>8</v>
@@ -9342,13 +9348,13 @@
         <v>443</v>
       </c>
       <c r="B104" t="s">
-        <v>138</v>
+        <v>342</v>
       </c>
       <c r="C104" t="s">
-        <v>166</v>
+        <v>8</v>
       </c>
       <c r="D104" t="s">
-        <v>302</v>
+        <v>8</v>
       </c>
       <c r="E104" t="s">
         <v>8</v>
@@ -9359,8 +9365,8 @@
       <c r="G104" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="H104">
-        <v>11</v>
+      <c r="H104" t="s">
+        <v>8</v>
       </c>
       <c r="I104" t="s">
         <v>8</v>
@@ -9377,10 +9383,10 @@
         <v>138</v>
       </c>
       <c r="C105" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="D105" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -9392,7 +9398,7 @@
         <v>446</v>
       </c>
       <c r="H105">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I105" t="s">
         <v>8</v>
@@ -9409,10 +9415,10 @@
         <v>138</v>
       </c>
       <c r="C106" t="s">
-        <v>169</v>
+        <v>72</v>
       </c>
       <c r="D106" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -9424,7 +9430,7 @@
         <v>448</v>
       </c>
       <c r="H106">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I106" t="s">
         <v>8</v>
@@ -9453,10 +9459,10 @@
         <v>8</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="H107">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I107" t="s">
         <v>8</v>
@@ -9467,16 +9473,16 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B108" t="s">
         <v>138</v>
       </c>
       <c r="C108" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D108" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -9485,10 +9491,10 @@
         <v>8</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="H108" t="s">
-        <v>8</v>
+        <v>434</v>
+      </c>
+      <c r="H108">
+        <v>1</v>
       </c>
       <c r="I108" t="s">
         <v>8</v>
@@ -9505,22 +9511,22 @@
         <v>138</v>
       </c>
       <c r="C109" t="s">
-        <v>44</v>
+        <v>171</v>
       </c>
       <c r="D109" t="s">
+        <v>300</v>
+      </c>
+      <c r="E109" t="s">
+        <v>8</v>
+      </c>
+      <c r="F109" t="s">
+        <v>8</v>
+      </c>
+      <c r="G109" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="E109" t="s">
-        <v>8</v>
-      </c>
-      <c r="F109" t="s">
-        <v>8</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="H109">
-        <v>7</v>
+      <c r="H109" t="s">
+        <v>8</v>
       </c>
       <c r="I109" t="s">
         <v>8</v>
@@ -9531,7 +9537,7 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B110" t="s">
         <v>138</v>
@@ -9540,7 +9546,7 @@
         <v>44</v>
       </c>
       <c r="D110" t="s">
-        <v>395</v>
+        <v>455</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -9552,7 +9558,7 @@
         <v>456</v>
       </c>
       <c r="H110">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I110" t="s">
         <v>8</v>
@@ -9569,10 +9575,10 @@
         <v>138</v>
       </c>
       <c r="C111" t="s">
-        <v>171</v>
+        <v>44</v>
       </c>
       <c r="D111" t="s">
-        <v>300</v>
+        <v>397</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -9583,7 +9589,7 @@
       <c r="G111" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="H111" t="s">
+      <c r="H111">
         <v>8</v>
       </c>
       <c r="I111" t="s">
@@ -9601,10 +9607,10 @@
         <v>138</v>
       </c>
       <c r="C112" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D112" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -9613,10 +9619,10 @@
         <v>8</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="H112">
-        <v>5</v>
+        <v>460</v>
+      </c>
+      <c r="H112" t="s">
+        <v>8</v>
       </c>
       <c r="I112" t="s">
         <v>8</v>
@@ -9627,16 +9633,16 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B113" t="s">
         <v>138</v>
       </c>
       <c r="C113" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D113" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -9645,10 +9651,10 @@
         <v>8</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H113" t="s">
-        <v>8</v>
+        <v>442</v>
+      </c>
+      <c r="H113">
+        <v>5</v>
       </c>
       <c r="I113" t="s">
         <v>8</v>
@@ -9659,16 +9665,16 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B114" t="s">
         <v>138</v>
       </c>
       <c r="C114" t="s">
-        <v>44</v>
+        <v>171</v>
       </c>
       <c r="D114" t="s">
-        <v>453</v>
+        <v>300</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -9677,7 +9683,7 @@
         <v>8</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -9697,10 +9703,10 @@
         <v>138</v>
       </c>
       <c r="C115" t="s">
-        <v>169</v>
+        <v>44</v>
       </c>
       <c r="D115" t="s">
-        <v>304</v>
+        <v>455</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -9709,10 +9715,10 @@
         <v>8</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="H115">
-        <v>6</v>
+        <v>464</v>
+      </c>
+      <c r="H115" t="s">
+        <v>8</v>
       </c>
       <c r="I115" t="s">
         <v>8</v>
@@ -9723,16 +9729,16 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B116" t="s">
         <v>138</v>
       </c>
       <c r="C116" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D116" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E116" t="s">
         <v>8</v>
@@ -9741,10 +9747,10 @@
         <v>8</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H116" t="s">
-        <v>8</v>
+        <v>450</v>
+      </c>
+      <c r="H116">
+        <v>6</v>
       </c>
       <c r="I116" t="s">
         <v>8</v>
@@ -9755,16 +9761,16 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B117" t="s">
         <v>138</v>
       </c>
       <c r="C117" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
       <c r="D117" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="E117" t="s">
         <v>8</v>
@@ -9787,16 +9793,16 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B118" t="s">
         <v>138</v>
       </c>
       <c r="C118" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D118" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -9805,7 +9811,7 @@
         <v>8</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>467</v>
+        <v>8</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -9857,10 +9863,10 @@
         <v>138</v>
       </c>
       <c r="C120" t="s">
-        <v>171</v>
+        <v>44</v>
       </c>
       <c r="D120" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="E120" t="s">
         <v>8</v>
@@ -9889,27 +9895,59 @@
         <v>138</v>
       </c>
       <c r="C121" t="s">
+        <v>171</v>
+      </c>
+      <c r="D121" t="s">
+        <v>300</v>
+      </c>
+      <c r="E121" t="s">
+        <v>8</v>
+      </c>
+      <c r="F121" t="s">
+        <v>8</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="H121" t="s">
+        <v>8</v>
+      </c>
+      <c r="I121" t="s">
+        <v>8</v>
+      </c>
+      <c r="J121" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A122" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="B122" t="s">
+        <v>138</v>
+      </c>
+      <c r="C122" t="s">
         <v>169</v>
       </c>
-      <c r="D121" t="s">
+      <c r="D122" t="s">
         <v>304</v>
       </c>
-      <c r="E121" t="s">
-        <v>8</v>
-      </c>
-      <c r="F121" t="s">
-        <v>8</v>
-      </c>
-      <c r="G121" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H121" t="s">
-        <v>8</v>
-      </c>
-      <c r="I121" t="s">
-        <v>8</v>
-      </c>
-      <c r="J121" t="s">
+      <c r="E122" t="s">
+        <v>8</v>
+      </c>
+      <c r="F122" t="s">
+        <v>8</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H122" t="s">
+        <v>8</v>
+      </c>
+      <c r="I122" t="s">
+        <v>8</v>
+      </c>
+      <c r="J122" t="s">
         <v>8</v>
       </c>
     </row>

--- a/content/jahrgaenge/Jg6.xlsx
+++ b/content/jahrgaenge/Jg6.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="477">
   <si>
     <t>Hinweise zu Jg6.xlsx</t>
   </si>
@@ -1078,6 +1078,9 @@
     <t>2026-11-09</t>
   </si>
   <si>
+    <t>Mikroskopieren: Einführung</t>
+  </si>
+  <si>
     <t>2026-11-10</t>
   </si>
   <si>
@@ -1100,6 +1103,9 @@
   </si>
   <si>
     <t>2026-11-13</t>
+  </si>
+  <si>
+    <t>Mikroskopieren: Zwiebelhäutchen</t>
   </si>
   <si>
     <t>2026-11-16</t>
@@ -7443,7 +7449,7 @@
         <v>8</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>8</v>
+        <v>352</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -7457,7 +7463,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B45" t="s">
         <v>138</v>
@@ -7466,7 +7472,7 @@
         <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -7475,7 +7481,7 @@
         <v>8</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -7489,7 +7495,7 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B46" t="s">
         <v>299</v>
@@ -7521,7 +7527,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B47" t="s">
         <v>138</v>
@@ -7539,7 +7545,7 @@
         <v>8</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H47">
         <v>11</v>
@@ -7553,7 +7559,7 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B48" t="s">
         <v>299</v>
@@ -7585,7 +7591,7 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B49" t="s">
         <v>299</v>
@@ -7594,7 +7600,7 @@
         <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -7617,7 +7623,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B50" t="s">
         <v>138</v>
@@ -7635,7 +7641,7 @@
         <v>8</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>8</v>
+        <v>361</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -7649,7 +7655,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B51" t="s">
         <v>138</v>
@@ -7667,7 +7673,7 @@
         <v>8</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>8</v>
+        <v>352</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -7681,7 +7687,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B52" t="s">
         <v>138</v>
@@ -7690,7 +7696,7 @@
         <v>44</v>
       </c>
       <c r="D52" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -7699,7 +7705,7 @@
         <v>8</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H52">
         <v>5</v>
@@ -7713,7 +7719,7 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B53" t="s">
         <v>299</v>
@@ -7745,7 +7751,7 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B54" t="s">
         <v>299</v>
@@ -7754,7 +7760,7 @@
         <v>8</v>
       </c>
       <c r="D54" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -7777,7 +7783,7 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B55" t="s">
         <v>138</v>
@@ -7795,7 +7801,7 @@
         <v>8</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>8</v>
+        <v>361</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -7809,7 +7815,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B56" t="s">
         <v>138</v>
@@ -7827,7 +7833,7 @@
         <v>8</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>8</v>
+        <v>352</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -7841,7 +7847,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B57" t="s">
         <v>138</v>
@@ -7850,7 +7856,7 @@
         <v>44</v>
       </c>
       <c r="D57" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -7859,7 +7865,7 @@
         <v>8</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -7873,7 +7879,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B58" t="s">
         <v>138</v>
@@ -7891,7 +7897,7 @@
         <v>8</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -7905,7 +7911,7 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B59" t="s">
         <v>299</v>
@@ -7937,7 +7943,7 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B60" t="s">
         <v>299</v>
@@ -7946,7 +7952,7 @@
         <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -7969,7 +7975,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B61" t="s">
         <v>138</v>
@@ -7987,7 +7993,7 @@
         <v>8</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>8</v>
+        <v>361</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -8001,7 +8007,7 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B62" t="s">
         <v>299</v>
@@ -8033,7 +8039,7 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B63" t="s">
         <v>299</v>
@@ -8065,7 +8071,7 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B64" t="s">
         <v>138</v>
@@ -8083,7 +8089,7 @@
         <v>8</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H64">
         <v>5</v>
@@ -8097,7 +8103,7 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B65" t="s">
         <v>138</v>
@@ -8129,7 +8135,7 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B66" t="s">
         <v>138</v>
@@ -8147,7 +8153,7 @@
         <v>8</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H66">
         <v>2</v>
@@ -8161,7 +8167,7 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B67" t="s">
         <v>138</v>
@@ -8179,7 +8185,7 @@
         <v>8</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="H67">
         <v>7</v>
@@ -8193,7 +8199,7 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B68" t="s">
         <v>299</v>
@@ -8225,7 +8231,7 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B69" t="s">
         <v>138</v>
@@ -8243,7 +8249,7 @@
         <v>8</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H69">
         <v>11</v>
@@ -8257,7 +8263,7 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B70" t="s">
         <v>138</v>
@@ -8275,7 +8281,7 @@
         <v>8</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="H70">
         <v>8</v>
@@ -8289,7 +8295,7 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B71" t="s">
         <v>342</v>
@@ -8307,7 +8313,7 @@
         <v>8</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -8321,7 +8327,7 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B72" t="s">
         <v>138</v>
@@ -8339,7 +8345,7 @@
         <v>8</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -8353,7 +8359,7 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B73" t="s">
         <v>138</v>
@@ -8371,7 +8377,7 @@
         <v>8</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -8385,7 +8391,7 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B74" t="s">
         <v>138</v>
@@ -8403,7 +8409,7 @@
         <v>8</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="H74">
         <v>9</v>
@@ -8417,7 +8423,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B75" t="s">
         <v>138</v>
@@ -8426,7 +8432,7 @@
         <v>44</v>
       </c>
       <c r="D75" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -8435,7 +8441,7 @@
         <v>8</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -8449,7 +8455,7 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B76" t="s">
         <v>138</v>
@@ -8467,7 +8473,7 @@
         <v>8</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H76">
         <v>3</v>
@@ -8481,7 +8487,7 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B77" t="s">
         <v>138</v>
@@ -8490,7 +8496,7 @@
         <v>44</v>
       </c>
       <c r="D77" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -8499,7 +8505,7 @@
         <v>8</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -8513,7 +8519,7 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B78" t="s">
         <v>138</v>
@@ -8522,7 +8528,7 @@
         <v>72</v>
       </c>
       <c r="D78" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -8531,7 +8537,7 @@
         <v>8</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H78">
         <v>5</v>
@@ -8545,7 +8551,7 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B79" t="s">
         <v>138</v>
@@ -8554,7 +8560,7 @@
         <v>44</v>
       </c>
       <c r="D79" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -8563,7 +8569,7 @@
         <v>8</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -8577,7 +8583,7 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B80" t="s">
         <v>138</v>
@@ -8595,7 +8601,7 @@
         <v>8</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="H80">
         <v>5</v>
@@ -8609,7 +8615,7 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B81" t="s">
         <v>138</v>
@@ -8618,7 +8624,7 @@
         <v>44</v>
       </c>
       <c r="D81" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -8627,7 +8633,7 @@
         <v>8</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -8641,7 +8647,7 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B82" t="s">
         <v>138</v>
@@ -8650,7 +8656,7 @@
         <v>72</v>
       </c>
       <c r="D82" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -8659,7 +8665,7 @@
         <v>8</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H82">
         <v>5</v>
@@ -8673,7 +8679,7 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B83" t="s">
         <v>342</v>
@@ -8705,7 +8711,7 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B84" t="s">
         <v>138</v>
@@ -8714,7 +8720,7 @@
         <v>44</v>
       </c>
       <c r="D84" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -8723,7 +8729,7 @@
         <v>8</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="H84">
         <v>18</v>
@@ -8737,7 +8743,7 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B85" t="s">
         <v>138</v>
@@ -8755,7 +8761,7 @@
         <v>8</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="H85">
         <v>8</v>
@@ -8769,7 +8775,7 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B86" t="s">
         <v>138</v>
@@ -8778,7 +8784,7 @@
         <v>44</v>
       </c>
       <c r="D86" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -8787,7 +8793,7 @@
         <v>8</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -8801,7 +8807,7 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B87" t="s">
         <v>138</v>
@@ -8810,7 +8816,7 @@
         <v>72</v>
       </c>
       <c r="D87" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -8819,7 +8825,7 @@
         <v>8</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H87">
         <v>5</v>
@@ -8833,7 +8839,7 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B88" t="s">
         <v>138</v>
@@ -8851,7 +8857,7 @@
         <v>8</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="H88">
         <v>2</v>
@@ -8865,7 +8871,7 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B89" t="s">
         <v>138</v>
@@ -8883,7 +8889,7 @@
         <v>8</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="H89">
         <v>2</v>
@@ -8897,7 +8903,7 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B90" t="s">
         <v>138</v>
@@ -8915,7 +8921,7 @@
         <v>8</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="H90">
         <v>6</v>
@@ -8929,7 +8935,7 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B91" t="s">
         <v>138</v>
@@ -8947,7 +8953,7 @@
         <v>8</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -8961,7 +8967,7 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B92" t="s">
         <v>138</v>
@@ -8979,7 +8985,7 @@
         <v>8</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="H92">
         <v>5</v>
@@ -8993,7 +8999,7 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B93" t="s">
         <v>138</v>
@@ -9011,7 +9017,7 @@
         <v>8</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -9025,7 +9031,7 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B94" t="s">
         <v>138</v>
@@ -9043,7 +9049,7 @@
         <v>8</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H94">
         <v>4</v>
@@ -9057,7 +9063,7 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B95" t="s">
         <v>138</v>
@@ -9075,7 +9081,7 @@
         <v>8</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="H95">
         <v>5</v>
@@ -9089,7 +9095,7 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B96" t="s">
         <v>138</v>
@@ -9107,7 +9113,7 @@
         <v>8</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -9121,7 +9127,7 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B97" t="s">
         <v>138</v>
@@ -9139,7 +9145,7 @@
         <v>8</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="H97">
         <v>6</v>
@@ -9153,7 +9159,7 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B98" t="s">
         <v>342</v>
@@ -9185,7 +9191,7 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B99" t="s">
         <v>138</v>
@@ -9203,7 +9209,7 @@
         <v>8</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -9217,7 +9223,7 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B100" t="s">
         <v>138</v>
@@ -9235,7 +9241,7 @@
         <v>8</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -9249,7 +9255,7 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B101" t="s">
         <v>138</v>
@@ -9267,7 +9273,7 @@
         <v>8</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="H101">
         <v>8</v>
@@ -9281,7 +9287,7 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B102" t="s">
         <v>138</v>
@@ -9299,7 +9305,7 @@
         <v>8</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H102">
         <v>8</v>
@@ -9313,7 +9319,7 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B103" t="s">
         <v>138</v>
@@ -9331,7 +9337,7 @@
         <v>8</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H103">
         <v>5</v>
@@ -9345,7 +9351,7 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B104" t="s">
         <v>342</v>
@@ -9363,7 +9369,7 @@
         <v>8</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -9377,7 +9383,7 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B105" t="s">
         <v>138</v>
@@ -9395,7 +9401,7 @@
         <v>8</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="H105">
         <v>11</v>
@@ -9409,7 +9415,7 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B106" t="s">
         <v>138</v>
@@ -9427,7 +9433,7 @@
         <v>8</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H106">
         <v>10</v>
@@ -9441,7 +9447,7 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B107" t="s">
         <v>138</v>
@@ -9459,7 +9465,7 @@
         <v>8</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="H107">
         <v>6</v>
@@ -9473,7 +9479,7 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B108" t="s">
         <v>138</v>
@@ -9491,7 +9497,7 @@
         <v>8</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H108">
         <v>1</v>
@@ -9505,7 +9511,7 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B109" t="s">
         <v>138</v>
@@ -9523,7 +9529,7 @@
         <v>8</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -9537,7 +9543,7 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B110" t="s">
         <v>138</v>
@@ -9546,7 +9552,7 @@
         <v>44</v>
       </c>
       <c r="D110" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -9555,7 +9561,7 @@
         <v>8</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="H110">
         <v>7</v>
@@ -9569,7 +9575,7 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B111" t="s">
         <v>138</v>
@@ -9578,7 +9584,7 @@
         <v>44</v>
       </c>
       <c r="D111" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -9587,7 +9593,7 @@
         <v>8</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="H111">
         <v>8</v>
@@ -9601,7 +9607,7 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B112" t="s">
         <v>138</v>
@@ -9619,7 +9625,7 @@
         <v>8</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -9633,7 +9639,7 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B113" t="s">
         <v>138</v>
@@ -9651,7 +9657,7 @@
         <v>8</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H113">
         <v>5</v>
@@ -9665,7 +9671,7 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B114" t="s">
         <v>138</v>
@@ -9683,7 +9689,7 @@
         <v>8</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -9697,7 +9703,7 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B115" t="s">
         <v>138</v>
@@ -9706,7 +9712,7 @@
         <v>44</v>
       </c>
       <c r="D115" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -9715,7 +9721,7 @@
         <v>8</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -9729,7 +9735,7 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B116" t="s">
         <v>138</v>
@@ -9747,7 +9753,7 @@
         <v>8</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="H116">
         <v>6</v>
@@ -9761,7 +9767,7 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B117" t="s">
         <v>138</v>
@@ -9793,7 +9799,7 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B118" t="s">
         <v>138</v>
@@ -9825,7 +9831,7 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B119" t="s">
         <v>138</v>
@@ -9843,7 +9849,7 @@
         <v>8</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -9857,7 +9863,7 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B120" t="s">
         <v>138</v>
@@ -9875,7 +9881,7 @@
         <v>8</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -9889,7 +9895,7 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B121" t="s">
         <v>138</v>
@@ -9907,7 +9913,7 @@
         <v>8</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -9921,7 +9927,7 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B122" t="s">
         <v>138</v>

--- a/content/jahrgaenge/Jg6.xlsx
+++ b/content/jahrgaenge/Jg6.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2996" uniqueCount="796">
   <si>
     <t>Hinweise zu Jg6.xlsx</t>
   </si>
@@ -622,6 +622,9 @@
     <t>Wirbellose Tiere in ihren Lebensräumen</t>
   </si>
   <si>
+    <t>Bienen Comic (M11)</t>
+  </si>
+  <si>
     <t>The Secret of Maple Hill</t>
   </si>
   <si>
@@ -640,18 +643,33 @@
     <t>Fabeln</t>
   </si>
   <si>
+    <t>Eine eigene Fabel schreiben</t>
+  </si>
+  <si>
     <t>Unter der Lupe</t>
   </si>
   <si>
+    <t>Herstellen eines Zellmodells</t>
+  </si>
+  <si>
     <t>Christmas</t>
   </si>
   <si>
+    <t>design a collage on what Christmas means to you</t>
+  </si>
+  <si>
     <t>Klima in Europa</t>
   </si>
   <si>
+    <t>Gelingensnachweis</t>
+  </si>
+  <si>
     <t>Der Wald als Lebensgemeinschaft</t>
   </si>
   <si>
+    <t>Ein Waldtier in das System des Waldes einordnen</t>
+  </si>
+  <si>
     <t>weitere Dreieckseigenschaften und Vierecksberechnung</t>
   </si>
   <si>
@@ -661,33 +679,60 @@
     <t>Peacemakers</t>
   </si>
   <si>
+    <t>give a report about a peacemaker</t>
+  </si>
+  <si>
     <t>Nordeuropa</t>
   </si>
   <si>
+    <t>Reise durch Europa</t>
+  </si>
+  <si>
     <t>Pip and the Umbrella Room</t>
   </si>
   <si>
+    <t>create a reading journal</t>
+  </si>
+  <si>
     <t>Eigenschaften und Darstellen von Prismen</t>
   </si>
   <si>
     <t>Samenpflanzen</t>
   </si>
   <si>
+    <t>Erstellen eines Lapbooks</t>
+  </si>
+  <si>
     <t>Beschreiben und Berichten</t>
   </si>
   <si>
+    <t>Journalistisches Schreibprojekt: Der Unfallbericht</t>
+  </si>
+  <si>
     <t>Südeuropa</t>
   </si>
   <si>
+    <t>Wahlstationen Vulkan oder Faltengebirge (Station 10 oder 11)</t>
+  </si>
+  <si>
     <t>Redewendungen und Sprichwörter</t>
   </si>
   <si>
+    <t>ein Sprichwort/eine Redensart erklären und eine Beispielgeschichte dazu schreiben</t>
+  </si>
+  <si>
     <t>Volumen von Prismen</t>
   </si>
   <si>
     <t>Exkursionen</t>
   </si>
   <si>
+    <t>Climate Co2llaboration</t>
+  </si>
+  <si>
+    <t>Ein eigenes Projekt erstellen und in einem digitalen Showroom präsentieren</t>
+  </si>
+  <si>
     <t>Sätze würfeln</t>
   </si>
   <si>
@@ -898,9 +943,6 @@
     <t>Lehrbuch, kariertes Papier, Millimeterpapier</t>
   </si>
   <si>
-    <t>Gelingensnachweis</t>
-  </si>
-  <si>
     <t>A11, Lehrbuch, Millimeterpapier</t>
   </si>
   <si>
@@ -916,6 +958,942 @@
     <t>A2, A3, A4, Atlas, Wandkarte</t>
   </si>
   <si>
+    <t>Die Entstehung von Fabeln</t>
+  </si>
+  <si>
+    <t>Merkmale von Fabeln</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Fabelhafte Tiere</t>
+  </si>
+  <si>
+    <t>A1, LB, Laptop</t>
+  </si>
+  <si>
+    <t>Der Rabe und der Fuchs – Textverständnis</t>
+  </si>
+  <si>
+    <t>LB</t>
+  </si>
+  <si>
+    <t>Der Aufbau einer Fabel (2 Seiten)</t>
+  </si>
+  <si>
+    <t>M2, M3</t>
+  </si>
+  <si>
+    <t>Das Präteritum in Fabeln</t>
+  </si>
+  <si>
+    <t>Wörtliche Rede in Fabeln</t>
+  </si>
+  <si>
+    <t>Laptop, A2 oder A3</t>
+  </si>
+  <si>
+    <t>Die Lehren einer Fabel</t>
+  </si>
+  <si>
+    <t>Eine Fabel untersuchen</t>
+  </si>
+  <si>
+    <t>M4, A4, Laptop</t>
+  </si>
+  <si>
+    <t>Der Drache und der Hase</t>
+  </si>
+  <si>
+    <t>Fabelhafter Kreativworkshop</t>
+  </si>
+  <si>
+    <t>Laptop, A5–A14</t>
+  </si>
+  <si>
+    <t>Läuft über 2 Termine à 90 Minuten.</t>
+  </si>
+  <si>
+    <t>Teste dich und dein fabelhaftes Wissen</t>
+  </si>
+  <si>
+    <t>A15, Laptop</t>
+  </si>
+  <si>
+    <t>Eine fabelhafte Geschichte</t>
+  </si>
+  <si>
+    <t>Personenbeschreibung</t>
+  </si>
+  <si>
+    <t>A1, M1</t>
+  </si>
+  <si>
+    <t>Wortarten-Check: Das Adjektiv</t>
+  </si>
+  <si>
+    <t>A2, A3</t>
+  </si>
+  <si>
+    <t>Ermittlung läuft – Das Phantombild</t>
+  </si>
+  <si>
+    <t>M2, Laptop</t>
+  </si>
+  <si>
+    <t>Wortarten-Check: Die Präposition</t>
+  </si>
+  <si>
+    <t>A4, A5</t>
+  </si>
+  <si>
+    <t>Wegbeschreibung</t>
+  </si>
+  <si>
+    <t>A6, M3, M4</t>
+  </si>
+  <si>
+    <t>Vorgangsbeschreibung</t>
+  </si>
+  <si>
+    <t>M5, M6</t>
+  </si>
+  <si>
+    <t>Die Sprache der Profis</t>
+  </si>
+  <si>
+    <t>Leporello, A7, M7, M8</t>
+  </si>
+  <si>
+    <t>Aktiv und Passiv</t>
+  </si>
+  <si>
+    <t>A8, A9, M9, M10</t>
+  </si>
+  <si>
+    <t>Mein Kochrezept</t>
+  </si>
+  <si>
+    <t>Leporello, M11</t>
+  </si>
+  <si>
+    <t>Zeitformen-Check</t>
+  </si>
+  <si>
+    <t>Checkliste eines Unfallbericht</t>
+  </si>
+  <si>
+    <t>W-Fragen – Reporter-Prüfung</t>
+  </si>
+  <si>
+    <t>A11, A12</t>
+  </si>
+  <si>
+    <t>Von Unfällen berichten</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>ESZ ermittelt – Mein Unfallbericht</t>
+  </si>
+  <si>
+    <t>M13</t>
+  </si>
+  <si>
+    <t>Wörterschmiede 1</t>
+  </si>
+  <si>
+    <t>Heft</t>
+  </si>
+  <si>
+    <t>Wörterschmiede 2</t>
+  </si>
+  <si>
+    <t>Wortbildung kreativ</t>
+  </si>
+  <si>
+    <t>Fremd-, Erb- und Lehnwörter</t>
+  </si>
+  <si>
+    <t>Lehrbuch, Laptop</t>
+  </si>
+  <si>
+    <t>Sprichwörter und Redewendungen</t>
+  </si>
+  <si>
+    <t>Laptop, A1</t>
+  </si>
+  <si>
+    <t>Bedeutungen von Redewendungen</t>
+  </si>
+  <si>
+    <t>Spiel 'Redewendungen'</t>
+  </si>
+  <si>
+    <t>Redewendungen kennen</t>
+  </si>
+  <si>
+    <t>Memorykarten, Spiel 'das große Quiz'</t>
+  </si>
+  <si>
+    <t>Gelingensnachweis: kreatives Schreiben</t>
+  </si>
+  <si>
+    <t>Redensart-Karte, A2, Laptop</t>
+  </si>
+  <si>
+    <t>A Christmas Card</t>
+  </si>
+  <si>
+    <t>The Yellow Elf</t>
+  </si>
+  <si>
+    <t>A1/A2, dictionary, schoolbook, laptop</t>
+  </si>
+  <si>
+    <t>Christmas Vocabulary Booklet</t>
+  </si>
+  <si>
+    <t>M2, M3, DIN-A3 Papier</t>
+  </si>
+  <si>
+    <t>Christmas Trees</t>
+  </si>
+  <si>
+    <t>M4, Christmas booklet</t>
+  </si>
+  <si>
+    <t>Christmas Carols</t>
+  </si>
+  <si>
+    <t>dictionary, laptop, Christmas booklet</t>
+  </si>
+  <si>
+    <t>Christmas Animals</t>
+  </si>
+  <si>
+    <t>A3, M5, laptop, dictionary</t>
+  </si>
+  <si>
+    <t>Christmas Presents</t>
+  </si>
+  <si>
+    <t>A4, dictionary, laptop</t>
+  </si>
+  <si>
+    <t>The Day Before Christmas</t>
+  </si>
+  <si>
+    <t>A5, A6, laptop, Christmas booklet</t>
+  </si>
+  <si>
+    <t>The Night before Christmas</t>
+  </si>
+  <si>
+    <t>A6 (completed), A7</t>
+  </si>
+  <si>
+    <t>Getting Around Who-Ville</t>
+  </si>
+  <si>
+    <t>A8, M6</t>
+  </si>
+  <si>
+    <t>How the Grinch Stole Christmas</t>
+  </si>
+  <si>
+    <t>A9, dictionary, Christmas booklet, laptop</t>
+  </si>
+  <si>
+    <t>The Grinch and Cindy-Lou</t>
+  </si>
+  <si>
+    <t>Laptop, dictionary</t>
+  </si>
+  <si>
+    <t>The Grinch's Christmas</t>
+  </si>
+  <si>
+    <t>The Grinch Changes His Face</t>
+  </si>
+  <si>
+    <t>dictionary</t>
+  </si>
+  <si>
+    <t>What Christmas is Actually About</t>
+  </si>
+  <si>
+    <t>That's Christmas For Me</t>
+  </si>
+  <si>
+    <t>M7, craft material</t>
+  </si>
+  <si>
+    <t>What Are Peacemakers?</t>
+  </si>
+  <si>
+    <t>Describing Peaceful People</t>
+  </si>
+  <si>
+    <t>M2, A1, text markers</t>
+  </si>
+  <si>
+    <t>Talking About Peace</t>
+  </si>
+  <si>
+    <t>Important Peacemakers</t>
+  </si>
+  <si>
+    <t>M4, a laptop</t>
+  </si>
+  <si>
+    <t>Martin Luther King, Jr.</t>
+  </si>
+  <si>
+    <t>M5, A2, dictionary</t>
+  </si>
+  <si>
+    <t>A Peacemaker Timeline</t>
+  </si>
+  <si>
+    <t>M5, A3, scissors, glue</t>
+  </si>
+  <si>
+    <t>“I Have a Dream…”</t>
+  </si>
+  <si>
+    <t>A4, glue, scissors</t>
+  </si>
+  <si>
+    <t>Songs of Peace</t>
+  </si>
+  <si>
+    <t>M6, A5, laptop, headphones</t>
+  </si>
+  <si>
+    <t>Mahatma Gandhi</t>
+  </si>
+  <si>
+    <t>M7, A6</t>
+  </si>
+  <si>
+    <t>Words of Peace</t>
+  </si>
+  <si>
+    <t>A7, M7, scissors, glue</t>
+  </si>
+  <si>
+    <t>Problems in South Africa</t>
+  </si>
+  <si>
+    <t>laptop</t>
+  </si>
+  <si>
+    <t>Nelson Mandela</t>
+  </si>
+  <si>
+    <t>A8, M8, a dictionary</t>
+  </si>
+  <si>
+    <t>Activist Word Search</t>
+  </si>
+  <si>
+    <t>A Long Walk to Freedom</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>Peaceful Heroes</t>
+  </si>
+  <si>
+    <t>A11, scissors</t>
+  </si>
+  <si>
+    <t>Young Peacemakers Today</t>
+  </si>
+  <si>
+    <t>M9 or M10, A12 or A13</t>
+  </si>
+  <si>
+    <t>Judging a Book by Its Cover</t>
+  </si>
+  <si>
+    <t>M1, M2</t>
+  </si>
+  <si>
+    <t>Getting Started: How to Team Reader (2.1)</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>Getting Started: My Reading Journal (2.2)</t>
+  </si>
+  <si>
+    <t>Strange Faces at Victoria Station</t>
+  </si>
+  <si>
+    <t>A2, laptop/iPad</t>
+  </si>
+  <si>
+    <t>A Day Out in London</t>
+  </si>
+  <si>
+    <t>M3, laptop/iPad</t>
+  </si>
+  <si>
+    <t>Looking for a Lost Umbrella</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>Silly Goose</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>Stubborn Goat</t>
+  </si>
+  <si>
+    <t>Greedy Pig</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>Mrs Morgan and the Evil Witch</t>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
+    <t>Taking a Closer Look: Mrs Morgan</t>
+  </si>
+  <si>
+    <t>A8</t>
+  </si>
+  <si>
+    <t>Goose Tale</t>
+  </si>
+  <si>
+    <t>Escape Goat</t>
+  </si>
+  <si>
+    <t>Stealth Pig</t>
+  </si>
+  <si>
+    <t>A11</t>
+  </si>
+  <si>
+    <t>Umbrella Action Team</t>
+  </si>
+  <si>
+    <t>A12</t>
+  </si>
+  <si>
+    <t>Pip's Plan</t>
+  </si>
+  <si>
+    <t>The Last Umbrella</t>
+  </si>
+  <si>
+    <t>A13, A14, or A15, M4</t>
+  </si>
+  <si>
+    <t>Vielfalt wirbelloser Tiere</t>
+  </si>
+  <si>
+    <t>M1, A1, Lehrbuch</t>
+  </si>
+  <si>
+    <t>Angepasstheit des Regenwurms</t>
+  </si>
+  <si>
+    <t>M2, M3, A2</t>
+  </si>
+  <si>
+    <t>Untersuchen eines Regenwurms</t>
+  </si>
+  <si>
+    <t>M4, A3, Materialien Versuch</t>
+  </si>
+  <si>
+    <t>Bau der Insekten</t>
+  </si>
+  <si>
+    <t>A4, Lehrbuch</t>
+  </si>
+  <si>
+    <t>Insektenordnungen</t>
+  </si>
+  <si>
+    <t>M5, A5, A6</t>
+  </si>
+  <si>
+    <t>Entwicklung der Insekten</t>
+  </si>
+  <si>
+    <t>A7, Lehrbuch, Laptop</t>
+  </si>
+  <si>
+    <t>Mundwerkzeuge der Insekten</t>
+  </si>
+  <si>
+    <t>A8, Lehrbuch</t>
+  </si>
+  <si>
+    <t>Flügel der Insekten</t>
+  </si>
+  <si>
+    <t>M6, A9, Lehrbuch</t>
+  </si>
+  <si>
+    <t>Gliedmaßen der Insekten</t>
+  </si>
+  <si>
+    <t>M7, A10, Lehrbuch, Laptop</t>
+  </si>
+  <si>
+    <t>Atmung der Insekten</t>
+  </si>
+  <si>
+    <t>M8, A11</t>
+  </si>
+  <si>
+    <t>Leben einer Arbeitsbiene</t>
+  </si>
+  <si>
+    <t>M9, M10, A12, A13</t>
+  </si>
+  <si>
+    <t>Tierstaat Honigbiene</t>
+  </si>
+  <si>
+    <t>M11, A14, Laptop</t>
+  </si>
+  <si>
+    <t>Nutzinsekten</t>
+  </si>
+  <si>
+    <t>Wirbellose Tiere als Parasiten</t>
+  </si>
+  <si>
+    <t>M13, M14, Laptop</t>
+  </si>
+  <si>
+    <t>Escape Game: Wirbeltiere und Wirbellose</t>
+  </si>
+  <si>
+    <t>A1, A2, Laptop</t>
+  </si>
+  <si>
+    <t>System der Wirbeltiere und Wirbellosen</t>
+  </si>
+  <si>
+    <t>A3, A4, A5, M1, Lehrbuch</t>
+  </si>
+  <si>
+    <t>Entwicklung der Zelllehre</t>
+  </si>
+  <si>
+    <t>A6, Lupe, Millimeterpapier, Laptop</t>
+  </si>
+  <si>
+    <t>Mikroskopieren I (Pflichtinput)</t>
+  </si>
+  <si>
+    <t>A7, M2, Lichtmikroskop, Dauerpräparat</t>
+  </si>
+  <si>
+    <t>Memory Lichtmikroskop</t>
+  </si>
+  <si>
+    <t>Form und Größe von Zellen</t>
+  </si>
+  <si>
+    <t>M4, Lehrbuch, (Millimeterpapier)</t>
+  </si>
+  <si>
+    <t>Bestandteile der Zelle II</t>
+  </si>
+  <si>
+    <t>M5, M6, Lehrbuch, Klebestift</t>
+  </si>
+  <si>
+    <t>Modelle pflanzlicher Zellen</t>
+  </si>
+  <si>
+    <t>M7, Material für Zellmodell</t>
+  </si>
+  <si>
+    <t>Anfertigen mikroskopischer Zeichnungen</t>
+  </si>
+  <si>
+    <t>A8, M8, Dauerpräparat, Lichtmikroskop</t>
+  </si>
+  <si>
+    <t>Mikroskopieren II (Pflichtinput)</t>
+  </si>
+  <si>
+    <t>A9, Bleistift, weißes A4-Blatt</t>
+  </si>
+  <si>
+    <t>Vergleich tierischer und pflanzlicher Zellen</t>
+  </si>
+  <si>
+    <t>Lehrbuch</t>
+  </si>
+  <si>
+    <t>Leben in der Pfütze</t>
+  </si>
+  <si>
+    <t>M9, Heuaufguss, Lichtmikroskop</t>
+  </si>
+  <si>
+    <t>Organisationsebenen des Lebens</t>
+  </si>
+  <si>
+    <t>M10, Laptop</t>
+  </si>
+  <si>
+    <t>Was weißt du schon über den Wald?</t>
+  </si>
+  <si>
+    <t>Die Stockwerke des Waldes</t>
+  </si>
+  <si>
+    <t>A2, M1, Lehrbuch, Laptop</t>
+  </si>
+  <si>
+    <t>Wer lebt wo im Wald?</t>
+  </si>
+  <si>
+    <t>A3, Lehrbuch, A2, M1</t>
+  </si>
+  <si>
+    <t>Der Wald im Jahresverlauf</t>
+  </si>
+  <si>
+    <t>Moose und Farne</t>
+  </si>
+  <si>
+    <t>A5, Lehrbuch, Petrischale mit Moos</t>
+  </si>
+  <si>
+    <t>Geheimnisvolle Welt der Pilze</t>
+  </si>
+  <si>
+    <t>A6, M2, Laptop, Lehrbuch, Pilzmodell</t>
+  </si>
+  <si>
+    <t>Pilze sammeln und bestimmen</t>
+  </si>
+  <si>
+    <t>M3 – Pilz-Lernkarteien, Laptop</t>
+  </si>
+  <si>
+    <t>Tiere und Pflanzen des Waldes</t>
+  </si>
+  <si>
+    <t>Laptop, Lehrbuch</t>
+  </si>
+  <si>
+    <t>Waldtiere im Wald</t>
+  </si>
+  <si>
+    <t>M4 – Memory Tierspuren</t>
+  </si>
+  <si>
+    <t>Nahrungsbeziehungen im Wald</t>
+  </si>
+  <si>
+    <t>A7, A8, Lehrbuch</t>
+  </si>
+  <si>
+    <t>Nahrungsnetze im Wald</t>
+  </si>
+  <si>
+    <t>M5 – Karten, Fadenrolle Holzklammern</t>
+  </si>
+  <si>
+    <t>Gefährdung und Schutz von Wäldern</t>
+  </si>
+  <si>
+    <t>Ein Waldtier im System Wald</t>
+  </si>
+  <si>
+    <t>M6, Lehrbuch, Laptop</t>
+  </si>
+  <si>
+    <t>Pflanzen können heilen</t>
+  </si>
+  <si>
+    <t>A9, M7 - Karten, Kiste der Kräuterfee</t>
+  </si>
+  <si>
+    <t>Das Lapbook</t>
+  </si>
+  <si>
+    <t>A3-Tonkarton (dickes Papier), Lehrbuch</t>
+  </si>
+  <si>
+    <t>Welche Pflanzen kennst du schon?</t>
+  </si>
+  <si>
+    <t>Der Aufbau von Samenpflanzen</t>
+  </si>
+  <si>
+    <t>A2, A3, M1, Lehrbuch</t>
+  </si>
+  <si>
+    <t>Gemüse – Pflanzenorgane als Nahrungsmittel</t>
+  </si>
+  <si>
+    <t>Das Laubblatt I</t>
+  </si>
+  <si>
+    <t>Das Laubblatt II</t>
+  </si>
+  <si>
+    <t>M1, A5, Pflanzenbestimmungsbuch</t>
+  </si>
+  <si>
+    <t>Der Aufbau der Blüte</t>
+  </si>
+  <si>
+    <t>M2, M3, A6, Laptop, Blütenmodelle</t>
+  </si>
+  <si>
+    <t>Legebild und Blütendiagramm</t>
+  </si>
+  <si>
+    <t>Kirschblüte, weißes A4-Blatt, Pinzette, Tesa, Zirkel, M4, M5</t>
+  </si>
+  <si>
+    <t>Die Bestäubung</t>
+  </si>
+  <si>
+    <t>Von der Blüte zur Frucht</t>
+  </si>
+  <si>
+    <t>M1, A7, M6, Lehrbuch, Laptop</t>
+  </si>
+  <si>
+    <t>Fruchttypen</t>
+  </si>
+  <si>
+    <t>Lehrbuch, Laptop, Pflanzenbestimmungsbuch</t>
+  </si>
+  <si>
+    <t>Pflanzenfamilien</t>
+  </si>
+  <si>
+    <t>A8, M7</t>
+  </si>
+  <si>
+    <t>Gewürze der Lippenblütler</t>
+  </si>
+  <si>
+    <t>Gewürzdosen</t>
+  </si>
+  <si>
+    <t>Wiederholung Topografie</t>
+  </si>
+  <si>
+    <t>Atlas, Laptop, Europakarte, rote und grüne Punkte</t>
+  </si>
+  <si>
+    <t>Mündliche LK</t>
+  </si>
+  <si>
+    <t>Beleuchtungszonen der Erde</t>
+  </si>
+  <si>
+    <t>M1, A1, A2, Laptop</t>
+  </si>
+  <si>
+    <t>Klima-Vegetationszonen NEEF</t>
+  </si>
+  <si>
+    <t>Lehrbuch, A3, A4, M2</t>
+  </si>
+  <si>
+    <t>Wind und Relief beeinflussen das Klima</t>
+  </si>
+  <si>
+    <t>Selbsttest Klima-Vegetationszonen</t>
+  </si>
+  <si>
+    <t>A5, A6</t>
+  </si>
+  <si>
+    <t>Der Golfstrom</t>
+  </si>
+  <si>
+    <t>Lehrbuch, A7, A8, M3, Atlas, Laptop</t>
+  </si>
+  <si>
+    <t>Golfstrom und der Klimawandel</t>
+  </si>
+  <si>
+    <t>A9, M4, M5, Laptop</t>
+  </si>
+  <si>
+    <t>Metropolen</t>
+  </si>
+  <si>
+    <t>A11, A15, Lehrbuch, A12 oder A13 oder A14</t>
+  </si>
+  <si>
+    <t>Satellitenbilder auswerten</t>
+  </si>
+  <si>
+    <t>M6, M7</t>
+  </si>
+  <si>
+    <t>Tipps (0)</t>
+  </si>
+  <si>
+    <t>Schmierpapier, bunte Stifte, A0</t>
+  </si>
+  <si>
+    <t>Topografie Nordeuropas</t>
+  </si>
+  <si>
+    <t>A1, A2, Atlas</t>
+  </si>
+  <si>
+    <t>Glaziale Serie</t>
+  </si>
+  <si>
+    <t>Lehrbuch, A3</t>
+  </si>
+  <si>
+    <t>Gletscher-Eis in Strömen</t>
+  </si>
+  <si>
+    <t>M1, A4</t>
+  </si>
+  <si>
+    <t>Ein Landschaftsprofil auswerten</t>
+  </si>
+  <si>
+    <t>M2, A5, Atlas</t>
+  </si>
+  <si>
+    <t>Löss – ein Geschenk des Windes</t>
+  </si>
+  <si>
+    <t>Lehrbuch, Laptop, A6, Atlas</t>
+  </si>
+  <si>
+    <t>Polartag / Polarnacht</t>
+  </si>
+  <si>
+    <t>Laptop, Atlas, Ordner, A7</t>
+  </si>
+  <si>
+    <t>Finnland und das grüne Gold</t>
+  </si>
+  <si>
+    <t>M3, M4, Lehrbuch</t>
+  </si>
+  <si>
+    <t>Nachhaltigkeit in der Forstwirtschaft</t>
+  </si>
+  <si>
+    <t>Laptop, M5, A8, A9</t>
+  </si>
+  <si>
+    <t>Island – Insel aus Feuer und Eis</t>
+  </si>
+  <si>
+    <t>M6, M7, A10, Laptop, Blatt Papier</t>
+  </si>
+  <si>
+    <t>Gelingensnachweis – Reise durch Europa</t>
+  </si>
+  <si>
+    <t>Atlas, Laptop, A11, A12, A13, A14, A15</t>
+  </si>
+  <si>
+    <t>Der Süden Europas – Topografie</t>
+  </si>
+  <si>
+    <t>Lehrbuch, A1, Transparentpapier, Atlas</t>
+  </si>
+  <si>
+    <t>Laptop, A2</t>
+  </si>
+  <si>
+    <t>Ein Flug über die Alpen</t>
+  </si>
+  <si>
+    <t>A3, Atlas, LB S. 102</t>
+  </si>
+  <si>
+    <t>Höhenstufen der Alpen</t>
+  </si>
+  <si>
+    <t>LB, A4, Ordner</t>
+  </si>
+  <si>
+    <t>Tiere im Alpenraum</t>
+  </si>
+  <si>
+    <t>A5, A6, Laptop</t>
+  </si>
+  <si>
+    <t>Wirtschaftsmotor Alpen</t>
+  </si>
+  <si>
+    <t>M1, A7</t>
+  </si>
+  <si>
+    <t>Gebirgsbildung der Alpen</t>
+  </si>
+  <si>
+    <t>Laptop, M2, A8</t>
+  </si>
+  <si>
+    <t>Mission Vulkan</t>
+  </si>
+  <si>
+    <t>M3, A9, A10, A11, A12, Laptop</t>
+  </si>
+  <si>
+    <t>Was sind eigentlich Erdbeben</t>
+  </si>
+  <si>
+    <t>Wahlaufgabe Vulkan</t>
+  </si>
+  <si>
+    <t>Laptop, Material zum Vulkanbau</t>
+  </si>
+  <si>
+    <t>Wahlaufgabe Gebirgsbildung</t>
+  </si>
+  <si>
+    <t>A13, optionale Materialien zu A13</t>
+  </si>
+  <si>
+    <t>Entdecke Digital Sparks</t>
+  </si>
+  <si>
+    <t>Discover</t>
+  </si>
+  <si>
+    <t>Create</t>
+  </si>
+  <si>
+    <t>Showtime</t>
+  </si>
+  <si>
     <t>2026-08-24</t>
   </si>
   <si>
@@ -967,9 +1945,6 @@
     <t>2026-09-02</t>
   </si>
   <si>
-    <t>Untersuchen eines Regenwurms</t>
-  </si>
-  <si>
     <t>2026-09-03</t>
   </si>
   <si>
@@ -1228,9 +2203,6 @@
     <t>2027-01-21</t>
   </si>
   <si>
-    <t>Moose und Farne</t>
-  </si>
-  <si>
     <t>2027-01-25</t>
   </si>
   <si>
@@ -1273,9 +2245,6 @@
     <t>2027-03-01</t>
   </si>
   <si>
-    <t>Glaziale Serie</t>
-  </si>
-  <si>
     <t>2027-03-02</t>
   </si>
   <si>
@@ -1309,9 +2278,6 @@
     <t>2027-03-15</t>
   </si>
   <si>
-    <t>Ein Landschaftsprofil auswerten</t>
-  </si>
-  <si>
     <t>2027-03-16</t>
   </si>
   <si>
@@ -1372,9 +2338,6 @@
     <t>2027-04-28</t>
   </si>
   <si>
-    <t>Von der Blüte zur Frucht</t>
-  </si>
-  <si>
     <t>2027-04-29</t>
   </si>
   <si>
@@ -1396,13 +2359,7 @@
     <t>TUC</t>
   </si>
   <si>
-    <t>Die Sprache der Profis</t>
-  </si>
-  <si>
     <t>2027-05-12</t>
-  </si>
-  <si>
-    <t>Aktiv und Passiv</t>
   </si>
   <si>
     <t>2027-05-13</t>
@@ -4184,7 +5141,7 @@
         <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="F4" t="s">
         <v>8</v>
@@ -4204,13 +5161,13 @@
         <v>169</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F5">
         <v>15</v>
@@ -4230,13 +5187,13 @@
         <v>171</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F6">
         <v>11</v>
@@ -4256,7 +5213,7 @@
         <v>166</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
@@ -4282,13 +5239,13 @@
         <v>44</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>8</v>
+        <v>207</v>
       </c>
       <c r="F8" t="s">
         <v>8</v>
@@ -4308,15 +5265,15 @@
         <v>72</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
+        <v>209</v>
+      </c>
+      <c r="F9">
         <v>8</v>
       </c>
       <c r="G9" s="2" t="s">
@@ -4334,16 +5291,16 @@
         <v>169</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>8</v>
+        <v>211</v>
+      </c>
+      <c r="F10">
+        <v>16</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>8</v>
@@ -4360,16 +5317,16 @@
         <v>171</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>8</v>
+        <v>213</v>
+      </c>
+      <c r="F11">
+        <v>9</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>8</v>
@@ -4386,16 +5343,16 @@
         <v>72</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>8</v>
+        <v>215</v>
+      </c>
+      <c r="F12">
+        <v>13</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>8</v>
@@ -4412,7 +5369,7 @@
         <v>166</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>8</v>
@@ -4438,10 +5395,10 @@
         <v>44</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>8</v>
@@ -4464,16 +5421,16 @@
         <v>169</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>8</v>
+        <v>219</v>
+      </c>
+      <c r="F15">
+        <v>16</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>8</v>
@@ -4490,16 +5447,16 @@
         <v>171</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>8</v>
+        <v>221</v>
+      </c>
+      <c r="F16">
+        <v>11</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>8</v>
@@ -4516,13 +5473,13 @@
         <v>169</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>8</v>
+        <v>223</v>
       </c>
       <c r="F17" t="s">
         <v>8</v>
@@ -4542,7 +5499,7 @@
         <v>166</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>8</v>
@@ -4568,13 +5525,13 @@
         <v>72</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>8</v>
+        <v>226</v>
       </c>
       <c r="F19" t="s">
         <v>8</v>
@@ -4594,13 +5551,13 @@
         <v>44</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>8</v>
+        <v>228</v>
       </c>
       <c r="F20" t="s">
         <v>8</v>
@@ -4620,13 +5577,13 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>8</v>
+        <v>230</v>
       </c>
       <c r="F21" t="s">
         <v>8</v>
@@ -4646,13 +5603,13 @@
         <v>44</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>8</v>
+        <v>232</v>
       </c>
       <c r="F22" t="s">
         <v>8</v>
@@ -4672,7 +5629,7 @@
         <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>8</v>
@@ -4698,7 +5655,7 @@
         <v>72</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>8</v>
@@ -4750,13 +5707,13 @@
         <v>171</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
+        <v>235</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>8</v>
+        <v>236</v>
       </c>
       <c r="F26" t="s">
         <v>8</v>
@@ -4785,7 +5742,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H220"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -4830,7 +5787,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D2" t="s">
         <v>93</v>
@@ -4842,7 +5799,7 @@
         <v>2</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>8</v>
@@ -4856,7 +5813,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="D3" t="s">
         <v>182</v>
@@ -4868,7 +5825,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>8</v>
@@ -4882,7 +5839,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="D4" t="s">
         <v>93</v>
@@ -4894,7 +5851,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>8</v>
@@ -4908,7 +5865,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="D5" t="s">
         <v>93</v>
@@ -4920,7 +5877,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>8</v>
@@ -4934,7 +5891,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="D6" t="s">
         <v>93</v>
@@ -4946,7 +5903,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>8</v>
@@ -4960,7 +5917,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="D7" t="s">
         <v>182</v>
@@ -4972,7 +5929,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>8</v>
@@ -4986,7 +5943,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="D8" t="s">
         <v>93</v>
@@ -4998,7 +5955,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>8</v>
@@ -5012,7 +5969,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="D9" t="s">
         <v>93</v>
@@ -5024,7 +5981,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>8</v>
@@ -5038,7 +5995,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="D10" t="s">
         <v>93</v>
@@ -5050,7 +6007,7 @@
         <v>3</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>8</v>
@@ -5064,7 +6021,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="D11" t="s">
         <v>93</v>
@@ -5076,7 +6033,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>8</v>
@@ -5090,7 +6047,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="D12" t="s">
         <v>93</v>
@@ -5102,7 +6059,7 @@
         <v>3</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>8</v>
@@ -5116,7 +6073,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="D13" t="s">
         <v>182</v>
@@ -5128,7 +6085,7 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>8</v>
@@ -5142,7 +6099,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="D14" t="s">
         <v>93</v>
@@ -5154,7 +6111,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>8</v>
@@ -5168,7 +6125,7 @@
         <v>2</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="D15" t="s">
         <v>93</v>
@@ -5180,7 +6137,7 @@
         <v>2</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>8</v>
@@ -5194,7 +6151,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
         <v>93</v>
@@ -5206,7 +6163,7 @@
         <v>2</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>8</v>
@@ -5220,7 +6177,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="D17" t="s">
         <v>93</v>
@@ -5232,7 +6189,7 @@
         <v>2</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>8</v>
@@ -5246,7 +6203,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="D18" t="s">
         <v>93</v>
@@ -5258,7 +6215,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>8</v>
@@ -5272,7 +6229,7 @@
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="D19" t="s">
         <v>93</v>
@@ -5284,7 +6241,7 @@
         <v>2</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>8</v>
@@ -5298,7 +6255,7 @@
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="D20" t="s">
         <v>182</v>
@@ -5310,7 +6267,7 @@
         <v>2</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>8</v>
@@ -5324,7 +6281,7 @@
         <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="D21" t="s">
         <v>93</v>
@@ -5336,7 +6293,7 @@
         <v>2</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>8</v>
@@ -5350,7 +6307,7 @@
         <v>9</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="D22" t="s">
         <v>93</v>
@@ -5362,7 +6319,7 @@
         <v>3</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>8</v>
@@ -5376,7 +6333,7 @@
         <v>10</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="D23" t="s">
         <v>93</v>
@@ -5388,7 +6345,7 @@
         <v>2</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>8</v>
@@ -5402,7 +6359,7 @@
         <v>11</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="D24" t="s">
         <v>93</v>
@@ -5414,7 +6371,7 @@
         <v>3</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>8</v>
@@ -5428,7 +6385,7 @@
         <v>12</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D25" t="s">
         <v>93</v>
@@ -5440,7 +6397,7 @@
         <v>3</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>8</v>
@@ -5454,7 +6411,7 @@
         <v>13</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="D26" t="s">
         <v>93</v>
@@ -5480,7 +6437,7 @@
         <v>14</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="D27" t="s">
         <v>93</v>
@@ -5492,7 +6449,7 @@
         <v>3</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>8</v>
@@ -5506,7 +6463,7 @@
         <v>15</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="D28" t="s">
         <v>93</v>
@@ -5518,7 +6475,7 @@
         <v>3</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>8</v>
@@ -5532,7 +6489,7 @@
         <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D29" t="s">
         <v>182</v>
@@ -5558,7 +6515,7 @@
         <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="D30" t="s">
         <v>182</v>
@@ -5584,7 +6541,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="D31" t="s">
         <v>93</v>
@@ -5596,7 +6553,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>8</v>
@@ -5610,7 +6567,7 @@
         <v>2</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="D32" t="s">
         <v>93</v>
@@ -5622,7 +6579,7 @@
         <v>2</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>8</v>
@@ -5636,7 +6593,7 @@
         <v>3</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="D33" t="s">
         <v>93</v>
@@ -5648,7 +6605,7 @@
         <v>2</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>8</v>
@@ -5662,7 +6619,7 @@
         <v>4</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="D34" t="s">
         <v>93</v>
@@ -5674,7 +6631,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>8</v>
@@ -5688,7 +6645,7 @@
         <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="D35" t="s">
         <v>93</v>
@@ -5700,7 +6657,7 @@
         <v>2</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>8</v>
@@ -5714,7 +6671,7 @@
         <v>6</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="D36" t="s">
         <v>182</v>
@@ -5726,7 +6683,7 @@
         <v>2</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>8</v>
@@ -5740,7 +6697,7 @@
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="D37" t="s">
         <v>93</v>
@@ -5752,7 +6709,7 @@
         <v>2</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>8</v>
@@ -5766,7 +6723,7 @@
         <v>8</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="D38" t="s">
         <v>93</v>
@@ -5778,7 +6735,7 @@
         <v>2</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>8</v>
@@ -5792,7 +6749,7 @@
         <v>9</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="D39" t="s">
         <v>93</v>
@@ -5804,7 +6761,7 @@
         <v>3</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>8</v>
@@ -5818,7 +6775,7 @@
         <v>10</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D40" t="s">
         <v>93</v>
@@ -5830,7 +6787,7 @@
         <v>3</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>8</v>
@@ -5844,7 +6801,7 @@
         <v>11</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>292</v>
+        <v>213</v>
       </c>
       <c r="D41" t="s">
         <v>93</v>
@@ -5856,7 +6813,7 @@
         <v>3</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>8</v>
@@ -5870,7 +6827,7 @@
         <v>12</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="D42" t="s">
         <v>182</v>
@@ -5882,7 +6839,7 @@
         <v>2</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>8</v>
@@ -5896,7 +6853,7 @@
         <v>13</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="D43" t="s">
         <v>93</v>
@@ -5908,9 +6865,4611 @@
         <v>2</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="H43" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>174</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D44" t="s">
+        <v>93</v>
+      </c>
+      <c r="E44">
+        <v>20</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>174</v>
+      </c>
+      <c r="B45">
+        <v>2</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D45" t="s">
+        <v>93</v>
+      </c>
+      <c r="E45">
+        <v>20</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>174</v>
+      </c>
+      <c r="B46">
+        <v>3</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D46" t="s">
+        <v>93</v>
+      </c>
+      <c r="E46">
+        <v>60</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>174</v>
+      </c>
+      <c r="B47">
+        <v>4</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D47" t="s">
+        <v>182</v>
+      </c>
+      <c r="E47">
+        <v>30</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>174</v>
+      </c>
+      <c r="B48">
+        <v>5</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D48" t="s">
+        <v>93</v>
+      </c>
+      <c r="E48">
+        <v>80</v>
+      </c>
+      <c r="F48">
+        <v>2</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>174</v>
+      </c>
+      <c r="B49">
+        <v>6</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D49" t="s">
+        <v>93</v>
+      </c>
+      <c r="E49">
+        <v>45</v>
+      </c>
+      <c r="F49">
+        <v>2</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>174</v>
+      </c>
+      <c r="B50">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D50" t="s">
+        <v>93</v>
+      </c>
+      <c r="E50">
+        <v>40</v>
+      </c>
+      <c r="F50">
+        <v>2</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>174</v>
+      </c>
+      <c r="B51">
+        <v>8</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D51" t="s">
+        <v>93</v>
+      </c>
+      <c r="E51">
+        <v>30</v>
+      </c>
+      <c r="F51">
+        <v>3</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>174</v>
+      </c>
+      <c r="B52">
+        <v>9</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D52" t="s">
+        <v>93</v>
+      </c>
+      <c r="E52">
+        <v>90</v>
+      </c>
+      <c r="F52">
+        <v>3</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>174</v>
+      </c>
+      <c r="B53">
+        <v>10</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D53" t="s">
+        <v>182</v>
+      </c>
+      <c r="E53">
+        <v>20</v>
+      </c>
+      <c r="F53">
+        <v>2</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>174</v>
+      </c>
+      <c r="B54">
+        <v>11</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D54" t="s">
+        <v>93</v>
+      </c>
+      <c r="E54">
+        <v>180</v>
+      </c>
+      <c r="F54">
+        <v>3</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>174</v>
+      </c>
+      <c r="B55">
+        <v>12</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D55" t="s">
+        <v>182</v>
+      </c>
+      <c r="E55">
+        <v>40</v>
+      </c>
+      <c r="F55">
+        <v>3</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>174</v>
+      </c>
+      <c r="B56">
+        <v>13</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D56" t="s">
+        <v>93</v>
+      </c>
+      <c r="E56">
+        <v>90</v>
+      </c>
+      <c r="F56">
+        <v>3</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>189</v>
+      </c>
+      <c r="B57">
+        <v>1</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D57" t="s">
+        <v>93</v>
+      </c>
+      <c r="E57">
+        <v>90</v>
+      </c>
+      <c r="F57">
+        <v>2</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>189</v>
+      </c>
+      <c r="B58">
+        <v>2</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D58" t="s">
+        <v>182</v>
+      </c>
+      <c r="E58">
+        <v>20</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>189</v>
+      </c>
+      <c r="B59">
+        <v>3</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D59" t="s">
+        <v>93</v>
+      </c>
+      <c r="E59">
+        <v>60</v>
+      </c>
+      <c r="F59">
+        <v>2</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>189</v>
+      </c>
+      <c r="B60">
+        <v>4</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D60" t="s">
+        <v>182</v>
+      </c>
+      <c r="E60">
+        <v>30</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>189</v>
+      </c>
+      <c r="B61">
+        <v>5</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="D61" t="s">
+        <v>93</v>
+      </c>
+      <c r="E61">
+        <v>60</v>
+      </c>
+      <c r="F61">
+        <v>2</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>189</v>
+      </c>
+      <c r="B62">
+        <v>6</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D62" t="s">
+        <v>93</v>
+      </c>
+      <c r="E62">
+        <v>30</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>189</v>
+      </c>
+      <c r="B63">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D63" t="s">
+        <v>93</v>
+      </c>
+      <c r="E63">
+        <v>40</v>
+      </c>
+      <c r="F63">
+        <v>2</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>189</v>
+      </c>
+      <c r="B64">
+        <v>8</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D64" t="s">
+        <v>93</v>
+      </c>
+      <c r="E64">
+        <v>30</v>
+      </c>
+      <c r="F64">
+        <v>2</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>189</v>
+      </c>
+      <c r="B65">
+        <v>9</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D65" t="s">
+        <v>93</v>
+      </c>
+      <c r="E65">
+        <v>45</v>
+      </c>
+      <c r="F65">
+        <v>3</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>189</v>
+      </c>
+      <c r="B66">
+        <v>10</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D66" t="s">
+        <v>182</v>
+      </c>
+      <c r="E66">
+        <v>15</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>189</v>
+      </c>
+      <c r="B67">
+        <v>11</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D67" t="s">
+        <v>93</v>
+      </c>
+      <c r="E67">
+        <v>15</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>189</v>
+      </c>
+      <c r="B68">
+        <v>12</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D68" t="s">
+        <v>93</v>
+      </c>
+      <c r="E68">
+        <v>45</v>
+      </c>
+      <c r="F68">
+        <v>2</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>189</v>
+      </c>
+      <c r="B69">
+        <v>13</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D69" t="s">
+        <v>93</v>
+      </c>
+      <c r="E69">
+        <v>60</v>
+      </c>
+      <c r="F69">
+        <v>3</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>189</v>
+      </c>
+      <c r="B70">
+        <v>14</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D70" t="s">
+        <v>93</v>
+      </c>
+      <c r="E70">
+        <v>180</v>
+      </c>
+      <c r="F70">
+        <v>3</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>191</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D71" t="s">
+        <v>93</v>
+      </c>
+      <c r="E71">
+        <v>30</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>191</v>
+      </c>
+      <c r="B72">
+        <v>2</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D72" t="s">
+        <v>93</v>
+      </c>
+      <c r="E72">
+        <v>30</v>
+      </c>
+      <c r="F72">
+        <v>2</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>191</v>
+      </c>
+      <c r="B73">
+        <v>3</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D73" t="s">
+        <v>182</v>
+      </c>
+      <c r="E73">
+        <v>10</v>
+      </c>
+      <c r="F73">
+        <v>2</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>191</v>
+      </c>
+      <c r="B74">
+        <v>4</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D74" t="s">
+        <v>93</v>
+      </c>
+      <c r="E74">
+        <v>60</v>
+      </c>
+      <c r="F74">
+        <v>2</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>191</v>
+      </c>
+      <c r="B75">
+        <v>5</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D75" t="s">
+        <v>93</v>
+      </c>
+      <c r="E75">
+        <v>45</v>
+      </c>
+      <c r="F75">
+        <v>2</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>191</v>
+      </c>
+      <c r="B76">
+        <v>6</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D76" t="s">
+        <v>93</v>
+      </c>
+      <c r="E76">
+        <v>30</v>
+      </c>
+      <c r="F76">
+        <v>2</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>191</v>
+      </c>
+      <c r="B77">
+        <v>7</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D77" t="s">
+        <v>182</v>
+      </c>
+      <c r="E77">
+        <v>60</v>
+      </c>
+      <c r="F77">
+        <v>3</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>191</v>
+      </c>
+      <c r="B78">
+        <v>8</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D78" t="s">
+        <v>93</v>
+      </c>
+      <c r="E78">
+        <v>90</v>
+      </c>
+      <c r="F78">
+        <v>2</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>176</v>
+      </c>
+      <c r="B79">
+        <v>1</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D79" t="s">
+        <v>93</v>
+      </c>
+      <c r="E79">
+        <v>35</v>
+      </c>
+      <c r="F79">
+        <v>1</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>176</v>
+      </c>
+      <c r="B80">
+        <v>2</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D80" t="s">
+        <v>93</v>
+      </c>
+      <c r="E80">
+        <v>55</v>
+      </c>
+      <c r="F80">
+        <v>2</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>176</v>
+      </c>
+      <c r="B81">
+        <v>3</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D81" t="s">
+        <v>93</v>
+      </c>
+      <c r="E81">
+        <v>50</v>
+      </c>
+      <c r="F81">
+        <v>1</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>176</v>
+      </c>
+      <c r="B82">
+        <v>4</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D82" t="s">
+        <v>93</v>
+      </c>
+      <c r="E82">
+        <v>40</v>
+      </c>
+      <c r="F82">
+        <v>1</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>176</v>
+      </c>
+      <c r="B83">
+        <v>5</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D83" t="s">
+        <v>182</v>
+      </c>
+      <c r="E83">
+        <v>35</v>
+      </c>
+      <c r="F83">
+        <v>3</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>176</v>
+      </c>
+      <c r="B84">
+        <v>6</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D84" t="s">
+        <v>93</v>
+      </c>
+      <c r="E84">
+        <v>90</v>
+      </c>
+      <c r="F84">
+        <v>3</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>176</v>
+      </c>
+      <c r="B85">
+        <v>7</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D85" t="s">
+        <v>93</v>
+      </c>
+      <c r="E85">
+        <v>90</v>
+      </c>
+      <c r="F85">
+        <v>3</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>176</v>
+      </c>
+      <c r="B86">
+        <v>8</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D86" t="s">
+        <v>93</v>
+      </c>
+      <c r="E86">
+        <v>40</v>
+      </c>
+      <c r="F86">
+        <v>2</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>176</v>
+      </c>
+      <c r="B87">
+        <v>9</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D87" t="s">
+        <v>93</v>
+      </c>
+      <c r="E87">
+        <v>80</v>
+      </c>
+      <c r="F87">
+        <v>2</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>176</v>
+      </c>
+      <c r="B88">
+        <v>10</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D88" t="s">
+        <v>182</v>
+      </c>
+      <c r="E88">
+        <v>30</v>
+      </c>
+      <c r="F88">
+        <v>2</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>176</v>
+      </c>
+      <c r="B89">
+        <v>11</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D89" t="s">
+        <v>93</v>
+      </c>
+      <c r="E89">
+        <v>45</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>176</v>
+      </c>
+      <c r="B90">
+        <v>12</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D90" t="s">
+        <v>93</v>
+      </c>
+      <c r="E90">
+        <v>60</v>
+      </c>
+      <c r="F90">
+        <v>3</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>176</v>
+      </c>
+      <c r="B91">
+        <v>13</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D91" t="s">
+        <v>93</v>
+      </c>
+      <c r="E91">
+        <v>40</v>
+      </c>
+      <c r="F91">
+        <v>2</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>176</v>
+      </c>
+      <c r="B92">
+        <v>14</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D92" t="s">
+        <v>93</v>
+      </c>
+      <c r="E92">
+        <v>30</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>176</v>
+      </c>
+      <c r="B93">
+        <v>15</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D93" t="s">
+        <v>93</v>
+      </c>
+      <c r="E93">
+        <v>60</v>
+      </c>
+      <c r="F93">
+        <v>3</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>176</v>
+      </c>
+      <c r="B94">
+        <v>16</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D94" t="s">
+        <v>93</v>
+      </c>
+      <c r="E94">
+        <v>90</v>
+      </c>
+      <c r="F94">
+        <v>2</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>183</v>
+      </c>
+      <c r="B95">
+        <v>1</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D95" t="s">
+        <v>93</v>
+      </c>
+      <c r="E95">
+        <v>60</v>
+      </c>
+      <c r="F95">
+        <v>2</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>183</v>
+      </c>
+      <c r="B96">
+        <v>2</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="D96" t="s">
+        <v>93</v>
+      </c>
+      <c r="E96">
+        <v>40</v>
+      </c>
+      <c r="F96">
+        <v>1</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>183</v>
+      </c>
+      <c r="B97">
+        <v>3</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D97" t="s">
+        <v>93</v>
+      </c>
+      <c r="E97">
+        <v>25</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>183</v>
+      </c>
+      <c r="B98">
+        <v>4</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D98" t="s">
+        <v>93</v>
+      </c>
+      <c r="E98">
+        <v>60</v>
+      </c>
+      <c r="F98">
+        <v>1</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>183</v>
+      </c>
+      <c r="B99">
+        <v>5</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D99" t="s">
+        <v>93</v>
+      </c>
+      <c r="E99">
+        <v>75</v>
+      </c>
+      <c r="F99">
+        <v>2</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>183</v>
+      </c>
+      <c r="B100">
+        <v>6</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D100" t="s">
+        <v>182</v>
+      </c>
+      <c r="E100">
+        <v>25</v>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>183</v>
+      </c>
+      <c r="B101">
+        <v>7</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D101" t="s">
+        <v>93</v>
+      </c>
+      <c r="E101">
+        <v>30</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>183</v>
+      </c>
+      <c r="B102">
+        <v>8</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="D102" t="s">
+        <v>93</v>
+      </c>
+      <c r="E102">
+        <v>45</v>
+      </c>
+      <c r="F102">
+        <v>1</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>183</v>
+      </c>
+      <c r="B103">
+        <v>9</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D103" t="s">
+        <v>93</v>
+      </c>
+      <c r="E103">
+        <v>75</v>
+      </c>
+      <c r="F103">
+        <v>3</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>183</v>
+      </c>
+      <c r="B104">
+        <v>10</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D104" t="s">
+        <v>182</v>
+      </c>
+      <c r="E104">
+        <v>45</v>
+      </c>
+      <c r="F104">
+        <v>1</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>183</v>
+      </c>
+      <c r="B105">
+        <v>11</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D105" t="s">
+        <v>93</v>
+      </c>
+      <c r="E105">
+        <v>75</v>
+      </c>
+      <c r="F105">
+        <v>3</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>183</v>
+      </c>
+      <c r="B106">
+        <v>12</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D106" t="s">
+        <v>93</v>
+      </c>
+      <c r="E106">
+        <v>75</v>
+      </c>
+      <c r="F106">
+        <v>3</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>183</v>
+      </c>
+      <c r="B107">
+        <v>13</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="D107" t="s">
+        <v>182</v>
+      </c>
+      <c r="E107">
+        <v>30</v>
+      </c>
+      <c r="F107">
+        <v>1</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>183</v>
+      </c>
+      <c r="B108">
+        <v>14</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D108" t="s">
+        <v>93</v>
+      </c>
+      <c r="E108">
+        <v>40</v>
+      </c>
+      <c r="F108">
+        <v>1</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>183</v>
+      </c>
+      <c r="B109">
+        <v>15</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D109" t="s">
+        <v>182</v>
+      </c>
+      <c r="E109">
+        <v>45</v>
+      </c>
+      <c r="F109">
+        <v>1</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>183</v>
+      </c>
+      <c r="B110">
+        <v>16</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D110" t="s">
+        <v>93</v>
+      </c>
+      <c r="E110">
+        <v>90</v>
+      </c>
+      <c r="F110">
+        <v>2</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>185</v>
+      </c>
+      <c r="B111">
+        <v>1</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="D111" t="s">
+        <v>93</v>
+      </c>
+      <c r="E111">
+        <v>45</v>
+      </c>
+      <c r="F111">
+        <v>1</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>185</v>
+      </c>
+      <c r="B112">
+        <v>2</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D112" t="s">
+        <v>93</v>
+      </c>
+      <c r="E112">
+        <v>20</v>
+      </c>
+      <c r="F112">
+        <v>1</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>185</v>
+      </c>
+      <c r="B113">
+        <v>3</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D113" t="s">
+        <v>93</v>
+      </c>
+      <c r="E113">
+        <v>10</v>
+      </c>
+      <c r="F113">
+        <v>1</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>185</v>
+      </c>
+      <c r="B114">
+        <v>4</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D114" t="s">
+        <v>93</v>
+      </c>
+      <c r="E114">
+        <v>80</v>
+      </c>
+      <c r="F114">
+        <v>2</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>185</v>
+      </c>
+      <c r="B115">
+        <v>5</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D115" t="s">
+        <v>182</v>
+      </c>
+      <c r="E115">
+        <v>45</v>
+      </c>
+      <c r="F115">
+        <v>2</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>185</v>
+      </c>
+      <c r="B116">
+        <v>6</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="D116" t="s">
+        <v>93</v>
+      </c>
+      <c r="E116">
+        <v>60</v>
+      </c>
+      <c r="F116">
+        <v>2</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>185</v>
+      </c>
+      <c r="B117">
+        <v>7</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="D117" t="s">
+        <v>93</v>
+      </c>
+      <c r="E117">
+        <v>60</v>
+      </c>
+      <c r="F117">
+        <v>2</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>185</v>
+      </c>
+      <c r="B118">
+        <v>8</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="D118" t="s">
+        <v>93</v>
+      </c>
+      <c r="E118">
+        <v>60</v>
+      </c>
+      <c r="F118">
+        <v>3</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>185</v>
+      </c>
+      <c r="B119">
+        <v>9</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D119" t="s">
+        <v>93</v>
+      </c>
+      <c r="E119">
+        <v>60</v>
+      </c>
+      <c r="F119">
+        <v>1</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>185</v>
+      </c>
+      <c r="B120">
+        <v>10</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D120" t="s">
+        <v>93</v>
+      </c>
+      <c r="E120">
+        <v>80</v>
+      </c>
+      <c r="F120">
+        <v>2</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>185</v>
+      </c>
+      <c r="B121">
+        <v>11</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D121" t="s">
+        <v>182</v>
+      </c>
+      <c r="E121">
+        <v>40</v>
+      </c>
+      <c r="F121">
+        <v>3</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>185</v>
+      </c>
+      <c r="B122">
+        <v>12</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D122" t="s">
+        <v>93</v>
+      </c>
+      <c r="E122">
+        <v>60</v>
+      </c>
+      <c r="F122">
+        <v>2</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>185</v>
+      </c>
+      <c r="B123">
+        <v>13</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D123" t="s">
+        <v>93</v>
+      </c>
+      <c r="E123">
+        <v>60</v>
+      </c>
+      <c r="F123">
+        <v>3</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>185</v>
+      </c>
+      <c r="B124">
+        <v>14</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="D124" t="s">
+        <v>93</v>
+      </c>
+      <c r="E124">
+        <v>60</v>
+      </c>
+      <c r="F124">
+        <v>1</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>185</v>
+      </c>
+      <c r="B125">
+        <v>15</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D125" t="s">
+        <v>93</v>
+      </c>
+      <c r="E125">
+        <v>40</v>
+      </c>
+      <c r="F125">
+        <v>3</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>185</v>
+      </c>
+      <c r="B126">
+        <v>16</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D126" t="s">
+        <v>93</v>
+      </c>
+      <c r="E126">
+        <v>120</v>
+      </c>
+      <c r="F126">
+        <v>3</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>185</v>
+      </c>
+      <c r="B127">
+        <v>17</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D127" t="s">
+        <v>93</v>
+      </c>
+      <c r="E127">
+        <v>160</v>
+      </c>
+      <c r="F127">
+        <v>3</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>167</v>
+      </c>
+      <c r="B128">
+        <v>1</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D128" t="s">
+        <v>93</v>
+      </c>
+      <c r="E128">
+        <v>30</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>167</v>
+      </c>
+      <c r="B129">
+        <v>2</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D129" t="s">
+        <v>93</v>
+      </c>
+      <c r="E129">
+        <v>60</v>
+      </c>
+      <c r="F129">
+        <v>2</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>167</v>
+      </c>
+      <c r="B130">
+        <v>3</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D130" t="s">
+        <v>93</v>
+      </c>
+      <c r="E130">
+        <v>80</v>
+      </c>
+      <c r="F130">
+        <v>3</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>167</v>
+      </c>
+      <c r="B131">
+        <v>4</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D131" t="s">
+        <v>93</v>
+      </c>
+      <c r="E131">
+        <v>20</v>
+      </c>
+      <c r="F131">
+        <v>1</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>167</v>
+      </c>
+      <c r="B132">
+        <v>5</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D132" t="s">
+        <v>93</v>
+      </c>
+      <c r="E132">
+        <v>80</v>
+      </c>
+      <c r="F132">
+        <v>2</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>167</v>
+      </c>
+      <c r="B133">
+        <v>6</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D133" t="s">
+        <v>93</v>
+      </c>
+      <c r="E133">
+        <v>45</v>
+      </c>
+      <c r="F133">
+        <v>1</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>167</v>
+      </c>
+      <c r="B134">
+        <v>7</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D134" t="s">
+        <v>93</v>
+      </c>
+      <c r="E134">
+        <v>45</v>
+      </c>
+      <c r="F134">
+        <v>1</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>167</v>
+      </c>
+      <c r="B135">
+        <v>8</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D135" t="s">
+        <v>182</v>
+      </c>
+      <c r="E135">
+        <v>40</v>
+      </c>
+      <c r="F135">
+        <v>2</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>167</v>
+      </c>
+      <c r="B136">
+        <v>9</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D136" t="s">
+        <v>93</v>
+      </c>
+      <c r="E136">
+        <v>45</v>
+      </c>
+      <c r="F136">
+        <v>2</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>167</v>
+      </c>
+      <c r="B137">
+        <v>10</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D137" t="s">
+        <v>182</v>
+      </c>
+      <c r="E137">
+        <v>30</v>
+      </c>
+      <c r="F137">
+        <v>1</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>167</v>
+      </c>
+      <c r="B138">
+        <v>11</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D138" t="s">
+        <v>182</v>
+      </c>
+      <c r="E138">
+        <v>80</v>
+      </c>
+      <c r="F138">
+        <v>2</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>167</v>
+      </c>
+      <c r="B139">
+        <v>12</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="D139" t="s">
+        <v>93</v>
+      </c>
+      <c r="E139">
+        <v>80</v>
+      </c>
+      <c r="F139">
+        <v>2</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>167</v>
+      </c>
+      <c r="B140">
+        <v>13</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D140" t="s">
+        <v>182</v>
+      </c>
+      <c r="E140">
+        <v>45</v>
+      </c>
+      <c r="F140">
+        <v>2</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>167</v>
+      </c>
+      <c r="B141">
+        <v>14</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D141" t="s">
+        <v>93</v>
+      </c>
+      <c r="E141">
+        <v>40</v>
+      </c>
+      <c r="F141">
+        <v>1</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>175</v>
+      </c>
+      <c r="B142">
+        <v>1</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="D142" t="s">
+        <v>93</v>
+      </c>
+      <c r="E142">
+        <v>60</v>
+      </c>
+      <c r="F142">
+        <v>3</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>175</v>
+      </c>
+      <c r="B143">
+        <v>2</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D143" t="s">
+        <v>93</v>
+      </c>
+      <c r="E143">
+        <v>80</v>
+      </c>
+      <c r="F143">
+        <v>3</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>175</v>
+      </c>
+      <c r="B144">
+        <v>3</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D144" t="s">
+        <v>93</v>
+      </c>
+      <c r="E144">
+        <v>60</v>
+      </c>
+      <c r="F144">
+        <v>2</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>175</v>
+      </c>
+      <c r="B145">
+        <v>4</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="D145" t="s">
+        <v>93</v>
+      </c>
+      <c r="E145">
+        <v>80</v>
+      </c>
+      <c r="F145">
+        <v>3</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>175</v>
+      </c>
+      <c r="B146">
+        <v>5</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D146" t="s">
+        <v>182</v>
+      </c>
+      <c r="E146">
+        <v>30</v>
+      </c>
+      <c r="F146">
+        <v>1</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>175</v>
+      </c>
+      <c r="B147">
+        <v>6</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D147" t="s">
+        <v>93</v>
+      </c>
+      <c r="E147">
+        <v>40</v>
+      </c>
+      <c r="F147">
+        <v>3</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>175</v>
+      </c>
+      <c r="B148">
+        <v>7</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D148" t="s">
+        <v>93</v>
+      </c>
+      <c r="E148">
+        <v>60</v>
+      </c>
+      <c r="F148">
+        <v>2</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>175</v>
+      </c>
+      <c r="B149">
+        <v>8</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="D149" t="s">
+        <v>93</v>
+      </c>
+      <c r="E149">
+        <v>80</v>
+      </c>
+      <c r="F149">
+        <v>2</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>175</v>
+      </c>
+      <c r="B150">
+        <v>9</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D150" t="s">
+        <v>93</v>
+      </c>
+      <c r="E150">
+        <v>40</v>
+      </c>
+      <c r="F150">
+        <v>2</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>175</v>
+      </c>
+      <c r="B151">
+        <v>10</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="D151" t="s">
+        <v>93</v>
+      </c>
+      <c r="E151">
+        <v>80</v>
+      </c>
+      <c r="F151">
+        <v>3</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>175</v>
+      </c>
+      <c r="B152">
+        <v>11</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="D152" t="s">
+        <v>93</v>
+      </c>
+      <c r="E152">
+        <v>60</v>
+      </c>
+      <c r="F152">
+        <v>2</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>175</v>
+      </c>
+      <c r="B153">
+        <v>12</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="D153" t="s">
+        <v>182</v>
+      </c>
+      <c r="E153">
+        <v>40</v>
+      </c>
+      <c r="F153">
+        <v>3</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>175</v>
+      </c>
+      <c r="B154">
+        <v>13</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="D154" t="s">
+        <v>182</v>
+      </c>
+      <c r="E154">
+        <v>30</v>
+      </c>
+      <c r="F154">
+        <v>2</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>175</v>
+      </c>
+      <c r="B155">
+        <v>14</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D155" t="s">
+        <v>182</v>
+      </c>
+      <c r="E155">
+        <v>45</v>
+      </c>
+      <c r="F155">
+        <v>2</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>178</v>
+      </c>
+      <c r="B156">
+        <v>1</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="D156" t="s">
+        <v>93</v>
+      </c>
+      <c r="E156">
+        <v>30</v>
+      </c>
+      <c r="F156">
+        <v>1</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>178</v>
+      </c>
+      <c r="B157">
+        <v>2</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D157" t="s">
+        <v>93</v>
+      </c>
+      <c r="E157">
+        <v>60</v>
+      </c>
+      <c r="F157">
+        <v>2</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>178</v>
+      </c>
+      <c r="B158">
+        <v>3</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D158" t="s">
+        <v>93</v>
+      </c>
+      <c r="E158">
+        <v>30</v>
+      </c>
+      <c r="F158">
+        <v>2</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>178</v>
+      </c>
+      <c r="B159">
+        <v>4</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="D159" t="s">
+        <v>93</v>
+      </c>
+      <c r="E159">
+        <v>45</v>
+      </c>
+      <c r="F159">
+        <v>3</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>178</v>
+      </c>
+      <c r="B160">
+        <v>5</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D160" t="s">
+        <v>93</v>
+      </c>
+      <c r="E160">
+        <v>45</v>
+      </c>
+      <c r="F160">
+        <v>2</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>178</v>
+      </c>
+      <c r="B161">
+        <v>6</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="D161" t="s">
+        <v>93</v>
+      </c>
+      <c r="E161">
+        <v>45</v>
+      </c>
+      <c r="F161">
+        <v>3</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>178</v>
+      </c>
+      <c r="B162">
+        <v>7</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D162" t="s">
+        <v>182</v>
+      </c>
+      <c r="E162">
+        <v>45</v>
+      </c>
+      <c r="F162">
+        <v>2</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>178</v>
+      </c>
+      <c r="B163">
+        <v>8</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="D163" t="s">
+        <v>93</v>
+      </c>
+      <c r="E163">
+        <v>30</v>
+      </c>
+      <c r="F163">
+        <v>1</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>178</v>
+      </c>
+      <c r="B164">
+        <v>9</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D164" t="s">
+        <v>182</v>
+      </c>
+      <c r="E164">
+        <v>30</v>
+      </c>
+      <c r="F164">
+        <v>2</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>178</v>
+      </c>
+      <c r="B165">
+        <v>10</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D165" t="s">
+        <v>93</v>
+      </c>
+      <c r="E165">
+        <v>60</v>
+      </c>
+      <c r="F165">
+        <v>3</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>178</v>
+      </c>
+      <c r="B166">
+        <v>11</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="D166" t="s">
+        <v>182</v>
+      </c>
+      <c r="E166">
+        <v>45</v>
+      </c>
+      <c r="F166">
+        <v>2</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>178</v>
+      </c>
+      <c r="B167">
+        <v>12</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D167" t="s">
+        <v>93</v>
+      </c>
+      <c r="E167">
+        <v>30</v>
+      </c>
+      <c r="F167">
+        <v>2</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="H167" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>178</v>
+      </c>
+      <c r="B168">
+        <v>13</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="D168" t="s">
+        <v>93</v>
+      </c>
+      <c r="E168">
+        <v>180</v>
+      </c>
+      <c r="F168">
+        <v>3</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="H168" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>178</v>
+      </c>
+      <c r="B169">
+        <v>14</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D169" t="s">
+        <v>182</v>
+      </c>
+      <c r="E169">
+        <v>45</v>
+      </c>
+      <c r="F169">
+        <v>3</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="H169" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>188</v>
+      </c>
+      <c r="B170">
+        <v>1</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D170" t="s">
+        <v>93</v>
+      </c>
+      <c r="E170">
+        <v>20</v>
+      </c>
+      <c r="F170">
+        <v>1</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="H170" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>188</v>
+      </c>
+      <c r="B171">
+        <v>2</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="D171" t="s">
+        <v>93</v>
+      </c>
+      <c r="E171">
+        <v>30</v>
+      </c>
+      <c r="F171">
+        <v>1</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="H171" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>188</v>
+      </c>
+      <c r="B172">
+        <v>3</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D172" t="s">
+        <v>93</v>
+      </c>
+      <c r="E172">
+        <v>80</v>
+      </c>
+      <c r="F172">
+        <v>2</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="H172" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>188</v>
+      </c>
+      <c r="B173">
+        <v>4</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="D173" t="s">
+        <v>93</v>
+      </c>
+      <c r="E173">
+        <v>20</v>
+      </c>
+      <c r="F173">
+        <v>1</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="H173" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>188</v>
+      </c>
+      <c r="B174">
+        <v>5</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="D174" t="s">
+        <v>93</v>
+      </c>
+      <c r="E174">
+        <v>40</v>
+      </c>
+      <c r="F174">
+        <v>3</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>188</v>
+      </c>
+      <c r="B175">
+        <v>6</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D175" t="s">
+        <v>93</v>
+      </c>
+      <c r="E175">
+        <v>40</v>
+      </c>
+      <c r="F175">
+        <v>2</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="H175" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>188</v>
+      </c>
+      <c r="B176">
+        <v>7</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="D176" t="s">
+        <v>93</v>
+      </c>
+      <c r="E176">
+        <v>40</v>
+      </c>
+      <c r="F176">
+        <v>2</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="H176" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>188</v>
+      </c>
+      <c r="B177">
+        <v>8</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="D177" t="s">
+        <v>93</v>
+      </c>
+      <c r="E177">
+        <v>80</v>
+      </c>
+      <c r="F177">
+        <v>3</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="H177" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>188</v>
+      </c>
+      <c r="B178">
+        <v>9</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="D178" t="s">
+        <v>93</v>
+      </c>
+      <c r="E178">
+        <v>30</v>
+      </c>
+      <c r="F178">
+        <v>2</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H178" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>188</v>
+      </c>
+      <c r="B179">
+        <v>10</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="D179" t="s">
+        <v>93</v>
+      </c>
+      <c r="E179">
+        <v>60</v>
+      </c>
+      <c r="F179">
+        <v>2</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="H179" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>188</v>
+      </c>
+      <c r="B180">
+        <v>11</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="D180" t="s">
+        <v>182</v>
+      </c>
+      <c r="E180">
+        <v>30</v>
+      </c>
+      <c r="F180">
+        <v>2</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="H180" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>188</v>
+      </c>
+      <c r="B181">
+        <v>12</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="D181" t="s">
+        <v>93</v>
+      </c>
+      <c r="E181">
+        <v>80</v>
+      </c>
+      <c r="F181">
+        <v>2</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="H181" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>188</v>
+      </c>
+      <c r="B182">
+        <v>13</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="D182" t="s">
+        <v>182</v>
+      </c>
+      <c r="E182">
+        <v>10</v>
+      </c>
+      <c r="F182">
+        <v>2</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>177</v>
+      </c>
+      <c r="B183">
+        <v>1</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D183" t="s">
+        <v>182</v>
+      </c>
+      <c r="E183">
+        <v>90</v>
+      </c>
+      <c r="F183">
+        <v>2</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="H183" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>177</v>
+      </c>
+      <c r="B184">
+        <v>2</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="D184" t="s">
+        <v>93</v>
+      </c>
+      <c r="E184">
+        <v>20</v>
+      </c>
+      <c r="F184">
+        <v>3</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="H184" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>177</v>
+      </c>
+      <c r="B185">
+        <v>3</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="D185" t="s">
+        <v>93</v>
+      </c>
+      <c r="E185">
+        <v>90</v>
+      </c>
+      <c r="F185">
+        <v>1</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="H185" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>177</v>
+      </c>
+      <c r="B186">
+        <v>4</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="D186" t="s">
+        <v>93</v>
+      </c>
+      <c r="E186">
+        <v>90</v>
+      </c>
+      <c r="F186">
+        <v>2</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="H186" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>177</v>
+      </c>
+      <c r="B187">
+        <v>5</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="D187" t="s">
+        <v>93</v>
+      </c>
+      <c r="E187">
+        <v>45</v>
+      </c>
+      <c r="F187">
+        <v>2</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="H187" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>177</v>
+      </c>
+      <c r="B188">
+        <v>6</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="D188" t="s">
+        <v>182</v>
+      </c>
+      <c r="E188">
+        <v>45</v>
+      </c>
+      <c r="F188">
+        <v>3</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="H188" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>177</v>
+      </c>
+      <c r="B189">
+        <v>7</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="D189" t="s">
+        <v>93</v>
+      </c>
+      <c r="E189">
+        <v>90</v>
+      </c>
+      <c r="F189">
+        <v>2</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="H189" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>177</v>
+      </c>
+      <c r="B190">
+        <v>8</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="D190" t="s">
+        <v>93</v>
+      </c>
+      <c r="E190">
+        <v>50</v>
+      </c>
+      <c r="F190">
+        <v>3</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="H190" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>177</v>
+      </c>
+      <c r="B191">
+        <v>9</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D191" t="s">
+        <v>93</v>
+      </c>
+      <c r="E191">
+        <v>45</v>
+      </c>
+      <c r="F191">
+        <v>3</v>
+      </c>
+      <c r="G191" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="H191" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>177</v>
+      </c>
+      <c r="B192">
+        <v>10</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="D192" t="s">
+        <v>93</v>
+      </c>
+      <c r="E192">
+        <v>90</v>
+      </c>
+      <c r="F192">
+        <v>2</v>
+      </c>
+      <c r="G192" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="H192" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>177</v>
+      </c>
+      <c r="B193">
+        <v>11</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="D193" t="s">
+        <v>182</v>
+      </c>
+      <c r="E193">
+        <v>65</v>
+      </c>
+      <c r="F193">
+        <v>2</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="H193" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>184</v>
+      </c>
+      <c r="B194">
+        <v>1</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="D194" t="s">
+        <v>182</v>
+      </c>
+      <c r="E194">
+        <v>20</v>
+      </c>
+      <c r="F194">
+        <v>1</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="H194" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>184</v>
+      </c>
+      <c r="B195">
+        <v>2</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="D195" t="s">
+        <v>93</v>
+      </c>
+      <c r="E195">
+        <v>60</v>
+      </c>
+      <c r="F195">
+        <v>2</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="H195" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>184</v>
+      </c>
+      <c r="B196">
+        <v>3</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="D196" t="s">
+        <v>93</v>
+      </c>
+      <c r="E196">
+        <v>45</v>
+      </c>
+      <c r="F196">
+        <v>2</v>
+      </c>
+      <c r="G196" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="H196" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>184</v>
+      </c>
+      <c r="B197">
+        <v>4</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="D197" t="s">
+        <v>93</v>
+      </c>
+      <c r="E197">
+        <v>45</v>
+      </c>
+      <c r="F197">
+        <v>2</v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="H197" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>184</v>
+      </c>
+      <c r="B198">
+        <v>5</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="D198" t="s">
+        <v>93</v>
+      </c>
+      <c r="E198">
+        <v>90</v>
+      </c>
+      <c r="F198">
+        <v>3</v>
+      </c>
+      <c r="G198" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="H198" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>184</v>
+      </c>
+      <c r="B199">
+        <v>6</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="D199" t="s">
+        <v>93</v>
+      </c>
+      <c r="E199">
+        <v>60</v>
+      </c>
+      <c r="F199">
+        <v>2</v>
+      </c>
+      <c r="G199" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="H199" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>184</v>
+      </c>
+      <c r="B200">
+        <v>7</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="D200" t="s">
+        <v>182</v>
+      </c>
+      <c r="E200">
+        <v>40</v>
+      </c>
+      <c r="F200">
+        <v>2</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="H200" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>184</v>
+      </c>
+      <c r="B201">
+        <v>8</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="D201" t="s">
+        <v>93</v>
+      </c>
+      <c r="E201">
+        <v>60</v>
+      </c>
+      <c r="F201">
+        <v>2</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="H201" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>184</v>
+      </c>
+      <c r="B202">
+        <v>9</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="D202" t="s">
+        <v>182</v>
+      </c>
+      <c r="E202">
+        <v>90</v>
+      </c>
+      <c r="F202">
+        <v>3</v>
+      </c>
+      <c r="G202" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="H202" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>184</v>
+      </c>
+      <c r="B203">
+        <v>10</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D203" t="s">
+        <v>93</v>
+      </c>
+      <c r="E203">
+        <v>90</v>
+      </c>
+      <c r="F203">
+        <v>2</v>
+      </c>
+      <c r="G203" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="H203" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>184</v>
+      </c>
+      <c r="B204">
+        <v>11</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="D204" t="s">
+        <v>93</v>
+      </c>
+      <c r="E204">
+        <v>120</v>
+      </c>
+      <c r="F204">
+        <v>2</v>
+      </c>
+      <c r="G204" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="H204" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>190</v>
+      </c>
+      <c r="B205">
+        <v>1</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="D205" t="s">
+        <v>93</v>
+      </c>
+      <c r="E205">
+        <v>90</v>
+      </c>
+      <c r="F205">
+        <v>2</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="H205" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>190</v>
+      </c>
+      <c r="B206">
+        <v>2</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D206" t="s">
+        <v>93</v>
+      </c>
+      <c r="E206">
+        <v>70</v>
+      </c>
+      <c r="F206">
+        <v>1</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="H206" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>190</v>
+      </c>
+      <c r="B207">
+        <v>3</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="D207" t="s">
+        <v>93</v>
+      </c>
+      <c r="E207">
+        <v>30</v>
+      </c>
+      <c r="F207">
+        <v>1</v>
+      </c>
+      <c r="G207" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="H207" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>190</v>
+      </c>
+      <c r="B208">
+        <v>4</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="D208" t="s">
+        <v>182</v>
+      </c>
+      <c r="E208">
+        <v>45</v>
+      </c>
+      <c r="F208">
+        <v>1</v>
+      </c>
+      <c r="G208" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="H208" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>190</v>
+      </c>
+      <c r="B209">
+        <v>5</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="D209" t="s">
+        <v>93</v>
+      </c>
+      <c r="E209">
+        <v>45</v>
+      </c>
+      <c r="F209">
+        <v>1</v>
+      </c>
+      <c r="G209" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="H209" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>190</v>
+      </c>
+      <c r="B210">
+        <v>6</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="D210" t="s">
+        <v>93</v>
+      </c>
+      <c r="E210">
+        <v>70</v>
+      </c>
+      <c r="F210">
+        <v>3</v>
+      </c>
+      <c r="G210" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="H210" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>190</v>
+      </c>
+      <c r="B211">
+        <v>7</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="D211" t="s">
+        <v>93</v>
+      </c>
+      <c r="E211">
+        <v>90</v>
+      </c>
+      <c r="F211">
+        <v>2</v>
+      </c>
+      <c r="G211" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="H211" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>190</v>
+      </c>
+      <c r="B212">
+        <v>8</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="D212" t="s">
+        <v>93</v>
+      </c>
+      <c r="E212">
+        <v>80</v>
+      </c>
+      <c r="F212">
+        <v>2</v>
+      </c>
+      <c r="G212" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="H212" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>190</v>
+      </c>
+      <c r="B213">
+        <v>9</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="D213" t="s">
+        <v>182</v>
+      </c>
+      <c r="E213">
+        <v>60</v>
+      </c>
+      <c r="F213">
+        <v>1</v>
+      </c>
+      <c r="G213" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="H213" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>190</v>
+      </c>
+      <c r="B214">
+        <v>10</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="D214" t="s">
+        <v>93</v>
+      </c>
+      <c r="E214">
+        <v>120</v>
+      </c>
+      <c r="F214">
+        <v>3</v>
+      </c>
+      <c r="G214" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="H214" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>190</v>
+      </c>
+      <c r="B215">
+        <v>11</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="D215" t="s">
+        <v>93</v>
+      </c>
+      <c r="E215">
+        <v>120</v>
+      </c>
+      <c r="F215">
+        <v>3</v>
+      </c>
+      <c r="G215" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="H215" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>190</v>
+      </c>
+      <c r="B216">
+        <v>12</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="D216" t="s">
+        <v>93</v>
+      </c>
+      <c r="E216">
+        <v>10</v>
+      </c>
+      <c r="F216">
+        <v>2</v>
+      </c>
+      <c r="G216" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="H216" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>195</v>
+      </c>
+      <c r="B217">
+        <v>1</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="D217" t="s">
+        <v>93</v>
+      </c>
+      <c r="E217">
+        <v>10</v>
+      </c>
+      <c r="F217">
+        <v>1</v>
+      </c>
+      <c r="G217" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H217" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>195</v>
+      </c>
+      <c r="B218">
+        <v>2</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="D218" t="s">
+        <v>93</v>
+      </c>
+      <c r="E218">
+        <v>180</v>
+      </c>
+      <c r="F218">
+        <v>2</v>
+      </c>
+      <c r="G218" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H218" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>195</v>
+      </c>
+      <c r="B219">
+        <v>3</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="D219" t="s">
+        <v>93</v>
+      </c>
+      <c r="E219">
+        <v>120</v>
+      </c>
+      <c r="F219">
+        <v>3</v>
+      </c>
+      <c r="G219" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H219" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>195</v>
+      </c>
+      <c r="B220">
+        <v>4</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="D220" t="s">
+        <v>93</v>
+      </c>
+      <c r="E220">
+        <v>20</v>
+      </c>
+      <c r="F220">
+        <v>2</v>
+      </c>
+      <c r="G220" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H220" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -6087,16 +11646,16 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>298</v>
+        <v>624</v>
       </c>
       <c r="B2" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>300</v>
+        <v>626</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -6119,7 +11678,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>301</v>
+        <v>627</v>
       </c>
       <c r="B3" t="s">
         <v>138</v>
@@ -6128,7 +11687,7 @@
         <v>166</v>
       </c>
       <c r="D3" t="s">
-        <v>302</v>
+        <v>628</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -6137,7 +11696,7 @@
         <v>8</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>303</v>
+        <v>629</v>
       </c>
       <c r="H3">
         <v>3</v>
@@ -6151,16 +11710,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>301</v>
+        <v>627</v>
       </c>
       <c r="B4" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>304</v>
+        <v>630</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -6183,16 +11742,16 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>305</v>
+        <v>631</v>
       </c>
       <c r="B5" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>306</v>
+        <v>632</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -6215,7 +11774,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>307</v>
+        <v>633</v>
       </c>
       <c r="B6" t="s">
         <v>138</v>
@@ -6224,7 +11783,7 @@
         <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>308</v>
+        <v>634</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -6233,7 +11792,7 @@
         <v>8</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>309</v>
+        <v>635</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -6247,16 +11806,16 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>307</v>
+        <v>633</v>
       </c>
       <c r="B7" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>310</v>
+        <v>636</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -6279,16 +11838,16 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>311</v>
+        <v>637</v>
       </c>
       <c r="B8" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>306</v>
+        <v>632</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -6314,13 +11873,13 @@
         <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>300</v>
+        <v>626</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -6343,7 +11902,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>312</v>
+        <v>638</v>
       </c>
       <c r="B10" t="s">
         <v>138</v>
@@ -6352,7 +11911,7 @@
         <v>166</v>
       </c>
       <c r="D10" t="s">
-        <v>302</v>
+        <v>628</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -6361,7 +11920,7 @@
         <v>8</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>313</v>
+        <v>639</v>
       </c>
       <c r="H10">
         <v>6</v>
@@ -6375,16 +11934,16 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>312</v>
+        <v>638</v>
       </c>
       <c r="B11" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>304</v>
+        <v>630</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -6407,7 +11966,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>314</v>
+        <v>640</v>
       </c>
       <c r="B12" t="s">
         <v>138</v>
@@ -6416,7 +11975,7 @@
         <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>306</v>
+        <v>632</v>
       </c>
       <c r="E12" t="s">
         <v>141</v>
@@ -6425,7 +11984,7 @@
         <v>8</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>315</v>
+        <v>465</v>
       </c>
       <c r="H12">
         <v>3</v>
@@ -6439,7 +11998,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>316</v>
+        <v>641</v>
       </c>
       <c r="B13" t="s">
         <v>138</v>
@@ -6448,7 +12007,7 @@
         <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>308</v>
+        <v>634</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -6457,7 +12016,7 @@
         <v>8</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>317</v>
+        <v>642</v>
       </c>
       <c r="H13">
         <v>5</v>
@@ -6471,16 +12030,16 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>316</v>
+        <v>641</v>
       </c>
       <c r="B14" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C14" t="s">
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>310</v>
+        <v>636</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -6503,7 +12062,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>318</v>
+        <v>643</v>
       </c>
       <c r="B15" t="s">
         <v>138</v>
@@ -6512,16 +12071,16 @@
         <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>306</v>
+        <v>632</v>
       </c>
       <c r="E15" t="s">
-        <v>319</v>
+        <v>644</v>
       </c>
       <c r="F15" t="s">
         <v>8</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>315</v>
+        <v>465</v>
       </c>
       <c r="H15">
         <v>3</v>
@@ -6538,13 +12097,13 @@
         <v>127</v>
       </c>
       <c r="B16" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C16" t="s">
         <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>300</v>
+        <v>626</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -6576,7 +12135,7 @@
         <v>166</v>
       </c>
       <c r="D17" t="s">
-        <v>302</v>
+        <v>628</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -6585,7 +12144,7 @@
         <v>8</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>320</v>
+        <v>645</v>
       </c>
       <c r="H17">
         <v>11</v>
@@ -6602,13 +12161,13 @@
         <v>136</v>
       </c>
       <c r="B18" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C18" t="s">
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>304</v>
+        <v>630</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -6631,7 +12190,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>321</v>
+        <v>646</v>
       </c>
       <c r="B19" t="s">
         <v>138</v>
@@ -6640,16 +12199,16 @@
         <v>72</v>
       </c>
       <c r="D19" t="s">
-        <v>306</v>
+        <v>632</v>
       </c>
       <c r="E19" t="s">
-        <v>322</v>
+        <v>647</v>
       </c>
       <c r="F19" t="s">
         <v>8</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>315</v>
+        <v>465</v>
       </c>
       <c r="H19">
         <v>3</v>
@@ -6663,7 +12222,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>323</v>
+        <v>648</v>
       </c>
       <c r="B20" t="s">
         <v>138</v>
@@ -6672,7 +12231,7 @@
         <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>308</v>
+        <v>634</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -6681,7 +12240,7 @@
         <v>8</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>324</v>
+        <v>649</v>
       </c>
       <c r="H20">
         <v>9</v>
@@ -6695,16 +12254,16 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>323</v>
+        <v>648</v>
       </c>
       <c r="B21" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C21" t="s">
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>310</v>
+        <v>636</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -6727,16 +12286,16 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>325</v>
+        <v>650</v>
       </c>
       <c r="B22" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C22" t="s">
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>306</v>
+        <v>632</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -6759,16 +12318,16 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>326</v>
+        <v>651</v>
       </c>
       <c r="B23" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C23" t="s">
         <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>300</v>
+        <v>626</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -6791,16 +12350,16 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>327</v>
+        <v>652</v>
       </c>
       <c r="B24" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C24" t="s">
         <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>328</v>
+        <v>653</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -6823,7 +12382,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>329</v>
+        <v>654</v>
       </c>
       <c r="B25" t="s">
         <v>138</v>
@@ -6832,7 +12391,7 @@
         <v>171</v>
       </c>
       <c r="D25" t="s">
-        <v>300</v>
+        <v>626</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -6841,7 +12400,7 @@
         <v>8</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>330</v>
+        <v>655</v>
       </c>
       <c r="H25">
         <v>9</v>
@@ -6855,7 +12414,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>331</v>
+        <v>656</v>
       </c>
       <c r="B26" t="s">
         <v>138</v>
@@ -6864,7 +12423,7 @@
         <v>44</v>
       </c>
       <c r="D26" t="s">
-        <v>308</v>
+        <v>634</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -6873,7 +12432,7 @@
         <v>8</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>332</v>
+        <v>657</v>
       </c>
       <c r="H26">
         <v>2</v>
@@ -6887,16 +12446,16 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>331</v>
+        <v>656</v>
       </c>
       <c r="B27" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C27" t="s">
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>304</v>
+        <v>630</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -6919,7 +12478,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>333</v>
+        <v>658</v>
       </c>
       <c r="B28" t="s">
         <v>138</v>
@@ -6928,7 +12487,7 @@
         <v>169</v>
       </c>
       <c r="D28" t="s">
-        <v>304</v>
+        <v>630</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -6937,7 +12496,7 @@
         <v>8</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>334</v>
+        <v>659</v>
       </c>
       <c r="H28">
         <v>2</v>
@@ -6951,16 +12510,16 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>333</v>
+        <v>658</v>
       </c>
       <c r="B29" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C29" t="s">
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>300</v>
+        <v>626</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -6986,13 +12545,13 @@
         <v>58</v>
       </c>
       <c r="B30" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C30" t="s">
         <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>328</v>
+        <v>653</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -7015,7 +12574,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>335</v>
+        <v>660</v>
       </c>
       <c r="B31" t="s">
         <v>138</v>
@@ -7024,7 +12583,7 @@
         <v>171</v>
       </c>
       <c r="D31" t="s">
-        <v>300</v>
+        <v>626</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -7033,7 +12592,7 @@
         <v>8</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>336</v>
+        <v>661</v>
       </c>
       <c r="H31">
         <v>10</v>
@@ -7047,7 +12606,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>337</v>
+        <v>662</v>
       </c>
       <c r="B32" t="s">
         <v>138</v>
@@ -7056,7 +12615,7 @@
         <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>308</v>
+        <v>634</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -7065,7 +12624,7 @@
         <v>8</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>338</v>
+        <v>663</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -7079,16 +12638,16 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>337</v>
+        <v>662</v>
       </c>
       <c r="B33" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C33" t="s">
         <v>8</v>
       </c>
       <c r="D33" t="s">
-        <v>304</v>
+        <v>630</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -7111,7 +12670,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>339</v>
+        <v>664</v>
       </c>
       <c r="B34" t="s">
         <v>138</v>
@@ -7120,7 +12679,7 @@
         <v>171</v>
       </c>
       <c r="D34" t="s">
-        <v>300</v>
+        <v>626</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -7129,7 +12688,7 @@
         <v>8</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>340</v>
+        <v>665</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -7143,16 +12702,16 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>341</v>
+        <v>666</v>
       </c>
       <c r="B35" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C35" t="s">
         <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>328</v>
+        <v>653</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -7178,7 +12737,7 @@
         <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>342</v>
+        <v>667</v>
       </c>
       <c r="C36" t="s">
         <v>8</v>
@@ -7193,7 +12752,7 @@
         <v>8</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>343</v>
+        <v>668</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -7207,7 +12766,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>344</v>
+        <v>669</v>
       </c>
       <c r="B37" t="s">
         <v>138</v>
@@ -7216,7 +12775,7 @@
         <v>44</v>
       </c>
       <c r="D37" t="s">
-        <v>308</v>
+        <v>634</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -7225,7 +12784,7 @@
         <v>8</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>345</v>
+        <v>670</v>
       </c>
       <c r="H37">
         <v>9</v>
@@ -7239,16 +12798,16 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>344</v>
+        <v>669</v>
       </c>
       <c r="B38" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C38" t="s">
         <v>8</v>
       </c>
       <c r="D38" t="s">
-        <v>304</v>
+        <v>630</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -7271,7 +12830,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>346</v>
+        <v>671</v>
       </c>
       <c r="B39" t="s">
         <v>138</v>
@@ -7280,7 +12839,7 @@
         <v>169</v>
       </c>
       <c r="D39" t="s">
-        <v>304</v>
+        <v>630</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -7289,7 +12848,7 @@
         <v>8</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>347</v>
+        <v>672</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -7303,16 +12862,16 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>346</v>
+        <v>671</v>
       </c>
       <c r="B40" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C40" t="s">
         <v>8</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>626</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -7335,16 +12894,16 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>348</v>
+        <v>673</v>
       </c>
       <c r="B41" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C41" t="s">
         <v>8</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>628</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -7367,7 +12926,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>349</v>
+        <v>674</v>
       </c>
       <c r="B42" t="s">
         <v>138</v>
@@ -7376,7 +12935,7 @@
         <v>166</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>628</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -7385,7 +12944,7 @@
         <v>8</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>350</v>
+        <v>675</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -7399,16 +12958,16 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>349</v>
+        <v>674</v>
       </c>
       <c r="B43" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C43" t="s">
         <v>8</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>632</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -7431,7 +12990,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>351</v>
+        <v>676</v>
       </c>
       <c r="B44" t="s">
         <v>138</v>
@@ -7449,7 +13008,7 @@
         <v>8</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>352</v>
+        <v>677</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -7463,7 +13022,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>353</v>
+        <v>678</v>
       </c>
       <c r="B45" t="s">
         <v>138</v>
@@ -7472,7 +13031,7 @@
         <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>354</v>
+        <v>679</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -7481,7 +13040,7 @@
         <v>8</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>355</v>
+        <v>680</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -7495,16 +13054,16 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>353</v>
+        <v>678</v>
       </c>
       <c r="B46" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C46" t="s">
         <v>8</v>
       </c>
       <c r="D46" t="s">
-        <v>302</v>
+        <v>628</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -7527,7 +13086,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>356</v>
+        <v>681</v>
       </c>
       <c r="B47" t="s">
         <v>138</v>
@@ -7536,7 +13095,7 @@
         <v>166</v>
       </c>
       <c r="D47" t="s">
-        <v>302</v>
+        <v>628</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -7545,7 +13104,7 @@
         <v>8</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>357</v>
+        <v>682</v>
       </c>
       <c r="H47">
         <v>11</v>
@@ -7559,16 +13118,16 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>356</v>
+        <v>681</v>
       </c>
       <c r="B48" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C48" t="s">
         <v>8</v>
       </c>
       <c r="D48" t="s">
-        <v>306</v>
+        <v>632</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -7591,16 +13150,16 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>358</v>
+        <v>683</v>
       </c>
       <c r="B49" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C49" t="s">
         <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>359</v>
+        <v>684</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -7623,7 +13182,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>360</v>
+        <v>685</v>
       </c>
       <c r="B50" t="s">
         <v>138</v>
@@ -7632,7 +13191,7 @@
         <v>72</v>
       </c>
       <c r="D50" t="s">
-        <v>306</v>
+        <v>632</v>
       </c>
       <c r="E50" t="s">
         <v>141</v>
@@ -7641,7 +13200,7 @@
         <v>8</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>361</v>
+        <v>686</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -7655,7 +13214,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>362</v>
+        <v>687</v>
       </c>
       <c r="B51" t="s">
         <v>138</v>
@@ -7667,13 +13226,13 @@
         <v>140</v>
       </c>
       <c r="E51" t="s">
-        <v>319</v>
+        <v>644</v>
       </c>
       <c r="F51" t="s">
         <v>8</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>352</v>
+        <v>677</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -7687,7 +13246,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>363</v>
+        <v>688</v>
       </c>
       <c r="B52" t="s">
         <v>138</v>
@@ -7696,7 +13255,7 @@
         <v>44</v>
       </c>
       <c r="D52" t="s">
-        <v>354</v>
+        <v>679</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -7705,7 +13264,7 @@
         <v>8</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>364</v>
+        <v>689</v>
       </c>
       <c r="H52">
         <v>5</v>
@@ -7719,16 +13278,16 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>363</v>
+        <v>688</v>
       </c>
       <c r="B53" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C53" t="s">
         <v>8</v>
       </c>
       <c r="D53" t="s">
-        <v>302</v>
+        <v>628</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -7751,16 +13310,16 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>365</v>
+        <v>690</v>
       </c>
       <c r="B54" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C54" t="s">
         <v>8</v>
       </c>
       <c r="D54" t="s">
-        <v>359</v>
+        <v>684</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -7783,7 +13342,7 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>366</v>
+        <v>691</v>
       </c>
       <c r="B55" t="s">
         <v>138</v>
@@ -7792,16 +13351,16 @@
         <v>72</v>
       </c>
       <c r="D55" t="s">
-        <v>306</v>
+        <v>632</v>
       </c>
       <c r="E55" t="s">
-        <v>319</v>
+        <v>644</v>
       </c>
       <c r="F55" t="s">
         <v>8</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>361</v>
+        <v>686</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -7815,7 +13374,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>367</v>
+        <v>692</v>
       </c>
       <c r="B56" t="s">
         <v>138</v>
@@ -7827,13 +13386,13 @@
         <v>140</v>
       </c>
       <c r="E56" t="s">
-        <v>322</v>
+        <v>647</v>
       </c>
       <c r="F56" t="s">
         <v>8</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>352</v>
+        <v>677</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -7847,7 +13406,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>368</v>
+        <v>693</v>
       </c>
       <c r="B57" t="s">
         <v>138</v>
@@ -7856,7 +13415,7 @@
         <v>44</v>
       </c>
       <c r="D57" t="s">
-        <v>354</v>
+        <v>679</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -7865,7 +13424,7 @@
         <v>8</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>369</v>
+        <v>694</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -7879,7 +13438,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>370</v>
+        <v>695</v>
       </c>
       <c r="B58" t="s">
         <v>138</v>
@@ -7888,7 +13447,7 @@
         <v>166</v>
       </c>
       <c r="D58" t="s">
-        <v>302</v>
+        <v>628</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -7897,7 +13456,7 @@
         <v>8</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>371</v>
+        <v>696</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -7911,16 +13470,16 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>370</v>
+        <v>695</v>
       </c>
       <c r="B59" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C59" t="s">
         <v>8</v>
       </c>
       <c r="D59" t="s">
-        <v>306</v>
+        <v>632</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -7943,16 +13502,16 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>372</v>
+        <v>697</v>
       </c>
       <c r="B60" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C60" t="s">
         <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>359</v>
+        <v>684</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -7975,7 +13534,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>373</v>
+        <v>698</v>
       </c>
       <c r="B61" t="s">
         <v>138</v>
@@ -7984,16 +13543,16 @@
         <v>72</v>
       </c>
       <c r="D61" t="s">
-        <v>306</v>
+        <v>632</v>
       </c>
       <c r="E61" t="s">
-        <v>322</v>
+        <v>647</v>
       </c>
       <c r="F61" t="s">
         <v>8</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>361</v>
+        <v>686</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -8007,16 +13566,16 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>374</v>
+        <v>699</v>
       </c>
       <c r="B62" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C62" t="s">
         <v>8</v>
       </c>
       <c r="D62" t="s">
-        <v>302</v>
+        <v>628</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -8039,16 +13598,16 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>375</v>
+        <v>700</v>
       </c>
       <c r="B63" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C63" t="s">
         <v>8</v>
       </c>
       <c r="D63" t="s">
-        <v>302</v>
+        <v>628</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -8071,7 +13630,7 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>376</v>
+        <v>701</v>
       </c>
       <c r="B64" t="s">
         <v>138</v>
@@ -8080,7 +13639,7 @@
         <v>171</v>
       </c>
       <c r="D64" t="s">
-        <v>300</v>
+        <v>626</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
@@ -8089,7 +13648,7 @@
         <v>8</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>377</v>
+        <v>702</v>
       </c>
       <c r="H64">
         <v>5</v>
@@ -8103,7 +13662,7 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>378</v>
+        <v>703</v>
       </c>
       <c r="B65" t="s">
         <v>138</v>
@@ -8112,7 +13671,7 @@
         <v>166</v>
       </c>
       <c r="D65" t="s">
-        <v>302</v>
+        <v>628</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -8121,7 +13680,7 @@
         <v>8</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>350</v>
+        <v>675</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -8135,7 +13694,7 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>379</v>
+        <v>704</v>
       </c>
       <c r="B66" t="s">
         <v>138</v>
@@ -8144,7 +13703,7 @@
         <v>169</v>
       </c>
       <c r="D66" t="s">
-        <v>304</v>
+        <v>630</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -8153,7 +13712,7 @@
         <v>8</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>380</v>
+        <v>705</v>
       </c>
       <c r="H66">
         <v>2</v>
@@ -8167,7 +13726,7 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>381</v>
+        <v>706</v>
       </c>
       <c r="B67" t="s">
         <v>138</v>
@@ -8176,7 +13735,7 @@
         <v>171</v>
       </c>
       <c r="D67" t="s">
-        <v>300</v>
+        <v>626</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -8185,7 +13744,7 @@
         <v>8</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>382</v>
+        <v>707</v>
       </c>
       <c r="H67">
         <v>7</v>
@@ -8199,16 +13758,16 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>381</v>
+        <v>706</v>
       </c>
       <c r="B68" t="s">
-        <v>299</v>
+        <v>625</v>
       </c>
       <c r="C68" t="s">
         <v>8</v>
       </c>
       <c r="D68" t="s">
-        <v>302</v>
+        <v>628</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -8231,7 +13790,7 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>383</v>
+        <v>708</v>
       </c>
       <c r="B69" t="s">
         <v>138</v>
@@ -8240,7 +13799,7 @@
         <v>166</v>
       </c>
       <c r="D69" t="s">
-        <v>302</v>
+        <v>628</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -8249,7 +13808,7 @@
         <v>8</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>357</v>
+        <v>682</v>
       </c>
       <c r="H69">
         <v>11</v>
@@ -8263,7 +13822,7 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>384</v>
+        <v>709</v>
       </c>
       <c r="B70" t="s">
         <v>138</v>
@@ -8272,7 +13831,7 @@
         <v>169</v>
       </c>
       <c r="D70" t="s">
-        <v>304</v>
+        <v>630</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -8281,7 +13840,7 @@
         <v>8</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>385</v>
+        <v>710</v>
       </c>
       <c r="H70">
         <v>8</v>
@@ -8295,10 +13854,10 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>386</v>
+        <v>711</v>
       </c>
       <c r="B71" t="s">
-        <v>342</v>
+        <v>667</v>
       </c>
       <c r="C71" t="s">
         <v>8</v>
@@ -8313,7 +13872,7 @@
         <v>8</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>387</v>
+        <v>712</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -8327,7 +13886,7 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>388</v>
+        <v>713</v>
       </c>
       <c r="B72" t="s">
         <v>138</v>
@@ -8336,7 +13895,7 @@
         <v>171</v>
       </c>
       <c r="D72" t="s">
-        <v>300</v>
+        <v>626</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -8345,7 +13904,7 @@
         <v>8</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>389</v>
+        <v>714</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -8359,7 +13918,7 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>390</v>
+        <v>715</v>
       </c>
       <c r="B73" t="s">
         <v>138</v>
@@ -8368,7 +13927,7 @@
         <v>166</v>
       </c>
       <c r="D73" t="s">
-        <v>302</v>
+        <v>628</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -8377,7 +13936,7 @@
         <v>8</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>371</v>
+        <v>696</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -8391,7 +13950,7 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>391</v>
+        <v>716</v>
       </c>
       <c r="B74" t="s">
         <v>138</v>
@@ -8400,7 +13959,7 @@
         <v>169</v>
       </c>
       <c r="D74" t="s">
-        <v>304</v>
+        <v>630</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -8409,7 +13968,7 @@
         <v>8</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>392</v>
+        <v>717</v>
       </c>
       <c r="H74">
         <v>9</v>
@@ -8423,7 +13982,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>393</v>
+        <v>718</v>
       </c>
       <c r="B75" t="s">
         <v>138</v>
@@ -8432,7 +13991,7 @@
         <v>44</v>
       </c>
       <c r="D75" t="s">
-        <v>394</v>
+        <v>719</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -8441,7 +14000,7 @@
         <v>8</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>395</v>
+        <v>720</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -8455,7 +14014,7 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>396</v>
+        <v>721</v>
       </c>
       <c r="B76" t="s">
         <v>138</v>
@@ -8464,7 +14023,7 @@
         <v>166</v>
       </c>
       <c r="D76" t="s">
-        <v>302</v>
+        <v>628</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -8473,7 +14032,7 @@
         <v>8</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>397</v>
+        <v>722</v>
       </c>
       <c r="H76">
         <v>3</v>
@@ -8487,7 +14046,7 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>398</v>
+        <v>723</v>
       </c>
       <c r="B77" t="s">
         <v>138</v>
@@ -8496,7 +14055,7 @@
         <v>44</v>
       </c>
       <c r="D77" t="s">
-        <v>399</v>
+        <v>724</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -8505,7 +14064,7 @@
         <v>8</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>400</v>
+        <v>725</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -8519,7 +14078,7 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>401</v>
+        <v>726</v>
       </c>
       <c r="B78" t="s">
         <v>138</v>
@@ -8528,7 +14087,7 @@
         <v>72</v>
       </c>
       <c r="D78" t="s">
-        <v>359</v>
+        <v>684</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -8537,7 +14096,7 @@
         <v>8</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>402</v>
+        <v>519</v>
       </c>
       <c r="H78">
         <v>5</v>
@@ -8551,7 +14110,7 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>403</v>
+        <v>727</v>
       </c>
       <c r="B79" t="s">
         <v>138</v>
@@ -8560,7 +14119,7 @@
         <v>44</v>
       </c>
       <c r="D79" t="s">
-        <v>394</v>
+        <v>719</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -8569,7 +14128,7 @@
         <v>8</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>404</v>
+        <v>728</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -8583,7 +14142,7 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>405</v>
+        <v>729</v>
       </c>
       <c r="B80" t="s">
         <v>138</v>
@@ -8592,7 +14151,7 @@
         <v>166</v>
       </c>
       <c r="D80" t="s">
-        <v>302</v>
+        <v>628</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -8601,7 +14160,7 @@
         <v>8</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>406</v>
+        <v>730</v>
       </c>
       <c r="H80">
         <v>5</v>
@@ -8615,7 +14174,7 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>407</v>
+        <v>731</v>
       </c>
       <c r="B81" t="s">
         <v>138</v>
@@ -8624,7 +14183,7 @@
         <v>44</v>
       </c>
       <c r="D81" t="s">
-        <v>399</v>
+        <v>724</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -8633,7 +14192,7 @@
         <v>8</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>400</v>
+        <v>725</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -8647,7 +14206,7 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>408</v>
+        <v>732</v>
       </c>
       <c r="B82" t="s">
         <v>138</v>
@@ -8656,7 +14215,7 @@
         <v>72</v>
       </c>
       <c r="D82" t="s">
-        <v>359</v>
+        <v>684</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -8665,7 +14224,7 @@
         <v>8</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>402</v>
+        <v>519</v>
       </c>
       <c r="H82">
         <v>5</v>
@@ -8679,10 +14238,10 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>409</v>
+        <v>733</v>
       </c>
       <c r="B83" t="s">
-        <v>342</v>
+        <v>667</v>
       </c>
       <c r="C83" t="s">
         <v>8</v>
@@ -8697,7 +14256,7 @@
         <v>8</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>343</v>
+        <v>668</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -8711,7 +14270,7 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>410</v>
+        <v>734</v>
       </c>
       <c r="B84" t="s">
         <v>138</v>
@@ -8720,7 +14279,7 @@
         <v>44</v>
       </c>
       <c r="D84" t="s">
-        <v>394</v>
+        <v>719</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -8729,7 +14288,7 @@
         <v>8</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>411</v>
+        <v>735</v>
       </c>
       <c r="H84">
         <v>18</v>
@@ -8743,7 +14302,7 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>412</v>
+        <v>736</v>
       </c>
       <c r="B85" t="s">
         <v>138</v>
@@ -8752,7 +14311,7 @@
         <v>166</v>
       </c>
       <c r="D85" t="s">
-        <v>302</v>
+        <v>628</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -8761,7 +14320,7 @@
         <v>8</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>413</v>
+        <v>737</v>
       </c>
       <c r="H85">
         <v>8</v>
@@ -8775,7 +14334,7 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>414</v>
+        <v>738</v>
       </c>
       <c r="B86" t="s">
         <v>138</v>
@@ -8784,7 +14343,7 @@
         <v>44</v>
       </c>
       <c r="D86" t="s">
-        <v>399</v>
+        <v>724</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -8793,7 +14352,7 @@
         <v>8</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>400</v>
+        <v>725</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -8807,7 +14366,7 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>415</v>
+        <v>739</v>
       </c>
       <c r="B87" t="s">
         <v>138</v>
@@ -8816,7 +14375,7 @@
         <v>72</v>
       </c>
       <c r="D87" t="s">
-        <v>359</v>
+        <v>684</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -8825,7 +14384,7 @@
         <v>8</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>402</v>
+        <v>519</v>
       </c>
       <c r="H87">
         <v>5</v>
@@ -8839,7 +14398,7 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>416</v>
+        <v>740</v>
       </c>
       <c r="B88" t="s">
         <v>138</v>
@@ -8848,7 +14407,7 @@
         <v>171</v>
       </c>
       <c r="D88" t="s">
-        <v>300</v>
+        <v>626</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -8857,7 +14416,7 @@
         <v>8</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>417</v>
+        <v>582</v>
       </c>
       <c r="H88">
         <v>2</v>
@@ -8871,7 +14430,7 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>418</v>
+        <v>741</v>
       </c>
       <c r="B89" t="s">
         <v>138</v>
@@ -8880,7 +14439,7 @@
         <v>169</v>
       </c>
       <c r="D89" t="s">
-        <v>304</v>
+        <v>630</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -8889,7 +14448,7 @@
         <v>8</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>419</v>
+        <v>742</v>
       </c>
       <c r="H89">
         <v>2</v>
@@ -8903,7 +14462,7 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>420</v>
+        <v>743</v>
       </c>
       <c r="B90" t="s">
         <v>138</v>
@@ -8912,7 +14471,7 @@
         <v>72</v>
       </c>
       <c r="D90" t="s">
-        <v>306</v>
+        <v>632</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -8921,7 +14480,7 @@
         <v>8</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>421</v>
+        <v>744</v>
       </c>
       <c r="H90">
         <v>6</v>
@@ -8935,7 +14494,7 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>422</v>
+        <v>745</v>
       </c>
       <c r="B91" t="s">
         <v>138</v>
@@ -8944,7 +14503,7 @@
         <v>171</v>
       </c>
       <c r="D91" t="s">
-        <v>300</v>
+        <v>626</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -8953,7 +14512,7 @@
         <v>8</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>423</v>
+        <v>746</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -8967,7 +14526,7 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>424</v>
+        <v>747</v>
       </c>
       <c r="B92" t="s">
         <v>138</v>
@@ -8976,7 +14535,7 @@
         <v>169</v>
       </c>
       <c r="D92" t="s">
-        <v>304</v>
+        <v>630</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -8985,7 +14544,7 @@
         <v>8</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>425</v>
+        <v>748</v>
       </c>
       <c r="H92">
         <v>5</v>
@@ -8999,7 +14558,7 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>426</v>
+        <v>749</v>
       </c>
       <c r="B93" t="s">
         <v>138</v>
@@ -9008,7 +14567,7 @@
         <v>72</v>
       </c>
       <c r="D93" t="s">
-        <v>306</v>
+        <v>632</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -9017,7 +14576,7 @@
         <v>8</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>427</v>
+        <v>750</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -9031,7 +14590,7 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>428</v>
+        <v>751</v>
       </c>
       <c r="B94" t="s">
         <v>138</v>
@@ -9040,7 +14599,7 @@
         <v>171</v>
       </c>
       <c r="D94" t="s">
-        <v>300</v>
+        <v>626</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -9049,7 +14608,7 @@
         <v>8</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>429</v>
+        <v>586</v>
       </c>
       <c r="H94">
         <v>4</v>
@@ -9063,7 +14622,7 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>430</v>
+        <v>752</v>
       </c>
       <c r="B95" t="s">
         <v>138</v>
@@ -9072,7 +14631,7 @@
         <v>169</v>
       </c>
       <c r="D95" t="s">
-        <v>304</v>
+        <v>630</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -9081,7 +14640,7 @@
         <v>8</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>425</v>
+        <v>748</v>
       </c>
       <c r="H95">
         <v>5</v>
@@ -9095,7 +14654,7 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>431</v>
+        <v>753</v>
       </c>
       <c r="B96" t="s">
         <v>138</v>
@@ -9104,7 +14663,7 @@
         <v>72</v>
       </c>
       <c r="D96" t="s">
-        <v>306</v>
+        <v>632</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -9113,7 +14672,7 @@
         <v>8</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>427</v>
+        <v>750</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -9127,7 +14686,7 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>432</v>
+        <v>754</v>
       </c>
       <c r="B97" t="s">
         <v>138</v>
@@ -9136,7 +14695,7 @@
         <v>166</v>
       </c>
       <c r="D97" t="s">
-        <v>302</v>
+        <v>628</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -9145,7 +14704,7 @@
         <v>8</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>433</v>
+        <v>755</v>
       </c>
       <c r="H97">
         <v>6</v>
@@ -9159,10 +14718,10 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>434</v>
+        <v>756</v>
       </c>
       <c r="B98" t="s">
-        <v>342</v>
+        <v>667</v>
       </c>
       <c r="C98" t="s">
         <v>8</v>
@@ -9177,7 +14736,7 @@
         <v>8</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>343</v>
+        <v>668</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -9191,7 +14750,7 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>435</v>
+        <v>757</v>
       </c>
       <c r="B99" t="s">
         <v>138</v>
@@ -9200,7 +14759,7 @@
         <v>169</v>
       </c>
       <c r="D99" t="s">
-        <v>304</v>
+        <v>630</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -9209,7 +14768,7 @@
         <v>8</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>436</v>
+        <v>758</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -9223,7 +14782,7 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>437</v>
+        <v>759</v>
       </c>
       <c r="B100" t="s">
         <v>138</v>
@@ -9232,7 +14791,7 @@
         <v>72</v>
       </c>
       <c r="D100" t="s">
-        <v>306</v>
+        <v>632</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
@@ -9241,7 +14800,7 @@
         <v>8</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>438</v>
+        <v>760</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -9255,7 +14814,7 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>439</v>
+        <v>761</v>
       </c>
       <c r="B101" t="s">
         <v>138</v>
@@ -9264,7 +14823,7 @@
         <v>166</v>
       </c>
       <c r="D101" t="s">
-        <v>302</v>
+        <v>628</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -9273,7 +14832,7 @@
         <v>8</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>440</v>
+        <v>762</v>
       </c>
       <c r="H101">
         <v>8</v>
@@ -9287,7 +14846,7 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>441</v>
+        <v>763</v>
       </c>
       <c r="B102" t="s">
         <v>138</v>
@@ -9296,7 +14855,7 @@
         <v>72</v>
       </c>
       <c r="D102" t="s">
-        <v>306</v>
+        <v>632</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -9305,7 +14864,7 @@
         <v>8</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>442</v>
+        <v>764</v>
       </c>
       <c r="H102">
         <v>8</v>
@@ -9319,7 +14878,7 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>443</v>
+        <v>765</v>
       </c>
       <c r="B103" t="s">
         <v>138</v>
@@ -9328,7 +14887,7 @@
         <v>169</v>
       </c>
       <c r="D103" t="s">
-        <v>304</v>
+        <v>630</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -9337,7 +14896,7 @@
         <v>8</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>444</v>
+        <v>766</v>
       </c>
       <c r="H103">
         <v>5</v>
@@ -9351,10 +14910,10 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>445</v>
+        <v>767</v>
       </c>
       <c r="B104" t="s">
-        <v>342</v>
+        <v>667</v>
       </c>
       <c r="C104" t="s">
         <v>8</v>
@@ -9369,7 +14928,7 @@
         <v>8</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>446</v>
+        <v>768</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -9383,7 +14942,7 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>447</v>
+        <v>769</v>
       </c>
       <c r="B105" t="s">
         <v>138</v>
@@ -9392,7 +14951,7 @@
         <v>166</v>
       </c>
       <c r="D105" t="s">
-        <v>302</v>
+        <v>628</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -9401,7 +14960,7 @@
         <v>8</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>448</v>
+        <v>770</v>
       </c>
       <c r="H105">
         <v>11</v>
@@ -9415,7 +14974,7 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>449</v>
+        <v>771</v>
       </c>
       <c r="B106" t="s">
         <v>138</v>
@@ -9424,7 +14983,7 @@
         <v>72</v>
       </c>
       <c r="D106" t="s">
-        <v>306</v>
+        <v>632</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -9433,7 +14992,7 @@
         <v>8</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>450</v>
+        <v>552</v>
       </c>
       <c r="H106">
         <v>10</v>
@@ -9447,7 +15006,7 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>451</v>
+        <v>772</v>
       </c>
       <c r="B107" t="s">
         <v>138</v>
@@ -9456,7 +15015,7 @@
         <v>169</v>
       </c>
       <c r="D107" t="s">
-        <v>304</v>
+        <v>630</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -9465,7 +15024,7 @@
         <v>8</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>452</v>
+        <v>773</v>
       </c>
       <c r="H107">
         <v>6</v>
@@ -9479,7 +15038,7 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>453</v>
+        <v>774</v>
       </c>
       <c r="B108" t="s">
         <v>138</v>
@@ -9488,7 +15047,7 @@
         <v>169</v>
       </c>
       <c r="D108" t="s">
-        <v>304</v>
+        <v>630</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -9497,7 +15056,7 @@
         <v>8</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>436</v>
+        <v>758</v>
       </c>
       <c r="H108">
         <v>1</v>
@@ -9511,7 +15070,7 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>454</v>
+        <v>775</v>
       </c>
       <c r="B109" t="s">
         <v>138</v>
@@ -9520,7 +15079,7 @@
         <v>171</v>
       </c>
       <c r="D109" t="s">
-        <v>300</v>
+        <v>626</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -9529,7 +15088,7 @@
         <v>8</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>455</v>
+        <v>776</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -9543,7 +15102,7 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>456</v>
+        <v>777</v>
       </c>
       <c r="B110" t="s">
         <v>138</v>
@@ -9552,7 +15111,7 @@
         <v>44</v>
       </c>
       <c r="D110" t="s">
-        <v>457</v>
+        <v>778</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -9561,7 +15120,7 @@
         <v>8</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>458</v>
+        <v>346</v>
       </c>
       <c r="H110">
         <v>7</v>
@@ -9575,7 +15134,7 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>459</v>
+        <v>779</v>
       </c>
       <c r="B111" t="s">
         <v>138</v>
@@ -9584,7 +15143,7 @@
         <v>44</v>
       </c>
       <c r="D111" t="s">
-        <v>399</v>
+        <v>724</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -9593,7 +15152,7 @@
         <v>8</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>460</v>
+        <v>348</v>
       </c>
       <c r="H111">
         <v>8</v>
@@ -9607,7 +15166,7 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>461</v>
+        <v>780</v>
       </c>
       <c r="B112" t="s">
         <v>138</v>
@@ -9616,7 +15175,7 @@
         <v>171</v>
       </c>
       <c r="D112" t="s">
-        <v>300</v>
+        <v>626</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -9625,7 +15184,7 @@
         <v>8</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>462</v>
+        <v>781</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -9639,7 +15198,7 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>463</v>
+        <v>782</v>
       </c>
       <c r="B113" t="s">
         <v>138</v>
@@ -9648,7 +15207,7 @@
         <v>169</v>
       </c>
       <c r="D113" t="s">
-        <v>304</v>
+        <v>630</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -9657,7 +15216,7 @@
         <v>8</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>444</v>
+        <v>766</v>
       </c>
       <c r="H113">
         <v>5</v>
@@ -9671,7 +15230,7 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>464</v>
+        <v>783</v>
       </c>
       <c r="B114" t="s">
         <v>138</v>
@@ -9680,7 +15239,7 @@
         <v>171</v>
       </c>
       <c r="D114" t="s">
-        <v>300</v>
+        <v>626</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -9689,7 +15248,7 @@
         <v>8</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>462</v>
+        <v>781</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -9703,7 +15262,7 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>465</v>
+        <v>784</v>
       </c>
       <c r="B115" t="s">
         <v>138</v>
@@ -9712,7 +15271,7 @@
         <v>44</v>
       </c>
       <c r="D115" t="s">
-        <v>457</v>
+        <v>778</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -9721,7 +15280,7 @@
         <v>8</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>466</v>
+        <v>785</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -9735,7 +15294,7 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>467</v>
+        <v>786</v>
       </c>
       <c r="B116" t="s">
         <v>138</v>
@@ -9744,7 +15303,7 @@
         <v>169</v>
       </c>
       <c r="D116" t="s">
-        <v>304</v>
+        <v>630</v>
       </c>
       <c r="E116" t="s">
         <v>8</v>
@@ -9753,7 +15312,7 @@
         <v>8</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>452</v>
+        <v>773</v>
       </c>
       <c r="H116">
         <v>6</v>
@@ -9767,7 +15326,7 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>468</v>
+        <v>787</v>
       </c>
       <c r="B117" t="s">
         <v>138</v>
@@ -9776,7 +15335,7 @@
         <v>166</v>
       </c>
       <c r="D117" t="s">
-        <v>302</v>
+        <v>628</v>
       </c>
       <c r="E117" t="s">
         <v>8</v>
@@ -9799,7 +15358,7 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>469</v>
+        <v>788</v>
       </c>
       <c r="B118" t="s">
         <v>138</v>
@@ -9808,7 +15367,7 @@
         <v>72</v>
       </c>
       <c r="D118" t="s">
-        <v>306</v>
+        <v>632</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -9831,7 +15390,7 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>470</v>
+        <v>789</v>
       </c>
       <c r="B119" t="s">
         <v>138</v>
@@ -9840,7 +15399,7 @@
         <v>44</v>
       </c>
       <c r="D119" t="s">
-        <v>308</v>
+        <v>634</v>
       </c>
       <c r="E119" t="s">
         <v>8</v>
@@ -9849,7 +15408,7 @@
         <v>8</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>471</v>
+        <v>790</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -9863,7 +15422,7 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>472</v>
+        <v>791</v>
       </c>
       <c r="B120" t="s">
         <v>138</v>
@@ -9872,7 +15431,7 @@
         <v>44</v>
       </c>
       <c r="D120" t="s">
-        <v>308</v>
+        <v>634</v>
       </c>
       <c r="E120" t="s">
         <v>8</v>
@@ -9881,7 +15440,7 @@
         <v>8</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>473</v>
+        <v>792</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -9895,7 +15454,7 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>474</v>
+        <v>793</v>
       </c>
       <c r="B121" t="s">
         <v>138</v>
@@ -9904,7 +15463,7 @@
         <v>171</v>
       </c>
       <c r="D121" t="s">
-        <v>300</v>
+        <v>626</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
@@ -9913,7 +15472,7 @@
         <v>8</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>475</v>
+        <v>794</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -9927,7 +15486,7 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>476</v>
+        <v>795</v>
       </c>
       <c r="B122" t="s">
         <v>138</v>
@@ -9936,7 +15495,7 @@
         <v>169</v>
       </c>
       <c r="D122" t="s">
-        <v>304</v>
+        <v>630</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>

--- a/content/jahrgaenge/Jg6.xlsx
+++ b/content/jahrgaenge/Jg6.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2996" uniqueCount="796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3156" uniqueCount="843">
   <si>
     <t>Hinweise zu Jg6.xlsx</t>
   </si>
@@ -676,6 +676,9 @@
     <t>Ocean City ODER Herr der Diebe</t>
   </si>
   <si>
+    <t>Ocean City: Flipbook als Lektürebegleitung. Herr der Diebe: Eine Textstelle umschreiben</t>
+  </si>
+  <si>
     <t>Peacemakers</t>
   </si>
   <si>
@@ -1876,6 +1879,9 @@
     <t>Laptop, Material zum Vulkanbau</t>
   </si>
   <si>
+    <t>Eine der beiden Wahlaufgaben (Station 10 oder 11) musst du machen.</t>
+  </si>
+  <si>
     <t>Wahlaufgabe Gebirgsbildung</t>
   </si>
   <si>
@@ -1892,6 +1898,141 @@
   </si>
   <si>
     <t>Showtime</t>
+  </si>
+  <si>
+    <t>Das Flipbook</t>
+  </si>
+  <si>
+    <t>Flipbook-Vorlage</t>
+  </si>
+  <si>
+    <t>Nur für Ocean City.</t>
+  </si>
+  <si>
+    <t>Der erste Eindruck</t>
+  </si>
+  <si>
+    <t>Flipbook</t>
+  </si>
+  <si>
+    <t>Ist das so richtig?</t>
+  </si>
+  <si>
+    <t>Mega-Floating-City: Ocean City</t>
+  </si>
+  <si>
+    <t>Flipbook, M1</t>
+  </si>
+  <si>
+    <t>Jackson, Crockie &amp; Henk</t>
+  </si>
+  <si>
+    <t>Macht durch Kontrolle</t>
+  </si>
+  <si>
+    <t>Zeit ist Geld</t>
+  </si>
+  <si>
+    <t>Beweg dich!</t>
+  </si>
+  <si>
+    <t>Der Transponder &amp; andere Erfindungen</t>
+  </si>
+  <si>
+    <t>Die Große Zeremonie</t>
+  </si>
+  <si>
+    <t>Flipbook, M2</t>
+  </si>
+  <si>
+    <t>Schulkleidung</t>
+  </si>
+  <si>
+    <t>Kommando „Matt Fuller“</t>
+  </si>
+  <si>
+    <t>Der Verrat</t>
+  </si>
+  <si>
+    <t>Die Rollen des Clark Kellington</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>Die Personenkonstellation</t>
+  </si>
+  <si>
+    <t>Der Autor &amp; der Cliffhanger</t>
+  </si>
+  <si>
+    <t>Flipbook, Laptop</t>
+  </si>
+  <si>
+    <t>Du bist dran!</t>
+  </si>
+  <si>
+    <t>weißes A4-Blatt</t>
+  </si>
+  <si>
+    <t>Eine Rezension schreiben</t>
+  </si>
+  <si>
+    <t>Flipbook, A3</t>
+  </si>
+  <si>
+    <t>Venedig</t>
+  </si>
+  <si>
+    <t>Laptop, Venedig-Quiz</t>
+  </si>
+  <si>
+    <t>Nur für Herr der Diebe.</t>
+  </si>
+  <si>
+    <t>Ein Auftrag für Victor und eine Kinderbande</t>
+  </si>
+  <si>
+    <t>Lektüre</t>
+  </si>
+  <si>
+    <t>Ein Auftrag für den Herrn der Diebe</t>
+  </si>
+  <si>
+    <t>Victor und die Kinder</t>
+  </si>
+  <si>
+    <t>Der Umschlag des Conte &amp; Victor in der Falle</t>
+  </si>
+  <si>
+    <t>Wut, Streit und ein Ehrenwort</t>
+  </si>
+  <si>
+    <t>Der Einbruch und eine alte Geschichte</t>
+  </si>
+  <si>
+    <t>Treffen mit dem Conte und die Geheime Insel &amp; Alles verloren?</t>
+  </si>
+  <si>
+    <t>Das Karussell &amp; Wie alle ein Zuhause finden</t>
+  </si>
+  <si>
+    <t>Die Vogelmaske</t>
+  </si>
+  <si>
+    <t>Detektivarbeit</t>
+  </si>
+  <si>
+    <t>Das Karussell</t>
+  </si>
+  <si>
+    <t>Alternatives Buchcover</t>
+  </si>
+  <si>
+    <t>Einen Erzähltext in eine Szene umschreiben</t>
+  </si>
+  <si>
+    <t>Lektüre, Laptop</t>
   </si>
   <si>
     <t>2026-08-24</t>
@@ -5401,7 +5542,7 @@
         <v>217</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="F14" t="s">
         <v>8</v>
@@ -5421,13 +5562,13 @@
         <v>169</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F15">
         <v>16</v>
@@ -5447,13 +5588,13 @@
         <v>171</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F16">
         <v>11</v>
@@ -5473,13 +5614,13 @@
         <v>169</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F17" t="s">
         <v>8</v>
@@ -5499,7 +5640,7 @@
         <v>166</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>8</v>
@@ -5525,13 +5666,13 @@
         <v>72</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F19" t="s">
         <v>8</v>
@@ -5551,13 +5692,13 @@
         <v>44</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F20" t="s">
         <v>8</v>
@@ -5577,13 +5718,13 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F21" t="s">
         <v>8</v>
@@ -5603,13 +5744,13 @@
         <v>44</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F22" t="s">
         <v>8</v>
@@ -5629,7 +5770,7 @@
         <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>8</v>
@@ -5655,7 +5796,7 @@
         <v>72</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>8</v>
@@ -5707,13 +5848,13 @@
         <v>171</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F26" t="s">
         <v>8</v>
@@ -5742,7 +5883,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H220"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -5787,7 +5928,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D2" t="s">
         <v>93</v>
@@ -5799,7 +5940,7 @@
         <v>2</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>8</v>
@@ -5813,7 +5954,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D3" t="s">
         <v>182</v>
@@ -5825,7 +5966,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>8</v>
@@ -5839,7 +5980,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D4" t="s">
         <v>93</v>
@@ -5851,7 +5992,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>8</v>
@@ -5865,7 +6006,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D5" t="s">
         <v>93</v>
@@ -5877,7 +6018,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>8</v>
@@ -5891,7 +6032,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D6" t="s">
         <v>93</v>
@@ -5903,7 +6044,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>8</v>
@@ -5917,7 +6058,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D7" t="s">
         <v>182</v>
@@ -5929,7 +6070,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>8</v>
@@ -5943,7 +6084,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D8" t="s">
         <v>93</v>
@@ -5955,7 +6096,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>8</v>
@@ -5969,7 +6110,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D9" t="s">
         <v>93</v>
@@ -5981,7 +6122,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>8</v>
@@ -5995,7 +6136,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D10" t="s">
         <v>93</v>
@@ -6007,7 +6148,7 @@
         <v>3</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>8</v>
@@ -6021,7 +6162,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D11" t="s">
         <v>93</v>
@@ -6033,7 +6174,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>8</v>
@@ -6047,7 +6188,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D12" t="s">
         <v>93</v>
@@ -6059,7 +6200,7 @@
         <v>3</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>8</v>
@@ -6073,7 +6214,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D13" t="s">
         <v>182</v>
@@ -6085,7 +6226,7 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>8</v>
@@ -6099,7 +6240,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
         <v>93</v>
@@ -6111,7 +6252,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>8</v>
@@ -6125,7 +6266,7 @@
         <v>2</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D15" t="s">
         <v>93</v>
@@ -6137,7 +6278,7 @@
         <v>2</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>8</v>
@@ -6151,7 +6292,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D16" t="s">
         <v>93</v>
@@ -6163,7 +6304,7 @@
         <v>2</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>8</v>
@@ -6177,7 +6318,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D17" t="s">
         <v>93</v>
@@ -6189,7 +6330,7 @@
         <v>2</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>8</v>
@@ -6203,7 +6344,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D18" t="s">
         <v>93</v>
@@ -6215,7 +6356,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>8</v>
@@ -6229,7 +6370,7 @@
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D19" t="s">
         <v>93</v>
@@ -6241,7 +6382,7 @@
         <v>2</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>8</v>
@@ -6255,7 +6396,7 @@
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D20" t="s">
         <v>182</v>
@@ -6267,7 +6408,7 @@
         <v>2</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>8</v>
@@ -6281,7 +6422,7 @@
         <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D21" t="s">
         <v>93</v>
@@ -6293,7 +6434,7 @@
         <v>2</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>8</v>
@@ -6307,7 +6448,7 @@
         <v>9</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D22" t="s">
         <v>93</v>
@@ -6319,7 +6460,7 @@
         <v>3</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>8</v>
@@ -6333,7 +6474,7 @@
         <v>10</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D23" t="s">
         <v>93</v>
@@ -6345,7 +6486,7 @@
         <v>2</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>8</v>
@@ -6359,7 +6500,7 @@
         <v>11</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D24" t="s">
         <v>93</v>
@@ -6371,7 +6512,7 @@
         <v>3</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>8</v>
@@ -6397,7 +6538,7 @@
         <v>3</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>8</v>
@@ -6411,7 +6552,7 @@
         <v>13</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D26" t="s">
         <v>93</v>
@@ -6437,7 +6578,7 @@
         <v>14</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D27" t="s">
         <v>93</v>
@@ -6449,7 +6590,7 @@
         <v>3</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>8</v>
@@ -6463,7 +6604,7 @@
         <v>15</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D28" t="s">
         <v>93</v>
@@ -6475,7 +6616,7 @@
         <v>3</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>8</v>
@@ -6489,7 +6630,7 @@
         <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D29" t="s">
         <v>182</v>
@@ -6515,7 +6656,7 @@
         <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D30" t="s">
         <v>182</v>
@@ -6541,7 +6682,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D31" t="s">
         <v>93</v>
@@ -6553,7 +6694,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>8</v>
@@ -6567,7 +6708,7 @@
         <v>2</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D32" t="s">
         <v>93</v>
@@ -6579,7 +6720,7 @@
         <v>2</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>8</v>
@@ -6593,7 +6734,7 @@
         <v>3</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D33" t="s">
         <v>93</v>
@@ -6605,7 +6746,7 @@
         <v>2</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>8</v>
@@ -6619,7 +6760,7 @@
         <v>4</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D34" t="s">
         <v>93</v>
@@ -6631,7 +6772,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>8</v>
@@ -6645,7 +6786,7 @@
         <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D35" t="s">
         <v>93</v>
@@ -6657,7 +6798,7 @@
         <v>2</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>8</v>
@@ -6671,7 +6812,7 @@
         <v>6</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D36" t="s">
         <v>182</v>
@@ -6683,7 +6824,7 @@
         <v>2</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>8</v>
@@ -6697,7 +6838,7 @@
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D37" t="s">
         <v>93</v>
@@ -6709,7 +6850,7 @@
         <v>2</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>8</v>
@@ -6723,7 +6864,7 @@
         <v>8</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D38" t="s">
         <v>93</v>
@@ -6735,7 +6876,7 @@
         <v>2</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>8</v>
@@ -6749,7 +6890,7 @@
         <v>9</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D39" t="s">
         <v>93</v>
@@ -6761,7 +6902,7 @@
         <v>3</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>8</v>
@@ -6787,7 +6928,7 @@
         <v>3</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>8</v>
@@ -6813,7 +6954,7 @@
         <v>3</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>8</v>
@@ -6827,7 +6968,7 @@
         <v>12</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D42" t="s">
         <v>182</v>
@@ -6839,7 +6980,7 @@
         <v>2</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>8</v>
@@ -6853,7 +6994,7 @@
         <v>13</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D43" t="s">
         <v>93</v>
@@ -6865,7 +7006,7 @@
         <v>2</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>8</v>
@@ -6879,7 +7020,7 @@
         <v>1</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D44" t="s">
         <v>93</v>
@@ -6891,7 +7032,7 @@
         <v>1</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>8</v>
@@ -6905,7 +7046,7 @@
         <v>2</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D45" t="s">
         <v>93</v>
@@ -6917,7 +7058,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>8</v>
@@ -6931,7 +7072,7 @@
         <v>3</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D46" t="s">
         <v>93</v>
@@ -6943,7 +7084,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>8</v>
@@ -6957,7 +7098,7 @@
         <v>4</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D47" t="s">
         <v>182</v>
@@ -6969,7 +7110,7 @@
         <v>1</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>8</v>
@@ -6983,7 +7124,7 @@
         <v>5</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D48" t="s">
         <v>93</v>
@@ -6995,7 +7136,7 @@
         <v>2</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>8</v>
@@ -7009,7 +7150,7 @@
         <v>6</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D49" t="s">
         <v>93</v>
@@ -7021,7 +7162,7 @@
         <v>2</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>8</v>
@@ -7035,7 +7176,7 @@
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D50" t="s">
         <v>93</v>
@@ -7047,7 +7188,7 @@
         <v>2</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>8</v>
@@ -7061,7 +7202,7 @@
         <v>8</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D51" t="s">
         <v>93</v>
@@ -7073,7 +7214,7 @@
         <v>3</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>8</v>
@@ -7087,7 +7228,7 @@
         <v>9</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D52" t="s">
         <v>93</v>
@@ -7099,7 +7240,7 @@
         <v>3</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>8</v>
@@ -7113,7 +7254,7 @@
         <v>10</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D53" t="s">
         <v>182</v>
@@ -7125,7 +7266,7 @@
         <v>2</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>8</v>
@@ -7139,7 +7280,7 @@
         <v>11</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D54" t="s">
         <v>93</v>
@@ -7151,10 +7292,10 @@
         <v>3</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -7165,7 +7306,7 @@
         <v>12</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D55" t="s">
         <v>182</v>
@@ -7177,7 +7318,7 @@
         <v>3</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>8</v>
@@ -7191,7 +7332,7 @@
         <v>13</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D56" t="s">
         <v>93</v>
@@ -7203,7 +7344,7 @@
         <v>3</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>8</v>
@@ -7217,7 +7358,7 @@
         <v>1</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D57" t="s">
         <v>93</v>
@@ -7229,7 +7370,7 @@
         <v>2</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>8</v>
@@ -7243,7 +7384,7 @@
         <v>2</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D58" t="s">
         <v>182</v>
@@ -7255,7 +7396,7 @@
         <v>1</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>8</v>
@@ -7269,7 +7410,7 @@
         <v>3</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D59" t="s">
         <v>93</v>
@@ -7281,7 +7422,7 @@
         <v>2</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>8</v>
@@ -7295,7 +7436,7 @@
         <v>4</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D60" t="s">
         <v>182</v>
@@ -7307,7 +7448,7 @@
         <v>1</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>8</v>
@@ -7321,7 +7462,7 @@
         <v>5</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D61" t="s">
         <v>93</v>
@@ -7333,7 +7474,7 @@
         <v>2</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>8</v>
@@ -7347,7 +7488,7 @@
         <v>6</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D62" t="s">
         <v>93</v>
@@ -7359,7 +7500,7 @@
         <v>1</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>8</v>
@@ -7373,7 +7514,7 @@
         <v>7</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D63" t="s">
         <v>93</v>
@@ -7385,7 +7526,7 @@
         <v>2</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>8</v>
@@ -7399,7 +7540,7 @@
         <v>8</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D64" t="s">
         <v>93</v>
@@ -7411,7 +7552,7 @@
         <v>2</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>8</v>
@@ -7425,7 +7566,7 @@
         <v>9</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D65" t="s">
         <v>93</v>
@@ -7437,7 +7578,7 @@
         <v>3</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>8</v>
@@ -7451,7 +7592,7 @@
         <v>10</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D66" t="s">
         <v>182</v>
@@ -7463,7 +7604,7 @@
         <v>1</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>8</v>
@@ -7477,7 +7618,7 @@
         <v>11</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D67" t="s">
         <v>93</v>
@@ -7489,7 +7630,7 @@
         <v>1</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>8</v>
@@ -7503,7 +7644,7 @@
         <v>12</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D68" t="s">
         <v>93</v>
@@ -7515,7 +7656,7 @@
         <v>2</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>8</v>
@@ -7529,7 +7670,7 @@
         <v>13</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D69" t="s">
         <v>93</v>
@@ -7541,7 +7682,7 @@
         <v>3</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>8</v>
@@ -7555,7 +7696,7 @@
         <v>14</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D70" t="s">
         <v>93</v>
@@ -7567,7 +7708,7 @@
         <v>3</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>8</v>
@@ -7581,7 +7722,7 @@
         <v>1</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D71" t="s">
         <v>93</v>
@@ -7593,7 +7734,7 @@
         <v>1</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>8</v>
@@ -7607,7 +7748,7 @@
         <v>2</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D72" t="s">
         <v>93</v>
@@ -7619,7 +7760,7 @@
         <v>2</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>8</v>
@@ -7633,7 +7774,7 @@
         <v>3</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D73" t="s">
         <v>182</v>
@@ -7645,7 +7786,7 @@
         <v>2</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>8</v>
@@ -7659,7 +7800,7 @@
         <v>4</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D74" t="s">
         <v>93</v>
@@ -7671,7 +7812,7 @@
         <v>2</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>8</v>
@@ -7685,7 +7826,7 @@
         <v>5</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D75" t="s">
         <v>93</v>
@@ -7697,7 +7838,7 @@
         <v>2</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>8</v>
@@ -7711,7 +7852,7 @@
         <v>6</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D76" t="s">
         <v>93</v>
@@ -7723,7 +7864,7 @@
         <v>2</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>8</v>
@@ -7737,7 +7878,7 @@
         <v>7</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D77" t="s">
         <v>182</v>
@@ -7749,7 +7890,7 @@
         <v>3</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>8</v>
@@ -7763,7 +7904,7 @@
         <v>8</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D78" t="s">
         <v>93</v>
@@ -7775,7 +7916,7 @@
         <v>2</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>8</v>
@@ -7789,7 +7930,7 @@
         <v>1</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D79" t="s">
         <v>93</v>
@@ -7801,7 +7942,7 @@
         <v>1</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>8</v>
@@ -7815,7 +7956,7 @@
         <v>2</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D80" t="s">
         <v>93</v>
@@ -7827,7 +7968,7 @@
         <v>2</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>8</v>
@@ -7841,7 +7982,7 @@
         <v>3</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D81" t="s">
         <v>93</v>
@@ -7853,7 +7994,7 @@
         <v>1</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>8</v>
@@ -7867,7 +8008,7 @@
         <v>4</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D82" t="s">
         <v>93</v>
@@ -7879,7 +8020,7 @@
         <v>1</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>8</v>
@@ -7893,7 +8034,7 @@
         <v>5</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D83" t="s">
         <v>182</v>
@@ -7905,7 +8046,7 @@
         <v>3</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>8</v>
@@ -7919,7 +8060,7 @@
         <v>6</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D84" t="s">
         <v>93</v>
@@ -7931,7 +8072,7 @@
         <v>3</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>8</v>
@@ -7945,7 +8086,7 @@
         <v>7</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D85" t="s">
         <v>93</v>
@@ -7957,7 +8098,7 @@
         <v>3</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>8</v>
@@ -7971,7 +8112,7 @@
         <v>8</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D86" t="s">
         <v>93</v>
@@ -7983,7 +8124,7 @@
         <v>2</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>8</v>
@@ -7997,7 +8138,7 @@
         <v>9</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D87" t="s">
         <v>93</v>
@@ -8009,7 +8150,7 @@
         <v>2</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>8</v>
@@ -8023,7 +8164,7 @@
         <v>10</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D88" t="s">
         <v>182</v>
@@ -8035,7 +8176,7 @@
         <v>2</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>8</v>
@@ -8049,7 +8190,7 @@
         <v>11</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D89" t="s">
         <v>93</v>
@@ -8061,7 +8202,7 @@
         <v>1</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>8</v>
@@ -8075,7 +8216,7 @@
         <v>12</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D90" t="s">
         <v>93</v>
@@ -8087,7 +8228,7 @@
         <v>3</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>8</v>
@@ -8101,7 +8242,7 @@
         <v>13</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D91" t="s">
         <v>93</v>
@@ -8127,7 +8268,7 @@
         <v>14</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D92" t="s">
         <v>93</v>
@@ -8139,7 +8280,7 @@
         <v>1</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>8</v>
@@ -8153,7 +8294,7 @@
         <v>15</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D93" t="s">
         <v>93</v>
@@ -8165,7 +8306,7 @@
         <v>3</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>8</v>
@@ -8179,7 +8320,7 @@
         <v>16</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D94" t="s">
         <v>93</v>
@@ -8191,7 +8332,7 @@
         <v>2</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>8</v>
@@ -8205,7 +8346,7 @@
         <v>1</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D95" t="s">
         <v>93</v>
@@ -8217,7 +8358,7 @@
         <v>2</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>8</v>
@@ -8231,7 +8372,7 @@
         <v>2</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D96" t="s">
         <v>93</v>
@@ -8243,7 +8384,7 @@
         <v>1</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>8</v>
@@ -8257,7 +8398,7 @@
         <v>3</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D97" t="s">
         <v>93</v>
@@ -8269,7 +8410,7 @@
         <v>1</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>8</v>
@@ -8283,7 +8424,7 @@
         <v>4</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D98" t="s">
         <v>93</v>
@@ -8295,7 +8436,7 @@
         <v>1</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>8</v>
@@ -8309,7 +8450,7 @@
         <v>5</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D99" t="s">
         <v>93</v>
@@ -8321,7 +8462,7 @@
         <v>2</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>8</v>
@@ -8335,7 +8476,7 @@
         <v>6</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D100" t="s">
         <v>182</v>
@@ -8347,7 +8488,7 @@
         <v>1</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>8</v>
@@ -8361,7 +8502,7 @@
         <v>7</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D101" t="s">
         <v>93</v>
@@ -8373,7 +8514,7 @@
         <v>1</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>8</v>
@@ -8387,7 +8528,7 @@
         <v>8</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D102" t="s">
         <v>93</v>
@@ -8399,7 +8540,7 @@
         <v>1</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>8</v>
@@ -8413,7 +8554,7 @@
         <v>9</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D103" t="s">
         <v>93</v>
@@ -8425,7 +8566,7 @@
         <v>3</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>8</v>
@@ -8439,7 +8580,7 @@
         <v>10</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D104" t="s">
         <v>182</v>
@@ -8451,7 +8592,7 @@
         <v>1</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>8</v>
@@ -8465,7 +8606,7 @@
         <v>11</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D105" t="s">
         <v>93</v>
@@ -8477,7 +8618,7 @@
         <v>3</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>8</v>
@@ -8491,7 +8632,7 @@
         <v>12</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D106" t="s">
         <v>93</v>
@@ -8503,7 +8644,7 @@
         <v>3</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>8</v>
@@ -8517,7 +8658,7 @@
         <v>13</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D107" t="s">
         <v>182</v>
@@ -8529,7 +8670,7 @@
         <v>1</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>8</v>
@@ -8543,7 +8684,7 @@
         <v>14</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D108" t="s">
         <v>93</v>
@@ -8555,7 +8696,7 @@
         <v>1</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>8</v>
@@ -8569,7 +8710,7 @@
         <v>15</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D109" t="s">
         <v>182</v>
@@ -8581,7 +8722,7 @@
         <v>1</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>8</v>
@@ -8595,7 +8736,7 @@
         <v>16</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D110" t="s">
         <v>93</v>
@@ -8607,7 +8748,7 @@
         <v>2</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>8</v>
@@ -8621,7 +8762,7 @@
         <v>1</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D111" t="s">
         <v>93</v>
@@ -8633,7 +8774,7 @@
         <v>1</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>8</v>
@@ -8647,7 +8788,7 @@
         <v>2</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D112" t="s">
         <v>93</v>
@@ -8659,7 +8800,7 @@
         <v>1</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>8</v>
@@ -8673,7 +8814,7 @@
         <v>3</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D113" t="s">
         <v>93</v>
@@ -8699,7 +8840,7 @@
         <v>4</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D114" t="s">
         <v>93</v>
@@ -8711,7 +8852,7 @@
         <v>2</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>8</v>
@@ -8725,7 +8866,7 @@
         <v>5</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D115" t="s">
         <v>182</v>
@@ -8737,7 +8878,7 @@
         <v>2</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>8</v>
@@ -8751,7 +8892,7 @@
         <v>6</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D116" t="s">
         <v>93</v>
@@ -8763,7 +8904,7 @@
         <v>2</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>8</v>
@@ -8777,7 +8918,7 @@
         <v>7</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D117" t="s">
         <v>93</v>
@@ -8789,7 +8930,7 @@
         <v>2</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>8</v>
@@ -8803,7 +8944,7 @@
         <v>8</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D118" t="s">
         <v>93</v>
@@ -8815,7 +8956,7 @@
         <v>3</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>8</v>
@@ -8829,7 +8970,7 @@
         <v>9</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D119" t="s">
         <v>93</v>
@@ -8841,7 +8982,7 @@
         <v>1</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>8</v>
@@ -8855,7 +8996,7 @@
         <v>10</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D120" t="s">
         <v>93</v>
@@ -8867,7 +9008,7 @@
         <v>2</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>8</v>
@@ -8881,7 +9022,7 @@
         <v>11</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D121" t="s">
         <v>182</v>
@@ -8893,7 +9034,7 @@
         <v>3</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>8</v>
@@ -8907,7 +9048,7 @@
         <v>12</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D122" t="s">
         <v>93</v>
@@ -8919,7 +9060,7 @@
         <v>2</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>8</v>
@@ -8933,7 +9074,7 @@
         <v>13</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D123" t="s">
         <v>93</v>
@@ -8945,7 +9086,7 @@
         <v>3</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>8</v>
@@ -8959,7 +9100,7 @@
         <v>14</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D124" t="s">
         <v>93</v>
@@ -8971,7 +9112,7 @@
         <v>1</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>8</v>
@@ -8985,7 +9126,7 @@
         <v>15</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D125" t="s">
         <v>93</v>
@@ -8997,7 +9138,7 @@
         <v>3</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>8</v>
@@ -9011,7 +9152,7 @@
         <v>16</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D126" t="s">
         <v>93</v>
@@ -9037,7 +9178,7 @@
         <v>17</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D127" t="s">
         <v>93</v>
@@ -9049,7 +9190,7 @@
         <v>3</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>8</v>
@@ -9063,7 +9204,7 @@
         <v>1</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D128" t="s">
         <v>93</v>
@@ -9075,7 +9216,7 @@
         <v>1</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>8</v>
@@ -9089,7 +9230,7 @@
         <v>2</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D129" t="s">
         <v>93</v>
@@ -9101,7 +9242,7 @@
         <v>2</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>8</v>
@@ -9115,7 +9256,7 @@
         <v>3</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D130" t="s">
         <v>93</v>
@@ -9127,7 +9268,7 @@
         <v>3</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>8</v>
@@ -9141,7 +9282,7 @@
         <v>4</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D131" t="s">
         <v>93</v>
@@ -9153,7 +9294,7 @@
         <v>1</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>8</v>
@@ -9167,7 +9308,7 @@
         <v>5</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D132" t="s">
         <v>93</v>
@@ -9179,7 +9320,7 @@
         <v>2</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>8</v>
@@ -9193,7 +9334,7 @@
         <v>6</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D133" t="s">
         <v>93</v>
@@ -9205,7 +9346,7 @@
         <v>1</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>8</v>
@@ -9219,7 +9360,7 @@
         <v>7</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D134" t="s">
         <v>93</v>
@@ -9231,7 +9372,7 @@
         <v>1</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>8</v>
@@ -9245,7 +9386,7 @@
         <v>8</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D135" t="s">
         <v>182</v>
@@ -9257,7 +9398,7 @@
         <v>2</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>8</v>
@@ -9271,7 +9412,7 @@
         <v>9</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D136" t="s">
         <v>93</v>
@@ -9283,7 +9424,7 @@
         <v>2</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>8</v>
@@ -9297,7 +9438,7 @@
         <v>10</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D137" t="s">
         <v>182</v>
@@ -9309,7 +9450,7 @@
         <v>1</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>8</v>
@@ -9323,7 +9464,7 @@
         <v>11</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D138" t="s">
         <v>182</v>
@@ -9335,7 +9476,7 @@
         <v>2</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>8</v>
@@ -9349,7 +9490,7 @@
         <v>12</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D139" t="s">
         <v>93</v>
@@ -9361,7 +9502,7 @@
         <v>2</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>8</v>
@@ -9375,7 +9516,7 @@
         <v>13</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D140" t="s">
         <v>182</v>
@@ -9387,7 +9528,7 @@
         <v>2</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>8</v>
@@ -9401,7 +9542,7 @@
         <v>14</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D141" t="s">
         <v>93</v>
@@ -9413,7 +9554,7 @@
         <v>1</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>8</v>
@@ -9427,7 +9568,7 @@
         <v>1</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D142" t="s">
         <v>93</v>
@@ -9439,7 +9580,7 @@
         <v>3</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>8</v>
@@ -9453,7 +9594,7 @@
         <v>2</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D143" t="s">
         <v>93</v>
@@ -9465,7 +9606,7 @@
         <v>3</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>8</v>
@@ -9479,7 +9620,7 @@
         <v>3</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D144" t="s">
         <v>93</v>
@@ -9491,7 +9632,7 @@
         <v>2</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>8</v>
@@ -9505,7 +9646,7 @@
         <v>4</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D145" t="s">
         <v>93</v>
@@ -9517,7 +9658,7 @@
         <v>3</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>8</v>
@@ -9531,7 +9672,7 @@
         <v>5</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D146" t="s">
         <v>182</v>
@@ -9543,7 +9684,7 @@
         <v>1</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>8</v>
@@ -9557,7 +9698,7 @@
         <v>6</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D147" t="s">
         <v>93</v>
@@ -9569,7 +9710,7 @@
         <v>3</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>8</v>
@@ -9583,7 +9724,7 @@
         <v>7</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D148" t="s">
         <v>93</v>
@@ -9595,7 +9736,7 @@
         <v>2</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>8</v>
@@ -9609,7 +9750,7 @@
         <v>8</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D149" t="s">
         <v>93</v>
@@ -9621,7 +9762,7 @@
         <v>2</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>8</v>
@@ -9635,7 +9776,7 @@
         <v>9</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D150" t="s">
         <v>93</v>
@@ -9647,7 +9788,7 @@
         <v>2</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>8</v>
@@ -9661,7 +9802,7 @@
         <v>10</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D151" t="s">
         <v>93</v>
@@ -9673,7 +9814,7 @@
         <v>3</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>8</v>
@@ -9687,7 +9828,7 @@
         <v>11</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D152" t="s">
         <v>93</v>
@@ -9699,7 +9840,7 @@
         <v>2</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>8</v>
@@ -9713,7 +9854,7 @@
         <v>12</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D153" t="s">
         <v>182</v>
@@ -9725,7 +9866,7 @@
         <v>3</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>8</v>
@@ -9739,7 +9880,7 @@
         <v>13</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D154" t="s">
         <v>182</v>
@@ -9751,7 +9892,7 @@
         <v>2</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>8</v>
@@ -9765,7 +9906,7 @@
         <v>14</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D155" t="s">
         <v>182</v>
@@ -9777,7 +9918,7 @@
         <v>2</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>8</v>
@@ -9791,7 +9932,7 @@
         <v>1</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D156" t="s">
         <v>93</v>
@@ -9803,7 +9944,7 @@
         <v>1</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>8</v>
@@ -9817,7 +9958,7 @@
         <v>2</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D157" t="s">
         <v>93</v>
@@ -9829,7 +9970,7 @@
         <v>2</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>8</v>
@@ -9843,7 +9984,7 @@
         <v>3</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D158" t="s">
         <v>93</v>
@@ -9855,7 +9996,7 @@
         <v>2</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>8</v>
@@ -9869,7 +10010,7 @@
         <v>4</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D159" t="s">
         <v>93</v>
@@ -9881,7 +10022,7 @@
         <v>3</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>8</v>
@@ -9895,7 +10036,7 @@
         <v>5</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D160" t="s">
         <v>93</v>
@@ -9907,7 +10048,7 @@
         <v>2</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>8</v>
@@ -9921,7 +10062,7 @@
         <v>6</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D161" t="s">
         <v>93</v>
@@ -9933,7 +10074,7 @@
         <v>3</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>8</v>
@@ -9947,7 +10088,7 @@
         <v>7</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D162" t="s">
         <v>182</v>
@@ -9959,7 +10100,7 @@
         <v>2</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>8</v>
@@ -9973,7 +10114,7 @@
         <v>8</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D163" t="s">
         <v>93</v>
@@ -9985,7 +10126,7 @@
         <v>1</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>8</v>
@@ -9999,7 +10140,7 @@
         <v>9</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D164" t="s">
         <v>182</v>
@@ -10011,7 +10152,7 @@
         <v>2</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>8</v>
@@ -10025,7 +10166,7 @@
         <v>10</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D165" t="s">
         <v>93</v>
@@ -10037,7 +10178,7 @@
         <v>3</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>8</v>
@@ -10051,7 +10192,7 @@
         <v>11</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D166" t="s">
         <v>182</v>
@@ -10063,7 +10204,7 @@
         <v>2</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>8</v>
@@ -10077,7 +10218,7 @@
         <v>12</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D167" t="s">
         <v>93</v>
@@ -10089,7 +10230,7 @@
         <v>2</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>8</v>
@@ -10103,7 +10244,7 @@
         <v>13</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D168" t="s">
         <v>93</v>
@@ -10115,10 +10256,10 @@
         <v>3</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
@@ -10129,7 +10270,7 @@
         <v>14</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D169" t="s">
         <v>182</v>
@@ -10141,7 +10282,7 @@
         <v>3</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>8</v>
@@ -10155,7 +10296,7 @@
         <v>1</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D170" t="s">
         <v>93</v>
@@ -10167,7 +10308,7 @@
         <v>1</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>8</v>
@@ -10181,7 +10322,7 @@
         <v>2</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D171" t="s">
         <v>93</v>
@@ -10193,7 +10334,7 @@
         <v>1</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>8</v>
@@ -10207,7 +10348,7 @@
         <v>3</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D172" t="s">
         <v>93</v>
@@ -10219,7 +10360,7 @@
         <v>2</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>8</v>
@@ -10233,7 +10374,7 @@
         <v>4</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D173" t="s">
         <v>93</v>
@@ -10245,7 +10386,7 @@
         <v>1</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>8</v>
@@ -10259,7 +10400,7 @@
         <v>5</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D174" t="s">
         <v>93</v>
@@ -10271,7 +10412,7 @@
         <v>3</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>8</v>
@@ -10285,7 +10426,7 @@
         <v>6</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D175" t="s">
         <v>93</v>
@@ -10297,7 +10438,7 @@
         <v>2</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>8</v>
@@ -10311,7 +10452,7 @@
         <v>7</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D176" t="s">
         <v>93</v>
@@ -10323,7 +10464,7 @@
         <v>2</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>8</v>
@@ -10337,7 +10478,7 @@
         <v>8</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D177" t="s">
         <v>93</v>
@@ -10349,7 +10490,7 @@
         <v>3</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>8</v>
@@ -10363,7 +10504,7 @@
         <v>9</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D178" t="s">
         <v>93</v>
@@ -10375,7 +10516,7 @@
         <v>2</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>8</v>
@@ -10389,7 +10530,7 @@
         <v>10</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D179" t="s">
         <v>93</v>
@@ -10401,7 +10542,7 @@
         <v>2</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>8</v>
@@ -10415,7 +10556,7 @@
         <v>11</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D180" t="s">
         <v>182</v>
@@ -10427,7 +10568,7 @@
         <v>2</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>8</v>
@@ -10441,7 +10582,7 @@
         <v>12</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D181" t="s">
         <v>93</v>
@@ -10453,7 +10594,7 @@
         <v>2</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>8</v>
@@ -10467,7 +10608,7 @@
         <v>13</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D182" t="s">
         <v>182</v>
@@ -10479,7 +10620,7 @@
         <v>2</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>8</v>
@@ -10493,7 +10634,7 @@
         <v>1</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D183" t="s">
         <v>182</v>
@@ -10505,7 +10646,7 @@
         <v>2</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>8</v>
@@ -10519,7 +10660,7 @@
         <v>2</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D184" t="s">
         <v>93</v>
@@ -10531,7 +10672,7 @@
         <v>3</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>8</v>
@@ -10545,7 +10686,7 @@
         <v>3</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D185" t="s">
         <v>93</v>
@@ -10557,7 +10698,7 @@
         <v>1</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>8</v>
@@ -10571,7 +10712,7 @@
         <v>4</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D186" t="s">
         <v>93</v>
@@ -10583,7 +10724,7 @@
         <v>2</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>8</v>
@@ -10597,7 +10738,7 @@
         <v>5</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D187" t="s">
         <v>93</v>
@@ -10609,7 +10750,7 @@
         <v>2</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>8</v>
@@ -10623,7 +10764,7 @@
         <v>6</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D188" t="s">
         <v>182</v>
@@ -10635,7 +10776,7 @@
         <v>3</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>8</v>
@@ -10649,7 +10790,7 @@
         <v>7</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D189" t="s">
         <v>93</v>
@@ -10661,7 +10802,7 @@
         <v>2</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>8</v>
@@ -10675,7 +10816,7 @@
         <v>8</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D190" t="s">
         <v>93</v>
@@ -10687,7 +10828,7 @@
         <v>3</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>8</v>
@@ -10713,7 +10854,7 @@
         <v>3</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>8</v>
@@ -10727,7 +10868,7 @@
         <v>10</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D192" t="s">
         <v>93</v>
@@ -10739,7 +10880,7 @@
         <v>2</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>8</v>
@@ -10753,7 +10894,7 @@
         <v>11</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D193" t="s">
         <v>182</v>
@@ -10765,7 +10906,7 @@
         <v>2</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>8</v>
@@ -10779,7 +10920,7 @@
         <v>1</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D194" t="s">
         <v>182</v>
@@ -10791,7 +10932,7 @@
         <v>1</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>8</v>
@@ -10805,7 +10946,7 @@
         <v>2</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D195" t="s">
         <v>93</v>
@@ -10817,7 +10958,7 @@
         <v>2</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>8</v>
@@ -10831,7 +10972,7 @@
         <v>3</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D196" t="s">
         <v>93</v>
@@ -10843,7 +10984,7 @@
         <v>2</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>8</v>
@@ -10857,7 +10998,7 @@
         <v>4</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D197" t="s">
         <v>93</v>
@@ -10869,7 +11010,7 @@
         <v>2</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>8</v>
@@ -10883,7 +11024,7 @@
         <v>5</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D198" t="s">
         <v>93</v>
@@ -10895,7 +11036,7 @@
         <v>3</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>8</v>
@@ -10909,7 +11050,7 @@
         <v>6</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D199" t="s">
         <v>93</v>
@@ -10921,7 +11062,7 @@
         <v>2</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>8</v>
@@ -10935,7 +11076,7 @@
         <v>7</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D200" t="s">
         <v>182</v>
@@ -10947,7 +11088,7 @@
         <v>2</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>8</v>
@@ -10961,7 +11102,7 @@
         <v>8</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D201" t="s">
         <v>93</v>
@@ -10973,7 +11114,7 @@
         <v>2</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>8</v>
@@ -10987,7 +11128,7 @@
         <v>9</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D202" t="s">
         <v>182</v>
@@ -10999,7 +11140,7 @@
         <v>3</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>8</v>
@@ -11013,7 +11154,7 @@
         <v>10</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D203" t="s">
         <v>93</v>
@@ -11025,7 +11166,7 @@
         <v>2</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>8</v>
@@ -11039,7 +11180,7 @@
         <v>11</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D204" t="s">
         <v>93</v>
@@ -11051,7 +11192,7 @@
         <v>2</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>8</v>
@@ -11065,7 +11206,7 @@
         <v>1</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D205" t="s">
         <v>93</v>
@@ -11077,7 +11218,7 @@
         <v>2</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>8</v>
@@ -11091,7 +11232,7 @@
         <v>2</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D206" t="s">
         <v>93</v>
@@ -11103,7 +11244,7 @@
         <v>1</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>8</v>
@@ -11117,7 +11258,7 @@
         <v>3</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D207" t="s">
         <v>93</v>
@@ -11129,7 +11270,7 @@
         <v>1</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>8</v>
@@ -11143,7 +11284,7 @@
         <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D208" t="s">
         <v>182</v>
@@ -11155,7 +11296,7 @@
         <v>1</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>8</v>
@@ -11169,7 +11310,7 @@
         <v>5</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D209" t="s">
         <v>93</v>
@@ -11181,7 +11322,7 @@
         <v>1</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>8</v>
@@ -11195,7 +11336,7 @@
         <v>6</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D210" t="s">
         <v>93</v>
@@ -11207,7 +11348,7 @@
         <v>3</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>8</v>
@@ -11221,7 +11362,7 @@
         <v>7</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D211" t="s">
         <v>93</v>
@@ -11233,7 +11374,7 @@
         <v>2</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>8</v>
@@ -11247,7 +11388,7 @@
         <v>8</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D212" t="s">
         <v>93</v>
@@ -11259,7 +11400,7 @@
         <v>2</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>8</v>
@@ -11273,7 +11414,7 @@
         <v>9</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D213" t="s">
         <v>182</v>
@@ -11285,7 +11426,7 @@
         <v>1</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>8</v>
@@ -11299,10 +11440,10 @@
         <v>10</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D214" t="s">
-        <v>93</v>
+        <v>182</v>
       </c>
       <c r="E214">
         <v>120</v>
@@ -11311,10 +11452,10 @@
         <v>3</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>8</v>
+        <v>619</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
@@ -11325,10 +11466,10 @@
         <v>11</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D215" t="s">
-        <v>93</v>
+        <v>182</v>
       </c>
       <c r="E215">
         <v>120</v>
@@ -11337,10 +11478,10 @@
         <v>3</v>
       </c>
       <c r="G215" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="H215" s="2" t="s">
         <v>619</v>
-      </c>
-      <c r="H215" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
@@ -11351,7 +11492,7 @@
         <v>12</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D216" t="s">
         <v>93</v>
@@ -11363,7 +11504,7 @@
         <v>2</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>8</v>
@@ -11377,7 +11518,7 @@
         <v>1</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="D217" t="s">
         <v>93</v>
@@ -11389,7 +11530,7 @@
         <v>1</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>8</v>
@@ -11403,7 +11544,7 @@
         <v>2</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D218" t="s">
         <v>93</v>
@@ -11415,10 +11556,10 @@
         <v>2</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
@@ -11429,7 +11570,7 @@
         <v>3</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D219" t="s">
         <v>93</v>
@@ -11441,7 +11582,7 @@
         <v>3</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>8</v>
@@ -11455,7 +11596,7 @@
         <v>4</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D220" t="s">
         <v>93</v>
@@ -11467,10 +11608,842 @@
         <v>2</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>181</v>
+      </c>
+      <c r="B221">
+        <v>1</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="D221" t="s">
+        <v>93</v>
+      </c>
+      <c r="E221">
+        <v>15</v>
+      </c>
+      <c r="F221">
+        <v>1</v>
+      </c>
+      <c r="G221" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="H221" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>181</v>
+      </c>
+      <c r="B222">
+        <v>2</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="D222" t="s">
+        <v>93</v>
+      </c>
+      <c r="E222">
+        <v>30</v>
+      </c>
+      <c r="F222">
+        <v>1</v>
+      </c>
+      <c r="G222" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="H222" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>181</v>
+      </c>
+      <c r="B223">
+        <v>3</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="D223" t="s">
+        <v>182</v>
+      </c>
+      <c r="E223">
+        <v>15</v>
+      </c>
+      <c r="F223">
+        <v>2</v>
+      </c>
+      <c r="G223" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H223" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>181</v>
+      </c>
+      <c r="B224">
+        <v>4</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="D224" t="s">
+        <v>93</v>
+      </c>
+      <c r="E224">
+        <v>45</v>
+      </c>
+      <c r="F224">
+        <v>2</v>
+      </c>
+      <c r="G224" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="H224" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>181</v>
+      </c>
+      <c r="B225">
+        <v>5</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="D225" t="s">
+        <v>93</v>
+      </c>
+      <c r="E225">
+        <v>45</v>
+      </c>
+      <c r="F225">
+        <v>3</v>
+      </c>
+      <c r="G225" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="H225" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>181</v>
+      </c>
+      <c r="B226">
+        <v>6</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="D226" t="s">
+        <v>93</v>
+      </c>
+      <c r="E226">
+        <v>30</v>
+      </c>
+      <c r="F226">
+        <v>2</v>
+      </c>
+      <c r="G226" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H226" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>181</v>
+      </c>
+      <c r="B227">
+        <v>7</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="D227" t="s">
+        <v>93</v>
+      </c>
+      <c r="E227">
+        <v>60</v>
+      </c>
+      <c r="F227">
+        <v>3</v>
+      </c>
+      <c r="G227" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="H227" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>181</v>
+      </c>
+      <c r="B228">
+        <v>8</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="D228" t="s">
+        <v>182</v>
+      </c>
+      <c r="E228">
+        <v>20</v>
+      </c>
+      <c r="F228">
+        <v>1</v>
+      </c>
+      <c r="G228" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H228" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>181</v>
+      </c>
+      <c r="B229">
+        <v>9</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="D229" t="s">
+        <v>93</v>
+      </c>
+      <c r="E229">
+        <v>60</v>
+      </c>
+      <c r="F229">
+        <v>2</v>
+      </c>
+      <c r="G229" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="H229" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>181</v>
+      </c>
+      <c r="B230">
+        <v>10</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="D230" t="s">
+        <v>93</v>
+      </c>
+      <c r="E230">
+        <v>30</v>
+      </c>
+      <c r="F230">
+        <v>2</v>
+      </c>
+      <c r="G230" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="H230" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>181</v>
+      </c>
+      <c r="B231">
+        <v>11</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="D231" t="s">
+        <v>182</v>
+      </c>
+      <c r="E231">
+        <v>30</v>
+      </c>
+      <c r="F231">
+        <v>1</v>
+      </c>
+      <c r="G231" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H231" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>181</v>
+      </c>
+      <c r="B232">
+        <v>12</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="D232" t="s">
+        <v>93</v>
+      </c>
+      <c r="E232">
+        <v>45</v>
+      </c>
+      <c r="F232">
+        <v>2</v>
+      </c>
+      <c r="G232" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="H232" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>181</v>
+      </c>
+      <c r="B233">
+        <v>13</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="D233" t="s">
+        <v>93</v>
+      </c>
+      <c r="E233">
+        <v>20</v>
+      </c>
+      <c r="F233">
+        <v>1</v>
+      </c>
+      <c r="G233" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H233" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>181</v>
+      </c>
+      <c r="B234">
+        <v>14</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="D234" t="s">
+        <v>93</v>
+      </c>
+      <c r="E234">
+        <v>45</v>
+      </c>
+      <c r="F234">
+        <v>2</v>
+      </c>
+      <c r="G234" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="H234" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>181</v>
+      </c>
+      <c r="B235">
+        <v>15</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="D235" t="s">
+        <v>93</v>
+      </c>
+      <c r="E235">
+        <v>25</v>
+      </c>
+      <c r="F235">
+        <v>3</v>
+      </c>
+      <c r="G235" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="H235" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>181</v>
+      </c>
+      <c r="B236">
+        <v>16</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="D236" t="s">
+        <v>182</v>
+      </c>
+      <c r="E236">
+        <v>30</v>
+      </c>
+      <c r="F236">
+        <v>2</v>
+      </c>
+      <c r="G236" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="H236" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>181</v>
+      </c>
+      <c r="B237">
+        <v>17</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="D237" t="s">
+        <v>93</v>
+      </c>
+      <c r="E237">
+        <v>90</v>
+      </c>
+      <c r="F237">
+        <v>3</v>
+      </c>
+      <c r="G237" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="H237" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>181</v>
+      </c>
+      <c r="B238">
+        <v>18</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="D238" t="s">
+        <v>93</v>
+      </c>
+      <c r="E238">
+        <v>45</v>
+      </c>
+      <c r="F238">
+        <v>3</v>
+      </c>
+      <c r="G238" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="H238" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>181</v>
+      </c>
+      <c r="B239">
+        <v>19</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="D239" t="s">
+        <v>93</v>
+      </c>
+      <c r="E239">
+        <v>7</v>
+      </c>
+      <c r="F239">
+        <v>1</v>
+      </c>
+      <c r="G239" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="H239" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>181</v>
+      </c>
+      <c r="B240">
+        <v>20</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="D240" t="s">
+        <v>93</v>
+      </c>
+      <c r="E240">
+        <v>45</v>
+      </c>
+      <c r="F240">
+        <v>1</v>
+      </c>
+      <c r="G240" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="H240" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>181</v>
+      </c>
+      <c r="B241">
+        <v>21</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="D241" t="s">
+        <v>93</v>
+      </c>
+      <c r="E241">
+        <v>45</v>
+      </c>
+      <c r="F241">
+        <v>1</v>
+      </c>
+      <c r="G241" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="H241" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>181</v>
+      </c>
+      <c r="B242">
+        <v>22</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="D242" t="s">
+        <v>93</v>
+      </c>
+      <c r="E242">
+        <v>45</v>
+      </c>
+      <c r="F242">
+        <v>1</v>
+      </c>
+      <c r="G242" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="H242" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>181</v>
+      </c>
+      <c r="B243">
+        <v>23</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="D243" t="s">
+        <v>93</v>
+      </c>
+      <c r="E243">
+        <v>60</v>
+      </c>
+      <c r="F243">
+        <v>1</v>
+      </c>
+      <c r="G243" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="H243" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>181</v>
+      </c>
+      <c r="B244">
+        <v>24</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="D244" t="s">
+        <v>93</v>
+      </c>
+      <c r="E244">
+        <v>45</v>
+      </c>
+      <c r="F244">
+        <v>1</v>
+      </c>
+      <c r="G244" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="H244" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>181</v>
+      </c>
+      <c r="B245">
+        <v>25</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="D245" t="s">
+        <v>93</v>
+      </c>
+      <c r="E245">
+        <v>45</v>
+      </c>
+      <c r="F245">
+        <v>1</v>
+      </c>
+      <c r="G245" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="H245" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>181</v>
+      </c>
+      <c r="B246">
+        <v>26</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="D246" t="s">
+        <v>93</v>
+      </c>
+      <c r="E246">
+        <v>60</v>
+      </c>
+      <c r="F246">
+        <v>1</v>
+      </c>
+      <c r="G246" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="H246" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>181</v>
+      </c>
+      <c r="B247">
+        <v>27</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="D247" t="s">
+        <v>93</v>
+      </c>
+      <c r="E247">
+        <v>60</v>
+      </c>
+      <c r="F247">
+        <v>1</v>
+      </c>
+      <c r="G247" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="H247" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>181</v>
+      </c>
+      <c r="B248">
+        <v>28</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="D248" t="s">
+        <v>182</v>
+      </c>
+      <c r="E248">
+        <v>30</v>
+      </c>
+      <c r="F248">
+        <v>3</v>
+      </c>
+      <c r="G248" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H248" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>181</v>
+      </c>
+      <c r="B249">
+        <v>29</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="D249" t="s">
+        <v>182</v>
+      </c>
+      <c r="E249">
+        <v>30</v>
+      </c>
+      <c r="F249">
+        <v>1</v>
+      </c>
+      <c r="G249" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="H249" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>181</v>
+      </c>
+      <c r="B250">
+        <v>30</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="D250" t="s">
+        <v>182</v>
+      </c>
+      <c r="E250">
+        <v>30</v>
+      </c>
+      <c r="F250">
+        <v>1</v>
+      </c>
+      <c r="G250" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H250" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>181</v>
+      </c>
+      <c r="B251">
+        <v>31</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="D251" t="s">
+        <v>182</v>
+      </c>
+      <c r="E251">
+        <v>45</v>
+      </c>
+      <c r="F251">
+        <v>1</v>
+      </c>
+      <c r="G251" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="H251" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>181</v>
+      </c>
+      <c r="B252">
+        <v>32</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="D252" t="s">
+        <v>93</v>
+      </c>
+      <c r="E252">
+        <v>120</v>
+      </c>
+      <c r="F252">
+        <v>3</v>
+      </c>
+      <c r="G252" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="H252" s="2" t="s">
+        <v>655</v>
       </c>
     </row>
   </sheetData>
@@ -11646,16 +12619,16 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>624</v>
+        <v>671</v>
       </c>
       <c r="B2" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>626</v>
+        <v>673</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -11678,7 +12651,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>627</v>
+        <v>674</v>
       </c>
       <c r="B3" t="s">
         <v>138</v>
@@ -11687,7 +12660,7 @@
         <v>166</v>
       </c>
       <c r="D3" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -11696,7 +12669,7 @@
         <v>8</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>629</v>
+        <v>676</v>
       </c>
       <c r="H3">
         <v>3</v>
@@ -11710,16 +12683,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>627</v>
+        <v>674</v>
       </c>
       <c r="B4" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -11742,16 +12715,16 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>631</v>
+        <v>678</v>
       </c>
       <c r="B5" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -11774,7 +12747,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>633</v>
+        <v>680</v>
       </c>
       <c r="B6" t="s">
         <v>138</v>
@@ -11783,7 +12756,7 @@
         <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>634</v>
+        <v>681</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -11792,7 +12765,7 @@
         <v>8</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>635</v>
+        <v>682</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -11806,16 +12779,16 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>633</v>
+        <v>680</v>
       </c>
       <c r="B7" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>636</v>
+        <v>683</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -11838,16 +12811,16 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>637</v>
+        <v>684</v>
       </c>
       <c r="B8" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -11873,13 +12846,13 @@
         <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>626</v>
+        <v>673</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -11902,7 +12875,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>638</v>
+        <v>685</v>
       </c>
       <c r="B10" t="s">
         <v>138</v>
@@ -11911,7 +12884,7 @@
         <v>166</v>
       </c>
       <c r="D10" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -11920,7 +12893,7 @@
         <v>8</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>639</v>
+        <v>686</v>
       </c>
       <c r="H10">
         <v>6</v>
@@ -11934,16 +12907,16 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>638</v>
+        <v>685</v>
       </c>
       <c r="B11" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -11966,7 +12939,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>640</v>
+        <v>687</v>
       </c>
       <c r="B12" t="s">
         <v>138</v>
@@ -11975,7 +12948,7 @@
         <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="E12" t="s">
         <v>141</v>
@@ -11984,7 +12957,7 @@
         <v>8</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H12">
         <v>3</v>
@@ -11998,7 +12971,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>641</v>
+        <v>688</v>
       </c>
       <c r="B13" t="s">
         <v>138</v>
@@ -12007,7 +12980,7 @@
         <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>634</v>
+        <v>681</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -12016,7 +12989,7 @@
         <v>8</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>642</v>
+        <v>689</v>
       </c>
       <c r="H13">
         <v>5</v>
@@ -12030,16 +13003,16 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>641</v>
+        <v>688</v>
       </c>
       <c r="B14" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C14" t="s">
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>636</v>
+        <v>683</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -12062,7 +13035,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>643</v>
+        <v>690</v>
       </c>
       <c r="B15" t="s">
         <v>138</v>
@@ -12071,16 +13044,16 @@
         <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="E15" t="s">
-        <v>644</v>
+        <v>691</v>
       </c>
       <c r="F15" t="s">
         <v>8</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H15">
         <v>3</v>
@@ -12097,13 +13070,13 @@
         <v>127</v>
       </c>
       <c r="B16" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C16" t="s">
         <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>626</v>
+        <v>673</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -12135,7 +13108,7 @@
         <v>166</v>
       </c>
       <c r="D17" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -12144,7 +13117,7 @@
         <v>8</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>645</v>
+        <v>692</v>
       </c>
       <c r="H17">
         <v>11</v>
@@ -12161,13 +13134,13 @@
         <v>136</v>
       </c>
       <c r="B18" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C18" t="s">
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -12190,7 +13163,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>646</v>
+        <v>693</v>
       </c>
       <c r="B19" t="s">
         <v>138</v>
@@ -12199,16 +13172,16 @@
         <v>72</v>
       </c>
       <c r="D19" t="s">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="E19" t="s">
-        <v>647</v>
+        <v>694</v>
       </c>
       <c r="F19" t="s">
         <v>8</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H19">
         <v>3</v>
@@ -12222,7 +13195,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>648</v>
+        <v>695</v>
       </c>
       <c r="B20" t="s">
         <v>138</v>
@@ -12231,7 +13204,7 @@
         <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>634</v>
+        <v>681</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -12240,7 +13213,7 @@
         <v>8</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>649</v>
+        <v>696</v>
       </c>
       <c r="H20">
         <v>9</v>
@@ -12254,16 +13227,16 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>648</v>
+        <v>695</v>
       </c>
       <c r="B21" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C21" t="s">
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>636</v>
+        <v>683</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -12286,16 +13259,16 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>650</v>
+        <v>697</v>
       </c>
       <c r="B22" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C22" t="s">
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -12318,16 +13291,16 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>651</v>
+        <v>698</v>
       </c>
       <c r="B23" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C23" t="s">
         <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>626</v>
+        <v>673</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -12350,16 +13323,16 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>652</v>
+        <v>699</v>
       </c>
       <c r="B24" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C24" t="s">
         <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>653</v>
+        <v>700</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -12382,7 +13355,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>654</v>
+        <v>701</v>
       </c>
       <c r="B25" t="s">
         <v>138</v>
@@ -12391,7 +13364,7 @@
         <v>171</v>
       </c>
       <c r="D25" t="s">
-        <v>626</v>
+        <v>673</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -12400,7 +13373,7 @@
         <v>8</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>655</v>
+        <v>702</v>
       </c>
       <c r="H25">
         <v>9</v>
@@ -12414,7 +13387,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>656</v>
+        <v>703</v>
       </c>
       <c r="B26" t="s">
         <v>138</v>
@@ -12423,7 +13396,7 @@
         <v>44</v>
       </c>
       <c r="D26" t="s">
-        <v>634</v>
+        <v>681</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -12432,7 +13405,7 @@
         <v>8</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>657</v>
+        <v>704</v>
       </c>
       <c r="H26">
         <v>2</v>
@@ -12446,16 +13419,16 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>656</v>
+        <v>703</v>
       </c>
       <c r="B27" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C27" t="s">
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -12478,7 +13451,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>658</v>
+        <v>705</v>
       </c>
       <c r="B28" t="s">
         <v>138</v>
@@ -12487,7 +13460,7 @@
         <v>169</v>
       </c>
       <c r="D28" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -12496,7 +13469,7 @@
         <v>8</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>659</v>
+        <v>706</v>
       </c>
       <c r="H28">
         <v>2</v>
@@ -12510,16 +13483,16 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>658</v>
+        <v>705</v>
       </c>
       <c r="B29" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C29" t="s">
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>626</v>
+        <v>673</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -12545,13 +13518,13 @@
         <v>58</v>
       </c>
       <c r="B30" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C30" t="s">
         <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>653</v>
+        <v>700</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -12574,7 +13547,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>660</v>
+        <v>707</v>
       </c>
       <c r="B31" t="s">
         <v>138</v>
@@ -12583,7 +13556,7 @@
         <v>171</v>
       </c>
       <c r="D31" t="s">
-        <v>626</v>
+        <v>673</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -12592,7 +13565,7 @@
         <v>8</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>661</v>
+        <v>708</v>
       </c>
       <c r="H31">
         <v>10</v>
@@ -12606,7 +13579,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>662</v>
+        <v>709</v>
       </c>
       <c r="B32" t="s">
         <v>138</v>
@@ -12615,7 +13588,7 @@
         <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>634</v>
+        <v>681</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -12624,7 +13597,7 @@
         <v>8</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>663</v>
+        <v>710</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -12638,16 +13611,16 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>662</v>
+        <v>709</v>
       </c>
       <c r="B33" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C33" t="s">
         <v>8</v>
       </c>
       <c r="D33" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -12670,7 +13643,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>664</v>
+        <v>711</v>
       </c>
       <c r="B34" t="s">
         <v>138</v>
@@ -12679,7 +13652,7 @@
         <v>171</v>
       </c>
       <c r="D34" t="s">
-        <v>626</v>
+        <v>673</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -12688,7 +13661,7 @@
         <v>8</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>665</v>
+        <v>712</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -12702,16 +13675,16 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>666</v>
+        <v>713</v>
       </c>
       <c r="B35" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C35" t="s">
         <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>653</v>
+        <v>700</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -12737,7 +13710,7 @@
         <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>667</v>
+        <v>714</v>
       </c>
       <c r="C36" t="s">
         <v>8</v>
@@ -12752,7 +13725,7 @@
         <v>8</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>668</v>
+        <v>715</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -12766,7 +13739,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>669</v>
+        <v>716</v>
       </c>
       <c r="B37" t="s">
         <v>138</v>
@@ -12775,7 +13748,7 @@
         <v>44</v>
       </c>
       <c r="D37" t="s">
-        <v>634</v>
+        <v>681</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -12784,7 +13757,7 @@
         <v>8</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>670</v>
+        <v>717</v>
       </c>
       <c r="H37">
         <v>9</v>
@@ -12798,16 +13771,16 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>669</v>
+        <v>716</v>
       </c>
       <c r="B38" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C38" t="s">
         <v>8</v>
       </c>
       <c r="D38" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -12830,7 +13803,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>671</v>
+        <v>718</v>
       </c>
       <c r="B39" t="s">
         <v>138</v>
@@ -12839,7 +13812,7 @@
         <v>169</v>
       </c>
       <c r="D39" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -12848,7 +13821,7 @@
         <v>8</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>672</v>
+        <v>719</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -12862,16 +13835,16 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>671</v>
+        <v>718</v>
       </c>
       <c r="B40" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C40" t="s">
         <v>8</v>
       </c>
       <c r="D40" t="s">
-        <v>626</v>
+        <v>673</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -12894,16 +13867,16 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>673</v>
+        <v>720</v>
       </c>
       <c r="B41" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C41" t="s">
         <v>8</v>
       </c>
       <c r="D41" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -12926,7 +13899,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>674</v>
+        <v>721</v>
       </c>
       <c r="B42" t="s">
         <v>138</v>
@@ -12935,7 +13908,7 @@
         <v>166</v>
       </c>
       <c r="D42" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -12944,7 +13917,7 @@
         <v>8</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>675</v>
+        <v>722</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -12958,16 +13931,16 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>674</v>
+        <v>721</v>
       </c>
       <c r="B43" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C43" t="s">
         <v>8</v>
       </c>
       <c r="D43" t="s">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -12990,7 +13963,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>676</v>
+        <v>723</v>
       </c>
       <c r="B44" t="s">
         <v>138</v>
@@ -13008,7 +13981,7 @@
         <v>8</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>677</v>
+        <v>724</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -13022,7 +13995,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>678</v>
+        <v>725</v>
       </c>
       <c r="B45" t="s">
         <v>138</v>
@@ -13031,7 +14004,7 @@
         <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>679</v>
+        <v>726</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -13040,7 +14013,7 @@
         <v>8</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>680</v>
+        <v>727</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -13054,16 +14027,16 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>678</v>
+        <v>725</v>
       </c>
       <c r="B46" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C46" t="s">
         <v>8</v>
       </c>
       <c r="D46" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -13086,7 +14059,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>681</v>
+        <v>728</v>
       </c>
       <c r="B47" t="s">
         <v>138</v>
@@ -13095,7 +14068,7 @@
         <v>166</v>
       </c>
       <c r="D47" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -13104,7 +14077,7 @@
         <v>8</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>682</v>
+        <v>729</v>
       </c>
       <c r="H47">
         <v>11</v>
@@ -13118,16 +14091,16 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>681</v>
+        <v>728</v>
       </c>
       <c r="B48" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C48" t="s">
         <v>8</v>
       </c>
       <c r="D48" t="s">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -13150,16 +14123,16 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>683</v>
+        <v>730</v>
       </c>
       <c r="B49" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C49" t="s">
         <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>684</v>
+        <v>731</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -13182,7 +14155,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>685</v>
+        <v>732</v>
       </c>
       <c r="B50" t="s">
         <v>138</v>
@@ -13191,7 +14164,7 @@
         <v>72</v>
       </c>
       <c r="D50" t="s">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="E50" t="s">
         <v>141</v>
@@ -13200,7 +14173,7 @@
         <v>8</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>686</v>
+        <v>733</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -13214,7 +14187,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>687</v>
+        <v>734</v>
       </c>
       <c r="B51" t="s">
         <v>138</v>
@@ -13226,13 +14199,13 @@
         <v>140</v>
       </c>
       <c r="E51" t="s">
-        <v>644</v>
+        <v>691</v>
       </c>
       <c r="F51" t="s">
         <v>8</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>677</v>
+        <v>724</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -13246,7 +14219,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>688</v>
+        <v>735</v>
       </c>
       <c r="B52" t="s">
         <v>138</v>
@@ -13255,7 +14228,7 @@
         <v>44</v>
       </c>
       <c r="D52" t="s">
-        <v>679</v>
+        <v>726</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -13264,7 +14237,7 @@
         <v>8</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>689</v>
+        <v>736</v>
       </c>
       <c r="H52">
         <v>5</v>
@@ -13278,16 +14251,16 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>688</v>
+        <v>735</v>
       </c>
       <c r="B53" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C53" t="s">
         <v>8</v>
       </c>
       <c r="D53" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -13310,16 +14283,16 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>690</v>
+        <v>737</v>
       </c>
       <c r="B54" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C54" t="s">
         <v>8</v>
       </c>
       <c r="D54" t="s">
-        <v>684</v>
+        <v>731</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -13342,7 +14315,7 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>691</v>
+        <v>738</v>
       </c>
       <c r="B55" t="s">
         <v>138</v>
@@ -13351,16 +14324,16 @@
         <v>72</v>
       </c>
       <c r="D55" t="s">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="E55" t="s">
-        <v>644</v>
+        <v>691</v>
       </c>
       <c r="F55" t="s">
         <v>8</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>686</v>
+        <v>733</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -13374,7 +14347,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>692</v>
+        <v>739</v>
       </c>
       <c r="B56" t="s">
         <v>138</v>
@@ -13386,13 +14359,13 @@
         <v>140</v>
       </c>
       <c r="E56" t="s">
-        <v>647</v>
+        <v>694</v>
       </c>
       <c r="F56" t="s">
         <v>8</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>677</v>
+        <v>724</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -13406,7 +14379,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>693</v>
+        <v>740</v>
       </c>
       <c r="B57" t="s">
         <v>138</v>
@@ -13415,7 +14388,7 @@
         <v>44</v>
       </c>
       <c r="D57" t="s">
-        <v>679</v>
+        <v>726</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -13424,7 +14397,7 @@
         <v>8</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>694</v>
+        <v>741</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -13438,7 +14411,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>695</v>
+        <v>742</v>
       </c>
       <c r="B58" t="s">
         <v>138</v>
@@ -13447,7 +14420,7 @@
         <v>166</v>
       </c>
       <c r="D58" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -13456,7 +14429,7 @@
         <v>8</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>696</v>
+        <v>743</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -13470,16 +14443,16 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>695</v>
+        <v>742</v>
       </c>
       <c r="B59" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C59" t="s">
         <v>8</v>
       </c>
       <c r="D59" t="s">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -13502,16 +14475,16 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>697</v>
+        <v>744</v>
       </c>
       <c r="B60" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C60" t="s">
         <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>684</v>
+        <v>731</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -13534,7 +14507,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>698</v>
+        <v>745</v>
       </c>
       <c r="B61" t="s">
         <v>138</v>
@@ -13543,16 +14516,16 @@
         <v>72</v>
       </c>
       <c r="D61" t="s">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="E61" t="s">
-        <v>647</v>
+        <v>694</v>
       </c>
       <c r="F61" t="s">
         <v>8</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>686</v>
+        <v>733</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -13566,16 +14539,16 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>699</v>
+        <v>746</v>
       </c>
       <c r="B62" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C62" t="s">
         <v>8</v>
       </c>
       <c r="D62" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -13598,16 +14571,16 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>700</v>
+        <v>747</v>
       </c>
       <c r="B63" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C63" t="s">
         <v>8</v>
       </c>
       <c r="D63" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -13630,7 +14603,7 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>701</v>
+        <v>748</v>
       </c>
       <c r="B64" t="s">
         <v>138</v>
@@ -13639,7 +14612,7 @@
         <v>171</v>
       </c>
       <c r="D64" t="s">
-        <v>626</v>
+        <v>673</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
@@ -13648,7 +14621,7 @@
         <v>8</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>702</v>
+        <v>749</v>
       </c>
       <c r="H64">
         <v>5</v>
@@ -13662,7 +14635,7 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>703</v>
+        <v>750</v>
       </c>
       <c r="B65" t="s">
         <v>138</v>
@@ -13671,7 +14644,7 @@
         <v>166</v>
       </c>
       <c r="D65" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -13680,7 +14653,7 @@
         <v>8</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>675</v>
+        <v>722</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -13694,7 +14667,7 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>704</v>
+        <v>751</v>
       </c>
       <c r="B66" t="s">
         <v>138</v>
@@ -13703,7 +14676,7 @@
         <v>169</v>
       </c>
       <c r="D66" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -13712,7 +14685,7 @@
         <v>8</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>705</v>
+        <v>752</v>
       </c>
       <c r="H66">
         <v>2</v>
@@ -13726,7 +14699,7 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>706</v>
+        <v>753</v>
       </c>
       <c r="B67" t="s">
         <v>138</v>
@@ -13735,7 +14708,7 @@
         <v>171</v>
       </c>
       <c r="D67" t="s">
-        <v>626</v>
+        <v>673</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -13744,7 +14717,7 @@
         <v>8</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>707</v>
+        <v>754</v>
       </c>
       <c r="H67">
         <v>7</v>
@@ -13758,16 +14731,16 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>706</v>
+        <v>753</v>
       </c>
       <c r="B68" t="s">
-        <v>625</v>
+        <v>672</v>
       </c>
       <c r="C68" t="s">
         <v>8</v>
       </c>
       <c r="D68" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -13790,7 +14763,7 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>708</v>
+        <v>755</v>
       </c>
       <c r="B69" t="s">
         <v>138</v>
@@ -13799,7 +14772,7 @@
         <v>166</v>
       </c>
       <c r="D69" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -13808,7 +14781,7 @@
         <v>8</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>682</v>
+        <v>729</v>
       </c>
       <c r="H69">
         <v>11</v>
@@ -13822,7 +14795,7 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>709</v>
+        <v>756</v>
       </c>
       <c r="B70" t="s">
         <v>138</v>
@@ -13831,7 +14804,7 @@
         <v>169</v>
       </c>
       <c r="D70" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -13840,7 +14813,7 @@
         <v>8</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>710</v>
+        <v>757</v>
       </c>
       <c r="H70">
         <v>8</v>
@@ -13854,10 +14827,10 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>711</v>
+        <v>758</v>
       </c>
       <c r="B71" t="s">
-        <v>667</v>
+        <v>714</v>
       </c>
       <c r="C71" t="s">
         <v>8</v>
@@ -13872,7 +14845,7 @@
         <v>8</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>712</v>
+        <v>759</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -13886,7 +14859,7 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>713</v>
+        <v>760</v>
       </c>
       <c r="B72" t="s">
         <v>138</v>
@@ -13895,7 +14868,7 @@
         <v>171</v>
       </c>
       <c r="D72" t="s">
-        <v>626</v>
+        <v>673</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -13904,7 +14877,7 @@
         <v>8</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>714</v>
+        <v>761</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -13918,7 +14891,7 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>715</v>
+        <v>762</v>
       </c>
       <c r="B73" t="s">
         <v>138</v>
@@ -13927,7 +14900,7 @@
         <v>166</v>
       </c>
       <c r="D73" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -13936,7 +14909,7 @@
         <v>8</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>696</v>
+        <v>743</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -13950,7 +14923,7 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>716</v>
+        <v>763</v>
       </c>
       <c r="B74" t="s">
         <v>138</v>
@@ -13959,7 +14932,7 @@
         <v>169</v>
       </c>
       <c r="D74" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -13968,7 +14941,7 @@
         <v>8</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>717</v>
+        <v>764</v>
       </c>
       <c r="H74">
         <v>9</v>
@@ -13982,7 +14955,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>718</v>
+        <v>765</v>
       </c>
       <c r="B75" t="s">
         <v>138</v>
@@ -13991,7 +14964,7 @@
         <v>44</v>
       </c>
       <c r="D75" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -14000,7 +14973,7 @@
         <v>8</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>720</v>
+        <v>767</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -14014,7 +14987,7 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>721</v>
+        <v>768</v>
       </c>
       <c r="B76" t="s">
         <v>138</v>
@@ -14023,7 +14996,7 @@
         <v>166</v>
       </c>
       <c r="D76" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -14032,7 +15005,7 @@
         <v>8</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>722</v>
+        <v>769</v>
       </c>
       <c r="H76">
         <v>3</v>
@@ -14046,7 +15019,7 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>723</v>
+        <v>770</v>
       </c>
       <c r="B77" t="s">
         <v>138</v>
@@ -14055,7 +15028,7 @@
         <v>44</v>
       </c>
       <c r="D77" t="s">
-        <v>724</v>
+        <v>771</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -14064,7 +15037,7 @@
         <v>8</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>725</v>
+        <v>772</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -14078,7 +15051,7 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>726</v>
+        <v>773</v>
       </c>
       <c r="B78" t="s">
         <v>138</v>
@@ -14087,7 +15060,7 @@
         <v>72</v>
       </c>
       <c r="D78" t="s">
-        <v>684</v>
+        <v>731</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -14096,7 +15069,7 @@
         <v>8</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H78">
         <v>5</v>
@@ -14110,7 +15083,7 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>727</v>
+        <v>774</v>
       </c>
       <c r="B79" t="s">
         <v>138</v>
@@ -14119,7 +15092,7 @@
         <v>44</v>
       </c>
       <c r="D79" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -14128,7 +15101,7 @@
         <v>8</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>728</v>
+        <v>775</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -14142,7 +15115,7 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>729</v>
+        <v>776</v>
       </c>
       <c r="B80" t="s">
         <v>138</v>
@@ -14151,7 +15124,7 @@
         <v>166</v>
       </c>
       <c r="D80" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -14160,7 +15133,7 @@
         <v>8</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>730</v>
+        <v>777</v>
       </c>
       <c r="H80">
         <v>5</v>
@@ -14174,7 +15147,7 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>731</v>
+        <v>778</v>
       </c>
       <c r="B81" t="s">
         <v>138</v>
@@ -14183,7 +15156,7 @@
         <v>44</v>
       </c>
       <c r="D81" t="s">
-        <v>724</v>
+        <v>771</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -14192,7 +15165,7 @@
         <v>8</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>725</v>
+        <v>772</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -14206,7 +15179,7 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>732</v>
+        <v>779</v>
       </c>
       <c r="B82" t="s">
         <v>138</v>
@@ -14215,7 +15188,7 @@
         <v>72</v>
       </c>
       <c r="D82" t="s">
-        <v>684</v>
+        <v>731</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -14224,7 +15197,7 @@
         <v>8</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H82">
         <v>5</v>
@@ -14238,10 +15211,10 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>733</v>
+        <v>780</v>
       </c>
       <c r="B83" t="s">
-        <v>667</v>
+        <v>714</v>
       </c>
       <c r="C83" t="s">
         <v>8</v>
@@ -14256,7 +15229,7 @@
         <v>8</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>668</v>
+        <v>715</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -14270,7 +15243,7 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>734</v>
+        <v>781</v>
       </c>
       <c r="B84" t="s">
         <v>138</v>
@@ -14279,7 +15252,7 @@
         <v>44</v>
       </c>
       <c r="D84" t="s">
-        <v>719</v>
+        <v>766</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -14288,7 +15261,7 @@
         <v>8</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>735</v>
+        <v>782</v>
       </c>
       <c r="H84">
         <v>18</v>
@@ -14302,7 +15275,7 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>736</v>
+        <v>783</v>
       </c>
       <c r="B85" t="s">
         <v>138</v>
@@ -14311,7 +15284,7 @@
         <v>166</v>
       </c>
       <c r="D85" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -14320,7 +15293,7 @@
         <v>8</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>737</v>
+        <v>784</v>
       </c>
       <c r="H85">
         <v>8</v>
@@ -14334,7 +15307,7 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>738</v>
+        <v>785</v>
       </c>
       <c r="B86" t="s">
         <v>138</v>
@@ -14343,7 +15316,7 @@
         <v>44</v>
       </c>
       <c r="D86" t="s">
-        <v>724</v>
+        <v>771</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -14352,7 +15325,7 @@
         <v>8</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>725</v>
+        <v>772</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -14366,7 +15339,7 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>739</v>
+        <v>786</v>
       </c>
       <c r="B87" t="s">
         <v>138</v>
@@ -14375,7 +15348,7 @@
         <v>72</v>
       </c>
       <c r="D87" t="s">
-        <v>684</v>
+        <v>731</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -14384,7 +15357,7 @@
         <v>8</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H87">
         <v>5</v>
@@ -14398,7 +15371,7 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>740</v>
+        <v>787</v>
       </c>
       <c r="B88" t="s">
         <v>138</v>
@@ -14407,7 +15380,7 @@
         <v>171</v>
       </c>
       <c r="D88" t="s">
-        <v>626</v>
+        <v>673</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -14416,7 +15389,7 @@
         <v>8</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H88">
         <v>2</v>
@@ -14430,7 +15403,7 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>741</v>
+        <v>788</v>
       </c>
       <c r="B89" t="s">
         <v>138</v>
@@ -14439,7 +15412,7 @@
         <v>169</v>
       </c>
       <c r="D89" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -14448,7 +15421,7 @@
         <v>8</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>742</v>
+        <v>789</v>
       </c>
       <c r="H89">
         <v>2</v>
@@ -14462,7 +15435,7 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>743</v>
+        <v>790</v>
       </c>
       <c r="B90" t="s">
         <v>138</v>
@@ -14471,7 +15444,7 @@
         <v>72</v>
       </c>
       <c r="D90" t="s">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -14480,7 +15453,7 @@
         <v>8</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>744</v>
+        <v>791</v>
       </c>
       <c r="H90">
         <v>6</v>
@@ -14494,7 +15467,7 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>745</v>
+        <v>792</v>
       </c>
       <c r="B91" t="s">
         <v>138</v>
@@ -14503,7 +15476,7 @@
         <v>171</v>
       </c>
       <c r="D91" t="s">
-        <v>626</v>
+        <v>673</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -14512,7 +15485,7 @@
         <v>8</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>746</v>
+        <v>793</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -14526,7 +15499,7 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>747</v>
+        <v>794</v>
       </c>
       <c r="B92" t="s">
         <v>138</v>
@@ -14535,7 +15508,7 @@
         <v>169</v>
       </c>
       <c r="D92" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -14544,7 +15517,7 @@
         <v>8</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>748</v>
+        <v>795</v>
       </c>
       <c r="H92">
         <v>5</v>
@@ -14558,7 +15531,7 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>749</v>
+        <v>796</v>
       </c>
       <c r="B93" t="s">
         <v>138</v>
@@ -14567,7 +15540,7 @@
         <v>72</v>
       </c>
       <c r="D93" t="s">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -14576,7 +15549,7 @@
         <v>8</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>750</v>
+        <v>797</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -14590,7 +15563,7 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>751</v>
+        <v>798</v>
       </c>
       <c r="B94" t="s">
         <v>138</v>
@@ -14599,7 +15572,7 @@
         <v>171</v>
       </c>
       <c r="D94" t="s">
-        <v>626</v>
+        <v>673</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -14608,7 +15581,7 @@
         <v>8</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H94">
         <v>4</v>
@@ -14622,7 +15595,7 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>752</v>
+        <v>799</v>
       </c>
       <c r="B95" t="s">
         <v>138</v>
@@ -14631,7 +15604,7 @@
         <v>169</v>
       </c>
       <c r="D95" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -14640,7 +15613,7 @@
         <v>8</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>748</v>
+        <v>795</v>
       </c>
       <c r="H95">
         <v>5</v>
@@ -14654,7 +15627,7 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>753</v>
+        <v>800</v>
       </c>
       <c r="B96" t="s">
         <v>138</v>
@@ -14663,7 +15636,7 @@
         <v>72</v>
       </c>
       <c r="D96" t="s">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -14672,7 +15645,7 @@
         <v>8</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>750</v>
+        <v>797</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -14686,7 +15659,7 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>754</v>
+        <v>801</v>
       </c>
       <c r="B97" t="s">
         <v>138</v>
@@ -14695,7 +15668,7 @@
         <v>166</v>
       </c>
       <c r="D97" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -14704,7 +15677,7 @@
         <v>8</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>755</v>
+        <v>802</v>
       </c>
       <c r="H97">
         <v>6</v>
@@ -14718,10 +15691,10 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>756</v>
+        <v>803</v>
       </c>
       <c r="B98" t="s">
-        <v>667</v>
+        <v>714</v>
       </c>
       <c r="C98" t="s">
         <v>8</v>
@@ -14736,7 +15709,7 @@
         <v>8</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>668</v>
+        <v>715</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -14750,7 +15723,7 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>757</v>
+        <v>804</v>
       </c>
       <c r="B99" t="s">
         <v>138</v>
@@ -14759,7 +15732,7 @@
         <v>169</v>
       </c>
       <c r="D99" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -14768,7 +15741,7 @@
         <v>8</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>758</v>
+        <v>805</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -14782,7 +15755,7 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>759</v>
+        <v>806</v>
       </c>
       <c r="B100" t="s">
         <v>138</v>
@@ -14791,7 +15764,7 @@
         <v>72</v>
       </c>
       <c r="D100" t="s">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
@@ -14800,7 +15773,7 @@
         <v>8</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>760</v>
+        <v>807</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -14814,7 +15787,7 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>761</v>
+        <v>808</v>
       </c>
       <c r="B101" t="s">
         <v>138</v>
@@ -14823,7 +15796,7 @@
         <v>166</v>
       </c>
       <c r="D101" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -14832,7 +15805,7 @@
         <v>8</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>762</v>
+        <v>809</v>
       </c>
       <c r="H101">
         <v>8</v>
@@ -14846,7 +15819,7 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>763</v>
+        <v>810</v>
       </c>
       <c r="B102" t="s">
         <v>138</v>
@@ -14855,7 +15828,7 @@
         <v>72</v>
       </c>
       <c r="D102" t="s">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -14864,7 +15837,7 @@
         <v>8</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>764</v>
+        <v>811</v>
       </c>
       <c r="H102">
         <v>8</v>
@@ -14878,7 +15851,7 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>765</v>
+        <v>812</v>
       </c>
       <c r="B103" t="s">
         <v>138</v>
@@ -14887,7 +15860,7 @@
         <v>169</v>
       </c>
       <c r="D103" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -14896,7 +15869,7 @@
         <v>8</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>766</v>
+        <v>813</v>
       </c>
       <c r="H103">
         <v>5</v>
@@ -14910,10 +15883,10 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>767</v>
+        <v>814</v>
       </c>
       <c r="B104" t="s">
-        <v>667</v>
+        <v>714</v>
       </c>
       <c r="C104" t="s">
         <v>8</v>
@@ -14928,7 +15901,7 @@
         <v>8</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>768</v>
+        <v>815</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -14942,7 +15915,7 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>769</v>
+        <v>816</v>
       </c>
       <c r="B105" t="s">
         <v>138</v>
@@ -14951,7 +15924,7 @@
         <v>166</v>
       </c>
       <c r="D105" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -14960,7 +15933,7 @@
         <v>8</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>770</v>
+        <v>817</v>
       </c>
       <c r="H105">
         <v>11</v>
@@ -14974,7 +15947,7 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>771</v>
+        <v>818</v>
       </c>
       <c r="B106" t="s">
         <v>138</v>
@@ -14983,7 +15956,7 @@
         <v>72</v>
       </c>
       <c r="D106" t="s">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -14992,7 +15965,7 @@
         <v>8</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H106">
         <v>10</v>
@@ -15006,7 +15979,7 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>772</v>
+        <v>819</v>
       </c>
       <c r="B107" t="s">
         <v>138</v>
@@ -15015,7 +15988,7 @@
         <v>169</v>
       </c>
       <c r="D107" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -15024,7 +15997,7 @@
         <v>8</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>773</v>
+        <v>820</v>
       </c>
       <c r="H107">
         <v>6</v>
@@ -15038,7 +16011,7 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>774</v>
+        <v>821</v>
       </c>
       <c r="B108" t="s">
         <v>138</v>
@@ -15047,7 +16020,7 @@
         <v>169</v>
       </c>
       <c r="D108" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -15056,7 +16029,7 @@
         <v>8</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>758</v>
+        <v>805</v>
       </c>
       <c r="H108">
         <v>1</v>
@@ -15070,7 +16043,7 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="B109" t="s">
         <v>138</v>
@@ -15079,7 +16052,7 @@
         <v>171</v>
       </c>
       <c r="D109" t="s">
-        <v>626</v>
+        <v>673</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -15088,7 +16061,7 @@
         <v>8</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>776</v>
+        <v>823</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -15102,7 +16075,7 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>777</v>
+        <v>824</v>
       </c>
       <c r="B110" t="s">
         <v>138</v>
@@ -15111,7 +16084,7 @@
         <v>44</v>
       </c>
       <c r="D110" t="s">
-        <v>778</v>
+        <v>825</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -15120,7 +16093,7 @@
         <v>8</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H110">
         <v>7</v>
@@ -15134,7 +16107,7 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>779</v>
+        <v>826</v>
       </c>
       <c r="B111" t="s">
         <v>138</v>
@@ -15143,7 +16116,7 @@
         <v>44</v>
       </c>
       <c r="D111" t="s">
-        <v>724</v>
+        <v>771</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -15152,7 +16125,7 @@
         <v>8</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H111">
         <v>8</v>
@@ -15166,7 +16139,7 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>780</v>
+        <v>827</v>
       </c>
       <c r="B112" t="s">
         <v>138</v>
@@ -15175,7 +16148,7 @@
         <v>171</v>
       </c>
       <c r="D112" t="s">
-        <v>626</v>
+        <v>673</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -15184,7 +16157,7 @@
         <v>8</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>781</v>
+        <v>828</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -15198,7 +16171,7 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>782</v>
+        <v>829</v>
       </c>
       <c r="B113" t="s">
         <v>138</v>
@@ -15207,7 +16180,7 @@
         <v>169</v>
       </c>
       <c r="D113" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -15216,7 +16189,7 @@
         <v>8</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>766</v>
+        <v>813</v>
       </c>
       <c r="H113">
         <v>5</v>
@@ -15230,7 +16203,7 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>783</v>
+        <v>830</v>
       </c>
       <c r="B114" t="s">
         <v>138</v>
@@ -15239,7 +16212,7 @@
         <v>171</v>
       </c>
       <c r="D114" t="s">
-        <v>626</v>
+        <v>673</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -15248,7 +16221,7 @@
         <v>8</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>781</v>
+        <v>828</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -15262,7 +16235,7 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>784</v>
+        <v>831</v>
       </c>
       <c r="B115" t="s">
         <v>138</v>
@@ -15271,7 +16244,7 @@
         <v>44</v>
       </c>
       <c r="D115" t="s">
-        <v>778</v>
+        <v>825</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -15280,7 +16253,7 @@
         <v>8</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>785</v>
+        <v>832</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -15294,7 +16267,7 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>786</v>
+        <v>833</v>
       </c>
       <c r="B116" t="s">
         <v>138</v>
@@ -15303,7 +16276,7 @@
         <v>169</v>
       </c>
       <c r="D116" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="E116" t="s">
         <v>8</v>
@@ -15312,7 +16285,7 @@
         <v>8</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>773</v>
+        <v>820</v>
       </c>
       <c r="H116">
         <v>6</v>
@@ -15326,7 +16299,7 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>787</v>
+        <v>834</v>
       </c>
       <c r="B117" t="s">
         <v>138</v>
@@ -15335,7 +16308,7 @@
         <v>166</v>
       </c>
       <c r="D117" t="s">
-        <v>628</v>
+        <v>675</v>
       </c>
       <c r="E117" t="s">
         <v>8</v>
@@ -15358,7 +16331,7 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>788</v>
+        <v>835</v>
       </c>
       <c r="B118" t="s">
         <v>138</v>
@@ -15367,7 +16340,7 @@
         <v>72</v>
       </c>
       <c r="D118" t="s">
-        <v>632</v>
+        <v>679</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -15390,7 +16363,7 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>789</v>
+        <v>836</v>
       </c>
       <c r="B119" t="s">
         <v>138</v>
@@ -15399,7 +16372,7 @@
         <v>44</v>
       </c>
       <c r="D119" t="s">
-        <v>634</v>
+        <v>681</v>
       </c>
       <c r="E119" t="s">
         <v>8</v>
@@ -15408,7 +16381,7 @@
         <v>8</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>790</v>
+        <v>837</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -15422,7 +16395,7 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>791</v>
+        <v>838</v>
       </c>
       <c r="B120" t="s">
         <v>138</v>
@@ -15431,7 +16404,7 @@
         <v>44</v>
       </c>
       <c r="D120" t="s">
-        <v>634</v>
+        <v>681</v>
       </c>
       <c r="E120" t="s">
         <v>8</v>
@@ -15440,7 +16413,7 @@
         <v>8</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>792</v>
+        <v>839</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -15454,7 +16427,7 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>793</v>
+        <v>840</v>
       </c>
       <c r="B121" t="s">
         <v>138</v>
@@ -15463,7 +16436,7 @@
         <v>171</v>
       </c>
       <c r="D121" t="s">
-        <v>626</v>
+        <v>673</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
@@ -15472,7 +16445,7 @@
         <v>8</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>794</v>
+        <v>841</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -15486,7 +16459,7 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>795</v>
+        <v>842</v>
       </c>
       <c r="B122" t="s">
         <v>138</v>
@@ -15495,7 +16468,7 @@
         <v>169</v>
       </c>
       <c r="D122" t="s">
-        <v>630</v>
+        <v>677</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>

--- a/content/jahrgaenge/Jg6.xlsx
+++ b/content/jahrgaenge/Jg6.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3156" uniqueCount="843">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3137" uniqueCount="845">
   <si>
     <t>Hinweise zu Jg6.xlsx</t>
   </si>
@@ -610,6 +610,9 @@
     <t>jg6-geo-5</t>
   </si>
   <si>
+    <t>jg6-de-3b</t>
+  </si>
+  <si>
     <t>Satzglieder</t>
   </si>
   <si>
@@ -673,10 +676,13 @@
     <t>weitere Dreieckseigenschaften und Vierecksberechnung</t>
   </si>
   <si>
+    <t>Ocean City</t>
+  </si>
+  <si>
     <t>Ocean City ODER Herr der Diebe</t>
   </si>
   <si>
-    <t>Ocean City: Flipbook als Lektürebegleitung. Herr der Diebe: Eine Textstelle umschreiben</t>
+    <t>Flipbook als Lektürebegleitung</t>
   </si>
   <si>
     <t>Peacemakers</t>
@@ -736,6 +742,12 @@
     <t>Ein eigenes Projekt erstellen und in einem digitalen Showroom präsentieren</t>
   </si>
   <si>
+    <t>Herr der Diebe</t>
+  </si>
+  <si>
+    <t>Eine Textstelle umschreiben</t>
+  </si>
+  <si>
     <t>Sätze würfeln</t>
   </si>
   <si>
@@ -1906,9 +1918,6 @@
     <t>Flipbook-Vorlage</t>
   </si>
   <si>
-    <t>Nur für Ocean City.</t>
-  </si>
-  <si>
     <t>Der erste Eindruck</t>
   </si>
   <si>
@@ -1985,9 +1994,6 @@
   </si>
   <si>
     <t>Laptop, Venedig-Quiz</t>
-  </si>
-  <si>
-    <t>Nur für Herr der Diebe.</t>
   </si>
   <si>
     <t>Ein Auftrag für Victor und eine Kinderbande</t>
@@ -4153,7 +4159,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -5151,6 +5157,44 @@
         <v>65</v>
       </c>
       <c r="L26" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>196</v>
+      </c>
+      <c r="B27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" t="s">
+        <v>179</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27">
+        <v>16</v>
+      </c>
+      <c r="G27" s="5">
+        <v>46398</v>
+      </c>
+      <c r="H27" s="5">
+        <v>46423</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" t="s">
+        <v>196</v>
+      </c>
+      <c r="K27" t="s">
+        <v>182</v>
+      </c>
+      <c r="L27" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -5177,7 +5221,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -5224,13 +5268,13 @@
         <v>44</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
@@ -5250,7 +5294,7 @@
         <v>166</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
@@ -5276,13 +5320,13 @@
         <v>72</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F4" t="s">
         <v>8</v>
@@ -5302,13 +5346,13 @@
         <v>169</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F5">
         <v>15</v>
@@ -5328,13 +5372,13 @@
         <v>171</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F6">
         <v>11</v>
@@ -5354,7 +5398,7 @@
         <v>166</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
@@ -5380,13 +5424,13 @@
         <v>44</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F8" t="s">
         <v>8</v>
@@ -5406,13 +5450,13 @@
         <v>72</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -5432,13 +5476,13 @@
         <v>169</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F10">
         <v>16</v>
@@ -5458,13 +5502,13 @@
         <v>171</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F11">
         <v>9</v>
@@ -5484,13 +5528,13 @@
         <v>72</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F12">
         <v>13</v>
@@ -5510,7 +5554,7 @@
         <v>166</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>8</v>
@@ -5536,13 +5580,13 @@
         <v>44</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F14" t="s">
         <v>8</v>
@@ -5562,13 +5606,13 @@
         <v>169</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F15">
         <v>16</v>
@@ -5588,13 +5632,13 @@
         <v>171</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F16">
         <v>11</v>
@@ -5614,13 +5658,13 @@
         <v>169</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F17" t="s">
         <v>8</v>
@@ -5640,7 +5684,7 @@
         <v>166</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>8</v>
@@ -5666,13 +5710,13 @@
         <v>72</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F19" t="s">
         <v>8</v>
@@ -5692,13 +5736,13 @@
         <v>44</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F20" t="s">
         <v>8</v>
@@ -5718,13 +5762,13 @@
         <v>171</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F21" t="s">
         <v>8</v>
@@ -5744,13 +5788,13 @@
         <v>44</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F22" t="s">
         <v>8</v>
@@ -5770,7 +5814,7 @@
         <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>8</v>
@@ -5796,7 +5840,7 @@
         <v>72</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>8</v>
@@ -5848,13 +5892,13 @@
         <v>171</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F26" t="s">
         <v>8</v>
@@ -5865,6 +5909,25 @@
       <c r="H26" s="2" t="s">
         <v>8</v>
       </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>196</v>
+      </c>
+      <c r="B27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
@@ -5928,7 +5991,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="D2" t="s">
         <v>93</v>
@@ -5940,7 +6003,7 @@
         <v>2</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>8</v>
@@ -5954,7 +6017,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D3" t="s">
         <v>182</v>
@@ -5966,7 +6029,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>8</v>
@@ -5980,7 +6043,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="D4" t="s">
         <v>93</v>
@@ -5992,7 +6055,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>8</v>
@@ -6006,7 +6069,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D5" t="s">
         <v>93</v>
@@ -6018,7 +6081,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>8</v>
@@ -6032,7 +6095,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="D6" t="s">
         <v>93</v>
@@ -6044,7 +6107,7 @@
         <v>2</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>8</v>
@@ -6058,7 +6121,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="D7" t="s">
         <v>182</v>
@@ -6070,7 +6133,7 @@
         <v>3</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>8</v>
@@ -6084,7 +6147,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="D8" t="s">
         <v>93</v>
@@ -6096,7 +6159,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>8</v>
@@ -6110,7 +6173,7 @@
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="D9" t="s">
         <v>93</v>
@@ -6122,7 +6185,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>8</v>
@@ -6136,7 +6199,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D10" t="s">
         <v>93</v>
@@ -6148,7 +6211,7 @@
         <v>3</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>8</v>
@@ -6162,7 +6225,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D11" t="s">
         <v>93</v>
@@ -6174,7 +6237,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>8</v>
@@ -6188,7 +6251,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D12" t="s">
         <v>93</v>
@@ -6200,7 +6263,7 @@
         <v>3</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>8</v>
@@ -6214,7 +6277,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D13" t="s">
         <v>182</v>
@@ -6226,7 +6289,7 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>8</v>
@@ -6240,7 +6303,7 @@
         <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D14" t="s">
         <v>93</v>
@@ -6252,7 +6315,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>8</v>
@@ -6266,7 +6329,7 @@
         <v>2</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D15" t="s">
         <v>93</v>
@@ -6278,7 +6341,7 @@
         <v>2</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>8</v>
@@ -6292,7 +6355,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D16" t="s">
         <v>93</v>
@@ -6304,7 +6367,7 @@
         <v>2</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>8</v>
@@ -6318,7 +6381,7 @@
         <v>4</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D17" t="s">
         <v>93</v>
@@ -6330,7 +6393,7 @@
         <v>2</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>8</v>
@@ -6344,7 +6407,7 @@
         <v>5</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D18" t="s">
         <v>93</v>
@@ -6356,7 +6419,7 @@
         <v>1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>8</v>
@@ -6370,7 +6433,7 @@
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="D19" t="s">
         <v>93</v>
@@ -6382,7 +6445,7 @@
         <v>2</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>8</v>
@@ -6396,7 +6459,7 @@
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D20" t="s">
         <v>182</v>
@@ -6408,7 +6471,7 @@
         <v>2</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>8</v>
@@ -6422,7 +6485,7 @@
         <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D21" t="s">
         <v>93</v>
@@ -6434,7 +6497,7 @@
         <v>2</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>8</v>
@@ -6448,7 +6511,7 @@
         <v>9</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D22" t="s">
         <v>93</v>
@@ -6460,7 +6523,7 @@
         <v>3</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>8</v>
@@ -6474,7 +6537,7 @@
         <v>10</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D23" t="s">
         <v>93</v>
@@ -6486,7 +6549,7 @@
         <v>2</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>8</v>
@@ -6500,7 +6563,7 @@
         <v>11</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D24" t="s">
         <v>93</v>
@@ -6512,7 +6575,7 @@
         <v>3</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>8</v>
@@ -6526,7 +6589,7 @@
         <v>12</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D25" t="s">
         <v>93</v>
@@ -6538,7 +6601,7 @@
         <v>3</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>8</v>
@@ -6552,7 +6615,7 @@
         <v>13</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D26" t="s">
         <v>93</v>
@@ -6578,7 +6641,7 @@
         <v>14</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D27" t="s">
         <v>93</v>
@@ -6590,7 +6653,7 @@
         <v>3</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>8</v>
@@ -6604,7 +6667,7 @@
         <v>15</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D28" t="s">
         <v>93</v>
@@ -6616,7 +6679,7 @@
         <v>3</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>8</v>
@@ -6630,7 +6693,7 @@
         <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D29" t="s">
         <v>182</v>
@@ -6656,7 +6719,7 @@
         <v>17</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D30" t="s">
         <v>182</v>
@@ -6682,7 +6745,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D31" t="s">
         <v>93</v>
@@ -6694,7 +6757,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>8</v>
@@ -6708,7 +6771,7 @@
         <v>2</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D32" t="s">
         <v>93</v>
@@ -6720,7 +6783,7 @@
         <v>2</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>8</v>
@@ -6734,7 +6797,7 @@
         <v>3</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D33" t="s">
         <v>93</v>
@@ -6746,7 +6809,7 @@
         <v>2</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>8</v>
@@ -6760,7 +6823,7 @@
         <v>4</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D34" t="s">
         <v>93</v>
@@ -6772,7 +6835,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>8</v>
@@ -6786,7 +6849,7 @@
         <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D35" t="s">
         <v>93</v>
@@ -6798,7 +6861,7 @@
         <v>2</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>8</v>
@@ -6812,7 +6875,7 @@
         <v>6</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D36" t="s">
         <v>182</v>
@@ -6824,7 +6887,7 @@
         <v>2</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>8</v>
@@ -6838,7 +6901,7 @@
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D37" t="s">
         <v>93</v>
@@ -6850,7 +6913,7 @@
         <v>2</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>8</v>
@@ -6864,7 +6927,7 @@
         <v>8</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D38" t="s">
         <v>93</v>
@@ -6876,7 +6939,7 @@
         <v>2</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>8</v>
@@ -6890,7 +6953,7 @@
         <v>9</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D39" t="s">
         <v>93</v>
@@ -6902,7 +6965,7 @@
         <v>3</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>8</v>
@@ -6916,7 +6979,7 @@
         <v>10</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D40" t="s">
         <v>93</v>
@@ -6928,7 +6991,7 @@
         <v>3</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>8</v>
@@ -6942,7 +7005,7 @@
         <v>11</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D41" t="s">
         <v>93</v>
@@ -6954,7 +7017,7 @@
         <v>3</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>8</v>
@@ -6968,7 +7031,7 @@
         <v>12</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="D42" t="s">
         <v>182</v>
@@ -6980,7 +7043,7 @@
         <v>2</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>8</v>
@@ -6994,7 +7057,7 @@
         <v>13</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D43" t="s">
         <v>93</v>
@@ -7006,7 +7069,7 @@
         <v>2</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>8</v>
@@ -7020,7 +7083,7 @@
         <v>1</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D44" t="s">
         <v>93</v>
@@ -7032,7 +7095,7 @@
         <v>1</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>8</v>
@@ -7046,7 +7109,7 @@
         <v>2</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D45" t="s">
         <v>93</v>
@@ -7058,7 +7121,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>8</v>
@@ -7072,7 +7135,7 @@
         <v>3</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D46" t="s">
         <v>93</v>
@@ -7084,7 +7147,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>8</v>
@@ -7098,7 +7161,7 @@
         <v>4</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D47" t="s">
         <v>182</v>
@@ -7110,7 +7173,7 @@
         <v>1</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>8</v>
@@ -7124,7 +7187,7 @@
         <v>5</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="D48" t="s">
         <v>93</v>
@@ -7136,7 +7199,7 @@
         <v>2</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>8</v>
@@ -7150,7 +7213,7 @@
         <v>6</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D49" t="s">
         <v>93</v>
@@ -7162,7 +7225,7 @@
         <v>2</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>8</v>
@@ -7176,7 +7239,7 @@
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D50" t="s">
         <v>93</v>
@@ -7188,7 +7251,7 @@
         <v>2</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>8</v>
@@ -7202,7 +7265,7 @@
         <v>8</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D51" t="s">
         <v>93</v>
@@ -7214,7 +7277,7 @@
         <v>3</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>8</v>
@@ -7228,7 +7291,7 @@
         <v>9</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D52" t="s">
         <v>93</v>
@@ -7240,7 +7303,7 @@
         <v>3</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>8</v>
@@ -7254,7 +7317,7 @@
         <v>10</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D53" t="s">
         <v>182</v>
@@ -7266,7 +7329,7 @@
         <v>2</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>8</v>
@@ -7280,7 +7343,7 @@
         <v>11</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D54" t="s">
         <v>93</v>
@@ -7292,10 +7355,10 @@
         <v>3</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -7306,7 +7369,7 @@
         <v>12</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D55" t="s">
         <v>182</v>
@@ -7318,7 +7381,7 @@
         <v>3</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>8</v>
@@ -7332,7 +7395,7 @@
         <v>13</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D56" t="s">
         <v>93</v>
@@ -7344,7 +7407,7 @@
         <v>3</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>8</v>
@@ -7358,7 +7421,7 @@
         <v>1</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D57" t="s">
         <v>93</v>
@@ -7370,7 +7433,7 @@
         <v>2</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>8</v>
@@ -7384,7 +7447,7 @@
         <v>2</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D58" t="s">
         <v>182</v>
@@ -7396,7 +7459,7 @@
         <v>1</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>8</v>
@@ -7410,7 +7473,7 @@
         <v>3</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="D59" t="s">
         <v>93</v>
@@ -7422,7 +7485,7 @@
         <v>2</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>8</v>
@@ -7436,7 +7499,7 @@
         <v>4</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D60" t="s">
         <v>182</v>
@@ -7448,7 +7511,7 @@
         <v>1</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>8</v>
@@ -7462,7 +7525,7 @@
         <v>5</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D61" t="s">
         <v>93</v>
@@ -7474,7 +7537,7 @@
         <v>2</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>8</v>
@@ -7488,7 +7551,7 @@
         <v>6</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D62" t="s">
         <v>93</v>
@@ -7500,7 +7563,7 @@
         <v>1</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>8</v>
@@ -7514,7 +7577,7 @@
         <v>7</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D63" t="s">
         <v>93</v>
@@ -7526,7 +7589,7 @@
         <v>2</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>8</v>
@@ -7540,7 +7603,7 @@
         <v>8</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D64" t="s">
         <v>93</v>
@@ -7552,7 +7615,7 @@
         <v>2</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>8</v>
@@ -7566,7 +7629,7 @@
         <v>9</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D65" t="s">
         <v>93</v>
@@ -7578,7 +7641,7 @@
         <v>3</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>8</v>
@@ -7592,7 +7655,7 @@
         <v>10</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="D66" t="s">
         <v>182</v>
@@ -7604,7 +7667,7 @@
         <v>1</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>8</v>
@@ -7618,7 +7681,7 @@
         <v>11</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D67" t="s">
         <v>93</v>
@@ -7630,7 +7693,7 @@
         <v>1</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>8</v>
@@ -7644,7 +7707,7 @@
         <v>12</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D68" t="s">
         <v>93</v>
@@ -7656,7 +7719,7 @@
         <v>2</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>8</v>
@@ -7670,7 +7733,7 @@
         <v>13</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D69" t="s">
         <v>93</v>
@@ -7682,7 +7745,7 @@
         <v>3</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>8</v>
@@ -7696,7 +7759,7 @@
         <v>14</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D70" t="s">
         <v>93</v>
@@ -7708,7 +7771,7 @@
         <v>3</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>8</v>
@@ -7722,7 +7785,7 @@
         <v>1</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D71" t="s">
         <v>93</v>
@@ -7734,7 +7797,7 @@
         <v>1</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>8</v>
@@ -7748,7 +7811,7 @@
         <v>2</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="D72" t="s">
         <v>93</v>
@@ -7760,7 +7823,7 @@
         <v>2</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>8</v>
@@ -7774,7 +7837,7 @@
         <v>3</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D73" t="s">
         <v>182</v>
@@ -7786,7 +7849,7 @@
         <v>2</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>8</v>
@@ -7800,7 +7863,7 @@
         <v>4</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D74" t="s">
         <v>93</v>
@@ -7812,7 +7875,7 @@
         <v>2</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>8</v>
@@ -7826,7 +7889,7 @@
         <v>5</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D75" t="s">
         <v>93</v>
@@ -7838,7 +7901,7 @@
         <v>2</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>8</v>
@@ -7852,7 +7915,7 @@
         <v>6</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D76" t="s">
         <v>93</v>
@@ -7864,7 +7927,7 @@
         <v>2</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>8</v>
@@ -7878,7 +7941,7 @@
         <v>7</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D77" t="s">
         <v>182</v>
@@ -7890,7 +7953,7 @@
         <v>3</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>8</v>
@@ -7904,7 +7967,7 @@
         <v>8</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D78" t="s">
         <v>93</v>
@@ -7916,7 +7979,7 @@
         <v>2</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>8</v>
@@ -7930,7 +7993,7 @@
         <v>1</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D79" t="s">
         <v>93</v>
@@ -7942,7 +8005,7 @@
         <v>1</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>8</v>
@@ -7956,7 +8019,7 @@
         <v>2</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D80" t="s">
         <v>93</v>
@@ -7968,7 +8031,7 @@
         <v>2</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>8</v>
@@ -7982,7 +8045,7 @@
         <v>3</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="D81" t="s">
         <v>93</v>
@@ -7994,7 +8057,7 @@
         <v>1</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>8</v>
@@ -8008,7 +8071,7 @@
         <v>4</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D82" t="s">
         <v>93</v>
@@ -8020,7 +8083,7 @@
         <v>1</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>8</v>
@@ -8034,7 +8097,7 @@
         <v>5</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D83" t="s">
         <v>182</v>
@@ -8046,7 +8109,7 @@
         <v>3</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>8</v>
@@ -8060,7 +8123,7 @@
         <v>6</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D84" t="s">
         <v>93</v>
@@ -8072,7 +8135,7 @@
         <v>3</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>8</v>
@@ -8086,7 +8149,7 @@
         <v>7</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D85" t="s">
         <v>93</v>
@@ -8098,7 +8161,7 @@
         <v>3</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>8</v>
@@ -8112,7 +8175,7 @@
         <v>8</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="D86" t="s">
         <v>93</v>
@@ -8124,7 +8187,7 @@
         <v>2</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>8</v>
@@ -8138,7 +8201,7 @@
         <v>9</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="D87" t="s">
         <v>93</v>
@@ -8150,7 +8213,7 @@
         <v>2</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>8</v>
@@ -8164,7 +8227,7 @@
         <v>10</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D88" t="s">
         <v>182</v>
@@ -8176,7 +8239,7 @@
         <v>2</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>8</v>
@@ -8190,7 +8253,7 @@
         <v>11</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="D89" t="s">
         <v>93</v>
@@ -8202,7 +8265,7 @@
         <v>1</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>8</v>
@@ -8216,7 +8279,7 @@
         <v>12</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D90" t="s">
         <v>93</v>
@@ -8228,7 +8291,7 @@
         <v>3</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>8</v>
@@ -8242,7 +8305,7 @@
         <v>13</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D91" t="s">
         <v>93</v>
@@ -8268,7 +8331,7 @@
         <v>14</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D92" t="s">
         <v>93</v>
@@ -8280,7 +8343,7 @@
         <v>1</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>8</v>
@@ -8294,7 +8357,7 @@
         <v>15</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D93" t="s">
         <v>93</v>
@@ -8306,7 +8369,7 @@
         <v>3</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>8</v>
@@ -8320,7 +8383,7 @@
         <v>16</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="D94" t="s">
         <v>93</v>
@@ -8332,7 +8395,7 @@
         <v>2</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>8</v>
@@ -8346,7 +8409,7 @@
         <v>1</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D95" t="s">
         <v>93</v>
@@ -8358,7 +8421,7 @@
         <v>2</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>8</v>
@@ -8372,7 +8435,7 @@
         <v>2</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D96" t="s">
         <v>93</v>
@@ -8384,7 +8447,7 @@
         <v>1</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>8</v>
@@ -8398,7 +8461,7 @@
         <v>3</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D97" t="s">
         <v>93</v>
@@ -8410,7 +8473,7 @@
         <v>1</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>8</v>
@@ -8424,7 +8487,7 @@
         <v>4</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D98" t="s">
         <v>93</v>
@@ -8436,7 +8499,7 @@
         <v>1</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>8</v>
@@ -8450,7 +8513,7 @@
         <v>5</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="D99" t="s">
         <v>93</v>
@@ -8462,7 +8525,7 @@
         <v>2</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>8</v>
@@ -8476,7 +8539,7 @@
         <v>6</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="D100" t="s">
         <v>182</v>
@@ -8488,7 +8551,7 @@
         <v>1</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>8</v>
@@ -8502,7 +8565,7 @@
         <v>7</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="D101" t="s">
         <v>93</v>
@@ -8514,7 +8577,7 @@
         <v>1</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>8</v>
@@ -8528,7 +8591,7 @@
         <v>8</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D102" t="s">
         <v>93</v>
@@ -8540,7 +8603,7 @@
         <v>1</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>8</v>
@@ -8554,7 +8617,7 @@
         <v>9</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="D103" t="s">
         <v>93</v>
@@ -8566,7 +8629,7 @@
         <v>3</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>8</v>
@@ -8580,7 +8643,7 @@
         <v>10</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="D104" t="s">
         <v>182</v>
@@ -8592,7 +8655,7 @@
         <v>1</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>8</v>
@@ -8606,7 +8669,7 @@
         <v>11</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D105" t="s">
         <v>93</v>
@@ -8618,7 +8681,7 @@
         <v>3</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>8</v>
@@ -8632,7 +8695,7 @@
         <v>12</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D106" t="s">
         <v>93</v>
@@ -8644,7 +8707,7 @@
         <v>3</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>8</v>
@@ -8658,7 +8721,7 @@
         <v>13</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="D107" t="s">
         <v>182</v>
@@ -8670,7 +8733,7 @@
         <v>1</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>8</v>
@@ -8684,7 +8747,7 @@
         <v>14</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="D108" t="s">
         <v>93</v>
@@ -8696,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>8</v>
@@ -8710,7 +8773,7 @@
         <v>15</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="D109" t="s">
         <v>182</v>
@@ -8722,7 +8785,7 @@
         <v>1</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>8</v>
@@ -8736,7 +8799,7 @@
         <v>16</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="D110" t="s">
         <v>93</v>
@@ -8748,7 +8811,7 @@
         <v>2</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>8</v>
@@ -8762,7 +8825,7 @@
         <v>1</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D111" t="s">
         <v>93</v>
@@ -8774,7 +8837,7 @@
         <v>1</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>8</v>
@@ -8788,7 +8851,7 @@
         <v>2</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="D112" t="s">
         <v>93</v>
@@ -8800,7 +8863,7 @@
         <v>1</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>8</v>
@@ -8814,7 +8877,7 @@
         <v>3</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="D113" t="s">
         <v>93</v>
@@ -8840,7 +8903,7 @@
         <v>4</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D114" t="s">
         <v>93</v>
@@ -8852,7 +8915,7 @@
         <v>2</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>8</v>
@@ -8866,7 +8929,7 @@
         <v>5</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="D115" t="s">
         <v>182</v>
@@ -8878,7 +8941,7 @@
         <v>2</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>8</v>
@@ -8892,7 +8955,7 @@
         <v>6</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="D116" t="s">
         <v>93</v>
@@ -8904,7 +8967,7 @@
         <v>2</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>8</v>
@@ -8918,7 +8981,7 @@
         <v>7</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D117" t="s">
         <v>93</v>
@@ -8930,7 +8993,7 @@
         <v>2</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>8</v>
@@ -8944,7 +9007,7 @@
         <v>8</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="D118" t="s">
         <v>93</v>
@@ -8956,7 +9019,7 @@
         <v>3</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>8</v>
@@ -8970,7 +9033,7 @@
         <v>9</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D119" t="s">
         <v>93</v>
@@ -8982,7 +9045,7 @@
         <v>1</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>8</v>
@@ -8996,7 +9059,7 @@
         <v>10</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D120" t="s">
         <v>93</v>
@@ -9008,7 +9071,7 @@
         <v>2</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>8</v>
@@ -9022,7 +9085,7 @@
         <v>11</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="D121" t="s">
         <v>182</v>
@@ -9034,7 +9097,7 @@
         <v>3</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>8</v>
@@ -9048,7 +9111,7 @@
         <v>12</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="D122" t="s">
         <v>93</v>
@@ -9060,7 +9123,7 @@
         <v>2</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>8</v>
@@ -9074,7 +9137,7 @@
         <v>13</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="D123" t="s">
         <v>93</v>
@@ -9086,7 +9149,7 @@
         <v>3</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>8</v>
@@ -9100,7 +9163,7 @@
         <v>14</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D124" t="s">
         <v>93</v>
@@ -9112,7 +9175,7 @@
         <v>1</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>8</v>
@@ -9126,7 +9189,7 @@
         <v>15</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="D125" t="s">
         <v>93</v>
@@ -9138,7 +9201,7 @@
         <v>3</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>8</v>
@@ -9152,7 +9215,7 @@
         <v>16</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="D126" t="s">
         <v>93</v>
@@ -9178,7 +9241,7 @@
         <v>17</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D127" t="s">
         <v>93</v>
@@ -9190,7 +9253,7 @@
         <v>3</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>8</v>
@@ -9204,7 +9267,7 @@
         <v>1</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="D128" t="s">
         <v>93</v>
@@ -9216,7 +9279,7 @@
         <v>1</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>8</v>
@@ -9230,7 +9293,7 @@
         <v>2</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="D129" t="s">
         <v>93</v>
@@ -9242,7 +9305,7 @@
         <v>2</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>8</v>
@@ -9256,7 +9319,7 @@
         <v>3</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="D130" t="s">
         <v>93</v>
@@ -9268,7 +9331,7 @@
         <v>3</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>8</v>
@@ -9282,7 +9345,7 @@
         <v>4</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="D131" t="s">
         <v>93</v>
@@ -9294,7 +9357,7 @@
         <v>1</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>8</v>
@@ -9308,7 +9371,7 @@
         <v>5</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="D132" t="s">
         <v>93</v>
@@ -9320,7 +9383,7 @@
         <v>2</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>8</v>
@@ -9334,7 +9397,7 @@
         <v>6</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D133" t="s">
         <v>93</v>
@@ -9346,7 +9409,7 @@
         <v>1</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>8</v>
@@ -9360,7 +9423,7 @@
         <v>7</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="D134" t="s">
         <v>93</v>
@@ -9372,7 +9435,7 @@
         <v>1</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>8</v>
@@ -9386,7 +9449,7 @@
         <v>8</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D135" t="s">
         <v>182</v>
@@ -9398,7 +9461,7 @@
         <v>2</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>8</v>
@@ -9412,7 +9475,7 @@
         <v>9</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D136" t="s">
         <v>93</v>
@@ -9424,7 +9487,7 @@
         <v>2</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>8</v>
@@ -9438,7 +9501,7 @@
         <v>10</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="D137" t="s">
         <v>182</v>
@@ -9450,7 +9513,7 @@
         <v>1</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>8</v>
@@ -9464,7 +9527,7 @@
         <v>11</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="D138" t="s">
         <v>182</v>
@@ -9476,7 +9539,7 @@
         <v>2</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>8</v>
@@ -9490,7 +9553,7 @@
         <v>12</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D139" t="s">
         <v>93</v>
@@ -9502,7 +9565,7 @@
         <v>2</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>8</v>
@@ -9516,7 +9579,7 @@
         <v>13</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="D140" t="s">
         <v>182</v>
@@ -9528,7 +9591,7 @@
         <v>2</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>8</v>
@@ -9542,7 +9605,7 @@
         <v>14</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="D141" t="s">
         <v>93</v>
@@ -9554,7 +9617,7 @@
         <v>1</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>8</v>
@@ -9568,7 +9631,7 @@
         <v>1</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="D142" t="s">
         <v>93</v>
@@ -9580,7 +9643,7 @@
         <v>3</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>8</v>
@@ -9594,7 +9657,7 @@
         <v>2</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D143" t="s">
         <v>93</v>
@@ -9606,7 +9669,7 @@
         <v>3</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>8</v>
@@ -9620,7 +9683,7 @@
         <v>3</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="D144" t="s">
         <v>93</v>
@@ -9632,7 +9695,7 @@
         <v>2</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>8</v>
@@ -9646,7 +9709,7 @@
         <v>4</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="D145" t="s">
         <v>93</v>
@@ -9658,7 +9721,7 @@
         <v>3</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>8</v>
@@ -9672,7 +9735,7 @@
         <v>5</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="D146" t="s">
         <v>182</v>
@@ -9684,7 +9747,7 @@
         <v>1</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>8</v>
@@ -9698,7 +9761,7 @@
         <v>6</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="D147" t="s">
         <v>93</v>
@@ -9710,7 +9773,7 @@
         <v>3</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>8</v>
@@ -9724,7 +9787,7 @@
         <v>7</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="D148" t="s">
         <v>93</v>
@@ -9736,7 +9799,7 @@
         <v>2</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>8</v>
@@ -9750,7 +9813,7 @@
         <v>8</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D149" t="s">
         <v>93</v>
@@ -9762,7 +9825,7 @@
         <v>2</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>8</v>
@@ -9776,7 +9839,7 @@
         <v>9</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D150" t="s">
         <v>93</v>
@@ -9788,7 +9851,7 @@
         <v>2</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>8</v>
@@ -9802,7 +9865,7 @@
         <v>10</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="D151" t="s">
         <v>93</v>
@@ -9814,7 +9877,7 @@
         <v>3</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>8</v>
@@ -9828,7 +9891,7 @@
         <v>11</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="D152" t="s">
         <v>93</v>
@@ -9840,7 +9903,7 @@
         <v>2</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>8</v>
@@ -9854,7 +9917,7 @@
         <v>12</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="D153" t="s">
         <v>182</v>
@@ -9866,7 +9929,7 @@
         <v>3</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>8</v>
@@ -9880,7 +9943,7 @@
         <v>13</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="D154" t="s">
         <v>182</v>
@@ -9892,7 +9955,7 @@
         <v>2</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>8</v>
@@ -9906,7 +9969,7 @@
         <v>14</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D155" t="s">
         <v>182</v>
@@ -9918,7 +9981,7 @@
         <v>2</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>8</v>
@@ -9932,7 +9995,7 @@
         <v>1</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="D156" t="s">
         <v>93</v>
@@ -9944,7 +10007,7 @@
         <v>1</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>8</v>
@@ -9958,7 +10021,7 @@
         <v>2</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="D157" t="s">
         <v>93</v>
@@ -9970,7 +10033,7 @@
         <v>2</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>8</v>
@@ -9984,7 +10047,7 @@
         <v>3</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="D158" t="s">
         <v>93</v>
@@ -9996,7 +10059,7 @@
         <v>2</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>8</v>
@@ -10010,7 +10073,7 @@
         <v>4</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="D159" t="s">
         <v>93</v>
@@ -10022,7 +10085,7 @@
         <v>3</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>8</v>
@@ -10036,7 +10099,7 @@
         <v>5</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="D160" t="s">
         <v>93</v>
@@ -10048,7 +10111,7 @@
         <v>2</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>8</v>
@@ -10062,7 +10125,7 @@
         <v>6</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="D161" t="s">
         <v>93</v>
@@ -10074,7 +10137,7 @@
         <v>3</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>8</v>
@@ -10088,7 +10151,7 @@
         <v>7</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="D162" t="s">
         <v>182</v>
@@ -10100,7 +10163,7 @@
         <v>2</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>8</v>
@@ -10114,7 +10177,7 @@
         <v>8</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="D163" t="s">
         <v>93</v>
@@ -10126,7 +10189,7 @@
         <v>1</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>8</v>
@@ -10140,7 +10203,7 @@
         <v>9</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="D164" t="s">
         <v>182</v>
@@ -10152,7 +10215,7 @@
         <v>2</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>8</v>
@@ -10166,7 +10229,7 @@
         <v>10</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D165" t="s">
         <v>93</v>
@@ -10178,7 +10241,7 @@
         <v>3</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>8</v>
@@ -10192,7 +10255,7 @@
         <v>11</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="D166" t="s">
         <v>182</v>
@@ -10204,7 +10267,7 @@
         <v>2</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>8</v>
@@ -10218,7 +10281,7 @@
         <v>12</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="D167" t="s">
         <v>93</v>
@@ -10230,7 +10293,7 @@
         <v>2</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>8</v>
@@ -10244,7 +10307,7 @@
         <v>13</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="D168" t="s">
         <v>93</v>
@@ -10256,10 +10319,10 @@
         <v>3</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
@@ -10270,7 +10333,7 @@
         <v>14</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="D169" t="s">
         <v>182</v>
@@ -10282,7 +10345,7 @@
         <v>3</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>8</v>
@@ -10296,7 +10359,7 @@
         <v>1</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="D170" t="s">
         <v>93</v>
@@ -10308,7 +10371,7 @@
         <v>1</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>8</v>
@@ -10322,7 +10385,7 @@
         <v>2</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="D171" t="s">
         <v>93</v>
@@ -10334,7 +10397,7 @@
         <v>1</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>8</v>
@@ -10348,7 +10411,7 @@
         <v>3</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="D172" t="s">
         <v>93</v>
@@ -10360,7 +10423,7 @@
         <v>2</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>8</v>
@@ -10374,7 +10437,7 @@
         <v>4</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="D173" t="s">
         <v>93</v>
@@ -10386,7 +10449,7 @@
         <v>1</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>8</v>
@@ -10400,7 +10463,7 @@
         <v>5</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="D174" t="s">
         <v>93</v>
@@ -10412,7 +10475,7 @@
         <v>3</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>8</v>
@@ -10426,7 +10489,7 @@
         <v>6</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="D175" t="s">
         <v>93</v>
@@ -10438,7 +10501,7 @@
         <v>2</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>8</v>
@@ -10452,7 +10515,7 @@
         <v>7</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="D176" t="s">
         <v>93</v>
@@ -10464,7 +10527,7 @@
         <v>2</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>8</v>
@@ -10478,7 +10541,7 @@
         <v>8</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="D177" t="s">
         <v>93</v>
@@ -10490,7 +10553,7 @@
         <v>3</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>8</v>
@@ -10504,7 +10567,7 @@
         <v>9</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="D178" t="s">
         <v>93</v>
@@ -10516,7 +10579,7 @@
         <v>2</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>8</v>
@@ -10530,7 +10593,7 @@
         <v>10</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="D179" t="s">
         <v>93</v>
@@ -10542,7 +10605,7 @@
         <v>2</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>8</v>
@@ -10556,7 +10619,7 @@
         <v>11</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D180" t="s">
         <v>182</v>
@@ -10568,7 +10631,7 @@
         <v>2</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>8</v>
@@ -10582,7 +10645,7 @@
         <v>12</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="D181" t="s">
         <v>93</v>
@@ -10594,7 +10657,7 @@
         <v>2</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>8</v>
@@ -10608,7 +10671,7 @@
         <v>13</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="D182" t="s">
         <v>182</v>
@@ -10620,7 +10683,7 @@
         <v>2</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>8</v>
@@ -10634,7 +10697,7 @@
         <v>1</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="D183" t="s">
         <v>182</v>
@@ -10646,7 +10709,7 @@
         <v>2</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>8</v>
@@ -10660,7 +10723,7 @@
         <v>2</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="D184" t="s">
         <v>93</v>
@@ -10672,7 +10735,7 @@
         <v>3</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>8</v>
@@ -10686,7 +10749,7 @@
         <v>3</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="D185" t="s">
         <v>93</v>
@@ -10698,7 +10761,7 @@
         <v>1</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>8</v>
@@ -10712,7 +10775,7 @@
         <v>4</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="D186" t="s">
         <v>93</v>
@@ -10724,7 +10787,7 @@
         <v>2</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>8</v>
@@ -10738,7 +10801,7 @@
         <v>5</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="D187" t="s">
         <v>93</v>
@@ -10750,7 +10813,7 @@
         <v>2</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>8</v>
@@ -10764,7 +10827,7 @@
         <v>6</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="D188" t="s">
         <v>182</v>
@@ -10776,7 +10839,7 @@
         <v>3</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>8</v>
@@ -10790,7 +10853,7 @@
         <v>7</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="D189" t="s">
         <v>93</v>
@@ -10802,7 +10865,7 @@
         <v>2</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>8</v>
@@ -10816,7 +10879,7 @@
         <v>8</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="D190" t="s">
         <v>93</v>
@@ -10828,7 +10891,7 @@
         <v>3</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>8</v>
@@ -10842,7 +10905,7 @@
         <v>9</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D191" t="s">
         <v>93</v>
@@ -10854,7 +10917,7 @@
         <v>3</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>8</v>
@@ -10868,7 +10931,7 @@
         <v>10</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="D192" t="s">
         <v>93</v>
@@ -10880,7 +10943,7 @@
         <v>2</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>8</v>
@@ -10894,7 +10957,7 @@
         <v>11</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="D193" t="s">
         <v>182</v>
@@ -10906,7 +10969,7 @@
         <v>2</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>8</v>
@@ -10920,7 +10983,7 @@
         <v>1</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="D194" t="s">
         <v>182</v>
@@ -10932,7 +10995,7 @@
         <v>1</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>8</v>
@@ -10946,7 +11009,7 @@
         <v>2</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="D195" t="s">
         <v>93</v>
@@ -10958,7 +11021,7 @@
         <v>2</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>8</v>
@@ -10972,7 +11035,7 @@
         <v>3</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="D196" t="s">
         <v>93</v>
@@ -10984,7 +11047,7 @@
         <v>2</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>8</v>
@@ -10998,7 +11061,7 @@
         <v>4</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="D197" t="s">
         <v>93</v>
@@ -11010,7 +11073,7 @@
         <v>2</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>8</v>
@@ -11024,7 +11087,7 @@
         <v>5</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="D198" t="s">
         <v>93</v>
@@ -11036,7 +11099,7 @@
         <v>3</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>8</v>
@@ -11050,7 +11113,7 @@
         <v>6</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="D199" t="s">
         <v>93</v>
@@ -11062,7 +11125,7 @@
         <v>2</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>8</v>
@@ -11076,7 +11139,7 @@
         <v>7</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="D200" t="s">
         <v>182</v>
@@ -11088,7 +11151,7 @@
         <v>2</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>8</v>
@@ -11102,7 +11165,7 @@
         <v>8</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="D201" t="s">
         <v>93</v>
@@ -11114,7 +11177,7 @@
         <v>2</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>8</v>
@@ -11128,7 +11191,7 @@
         <v>9</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="D202" t="s">
         <v>182</v>
@@ -11140,7 +11203,7 @@
         <v>3</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>8</v>
@@ -11154,7 +11217,7 @@
         <v>10</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="D203" t="s">
         <v>93</v>
@@ -11166,7 +11229,7 @@
         <v>2</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>8</v>
@@ -11180,7 +11243,7 @@
         <v>11</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="D204" t="s">
         <v>93</v>
@@ -11192,7 +11255,7 @@
         <v>2</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>8</v>
@@ -11206,7 +11269,7 @@
         <v>1</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="D205" t="s">
         <v>93</v>
@@ -11218,7 +11281,7 @@
         <v>2</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>8</v>
@@ -11232,7 +11295,7 @@
         <v>2</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D206" t="s">
         <v>93</v>
@@ -11244,7 +11307,7 @@
         <v>1</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>8</v>
@@ -11258,7 +11321,7 @@
         <v>3</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="D207" t="s">
         <v>93</v>
@@ -11270,7 +11333,7 @@
         <v>1</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>8</v>
@@ -11284,7 +11347,7 @@
         <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="D208" t="s">
         <v>182</v>
@@ -11296,7 +11359,7 @@
         <v>1</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>8</v>
@@ -11310,7 +11373,7 @@
         <v>5</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="D209" t="s">
         <v>93</v>
@@ -11322,7 +11385,7 @@
         <v>1</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>8</v>
@@ -11336,7 +11399,7 @@
         <v>6</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="D210" t="s">
         <v>93</v>
@@ -11348,7 +11411,7 @@
         <v>3</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>8</v>
@@ -11362,7 +11425,7 @@
         <v>7</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="D211" t="s">
         <v>93</v>
@@ -11374,7 +11437,7 @@
         <v>2</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>8</v>
@@ -11388,7 +11451,7 @@
         <v>8</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D212" t="s">
         <v>93</v>
@@ -11400,7 +11463,7 @@
         <v>2</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>8</v>
@@ -11414,7 +11477,7 @@
         <v>9</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="D213" t="s">
         <v>182</v>
@@ -11426,7 +11489,7 @@
         <v>1</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>8</v>
@@ -11440,7 +11503,7 @@
         <v>10</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="D214" t="s">
         <v>182</v>
@@ -11452,10 +11515,10 @@
         <v>3</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
@@ -11466,7 +11529,7 @@
         <v>11</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D215" t="s">
         <v>182</v>
@@ -11478,10 +11541,10 @@
         <v>3</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
@@ -11492,7 +11555,7 @@
         <v>12</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="D216" t="s">
         <v>93</v>
@@ -11504,7 +11567,7 @@
         <v>2</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>8</v>
@@ -11518,7 +11581,7 @@
         <v>1</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D217" t="s">
         <v>93</v>
@@ -11530,7 +11593,7 @@
         <v>1</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>8</v>
@@ -11544,7 +11607,7 @@
         <v>2</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="D218" t="s">
         <v>93</v>
@@ -11556,10 +11619,10 @@
         <v>2</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
@@ -11570,7 +11633,7 @@
         <v>3</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D219" t="s">
         <v>93</v>
@@ -11582,7 +11645,7 @@
         <v>3</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>8</v>
@@ -11596,7 +11659,7 @@
         <v>4</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="D220" t="s">
         <v>93</v>
@@ -11608,7 +11671,7 @@
         <v>2</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>8</v>
@@ -11622,7 +11685,7 @@
         <v>1</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D221" t="s">
         <v>93</v>
@@ -11634,11 +11697,9 @@
         <v>1</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="H221" s="2" t="s">
-        <v>628</v>
-      </c>
+        <v>631</v>
+      </c>
+      <c r="H221" s="2"/>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
@@ -11648,7 +11709,7 @@
         <v>2</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="D222" t="s">
         <v>93</v>
@@ -11660,11 +11721,9 @@
         <v>1</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="H222" s="2" t="s">
-        <v>628</v>
-      </c>
+        <v>633</v>
+      </c>
+      <c r="H222" s="2"/>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
@@ -11674,7 +11733,7 @@
         <v>3</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="D223" t="s">
         <v>182</v>
@@ -11686,11 +11745,9 @@
         <v>2</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="H223" s="2" t="s">
-        <v>628</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="H223" s="2"/>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
@@ -11700,7 +11757,7 @@
         <v>4</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="D224" t="s">
         <v>93</v>
@@ -11712,11 +11769,9 @@
         <v>2</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="H224" s="2" t="s">
-        <v>628</v>
-      </c>
+        <v>636</v>
+      </c>
+      <c r="H224" s="2"/>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
@@ -11726,7 +11781,7 @@
         <v>5</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D225" t="s">
         <v>93</v>
@@ -11738,11 +11793,9 @@
         <v>3</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="H225" s="2" t="s">
-        <v>628</v>
-      </c>
+        <v>633</v>
+      </c>
+      <c r="H225" s="2"/>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
@@ -11752,7 +11805,7 @@
         <v>6</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="D226" t="s">
         <v>93</v>
@@ -11764,11 +11817,9 @@
         <v>2</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="H226" s="2" t="s">
-        <v>628</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="H226" s="2"/>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
@@ -11778,7 +11829,7 @@
         <v>7</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="D227" t="s">
         <v>93</v>
@@ -11790,11 +11841,9 @@
         <v>3</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="H227" s="2" t="s">
-        <v>628</v>
-      </c>
+        <v>633</v>
+      </c>
+      <c r="H227" s="2"/>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
@@ -11804,7 +11853,7 @@
         <v>8</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="D228" t="s">
         <v>182</v>
@@ -11816,11 +11865,9 @@
         <v>1</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="H228" s="2" t="s">
-        <v>628</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="H228" s="2"/>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
@@ -11830,7 +11877,7 @@
         <v>9</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D229" t="s">
         <v>93</v>
@@ -11842,11 +11889,9 @@
         <v>2</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="H229" s="2" t="s">
-        <v>628</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="H229" s="2"/>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
@@ -11856,7 +11901,7 @@
         <v>10</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="D230" t="s">
         <v>93</v>
@@ -11868,11 +11913,9 @@
         <v>2</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="H230" s="2" t="s">
-        <v>628</v>
-      </c>
+        <v>643</v>
+      </c>
+      <c r="H230" s="2"/>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
@@ -11882,7 +11925,7 @@
         <v>11</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D231" t="s">
         <v>182</v>
@@ -11894,11 +11937,9 @@
         <v>1</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="H231" s="2" t="s">
-        <v>628</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="H231" s="2"/>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
@@ -11908,7 +11949,7 @@
         <v>12</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="D232" t="s">
         <v>93</v>
@@ -11920,11 +11961,9 @@
         <v>2</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="H232" s="2" t="s">
-        <v>628</v>
-      </c>
+        <v>633</v>
+      </c>
+      <c r="H232" s="2"/>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
@@ -11934,7 +11973,7 @@
         <v>13</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="D233" t="s">
         <v>93</v>
@@ -11946,11 +11985,9 @@
         <v>1</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="H233" s="2" t="s">
-        <v>628</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="H233" s="2"/>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
@@ -11960,7 +11997,7 @@
         <v>14</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="D234" t="s">
         <v>93</v>
@@ -11972,11 +12009,9 @@
         <v>2</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>645</v>
-      </c>
-      <c r="H234" s="2" t="s">
-        <v>628</v>
-      </c>
+        <v>648</v>
+      </c>
+      <c r="H234" s="2"/>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
@@ -11986,7 +12021,7 @@
         <v>15</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="D235" t="s">
         <v>93</v>
@@ -11998,11 +12033,9 @@
         <v>3</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="H235" s="2" t="s">
-        <v>628</v>
-      </c>
+        <v>633</v>
+      </c>
+      <c r="H235" s="2"/>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
@@ -12012,7 +12045,7 @@
         <v>16</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="D236" t="s">
         <v>182</v>
@@ -12024,11 +12057,9 @@
         <v>2</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>648</v>
-      </c>
-      <c r="H236" s="2" t="s">
-        <v>628</v>
-      </c>
+        <v>651</v>
+      </c>
+      <c r="H236" s="2"/>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
@@ -12038,7 +12069,7 @@
         <v>17</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="D237" t="s">
         <v>93</v>
@@ -12050,11 +12081,9 @@
         <v>3</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="H237" s="2" t="s">
-        <v>628</v>
-      </c>
+        <v>653</v>
+      </c>
+      <c r="H237" s="2"/>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
@@ -12064,7 +12093,7 @@
         <v>18</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="D238" t="s">
         <v>93</v>
@@ -12076,21 +12105,19 @@
         <v>3</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="H238" s="2" t="s">
-        <v>628</v>
-      </c>
+        <v>655</v>
+      </c>
+      <c r="H238" s="2"/>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="B239">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="D239" t="s">
         <v>93</v>
@@ -12102,21 +12129,19 @@
         <v>1</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="H239" s="2" t="s">
-        <v>655</v>
-      </c>
+        <v>657</v>
+      </c>
+      <c r="H239" s="2"/>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="B240">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="D240" t="s">
         <v>93</v>
@@ -12128,21 +12153,19 @@
         <v>1</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="H240" s="2" t="s">
-        <v>655</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="H240" s="2"/>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="B241">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="D241" t="s">
         <v>93</v>
@@ -12154,21 +12177,19 @@
         <v>1</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="H241" s="2" t="s">
-        <v>655</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="H241" s="2"/>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="B242">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="D242" t="s">
         <v>93</v>
@@ -12180,21 +12201,19 @@
         <v>1</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="H242" s="2" t="s">
-        <v>655</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="H242" s="2"/>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="B243">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="D243" t="s">
         <v>93</v>
@@ -12206,21 +12225,19 @@
         <v>1</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="H243" s="2" t="s">
-        <v>655</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="H243" s="2"/>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="B244">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D244" t="s">
         <v>93</v>
@@ -12232,21 +12249,19 @@
         <v>1</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="H244" s="2" t="s">
-        <v>655</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="H244" s="2"/>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="B245">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="D245" t="s">
         <v>93</v>
@@ -12258,21 +12273,19 @@
         <v>1</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="H245" s="2" t="s">
-        <v>655</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="H245" s="2"/>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="B246">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="D246" t="s">
         <v>93</v>
@@ -12284,21 +12297,19 @@
         <v>1</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="H246" s="2" t="s">
-        <v>655</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="H246" s="2"/>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="B247">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="D247" t="s">
         <v>93</v>
@@ -12310,21 +12321,19 @@
         <v>1</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>657</v>
-      </c>
-      <c r="H247" s="2" t="s">
-        <v>655</v>
-      </c>
+        <v>659</v>
+      </c>
+      <c r="H247" s="2"/>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="B248">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D248" t="s">
         <v>182</v>
@@ -12336,21 +12345,19 @@
         <v>3</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="H248" s="2" t="s">
-        <v>655</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="H248" s="2"/>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="B249">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="D249" t="s">
         <v>182</v>
@@ -12362,21 +12369,19 @@
         <v>1</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="H249" s="2" t="s">
-        <v>655</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="H249" s="2"/>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="B250">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D250" t="s">
         <v>182</v>
@@ -12388,21 +12393,19 @@
         <v>1</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="H250" s="2" t="s">
-        <v>655</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="H250" s="2"/>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="B251">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="D251" t="s">
         <v>182</v>
@@ -12414,21 +12417,19 @@
         <v>1</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="H251" s="2" t="s">
-        <v>655</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="H251" s="2"/>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="B252">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D252" t="s">
         <v>93</v>
@@ -12440,11 +12441,9 @@
         <v>3</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="H252" s="2" t="s">
-        <v>655</v>
-      </c>
+        <v>672</v>
+      </c>
+      <c r="H252" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
@@ -12619,16 +12618,16 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B2" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -12651,7 +12650,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B3" t="s">
         <v>138</v>
@@ -12660,7 +12659,7 @@
         <v>166</v>
       </c>
       <c r="D3" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -12669,7 +12668,7 @@
         <v>8</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="H3">
         <v>3</v>
@@ -12683,16 +12682,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="B4" t="s">
         <v>674</v>
       </c>
-      <c r="B4" t="s">
-        <v>672</v>
-      </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -12715,16 +12714,16 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B5" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C5" t="s">
         <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -12747,7 +12746,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B6" t="s">
         <v>138</v>
@@ -12756,7 +12755,7 @@
         <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -12765,7 +12764,7 @@
         <v>8</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -12779,16 +12778,16 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B7" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -12811,16 +12810,16 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B8" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -12846,13 +12845,13 @@
         <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -12875,7 +12874,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B10" t="s">
         <v>138</v>
@@ -12884,7 +12883,7 @@
         <v>166</v>
       </c>
       <c r="D10" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -12893,7 +12892,7 @@
         <v>8</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="H10">
         <v>6</v>
@@ -12907,16 +12906,16 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B11" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -12939,7 +12938,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B12" t="s">
         <v>138</v>
@@ -12948,7 +12947,7 @@
         <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E12" t="s">
         <v>141</v>
@@ -12957,7 +12956,7 @@
         <v>8</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="H12">
         <v>3</v>
@@ -12971,7 +12970,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B13" t="s">
         <v>138</v>
@@ -12980,7 +12979,7 @@
         <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -12989,7 +12988,7 @@
         <v>8</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="H13">
         <v>5</v>
@@ -13003,16 +13002,16 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B14" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C14" t="s">
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -13035,7 +13034,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B15" t="s">
         <v>138</v>
@@ -13044,16 +13043,16 @@
         <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E15" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="F15" t="s">
         <v>8</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="H15">
         <v>3</v>
@@ -13070,13 +13069,13 @@
         <v>127</v>
       </c>
       <c r="B16" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C16" t="s">
         <v>8</v>
       </c>
       <c r="D16" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -13108,7 +13107,7 @@
         <v>166</v>
       </c>
       <c r="D17" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -13117,7 +13116,7 @@
         <v>8</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="H17">
         <v>11</v>
@@ -13134,13 +13133,13 @@
         <v>136</v>
       </c>
       <c r="B18" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C18" t="s">
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -13163,7 +13162,7 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B19" t="s">
         <v>138</v>
@@ -13172,16 +13171,16 @@
         <v>72</v>
       </c>
       <c r="D19" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E19" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="F19" t="s">
         <v>8</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="H19">
         <v>3</v>
@@ -13195,7 +13194,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B20" t="s">
         <v>138</v>
@@ -13204,7 +13203,7 @@
         <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -13213,7 +13212,7 @@
         <v>8</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="H20">
         <v>9</v>
@@ -13227,16 +13226,16 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B21" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C21" t="s">
         <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -13259,16 +13258,16 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B22" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C22" t="s">
         <v>8</v>
       </c>
       <c r="D22" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -13291,16 +13290,16 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B23" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C23" t="s">
         <v>8</v>
       </c>
       <c r="D23" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
@@ -13323,16 +13322,16 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B24" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C24" t="s">
         <v>8</v>
       </c>
       <c r="D24" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -13355,7 +13354,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B25" t="s">
         <v>138</v>
@@ -13364,7 +13363,7 @@
         <v>171</v>
       </c>
       <c r="D25" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -13373,7 +13372,7 @@
         <v>8</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="H25">
         <v>9</v>
@@ -13387,7 +13386,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B26" t="s">
         <v>138</v>
@@ -13396,7 +13395,7 @@
         <v>44</v>
       </c>
       <c r="D26" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -13405,7 +13404,7 @@
         <v>8</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="H26">
         <v>2</v>
@@ -13419,16 +13418,16 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B27" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C27" t="s">
         <v>8</v>
       </c>
       <c r="D27" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -13451,7 +13450,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B28" t="s">
         <v>138</v>
@@ -13460,7 +13459,7 @@
         <v>169</v>
       </c>
       <c r="D28" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -13469,7 +13468,7 @@
         <v>8</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="H28">
         <v>2</v>
@@ -13483,16 +13482,16 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B29" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C29" t="s">
         <v>8</v>
       </c>
       <c r="D29" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -13518,13 +13517,13 @@
         <v>58</v>
       </c>
       <c r="B30" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C30" t="s">
         <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -13547,7 +13546,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B31" t="s">
         <v>138</v>
@@ -13556,7 +13555,7 @@
         <v>171</v>
       </c>
       <c r="D31" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -13565,7 +13564,7 @@
         <v>8</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="H31">
         <v>10</v>
@@ -13579,7 +13578,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="B32" t="s">
         <v>138</v>
@@ -13588,7 +13587,7 @@
         <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
@@ -13597,7 +13596,7 @@
         <v>8</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -13611,16 +13610,16 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="B33" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C33" t="s">
         <v>8</v>
       </c>
       <c r="D33" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -13643,7 +13642,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="B34" t="s">
         <v>138</v>
@@ -13652,7 +13651,7 @@
         <v>171</v>
       </c>
       <c r="D34" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
@@ -13661,7 +13660,7 @@
         <v>8</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -13675,16 +13674,16 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B35" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C35" t="s">
         <v>8</v>
       </c>
       <c r="D35" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
@@ -13710,7 +13709,7 @@
         <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C36" t="s">
         <v>8</v>
@@ -13725,7 +13724,7 @@
         <v>8</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -13739,7 +13738,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B37" t="s">
         <v>138</v>
@@ -13748,7 +13747,7 @@
         <v>44</v>
       </c>
       <c r="D37" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
@@ -13757,7 +13756,7 @@
         <v>8</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="H37">
         <v>9</v>
@@ -13771,16 +13770,16 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B38" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C38" t="s">
         <v>8</v>
       </c>
       <c r="D38" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E38" t="s">
         <v>8</v>
@@ -13803,7 +13802,7 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B39" t="s">
         <v>138</v>
@@ -13812,7 +13811,7 @@
         <v>169</v>
       </c>
       <c r="D39" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
@@ -13821,7 +13820,7 @@
         <v>8</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -13835,16 +13834,16 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B40" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C40" t="s">
         <v>8</v>
       </c>
       <c r="D40" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -13867,16 +13866,16 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B41" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C41" t="s">
         <v>8</v>
       </c>
       <c r="D41" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
@@ -13899,7 +13898,7 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B42" t="s">
         <v>138</v>
@@ -13908,7 +13907,7 @@
         <v>166</v>
       </c>
       <c r="D42" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
@@ -13917,7 +13916,7 @@
         <v>8</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -13931,16 +13930,16 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B43" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C43" t="s">
         <v>8</v>
       </c>
       <c r="D43" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -13963,7 +13962,7 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B44" t="s">
         <v>138</v>
@@ -13981,7 +13980,7 @@
         <v>8</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -13995,7 +13994,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B45" t="s">
         <v>138</v>
@@ -14004,7 +14003,7 @@
         <v>44</v>
       </c>
       <c r="D45" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -14013,7 +14012,7 @@
         <v>8</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -14027,16 +14026,16 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B46" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C46" t="s">
         <v>8</v>
       </c>
       <c r="D46" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -14059,7 +14058,7 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B47" t="s">
         <v>138</v>
@@ -14068,7 +14067,7 @@
         <v>166</v>
       </c>
       <c r="D47" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
@@ -14077,7 +14076,7 @@
         <v>8</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="H47">
         <v>11</v>
@@ -14091,16 +14090,16 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B48" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C48" t="s">
         <v>8</v>
       </c>
       <c r="D48" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -14123,16 +14122,16 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B49" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C49" t="s">
         <v>8</v>
       </c>
       <c r="D49" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -14155,7 +14154,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B50" t="s">
         <v>138</v>
@@ -14164,7 +14163,7 @@
         <v>72</v>
       </c>
       <c r="D50" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E50" t="s">
         <v>141</v>
@@ -14173,7 +14172,7 @@
         <v>8</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -14187,7 +14186,7 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B51" t="s">
         <v>138</v>
@@ -14199,13 +14198,13 @@
         <v>140</v>
       </c>
       <c r="E51" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="F51" t="s">
         <v>8</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -14219,7 +14218,7 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B52" t="s">
         <v>138</v>
@@ -14228,7 +14227,7 @@
         <v>44</v>
       </c>
       <c r="D52" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -14237,7 +14236,7 @@
         <v>8</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="H52">
         <v>5</v>
@@ -14251,16 +14250,16 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B53" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C53" t="s">
         <v>8</v>
       </c>
       <c r="D53" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -14283,16 +14282,16 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B54" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C54" t="s">
         <v>8</v>
       </c>
       <c r="D54" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -14315,7 +14314,7 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B55" t="s">
         <v>138</v>
@@ -14324,16 +14323,16 @@
         <v>72</v>
       </c>
       <c r="D55" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E55" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="F55" t="s">
         <v>8</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -14347,7 +14346,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B56" t="s">
         <v>138</v>
@@ -14359,13 +14358,13 @@
         <v>140</v>
       </c>
       <c r="E56" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="F56" t="s">
         <v>8</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -14379,7 +14378,7 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B57" t="s">
         <v>138</v>
@@ -14388,7 +14387,7 @@
         <v>44</v>
       </c>
       <c r="D57" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -14397,7 +14396,7 @@
         <v>8</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -14411,7 +14410,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B58" t="s">
         <v>138</v>
@@ -14420,7 +14419,7 @@
         <v>166</v>
       </c>
       <c r="D58" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -14429,7 +14428,7 @@
         <v>8</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -14443,16 +14442,16 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B59" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C59" t="s">
         <v>8</v>
       </c>
       <c r="D59" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -14475,16 +14474,16 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B60" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C60" t="s">
         <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -14507,7 +14506,7 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B61" t="s">
         <v>138</v>
@@ -14516,16 +14515,16 @@
         <v>72</v>
       </c>
       <c r="D61" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E61" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="F61" t="s">
         <v>8</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -14539,16 +14538,16 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B62" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C62" t="s">
         <v>8</v>
       </c>
       <c r="D62" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
@@ -14571,16 +14570,16 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B63" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C63" t="s">
         <v>8</v>
       </c>
       <c r="D63" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
@@ -14603,7 +14602,7 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B64" t="s">
         <v>138</v>
@@ -14612,7 +14611,7 @@
         <v>171</v>
       </c>
       <c r="D64" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E64" t="s">
         <v>8</v>
@@ -14621,7 +14620,7 @@
         <v>8</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="H64">
         <v>5</v>
@@ -14635,7 +14634,7 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B65" t="s">
         <v>138</v>
@@ -14644,7 +14643,7 @@
         <v>166</v>
       </c>
       <c r="D65" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E65" t="s">
         <v>8</v>
@@ -14653,7 +14652,7 @@
         <v>8</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -14667,7 +14666,7 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B66" t="s">
         <v>138</v>
@@ -14676,7 +14675,7 @@
         <v>169</v>
       </c>
       <c r="D66" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E66" t="s">
         <v>8</v>
@@ -14685,7 +14684,7 @@
         <v>8</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="H66">
         <v>2</v>
@@ -14699,7 +14698,7 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B67" t="s">
         <v>138</v>
@@ -14708,7 +14707,7 @@
         <v>171</v>
       </c>
       <c r="D67" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E67" t="s">
         <v>8</v>
@@ -14717,7 +14716,7 @@
         <v>8</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="H67">
         <v>7</v>
@@ -14731,16 +14730,16 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B68" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C68" t="s">
         <v>8</v>
       </c>
       <c r="D68" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E68" t="s">
         <v>8</v>
@@ -14763,7 +14762,7 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B69" t="s">
         <v>138</v>
@@ -14772,7 +14771,7 @@
         <v>166</v>
       </c>
       <c r="D69" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E69" t="s">
         <v>8</v>
@@ -14781,7 +14780,7 @@
         <v>8</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="H69">
         <v>11</v>
@@ -14795,7 +14794,7 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B70" t="s">
         <v>138</v>
@@ -14804,7 +14803,7 @@
         <v>169</v>
       </c>
       <c r="D70" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
@@ -14813,7 +14812,7 @@
         <v>8</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="H70">
         <v>8</v>
@@ -14827,10 +14826,10 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B71" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C71" t="s">
         <v>8</v>
@@ -14845,7 +14844,7 @@
         <v>8</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -14859,7 +14858,7 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B72" t="s">
         <v>138</v>
@@ -14868,7 +14867,7 @@
         <v>171</v>
       </c>
       <c r="D72" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E72" t="s">
         <v>8</v>
@@ -14877,7 +14876,7 @@
         <v>8</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -14891,7 +14890,7 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B73" t="s">
         <v>138</v>
@@ -14900,7 +14899,7 @@
         <v>166</v>
       </c>
       <c r="D73" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E73" t="s">
         <v>8</v>
@@ -14909,7 +14908,7 @@
         <v>8</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -14923,7 +14922,7 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="B74" t="s">
         <v>138</v>
@@ -14932,7 +14931,7 @@
         <v>169</v>
       </c>
       <c r="D74" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E74" t="s">
         <v>8</v>
@@ -14941,7 +14940,7 @@
         <v>8</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="H74">
         <v>9</v>
@@ -14955,7 +14954,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="B75" t="s">
         <v>138</v>
@@ -14964,7 +14963,7 @@
         <v>44</v>
       </c>
       <c r="D75" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="E75" t="s">
         <v>8</v>
@@ -14973,7 +14972,7 @@
         <v>8</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -14987,7 +14986,7 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B76" t="s">
         <v>138</v>
@@ -14996,7 +14995,7 @@
         <v>166</v>
       </c>
       <c r="D76" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E76" t="s">
         <v>8</v>
@@ -15005,7 +15004,7 @@
         <v>8</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="H76">
         <v>3</v>
@@ -15019,7 +15018,7 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B77" t="s">
         <v>138</v>
@@ -15028,7 +15027,7 @@
         <v>44</v>
       </c>
       <c r="D77" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="E77" t="s">
         <v>8</v>
@@ -15037,7 +15036,7 @@
         <v>8</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -15051,7 +15050,7 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B78" t="s">
         <v>138</v>
@@ -15060,7 +15059,7 @@
         <v>72</v>
       </c>
       <c r="D78" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E78" t="s">
         <v>8</v>
@@ -15069,7 +15068,7 @@
         <v>8</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="H78">
         <v>5</v>
@@ -15083,7 +15082,7 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="B79" t="s">
         <v>138</v>
@@ -15092,7 +15091,7 @@
         <v>44</v>
       </c>
       <c r="D79" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="E79" t="s">
         <v>8</v>
@@ -15101,7 +15100,7 @@
         <v>8</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -15115,7 +15114,7 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="B80" t="s">
         <v>138</v>
@@ -15124,7 +15123,7 @@
         <v>166</v>
       </c>
       <c r="D80" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E80" t="s">
         <v>8</v>
@@ -15133,7 +15132,7 @@
         <v>8</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="H80">
         <v>5</v>
@@ -15147,7 +15146,7 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="B81" t="s">
         <v>138</v>
@@ -15156,7 +15155,7 @@
         <v>44</v>
       </c>
       <c r="D81" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="E81" t="s">
         <v>8</v>
@@ -15165,7 +15164,7 @@
         <v>8</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -15179,7 +15178,7 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B82" t="s">
         <v>138</v>
@@ -15188,7 +15187,7 @@
         <v>72</v>
       </c>
       <c r="D82" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E82" t="s">
         <v>8</v>
@@ -15197,7 +15196,7 @@
         <v>8</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="H82">
         <v>5</v>
@@ -15211,10 +15210,10 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B83" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C83" t="s">
         <v>8</v>
@@ -15229,7 +15228,7 @@
         <v>8</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -15243,7 +15242,7 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="B84" t="s">
         <v>138</v>
@@ -15252,7 +15251,7 @@
         <v>44</v>
       </c>
       <c r="D84" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="E84" t="s">
         <v>8</v>
@@ -15261,7 +15260,7 @@
         <v>8</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="H84">
         <v>18</v>
@@ -15275,7 +15274,7 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B85" t="s">
         <v>138</v>
@@ -15284,7 +15283,7 @@
         <v>166</v>
       </c>
       <c r="D85" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E85" t="s">
         <v>8</v>
@@ -15293,7 +15292,7 @@
         <v>8</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="H85">
         <v>8</v>
@@ -15307,7 +15306,7 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B86" t="s">
         <v>138</v>
@@ -15316,7 +15315,7 @@
         <v>44</v>
       </c>
       <c r="D86" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="E86" t="s">
         <v>8</v>
@@ -15325,7 +15324,7 @@
         <v>8</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -15339,7 +15338,7 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B87" t="s">
         <v>138</v>
@@ -15348,7 +15347,7 @@
         <v>72</v>
       </c>
       <c r="D87" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="E87" t="s">
         <v>8</v>
@@ -15357,7 +15356,7 @@
         <v>8</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="H87">
         <v>5</v>
@@ -15371,7 +15370,7 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="B88" t="s">
         <v>138</v>
@@ -15380,7 +15379,7 @@
         <v>171</v>
       </c>
       <c r="D88" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E88" t="s">
         <v>8</v>
@@ -15389,7 +15388,7 @@
         <v>8</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="H88">
         <v>2</v>
@@ -15403,7 +15402,7 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B89" t="s">
         <v>138</v>
@@ -15412,7 +15411,7 @@
         <v>169</v>
       </c>
       <c r="D89" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E89" t="s">
         <v>8</v>
@@ -15421,7 +15420,7 @@
         <v>8</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="H89">
         <v>2</v>
@@ -15435,7 +15434,7 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B90" t="s">
         <v>138</v>
@@ -15444,7 +15443,7 @@
         <v>72</v>
       </c>
       <c r="D90" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E90" t="s">
         <v>8</v>
@@ -15453,7 +15452,7 @@
         <v>8</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="H90">
         <v>6</v>
@@ -15467,7 +15466,7 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B91" t="s">
         <v>138</v>
@@ -15476,7 +15475,7 @@
         <v>171</v>
       </c>
       <c r="D91" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E91" t="s">
         <v>8</v>
@@ -15485,7 +15484,7 @@
         <v>8</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -15499,7 +15498,7 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B92" t="s">
         <v>138</v>
@@ -15508,7 +15507,7 @@
         <v>169</v>
       </c>
       <c r="D92" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E92" t="s">
         <v>8</v>
@@ -15517,7 +15516,7 @@
         <v>8</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="H92">
         <v>5</v>
@@ -15531,7 +15530,7 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="B93" t="s">
         <v>138</v>
@@ -15540,7 +15539,7 @@
         <v>72</v>
       </c>
       <c r="D93" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E93" t="s">
         <v>8</v>
@@ -15549,7 +15548,7 @@
         <v>8</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -15563,7 +15562,7 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B94" t="s">
         <v>138</v>
@@ -15572,7 +15571,7 @@
         <v>171</v>
       </c>
       <c r="D94" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E94" t="s">
         <v>8</v>
@@ -15581,7 +15580,7 @@
         <v>8</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="H94">
         <v>4</v>
@@ -15595,7 +15594,7 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B95" t="s">
         <v>138</v>
@@ -15604,7 +15603,7 @@
         <v>169</v>
       </c>
       <c r="D95" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E95" t="s">
         <v>8</v>
@@ -15613,7 +15612,7 @@
         <v>8</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="H95">
         <v>5</v>
@@ -15627,7 +15626,7 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B96" t="s">
         <v>138</v>
@@ -15636,7 +15635,7 @@
         <v>72</v>
       </c>
       <c r="D96" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E96" t="s">
         <v>8</v>
@@ -15645,7 +15644,7 @@
         <v>8</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -15659,7 +15658,7 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B97" t="s">
         <v>138</v>
@@ -15668,7 +15667,7 @@
         <v>166</v>
       </c>
       <c r="D97" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E97" t="s">
         <v>8</v>
@@ -15677,7 +15676,7 @@
         <v>8</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="H97">
         <v>6</v>
@@ -15691,10 +15690,10 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B98" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C98" t="s">
         <v>8</v>
@@ -15709,7 +15708,7 @@
         <v>8</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -15723,7 +15722,7 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B99" t="s">
         <v>138</v>
@@ -15732,7 +15731,7 @@
         <v>169</v>
       </c>
       <c r="D99" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E99" t="s">
         <v>8</v>
@@ -15741,7 +15740,7 @@
         <v>8</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -15755,7 +15754,7 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="B100" t="s">
         <v>138</v>
@@ -15764,7 +15763,7 @@
         <v>72</v>
       </c>
       <c r="D100" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E100" t="s">
         <v>8</v>
@@ -15773,7 +15772,7 @@
         <v>8</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -15787,7 +15786,7 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B101" t="s">
         <v>138</v>
@@ -15796,7 +15795,7 @@
         <v>166</v>
       </c>
       <c r="D101" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E101" t="s">
         <v>8</v>
@@ -15805,7 +15804,7 @@
         <v>8</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="H101">
         <v>8</v>
@@ -15819,7 +15818,7 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B102" t="s">
         <v>138</v>
@@ -15828,7 +15827,7 @@
         <v>72</v>
       </c>
       <c r="D102" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E102" t="s">
         <v>8</v>
@@ -15837,7 +15836,7 @@
         <v>8</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="H102">
         <v>8</v>
@@ -15851,7 +15850,7 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="B103" t="s">
         <v>138</v>
@@ -15860,7 +15859,7 @@
         <v>169</v>
       </c>
       <c r="D103" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E103" t="s">
         <v>8</v>
@@ -15869,7 +15868,7 @@
         <v>8</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="H103">
         <v>5</v>
@@ -15883,10 +15882,10 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B104" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C104" t="s">
         <v>8</v>
@@ -15901,7 +15900,7 @@
         <v>8</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -15915,7 +15914,7 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B105" t="s">
         <v>138</v>
@@ -15924,7 +15923,7 @@
         <v>166</v>
       </c>
       <c r="D105" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E105" t="s">
         <v>8</v>
@@ -15933,7 +15932,7 @@
         <v>8</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="H105">
         <v>11</v>
@@ -15947,7 +15946,7 @@
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B106" t="s">
         <v>138</v>
@@ -15956,7 +15955,7 @@
         <v>72</v>
       </c>
       <c r="D106" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E106" t="s">
         <v>8</v>
@@ -15965,7 +15964,7 @@
         <v>8</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="H106">
         <v>10</v>
@@ -15979,7 +15978,7 @@
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B107" t="s">
         <v>138</v>
@@ -15988,7 +15987,7 @@
         <v>169</v>
       </c>
       <c r="D107" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E107" t="s">
         <v>8</v>
@@ -15997,7 +15996,7 @@
         <v>8</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="H107">
         <v>6</v>
@@ -16011,7 +16010,7 @@
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="B108" t="s">
         <v>138</v>
@@ -16020,7 +16019,7 @@
         <v>169</v>
       </c>
       <c r="D108" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E108" t="s">
         <v>8</v>
@@ -16029,7 +16028,7 @@
         <v>8</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="H108">
         <v>1</v>
@@ -16043,7 +16042,7 @@
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B109" t="s">
         <v>138</v>
@@ -16052,7 +16051,7 @@
         <v>171</v>
       </c>
       <c r="D109" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E109" t="s">
         <v>8</v>
@@ -16061,7 +16060,7 @@
         <v>8</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -16075,7 +16074,7 @@
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B110" t="s">
         <v>138</v>
@@ -16084,7 +16083,7 @@
         <v>44</v>
       </c>
       <c r="D110" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="E110" t="s">
         <v>8</v>
@@ -16093,7 +16092,7 @@
         <v>8</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="H110">
         <v>7</v>
@@ -16107,7 +16106,7 @@
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B111" t="s">
         <v>138</v>
@@ -16116,7 +16115,7 @@
         <v>44</v>
       </c>
       <c r="D111" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="E111" t="s">
         <v>8</v>
@@ -16125,7 +16124,7 @@
         <v>8</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="H111">
         <v>8</v>
@@ -16139,7 +16138,7 @@
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="B112" t="s">
         <v>138</v>
@@ -16148,7 +16147,7 @@
         <v>171</v>
       </c>
       <c r="D112" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E112" t="s">
         <v>8</v>
@@ -16157,7 +16156,7 @@
         <v>8</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -16171,7 +16170,7 @@
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="B113" t="s">
         <v>138</v>
@@ -16180,7 +16179,7 @@
         <v>169</v>
       </c>
       <c r="D113" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E113" t="s">
         <v>8</v>
@@ -16189,7 +16188,7 @@
         <v>8</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="H113">
         <v>5</v>
@@ -16203,7 +16202,7 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B114" t="s">
         <v>138</v>
@@ -16212,7 +16211,7 @@
         <v>171</v>
       </c>
       <c r="D114" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E114" t="s">
         <v>8</v>
@@ -16221,7 +16220,7 @@
         <v>8</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -16235,7 +16234,7 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B115" t="s">
         <v>138</v>
@@ -16244,7 +16243,7 @@
         <v>44</v>
       </c>
       <c r="D115" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="E115" t="s">
         <v>8</v>
@@ -16253,7 +16252,7 @@
         <v>8</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -16267,7 +16266,7 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B116" t="s">
         <v>138</v>
@@ -16276,7 +16275,7 @@
         <v>169</v>
       </c>
       <c r="D116" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E116" t="s">
         <v>8</v>
@@ -16285,7 +16284,7 @@
         <v>8</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="H116">
         <v>6</v>
@@ -16299,7 +16298,7 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B117" t="s">
         <v>138</v>
@@ -16308,7 +16307,7 @@
         <v>166</v>
       </c>
       <c r="D117" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="E117" t="s">
         <v>8</v>
@@ -16331,7 +16330,7 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="B118" t="s">
         <v>138</v>
@@ -16340,7 +16339,7 @@
         <v>72</v>
       </c>
       <c r="D118" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="E118" t="s">
         <v>8</v>
@@ -16363,7 +16362,7 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B119" t="s">
         <v>138</v>
@@ -16372,7 +16371,7 @@
         <v>44</v>
       </c>
       <c r="D119" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E119" t="s">
         <v>8</v>
@@ -16381,7 +16380,7 @@
         <v>8</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -16395,7 +16394,7 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B120" t="s">
         <v>138</v>
@@ -16404,7 +16403,7 @@
         <v>44</v>
       </c>
       <c r="D120" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="E120" t="s">
         <v>8</v>
@@ -16413,7 +16412,7 @@
         <v>8</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -16427,7 +16426,7 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B121" t="s">
         <v>138</v>
@@ -16436,7 +16435,7 @@
         <v>171</v>
       </c>
       <c r="D121" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="E121" t="s">
         <v>8</v>
@@ -16445,7 +16444,7 @@
         <v>8</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -16459,7 +16458,7 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B122" t="s">
         <v>138</v>
@@ -16468,7 +16467,7 @@
         <v>169</v>
       </c>
       <c r="D122" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E122" t="s">
         <v>8</v>

--- a/content/jahrgaenge/Jg6.xlsx
+++ b/content/jahrgaenge/Jg6.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3137" uniqueCount="845">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3173" uniqueCount="878">
   <si>
     <t>Hinweise zu Jg6.xlsx</t>
   </si>
@@ -2555,6 +2555,105 @@
   </si>
   <si>
     <t>2027-06-29</t>
+  </si>
+  <si>
+    <t>jg6-r1</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>Bausteinzeitraum 17.08. bis 11.09.2026</t>
+  </si>
+  <si>
+    <t>jg6-r2</t>
+  </si>
+  <si>
+    <t>2026-09-21</t>
+  </si>
+  <si>
+    <t>2026-10-30</t>
+  </si>
+  <si>
+    <t>Bausteinzeitraum 21.09. bis 30.10.2026</t>
+  </si>
+  <si>
+    <t>jg6-r3</t>
+  </si>
+  <si>
+    <t>2026-11-02</t>
+  </si>
+  <si>
+    <t>Bausteinzeitraum 02.11. bis 27.11.2026</t>
+  </si>
+  <si>
+    <t>jg6-r4</t>
+  </si>
+  <si>
+    <t>2027-01-08</t>
+  </si>
+  <si>
+    <t>Bausteinzeitraum 30.11. bis 08.01.2027</t>
+  </si>
+  <si>
+    <t>jg6-r5</t>
+  </si>
+  <si>
+    <t>2027-01-11</t>
+  </si>
+  <si>
+    <t>2027-02-05</t>
+  </si>
+  <si>
+    <t>Bausteinzeitraum 11.01. bis 05.02.2027</t>
+  </si>
+  <si>
+    <t>jg6-r6</t>
+  </si>
+  <si>
+    <t>2027-02-22</t>
+  </si>
+  <si>
+    <t>2027-03-19</t>
+  </si>
+  <si>
+    <t>Bausteinzeitraum 22.02. bis 19.03.2027</t>
+  </si>
+  <si>
+    <t>jg6-r7</t>
+  </si>
+  <si>
+    <t>2027-04-05</t>
+  </si>
+  <si>
+    <t>2027-04-30</t>
+  </si>
+  <si>
+    <t>Bausteinzeitraum 05.04. bis 30.04.2027</t>
+  </si>
+  <si>
+    <t>jg6-r8</t>
+  </si>
+  <si>
+    <t>2027-05-03</t>
+  </si>
+  <si>
+    <t>2027-06-04</t>
+  </si>
+  <si>
+    <t>Bausteinzeitraum 03.05. bis 04.06.2027</t>
+  </si>
+  <si>
+    <t>jg6-r9</t>
+  </si>
+  <si>
+    <t>2027-06-07</t>
+  </si>
+  <si>
+    <t>2027-07-02</t>
+  </si>
+  <si>
+    <t>Bausteinzeitraum 07.06. bis 02.07.2027</t>
   </si>
 </sst>
 </file>
@@ -3991,7 +4090,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4011,6 +4110,132 @@
       </c>
       <c r="D1" s="7" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>845</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>846</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>699</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>848</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>849</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>850</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>852</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>853</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>747</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>855</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>748</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>856</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>858</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>859</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>860</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>862</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>864</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>866</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>867</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>870</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>871</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>872</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>874</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>875</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>876</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>877</v>
       </c>
     </row>
   </sheetData>
